--- a/testing/load/load_report.xlsx
+++ b/testing/load/load_report.xlsx
@@ -1648,10 +1648,10 @@
         <v>10</v>
       </c>
       <c r="F2" s="5">
-        <v>370</v>
+        <v>330</v>
       </c>
       <c r="G2" s="5">
-        <v>370</v>
+        <v>330</v>
       </c>
       <c r="H2" s="5">
         <v>0</v>
@@ -1660,13 +1660,13 @@
         <v>9</v>
       </c>
       <c r="J2" s="6">
-        <v>118</v>
+        <v>132</v>
       </c>
       <c r="K2" s="6">
         <v>31</v>
       </c>
       <c r="L2" s="7">
-        <v>139.78</v>
+        <v>130.8</v>
       </c>
       <c r="M2" s="8" t="s">
         <v>18</v>
@@ -1692,10 +1692,10 @@
         <v>25</v>
       </c>
       <c r="F3" s="11">
-        <v>500</v>
+        <v>925</v>
       </c>
       <c r="G3" s="11">
-        <v>500</v>
+        <v>925</v>
       </c>
       <c r="H3" s="11">
         <v>0</v>
@@ -1704,13 +1704,13 @@
         <v>37</v>
       </c>
       <c r="J3" s="12">
-        <v>777</v>
+        <v>692</v>
       </c>
       <c r="K3" s="12">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="L3" s="13">
-        <v>128.87</v>
+        <v>155.72</v>
       </c>
       <c r="M3" s="14" t="s">
         <v>18</v>
@@ -1736,25 +1736,25 @@
         <v>50</v>
       </c>
       <c r="F4" s="5">
-        <v>2500</v>
+        <v>3300</v>
       </c>
       <c r="G4" s="5">
-        <v>2500</v>
+        <v>3300</v>
       </c>
       <c r="H4" s="5">
         <v>0</v>
       </c>
       <c r="I4" s="6">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="J4" s="6">
-        <v>146</v>
+        <v>134</v>
       </c>
       <c r="K4" s="6">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="L4" s="7">
-        <v>806.45</v>
+        <v>930.63</v>
       </c>
       <c r="M4" s="8" t="s">
         <v>18</v>
@@ -1780,25 +1780,25 @@
         <v>100</v>
       </c>
       <c r="F5" s="11">
-        <v>3500</v>
+        <v>2900</v>
       </c>
       <c r="G5" s="11">
-        <v>3500</v>
+        <v>2900</v>
       </c>
       <c r="H5" s="11">
         <v>0</v>
       </c>
       <c r="I5" s="12">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="J5" s="12">
-        <v>122</v>
+        <v>161</v>
       </c>
       <c r="K5" s="12">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="L5" s="13">
-        <v>1318.27</v>
+        <v>1166.53</v>
       </c>
       <c r="M5" s="14" t="s">
         <v>18</v>
@@ -1824,25 +1824,25 @@
         <v>150</v>
       </c>
       <c r="F6" s="5">
-        <v>7650</v>
+        <v>6150</v>
       </c>
       <c r="G6" s="5">
-        <v>7650</v>
+        <v>6150</v>
       </c>
       <c r="H6" s="5">
         <v>0</v>
       </c>
       <c r="I6" s="6">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="J6" s="6">
-        <v>135</v>
+        <v>119</v>
       </c>
       <c r="K6" s="6">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="L6" s="7">
-        <v>2225.13</v>
+        <v>2066.53</v>
       </c>
       <c r="M6" s="8" t="s">
         <v>18</v>
@@ -1868,10 +1868,10 @@
         <v>200</v>
       </c>
       <c r="F7" s="11">
-        <v>11800</v>
+        <v>12800</v>
       </c>
       <c r="G7" s="11">
-        <v>11800</v>
+        <v>12800</v>
       </c>
       <c r="H7" s="11">
         <v>0</v>
@@ -1883,10 +1883,10 @@
         <v>133</v>
       </c>
       <c r="K7" s="12">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="L7" s="13">
-        <v>3010.97</v>
+        <v>3152.71</v>
       </c>
       <c r="M7" s="14" t="s">
         <v>18</v>
@@ -1912,10 +1912,10 @@
         <v>300</v>
       </c>
       <c r="F8" s="5">
-        <v>12600</v>
+        <v>16200</v>
       </c>
       <c r="G8" s="5">
-        <v>12600</v>
+        <v>16200</v>
       </c>
       <c r="H8" s="5">
         <v>0</v>
@@ -1924,13 +1924,13 @@
         <v>10</v>
       </c>
       <c r="J8" s="6">
-        <v>163</v>
+        <v>148</v>
       </c>
       <c r="K8" s="6">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="L8" s="7">
-        <v>3763.44</v>
+        <v>4238.62</v>
       </c>
       <c r="M8" s="8" t="s">
         <v>18</v>
@@ -1956,10 +1956,10 @@
         <v>400</v>
       </c>
       <c r="F9" s="11">
-        <v>22800</v>
+        <v>22000</v>
       </c>
       <c r="G9" s="11">
-        <v>22800</v>
+        <v>22000</v>
       </c>
       <c r="H9" s="11">
         <v>0</v>
@@ -1968,13 +1968,13 @@
         <v>9</v>
       </c>
       <c r="J9" s="12">
-        <v>231</v>
+        <v>234</v>
       </c>
       <c r="K9" s="12">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="L9" s="13">
-        <v>5241.38</v>
+        <v>5110.34</v>
       </c>
       <c r="M9" s="14" t="s">
         <v>18</v>
@@ -2000,10 +2000,10 @@
         <v>500</v>
       </c>
       <c r="F10" s="5">
-        <v>17500</v>
+        <v>28500</v>
       </c>
       <c r="G10" s="5">
-        <v>17500</v>
+        <v>28500</v>
       </c>
       <c r="H10" s="5">
         <v>0</v>
@@ -2012,13 +2012,13 @@
         <v>36</v>
       </c>
       <c r="J10" s="6">
-        <v>1130</v>
+        <v>1075</v>
       </c>
       <c r="K10" s="6">
-        <v>190</v>
+        <v>198</v>
       </c>
       <c r="L10" s="7">
-        <v>2147.24</v>
+        <v>2229</v>
       </c>
       <c r="M10" s="8" t="s">
         <v>18</v>
@@ -2044,10 +2044,10 @@
         <v>10</v>
       </c>
       <c r="F11" s="11">
-        <v>360</v>
+        <v>490</v>
       </c>
       <c r="G11" s="11">
-        <v>360</v>
+        <v>490</v>
       </c>
       <c r="H11" s="11">
         <v>0</v>
@@ -2056,13 +2056,13 @@
         <v>9</v>
       </c>
       <c r="J11" s="12">
-        <v>120</v>
+        <v>108</v>
       </c>
       <c r="K11" s="12">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="L11" s="13">
-        <v>139.53</v>
+        <v>162.31</v>
       </c>
       <c r="M11" s="14" t="s">
         <v>18</v>
@@ -2088,25 +2088,25 @@
         <v>25</v>
       </c>
       <c r="F12" s="5">
-        <v>1400</v>
+        <v>850</v>
       </c>
       <c r="G12" s="5">
-        <v>1400</v>
+        <v>850</v>
       </c>
       <c r="H12" s="5">
         <v>0</v>
       </c>
       <c r="I12" s="6">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="J12" s="6">
-        <v>1895</v>
+        <v>1658</v>
       </c>
       <c r="K12" s="6">
-        <v>325</v>
+        <v>344</v>
       </c>
       <c r="L12" s="7">
-        <v>71.07</v>
+        <v>64.41</v>
       </c>
       <c r="M12" s="8" t="s">
         <v>18</v>
@@ -2132,25 +2132,25 @@
         <v>50</v>
       </c>
       <c r="F13" s="11">
-        <v>1050</v>
+        <v>2300</v>
       </c>
       <c r="G13" s="11">
-        <v>1050</v>
+        <v>2300</v>
       </c>
       <c r="H13" s="11">
         <v>0</v>
       </c>
       <c r="I13" s="12">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="J13" s="12">
-        <v>152</v>
+        <v>137</v>
       </c>
       <c r="K13" s="12">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="L13" s="13">
-        <v>478.8</v>
+        <v>773.89</v>
       </c>
       <c r="M13" s="14" t="s">
         <v>18</v>
@@ -2176,10 +2176,10 @@
         <v>100</v>
       </c>
       <c r="F14" s="5">
-        <v>4500</v>
+        <v>2800</v>
       </c>
       <c r="G14" s="5">
-        <v>4500</v>
+        <v>2800</v>
       </c>
       <c r="H14" s="5">
         <v>0</v>
@@ -2188,13 +2188,13 @@
         <v>36</v>
       </c>
       <c r="J14" s="6">
-        <v>631</v>
+        <v>879</v>
       </c>
       <c r="K14" s="6">
-        <v>130</v>
+        <v>121</v>
       </c>
       <c r="L14" s="7">
-        <v>612.24</v>
+        <v>572.83</v>
       </c>
       <c r="M14" s="8" t="s">
         <v>18</v>
@@ -2220,10 +2220,10 @@
         <v>150</v>
       </c>
       <c r="F15" s="11">
-        <v>3450</v>
+        <v>8250</v>
       </c>
       <c r="G15" s="11">
-        <v>3450</v>
+        <v>8250</v>
       </c>
       <c r="H15" s="11">
         <v>0</v>
@@ -2232,13 +2232,13 @@
         <v>9</v>
       </c>
       <c r="J15" s="12">
-        <v>143</v>
+        <v>138</v>
       </c>
       <c r="K15" s="12">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="L15" s="13">
-        <v>1453.24</v>
+        <v>2370.69</v>
       </c>
       <c r="M15" s="14" t="s">
         <v>18</v>
@@ -2264,10 +2264,10 @@
         <v>200</v>
       </c>
       <c r="F16" s="5">
-        <v>4600</v>
+        <v>5000</v>
       </c>
       <c r="G16" s="5">
-        <v>4600</v>
+        <v>5000</v>
       </c>
       <c r="H16" s="5">
         <v>0</v>
@@ -2276,13 +2276,13 @@
         <v>10</v>
       </c>
       <c r="J16" s="6">
-        <v>138</v>
+        <v>142</v>
       </c>
       <c r="K16" s="6">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="L16" s="7">
-        <v>1900.83</v>
+        <v>1980.2</v>
       </c>
       <c r="M16" s="8" t="s">
         <v>18</v>
@@ -2308,25 +2308,25 @@
         <v>300</v>
       </c>
       <c r="F17" s="11">
-        <v>6000</v>
+        <v>9000</v>
       </c>
       <c r="G17" s="11">
-        <v>6000</v>
+        <v>9000</v>
       </c>
       <c r="H17" s="11">
         <v>0</v>
       </c>
       <c r="I17" s="12">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="J17" s="12">
-        <v>176</v>
+        <v>164</v>
       </c>
       <c r="K17" s="12">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="L17" s="13">
-        <v>2564.1</v>
+        <v>3191.49</v>
       </c>
       <c r="M17" s="14" t="s">
         <v>18</v>
@@ -2352,25 +2352,25 @@
         <v>400</v>
       </c>
       <c r="F18" s="5">
-        <v>12400</v>
+        <v>23600</v>
       </c>
       <c r="G18" s="5">
-        <v>12400</v>
+        <v>23600</v>
       </c>
       <c r="H18" s="5">
         <v>0</v>
       </c>
       <c r="I18" s="6">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="J18" s="6">
-        <v>178</v>
+        <v>162</v>
       </c>
       <c r="K18" s="6">
-        <v>46</v>
+        <v>50</v>
       </c>
       <c r="L18" s="7">
-        <v>4237.87</v>
+        <v>5303.37</v>
       </c>
       <c r="M18" s="8" t="s">
         <v>18</v>
@@ -2396,10 +2396,10 @@
         <v>500</v>
       </c>
       <c r="F19" s="11">
-        <v>21500</v>
+        <v>22500</v>
       </c>
       <c r="G19" s="11">
-        <v>21500</v>
+        <v>22500</v>
       </c>
       <c r="H19" s="11">
         <v>0</v>
@@ -2408,13 +2408,13 @@
         <v>9</v>
       </c>
       <c r="J19" s="12">
-        <v>227</v>
+        <v>181</v>
       </c>
       <c r="K19" s="12">
-        <v>56</v>
+        <v>53</v>
       </c>
       <c r="L19" s="13">
-        <v>5501.54</v>
+        <v>5791.51</v>
       </c>
       <c r="M19" s="14" t="s">
         <v>18</v>
@@ -2440,25 +2440,25 @@
         <v>10</v>
       </c>
       <c r="F20" s="5">
-        <v>310</v>
+        <v>490</v>
       </c>
       <c r="G20" s="5">
-        <v>310</v>
+        <v>490</v>
       </c>
       <c r="H20" s="5">
         <v>0</v>
       </c>
       <c r="I20" s="6">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="J20" s="6">
-        <v>114</v>
+        <v>145</v>
       </c>
       <c r="K20" s="6">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="L20" s="7">
-        <v>129.22</v>
+        <v>162.31</v>
       </c>
       <c r="M20" s="8" t="s">
         <v>18</v>
@@ -2484,25 +2484,25 @@
         <v>25</v>
       </c>
       <c r="F21" s="11">
-        <v>750</v>
+        <v>725</v>
       </c>
       <c r="G21" s="11">
-        <v>750</v>
+        <v>725</v>
       </c>
       <c r="H21" s="11">
         <v>0</v>
       </c>
       <c r="I21" s="12">
-        <v>39</v>
+        <v>43</v>
       </c>
       <c r="J21" s="12">
-        <v>698</v>
+        <v>700</v>
       </c>
       <c r="K21" s="12">
-        <v>117</v>
+        <v>111</v>
       </c>
       <c r="L21" s="13">
-        <v>149.7</v>
+        <v>153.63</v>
       </c>
       <c r="M21" s="14" t="s">
         <v>18</v>
@@ -2528,25 +2528,25 @@
         <v>50</v>
       </c>
       <c r="F22" s="5">
-        <v>2250</v>
+        <v>1750</v>
       </c>
       <c r="G22" s="5">
-        <v>2250</v>
+        <v>1750</v>
       </c>
       <c r="H22" s="5">
         <v>0</v>
       </c>
       <c r="I22" s="6">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="J22" s="6">
-        <v>134</v>
+        <v>128</v>
       </c>
       <c r="K22" s="6">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="L22" s="7">
-        <v>765.31</v>
+        <v>686.27</v>
       </c>
       <c r="M22" s="8" t="s">
         <v>18</v>
@@ -2572,25 +2572,25 @@
         <v>100</v>
       </c>
       <c r="F23" s="11">
-        <v>4700</v>
+        <v>4900</v>
       </c>
       <c r="G23" s="11">
-        <v>4700</v>
+        <v>4900</v>
       </c>
       <c r="H23" s="11">
         <v>0</v>
       </c>
       <c r="I23" s="12">
-        <v>118</v>
+        <v>122</v>
       </c>
       <c r="J23" s="12">
-        <v>1897</v>
+        <v>2021</v>
       </c>
       <c r="K23" s="12">
-        <v>367</v>
+        <v>387</v>
       </c>
       <c r="L23" s="13">
-        <v>250.68</v>
+        <v>239.46</v>
       </c>
       <c r="M23" s="14" t="s">
         <v>18</v>
@@ -2616,10 +2616,10 @@
         <v>150</v>
       </c>
       <c r="F24" s="5">
-        <v>3300</v>
+        <v>3600</v>
       </c>
       <c r="G24" s="5">
-        <v>3300</v>
+        <v>3600</v>
       </c>
       <c r="H24" s="5">
         <v>0</v>
@@ -2628,13 +2628,13 @@
         <v>10</v>
       </c>
       <c r="J24" s="6">
-        <v>155</v>
+        <v>165</v>
       </c>
       <c r="K24" s="6">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="L24" s="7">
-        <v>1453.74</v>
+        <v>1522.84</v>
       </c>
       <c r="M24" s="8" t="s">
         <v>18</v>
@@ -2660,25 +2660,25 @@
         <v>200</v>
       </c>
       <c r="F25" s="11">
-        <v>10400</v>
+        <v>13600</v>
       </c>
       <c r="G25" s="11">
-        <v>10400</v>
+        <v>13600</v>
       </c>
       <c r="H25" s="11">
         <v>0</v>
       </c>
       <c r="I25" s="12">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="J25" s="12">
-        <v>799</v>
+        <v>702</v>
       </c>
       <c r="K25" s="12">
-        <v>145</v>
+        <v>142</v>
       </c>
       <c r="L25" s="13">
-        <v>1150.44</v>
+        <v>1219.07</v>
       </c>
       <c r="M25" s="14" t="s">
         <v>18</v>
@@ -2704,25 +2704,25 @@
         <v>300</v>
       </c>
       <c r="F26" s="5">
-        <v>9900</v>
+        <v>17400</v>
       </c>
       <c r="G26" s="5">
-        <v>9900</v>
+        <v>17400</v>
       </c>
       <c r="H26" s="5">
         <v>0</v>
       </c>
       <c r="I26" s="6">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="J26" s="6">
-        <v>196</v>
+        <v>151</v>
       </c>
       <c r="K26" s="6">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="L26" s="7">
-        <v>3391.57</v>
+        <v>4294.18</v>
       </c>
       <c r="M26" s="8" t="s">
         <v>18</v>
@@ -2748,25 +2748,25 @@
         <v>400</v>
       </c>
       <c r="F27" s="11">
-        <v>23600</v>
+        <v>24000</v>
       </c>
       <c r="G27" s="11">
-        <v>23600</v>
+        <v>24000</v>
       </c>
       <c r="H27" s="11">
         <v>0</v>
       </c>
       <c r="I27" s="12">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="J27" s="12">
-        <v>185</v>
+        <v>158</v>
       </c>
       <c r="K27" s="12">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="L27" s="13">
-        <v>5374.63</v>
+        <v>5479.45</v>
       </c>
       <c r="M27" s="14" t="s">
         <v>18</v>
@@ -2792,25 +2792,25 @@
         <v>500</v>
       </c>
       <c r="F28" s="5">
-        <v>15500</v>
+        <v>13500</v>
       </c>
       <c r="G28" s="5">
-        <v>15500</v>
+        <v>13500</v>
       </c>
       <c r="H28" s="5">
         <v>0</v>
       </c>
       <c r="I28" s="6">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="J28" s="6">
-        <v>239</v>
+        <v>232</v>
       </c>
       <c r="K28" s="6">
         <v>52</v>
       </c>
       <c r="L28" s="7">
-        <v>4980.72</v>
+        <v>4648.76</v>
       </c>
       <c r="M28" s="8" t="s">
         <v>18</v>
@@ -2836,10 +2836,10 @@
         <v>10</v>
       </c>
       <c r="F29" s="11">
-        <v>670</v>
+        <v>380</v>
       </c>
       <c r="G29" s="11">
-        <v>670</v>
+        <v>380</v>
       </c>
       <c r="H29" s="11">
         <v>0</v>
@@ -2848,13 +2848,13 @@
         <v>9</v>
       </c>
       <c r="J29" s="12">
-        <v>129</v>
+        <v>144</v>
       </c>
       <c r="K29" s="12">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="L29" s="13">
-        <v>194.6</v>
+        <v>141.9</v>
       </c>
       <c r="M29" s="14" t="s">
         <v>18</v>
@@ -2880,25 +2880,25 @@
         <v>25</v>
       </c>
       <c r="F30" s="5">
-        <v>1375</v>
+        <v>625</v>
       </c>
       <c r="G30" s="5">
-        <v>1375</v>
+        <v>625</v>
       </c>
       <c r="H30" s="5">
         <v>0</v>
       </c>
       <c r="I30" s="6">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="J30" s="6">
-        <v>144</v>
+        <v>116</v>
       </c>
       <c r="K30" s="6">
         <v>32</v>
       </c>
       <c r="L30" s="7">
-        <v>421.78</v>
+        <v>271.74</v>
       </c>
       <c r="M30" s="8" t="s">
         <v>18</v>
@@ -2924,25 +2924,25 @@
         <v>50</v>
       </c>
       <c r="F31" s="11">
-        <v>3200</v>
+        <v>3350</v>
       </c>
       <c r="G31" s="11">
-        <v>3200</v>
+        <v>3350</v>
       </c>
       <c r="H31" s="11">
         <v>0</v>
       </c>
       <c r="I31" s="12">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="J31" s="12">
-        <v>117</v>
+        <v>143</v>
       </c>
       <c r="K31" s="12">
         <v>32</v>
       </c>
       <c r="L31" s="13">
-        <v>901.92</v>
+        <v>919.32</v>
       </c>
       <c r="M31" s="14" t="s">
         <v>18</v>
@@ -2968,25 +2968,25 @@
         <v>100</v>
       </c>
       <c r="F32" s="5">
-        <v>6700</v>
+        <v>4600</v>
       </c>
       <c r="G32" s="5">
-        <v>6700</v>
+        <v>4600</v>
       </c>
       <c r="H32" s="5">
         <v>0</v>
       </c>
       <c r="I32" s="6">
-        <v>43</v>
+        <v>37</v>
       </c>
       <c r="J32" s="6">
-        <v>722</v>
+        <v>773</v>
       </c>
       <c r="K32" s="6">
-        <v>122</v>
+        <v>131</v>
       </c>
       <c r="L32" s="7">
-        <v>692.58</v>
+        <v>611.21</v>
       </c>
       <c r="M32" s="8" t="s">
         <v>18</v>
@@ -3012,10 +3012,10 @@
         <v>150</v>
       </c>
       <c r="F33" s="11">
-        <v>9750</v>
+        <v>5250</v>
       </c>
       <c r="G33" s="11">
-        <v>9750</v>
+        <v>5250</v>
       </c>
       <c r="H33" s="11">
         <v>0</v>
@@ -3024,13 +3024,13 @@
         <v>9</v>
       </c>
       <c r="J33" s="12">
-        <v>133</v>
+        <v>155</v>
       </c>
       <c r="K33" s="12">
         <v>38</v>
       </c>
       <c r="L33" s="13">
-        <v>2455.92</v>
+        <v>1855.12</v>
       </c>
       <c r="M33" s="14" t="s">
         <v>18</v>
@@ -3056,25 +3056,25 @@
         <v>200</v>
       </c>
       <c r="F34" s="5">
-        <v>10200</v>
+        <v>5800</v>
       </c>
       <c r="G34" s="5">
-        <v>10200</v>
+        <v>5800</v>
       </c>
       <c r="H34" s="5">
         <v>0</v>
       </c>
       <c r="I34" s="6">
-        <v>113</v>
+        <v>119</v>
       </c>
       <c r="J34" s="6">
-        <v>2541</v>
+        <v>1933</v>
       </c>
       <c r="K34" s="6">
-        <v>420</v>
+        <v>401</v>
       </c>
       <c r="L34" s="7">
-        <v>445.03</v>
+        <v>441.77</v>
       </c>
       <c r="M34" s="8" t="s">
         <v>18</v>
@@ -3100,25 +3100,25 @@
         <v>300</v>
       </c>
       <c r="F35" s="11">
-        <v>6300</v>
+        <v>15300</v>
       </c>
       <c r="G35" s="11">
-        <v>6300</v>
+        <v>15300</v>
       </c>
       <c r="H35" s="11">
         <v>0</v>
       </c>
       <c r="I35" s="12">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="J35" s="12">
-        <v>155</v>
+        <v>186</v>
       </c>
       <c r="K35" s="12">
         <v>46</v>
       </c>
       <c r="L35" s="13">
-        <v>2554.74</v>
+        <v>3978.16</v>
       </c>
       <c r="M35" s="14" t="s">
         <v>18</v>
@@ -3144,25 +3144,25 @@
         <v>400</v>
       </c>
       <c r="F36" s="5">
-        <v>13600</v>
+        <v>12400</v>
       </c>
       <c r="G36" s="5">
-        <v>13600</v>
+        <v>12400</v>
       </c>
       <c r="H36" s="5">
         <v>0</v>
       </c>
       <c r="I36" s="6">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="J36" s="6">
-        <v>868</v>
+        <v>1145</v>
       </c>
       <c r="K36" s="6">
-        <v>177</v>
+        <v>175</v>
       </c>
       <c r="L36" s="7">
-        <v>1808.99</v>
+        <v>1790.61</v>
       </c>
       <c r="M36" s="8" t="s">
         <v>18</v>
@@ -3188,10 +3188,10 @@
         <v>500</v>
       </c>
       <c r="F37" s="11">
-        <v>20500</v>
+        <v>34000</v>
       </c>
       <c r="G37" s="11">
-        <v>20500</v>
+        <v>34000</v>
       </c>
       <c r="H37" s="11">
         <v>0</v>
@@ -3200,13 +3200,13 @@
         <v>10</v>
       </c>
       <c r="J37" s="12">
-        <v>189</v>
+        <v>207</v>
       </c>
       <c r="K37" s="12">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="L37" s="13">
-        <v>5519.66</v>
+        <v>6751.39</v>
       </c>
       <c r="M37" s="14" t="s">
         <v>18</v>
@@ -3232,10 +3232,10 @@
         <v>10</v>
       </c>
       <c r="F38" s="5">
-        <v>380</v>
+        <v>680</v>
       </c>
       <c r="G38" s="5">
-        <v>380</v>
+        <v>680</v>
       </c>
       <c r="H38" s="5">
         <v>0</v>
@@ -3244,13 +3244,13 @@
         <v>10</v>
       </c>
       <c r="J38" s="6">
-        <v>141</v>
+        <v>129</v>
       </c>
       <c r="K38" s="6">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="L38" s="7">
-        <v>146.04</v>
+        <v>188.47</v>
       </c>
       <c r="M38" s="8" t="s">
         <v>18</v>
@@ -3276,10 +3276,10 @@
         <v>25</v>
       </c>
       <c r="F39" s="11">
-        <v>925</v>
+        <v>1450</v>
       </c>
       <c r="G39" s="11">
-        <v>925</v>
+        <v>1450</v>
       </c>
       <c r="H39" s="11">
         <v>0</v>
@@ -3288,13 +3288,13 @@
         <v>9</v>
       </c>
       <c r="J39" s="12">
-        <v>117</v>
+        <v>120</v>
       </c>
       <c r="K39" s="12">
         <v>30</v>
       </c>
       <c r="L39" s="13">
-        <v>354.41</v>
+        <v>447.53</v>
       </c>
       <c r="M39" s="14" t="s">
         <v>18</v>
@@ -3320,10 +3320,10 @@
         <v>50</v>
       </c>
       <c r="F40" s="5">
-        <v>2300</v>
+        <v>1400</v>
       </c>
       <c r="G40" s="5">
-        <v>2300</v>
+        <v>1400</v>
       </c>
       <c r="H40" s="5">
         <v>0</v>
@@ -3332,13 +3332,13 @@
         <v>10</v>
       </c>
       <c r="J40" s="6">
-        <v>118</v>
+        <v>147</v>
       </c>
       <c r="K40" s="6">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="L40" s="7">
-        <v>762.09</v>
+        <v>591.22</v>
       </c>
       <c r="M40" s="8" t="s">
         <v>18</v>
@@ -3364,10 +3364,10 @@
         <v>100</v>
       </c>
       <c r="F41" s="11">
-        <v>3700</v>
+        <v>2600</v>
       </c>
       <c r="G41" s="11">
-        <v>3700</v>
+        <v>2600</v>
       </c>
       <c r="H41" s="11">
         <v>0</v>
@@ -3376,13 +3376,13 @@
         <v>9</v>
       </c>
       <c r="J41" s="12">
-        <v>125</v>
+        <v>114</v>
       </c>
       <c r="K41" s="12">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="L41" s="13">
-        <v>1306.5</v>
+        <v>1090.6</v>
       </c>
       <c r="M41" s="14" t="s">
         <v>18</v>
@@ -3408,10 +3408,10 @@
         <v>150</v>
       </c>
       <c r="F42" s="5">
-        <v>8700</v>
+        <v>4500</v>
       </c>
       <c r="G42" s="5">
-        <v>8700</v>
+        <v>4500</v>
       </c>
       <c r="H42" s="5">
         <v>0</v>
@@ -3420,13 +3420,13 @@
         <v>9</v>
       </c>
       <c r="J42" s="6">
-        <v>127</v>
+        <v>147</v>
       </c>
       <c r="K42" s="6">
         <v>36</v>
       </c>
       <c r="L42" s="7">
-        <v>2424.75</v>
+        <v>1744.19</v>
       </c>
       <c r="M42" s="8" t="s">
         <v>18</v>
@@ -3452,25 +3452,25 @@
         <v>200</v>
       </c>
       <c r="F43" s="11">
-        <v>6000</v>
+        <v>11200</v>
       </c>
       <c r="G43" s="11">
-        <v>6000</v>
+        <v>11200</v>
       </c>
       <c r="H43" s="11">
         <v>0</v>
       </c>
       <c r="I43" s="12">
-        <v>39</v>
+        <v>43</v>
       </c>
       <c r="J43" s="12">
-        <v>863</v>
+        <v>899</v>
       </c>
       <c r="K43" s="12">
-        <v>140</v>
+        <v>138</v>
       </c>
       <c r="L43" s="13">
-        <v>1052.63</v>
+        <v>1213.7</v>
       </c>
       <c r="M43" s="14" t="s">
         <v>18</v>
@@ -3508,13 +3508,13 @@
         <v>10</v>
       </c>
       <c r="J44" s="6">
-        <v>164</v>
+        <v>183</v>
       </c>
       <c r="K44" s="6">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="L44" s="7">
-        <v>3947.37</v>
+        <v>4054.05</v>
       </c>
       <c r="M44" s="8" t="s">
         <v>18</v>
@@ -3540,25 +3540,25 @@
         <v>400</v>
       </c>
       <c r="F45" s="11">
-        <v>12800</v>
+        <v>26000</v>
       </c>
       <c r="G45" s="11">
-        <v>12800</v>
+        <v>26000</v>
       </c>
       <c r="H45" s="11">
         <v>0</v>
       </c>
       <c r="I45" s="12">
-        <v>119</v>
+        <v>121</v>
       </c>
       <c r="J45" s="12">
-        <v>3435</v>
+        <v>3301</v>
       </c>
       <c r="K45" s="12">
-        <v>513</v>
+        <v>499</v>
       </c>
       <c r="L45" s="13">
-        <v>714.45</v>
+        <v>766.17</v>
       </c>
       <c r="M45" s="14" t="s">
         <v>18</v>
@@ -3584,25 +3584,25 @@
         <v>500</v>
       </c>
       <c r="F46" s="5">
-        <v>20500</v>
+        <v>24000</v>
       </c>
       <c r="G46" s="5">
-        <v>20500</v>
+        <v>24000</v>
       </c>
       <c r="H46" s="5">
         <v>0</v>
       </c>
       <c r="I46" s="6">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="J46" s="6">
-        <v>202</v>
+        <v>239</v>
       </c>
       <c r="K46" s="6">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="L46" s="7">
-        <v>5459.39</v>
+        <v>5865.1</v>
       </c>
       <c r="M46" s="8" t="s">
         <v>18</v>
@@ -3628,25 +3628,25 @@
         <v>10</v>
       </c>
       <c r="F47" s="11">
-        <v>550</v>
+        <v>680</v>
       </c>
       <c r="G47" s="11">
-        <v>550</v>
+        <v>680</v>
       </c>
       <c r="H47" s="11">
         <v>0</v>
       </c>
       <c r="I47" s="12">
-        <v>43</v>
+        <v>38</v>
       </c>
       <c r="J47" s="12">
-        <v>790</v>
+        <v>578</v>
       </c>
       <c r="K47" s="12">
-        <v>112</v>
+        <v>115</v>
       </c>
       <c r="L47" s="13">
-        <v>71.8</v>
+        <v>72.96</v>
       </c>
       <c r="M47" s="14" t="s">
         <v>18</v>
@@ -3672,10 +3672,10 @@
         <v>25</v>
       </c>
       <c r="F48" s="5">
-        <v>1725</v>
+        <v>950</v>
       </c>
       <c r="G48" s="5">
-        <v>1725</v>
+        <v>950</v>
       </c>
       <c r="H48" s="5">
         <v>0</v>
@@ -3684,13 +3684,13 @@
         <v>10</v>
       </c>
       <c r="J48" s="6">
-        <v>101</v>
+        <v>117</v>
       </c>
       <c r="K48" s="6">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="L48" s="7">
-        <v>474.03</v>
+        <v>359.85</v>
       </c>
       <c r="M48" s="8" t="s">
         <v>18</v>
@@ -3716,10 +3716,10 @@
         <v>50</v>
       </c>
       <c r="F49" s="11">
-        <v>1600</v>
+        <v>2300</v>
       </c>
       <c r="G49" s="11">
-        <v>1600</v>
+        <v>2300</v>
       </c>
       <c r="H49" s="11">
         <v>0</v>
@@ -3728,13 +3728,13 @@
         <v>9</v>
       </c>
       <c r="J49" s="12">
-        <v>144</v>
+        <v>118</v>
       </c>
       <c r="K49" s="12">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="L49" s="13">
-        <v>633.91</v>
+        <v>786.06</v>
       </c>
       <c r="M49" s="14" t="s">
         <v>18</v>
@@ -3760,25 +3760,25 @@
         <v>100</v>
       </c>
       <c r="F50" s="5">
-        <v>2500</v>
+        <v>3200</v>
       </c>
       <c r="G50" s="5">
-        <v>2500</v>
+        <v>3200</v>
       </c>
       <c r="H50" s="5">
         <v>0</v>
       </c>
       <c r="I50" s="6">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="J50" s="6">
-        <v>141</v>
+        <v>132</v>
       </c>
       <c r="K50" s="6">
         <v>33</v>
       </c>
       <c r="L50" s="7">
-        <v>1075.27</v>
+        <v>1251.96</v>
       </c>
       <c r="M50" s="8" t="s">
         <v>18</v>
@@ -3804,10 +3804,10 @@
         <v>150</v>
       </c>
       <c r="F51" s="11">
-        <v>4050</v>
+        <v>8550</v>
       </c>
       <c r="G51" s="11">
-        <v>4050</v>
+        <v>8550</v>
       </c>
       <c r="H51" s="11">
         <v>0</v>
@@ -3816,13 +3816,13 @@
         <v>9</v>
       </c>
       <c r="J51" s="12">
-        <v>124</v>
+        <v>119</v>
       </c>
       <c r="K51" s="12">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="L51" s="13">
-        <v>1620.65</v>
+        <v>2332.24</v>
       </c>
       <c r="M51" s="14" t="s">
         <v>18</v>
@@ -3848,10 +3848,10 @@
         <v>200</v>
       </c>
       <c r="F52" s="5">
-        <v>10000</v>
+        <v>13000</v>
       </c>
       <c r="G52" s="5">
-        <v>10000</v>
+        <v>13000</v>
       </c>
       <c r="H52" s="5">
         <v>0</v>
@@ -3860,13 +3860,13 @@
         <v>10</v>
       </c>
       <c r="J52" s="6">
-        <v>153</v>
+        <v>168</v>
       </c>
       <c r="K52" s="6">
         <v>40</v>
       </c>
       <c r="L52" s="7">
-        <v>2857.14</v>
+        <v>3170.73</v>
       </c>
       <c r="M52" s="8" t="s">
         <v>18</v>
@@ -3892,25 +3892,25 @@
         <v>300</v>
       </c>
       <c r="F53" s="11">
-        <v>15300</v>
+        <v>10800</v>
       </c>
       <c r="G53" s="11">
-        <v>15300</v>
+        <v>10800</v>
       </c>
       <c r="H53" s="11">
         <v>0</v>
       </c>
       <c r="I53" s="12">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="J53" s="12">
-        <v>169</v>
+        <v>204</v>
       </c>
       <c r="K53" s="12">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="L53" s="13">
-        <v>4086.54</v>
+        <v>3422.05</v>
       </c>
       <c r="M53" s="14" t="s">
         <v>18</v>
@@ -3936,25 +3936,25 @@
         <v>400</v>
       </c>
       <c r="F54" s="5">
-        <v>20000</v>
+        <v>11200</v>
       </c>
       <c r="G54" s="5">
-        <v>20000</v>
+        <v>11200</v>
       </c>
       <c r="H54" s="5">
         <v>0</v>
       </c>
       <c r="I54" s="6">
-        <v>39</v>
+        <v>43</v>
       </c>
       <c r="J54" s="6">
-        <v>1011</v>
+        <v>953</v>
       </c>
       <c r="K54" s="6">
-        <v>171</v>
+        <v>181</v>
       </c>
       <c r="L54" s="7">
-        <v>1990.05</v>
+        <v>1705.24</v>
       </c>
       <c r="M54" s="8" t="s">
         <v>18</v>
@@ -3980,10 +3980,10 @@
         <v>500</v>
       </c>
       <c r="F55" s="11">
-        <v>31000</v>
+        <v>27500</v>
       </c>
       <c r="G55" s="11">
-        <v>31000</v>
+        <v>27500</v>
       </c>
       <c r="H55" s="11">
         <v>0</v>
@@ -3992,13 +3992,13 @@
         <v>10</v>
       </c>
       <c r="J55" s="12">
-        <v>174</v>
+        <v>233</v>
       </c>
       <c r="K55" s="12">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="L55" s="13">
-        <v>6477.23</v>
+        <v>6387.92</v>
       </c>
       <c r="M55" s="14" t="s">
         <v>18</v>
@@ -4024,25 +4024,25 @@
         <v>10</v>
       </c>
       <c r="F56" s="5">
-        <v>340</v>
+        <v>510</v>
       </c>
       <c r="G56" s="5">
-        <v>340</v>
+        <v>510</v>
       </c>
       <c r="H56" s="5">
         <v>0</v>
       </c>
       <c r="I56" s="6">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="J56" s="6">
-        <v>2039</v>
+        <v>2016</v>
       </c>
       <c r="K56" s="6">
-        <v>313</v>
+        <v>311</v>
       </c>
       <c r="L56" s="7">
-        <v>28</v>
+        <v>29.38</v>
       </c>
       <c r="M56" s="8" t="s">
         <v>18</v>
@@ -4068,25 +4068,25 @@
         <v>25</v>
       </c>
       <c r="F57" s="11">
-        <v>1175</v>
+        <v>1050</v>
       </c>
       <c r="G57" s="11">
-        <v>1175</v>
+        <v>1050</v>
       </c>
       <c r="H57" s="11">
         <v>0</v>
       </c>
       <c r="I57" s="12">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="J57" s="12">
-        <v>146</v>
+        <v>148</v>
       </c>
       <c r="K57" s="12">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="L57" s="13">
-        <v>410.41</v>
+        <v>374.73</v>
       </c>
       <c r="M57" s="14" t="s">
         <v>18</v>
@@ -4112,25 +4112,25 @@
         <v>50</v>
       </c>
       <c r="F58" s="5">
-        <v>2450</v>
+        <v>1400</v>
       </c>
       <c r="G58" s="5">
-        <v>2450</v>
+        <v>1400</v>
       </c>
       <c r="H58" s="5">
         <v>0</v>
       </c>
       <c r="I58" s="6">
-        <v>42</v>
+        <v>39</v>
       </c>
       <c r="J58" s="6">
-        <v>670</v>
+        <v>767</v>
       </c>
       <c r="K58" s="6">
-        <v>115</v>
+        <v>120</v>
       </c>
       <c r="L58" s="7">
-        <v>343.38</v>
+        <v>288.07</v>
       </c>
       <c r="M58" s="8" t="s">
         <v>18</v>
@@ -4156,25 +4156,25 @@
         <v>100</v>
       </c>
       <c r="F59" s="11">
-        <v>5800</v>
+        <v>5400</v>
       </c>
       <c r="G59" s="11">
-        <v>5800</v>
+        <v>5400</v>
       </c>
       <c r="H59" s="11">
         <v>0</v>
       </c>
       <c r="I59" s="12">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="J59" s="12">
-        <v>158</v>
+        <v>142</v>
       </c>
       <c r="K59" s="12">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="L59" s="13">
-        <v>1670.51</v>
+        <v>1567.94</v>
       </c>
       <c r="M59" s="14" t="s">
         <v>18</v>
@@ -4200,10 +4200,10 @@
         <v>150</v>
       </c>
       <c r="F60" s="5">
-        <v>3450</v>
+        <v>3150</v>
       </c>
       <c r="G60" s="5">
-        <v>3450</v>
+        <v>3150</v>
       </c>
       <c r="H60" s="5">
         <v>0</v>
@@ -4212,13 +4212,13 @@
         <v>9</v>
       </c>
       <c r="J60" s="6">
-        <v>178</v>
+        <v>127</v>
       </c>
       <c r="K60" s="6">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="L60" s="7">
-        <v>1481.96</v>
+        <v>1383.4</v>
       </c>
       <c r="M60" s="8" t="s">
         <v>18</v>
@@ -4244,25 +4244,25 @@
         <v>200</v>
       </c>
       <c r="F61" s="11">
-        <v>5800</v>
+        <v>9600</v>
       </c>
       <c r="G61" s="11">
-        <v>5800</v>
+        <v>9600</v>
       </c>
       <c r="H61" s="11">
         <v>0</v>
       </c>
       <c r="I61" s="12">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="J61" s="12">
-        <v>154</v>
+        <v>164</v>
       </c>
       <c r="K61" s="12">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="L61" s="13">
-        <v>2229.05</v>
+        <v>2846.98</v>
       </c>
       <c r="M61" s="14" t="s">
         <v>18</v>
@@ -4288,25 +4288,25 @@
         <v>300</v>
       </c>
       <c r="F62" s="5">
-        <v>17700</v>
+        <v>15000</v>
       </c>
       <c r="G62" s="5">
-        <v>17700</v>
+        <v>15000</v>
       </c>
       <c r="H62" s="5">
         <v>0</v>
       </c>
       <c r="I62" s="6">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="J62" s="6">
-        <v>186</v>
+        <v>161</v>
       </c>
       <c r="K62" s="6">
-        <v>42</v>
+        <v>46</v>
       </c>
       <c r="L62" s="7">
-        <v>4449.47</v>
+        <v>3947.37</v>
       </c>
       <c r="M62" s="8" t="s">
         <v>18</v>
@@ -4332,25 +4332,25 @@
         <v>400</v>
       </c>
       <c r="F63" s="11">
-        <v>22800</v>
+        <v>24400</v>
       </c>
       <c r="G63" s="11">
-        <v>22800</v>
+        <v>24400</v>
       </c>
       <c r="H63" s="11">
         <v>0</v>
       </c>
       <c r="I63" s="12">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="J63" s="12">
-        <v>170</v>
+        <v>158</v>
       </c>
       <c r="K63" s="12">
         <v>47</v>
       </c>
       <c r="L63" s="13">
-        <v>5455.85</v>
+        <v>5587.36</v>
       </c>
       <c r="M63" s="14" t="s">
         <v>18</v>
@@ -4376,25 +4376,25 @@
         <v>500</v>
       </c>
       <c r="F64" s="5">
-        <v>19500</v>
+        <v>16000</v>
       </c>
       <c r="G64" s="5">
-        <v>19500</v>
+        <v>16000</v>
       </c>
       <c r="H64" s="5">
         <v>0</v>
       </c>
       <c r="I64" s="6">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="J64" s="6">
-        <v>175</v>
+        <v>257</v>
       </c>
       <c r="K64" s="6">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="L64" s="7">
-        <v>5407.65</v>
+        <v>5056.89</v>
       </c>
       <c r="M64" s="8" t="s">
         <v>18</v>
@@ -4420,25 +4420,25 @@
         <v>10</v>
       </c>
       <c r="F65" s="11">
-        <v>320</v>
+        <v>220</v>
       </c>
       <c r="G65" s="11">
-        <v>320</v>
+        <v>220</v>
       </c>
       <c r="H65" s="11">
         <v>0</v>
       </c>
       <c r="I65" s="12">
-        <v>38</v>
+        <v>43</v>
       </c>
       <c r="J65" s="12">
-        <v>757</v>
+        <v>734</v>
       </c>
       <c r="K65" s="12">
         <v>114</v>
       </c>
       <c r="L65" s="13">
-        <v>62.16</v>
+        <v>54.89</v>
       </c>
       <c r="M65" s="14" t="s">
         <v>18</v>
@@ -4464,10 +4464,10 @@
         <v>25</v>
       </c>
       <c r="F66" s="5">
-        <v>1375</v>
+        <v>1600</v>
       </c>
       <c r="G66" s="5">
-        <v>1375</v>
+        <v>1600</v>
       </c>
       <c r="H66" s="5">
         <v>0</v>
@@ -4476,13 +4476,13 @@
         <v>9</v>
       </c>
       <c r="J66" s="6">
-        <v>138</v>
+        <v>119</v>
       </c>
       <c r="K66" s="6">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="L66" s="7">
-        <v>429.02</v>
+        <v>467.84</v>
       </c>
       <c r="M66" s="8" t="s">
         <v>18</v>
@@ -4508,25 +4508,25 @@
         <v>50</v>
       </c>
       <c r="F67" s="11">
-        <v>2000</v>
+        <v>1500</v>
       </c>
       <c r="G67" s="11">
-        <v>2000</v>
+        <v>1500</v>
       </c>
       <c r="H67" s="11">
         <v>0</v>
       </c>
       <c r="I67" s="12">
-        <v>114</v>
+        <v>108</v>
       </c>
       <c r="J67" s="12">
-        <v>1849</v>
+        <v>1646</v>
       </c>
       <c r="K67" s="12">
-        <v>359</v>
+        <v>334</v>
       </c>
       <c r="L67" s="13">
-        <v>126.1</v>
+        <v>130.21</v>
       </c>
       <c r="M67" s="14" t="s">
         <v>18</v>
@@ -4552,10 +4552,10 @@
         <v>100</v>
       </c>
       <c r="F68" s="5">
-        <v>2600</v>
+        <v>6600</v>
       </c>
       <c r="G68" s="5">
-        <v>2600</v>
+        <v>6600</v>
       </c>
       <c r="H68" s="5">
         <v>0</v>
@@ -4564,13 +4564,13 @@
         <v>10</v>
       </c>
       <c r="J68" s="6">
-        <v>142</v>
+        <v>114</v>
       </c>
       <c r="K68" s="6">
         <v>33</v>
       </c>
       <c r="L68" s="7">
-        <v>1102.63</v>
+        <v>1794.45</v>
       </c>
       <c r="M68" s="8" t="s">
         <v>18</v>
@@ -4596,25 +4596,25 @@
         <v>150</v>
       </c>
       <c r="F69" s="11">
-        <v>10050</v>
+        <v>4500</v>
       </c>
       <c r="G69" s="11">
-        <v>10050</v>
+        <v>4500</v>
       </c>
       <c r="H69" s="11">
         <v>0</v>
       </c>
       <c r="I69" s="12">
-        <v>42</v>
+        <v>38</v>
       </c>
       <c r="J69" s="12">
-        <v>831</v>
+        <v>902</v>
       </c>
       <c r="K69" s="12">
-        <v>136</v>
+        <v>138</v>
       </c>
       <c r="L69" s="13">
-        <v>947.04</v>
+        <v>797.87</v>
       </c>
       <c r="M69" s="14" t="s">
         <v>18</v>
@@ -4640,10 +4640,10 @@
         <v>200</v>
       </c>
       <c r="F70" s="5">
-        <v>13400</v>
+        <v>8600</v>
       </c>
       <c r="G70" s="5">
-        <v>13400</v>
+        <v>8600</v>
       </c>
       <c r="H70" s="5">
         <v>0</v>
@@ -4652,13 +4652,13 @@
         <v>9</v>
       </c>
       <c r="J70" s="6">
-        <v>152</v>
+        <v>172</v>
       </c>
       <c r="K70" s="6">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="L70" s="7">
-        <v>3311.91</v>
+        <v>2706.96</v>
       </c>
       <c r="M70" s="8" t="s">
         <v>18</v>
@@ -4684,10 +4684,10 @@
         <v>300</v>
       </c>
       <c r="F71" s="11">
-        <v>17400</v>
+        <v>9000</v>
       </c>
       <c r="G71" s="11">
-        <v>17400</v>
+        <v>9000</v>
       </c>
       <c r="H71" s="11">
         <v>0</v>
@@ -4696,13 +4696,13 @@
         <v>10</v>
       </c>
       <c r="J71" s="12">
-        <v>197</v>
+        <v>206</v>
       </c>
       <c r="K71" s="12">
         <v>45</v>
       </c>
       <c r="L71" s="13">
-        <v>4233.58</v>
+        <v>3157.89</v>
       </c>
       <c r="M71" s="14" t="s">
         <v>18</v>
@@ -4728,25 +4728,25 @@
         <v>400</v>
       </c>
       <c r="F72" s="5">
-        <v>23600</v>
+        <v>19600</v>
       </c>
       <c r="G72" s="5">
-        <v>23600</v>
+        <v>19600</v>
       </c>
       <c r="H72" s="5">
         <v>0</v>
       </c>
       <c r="I72" s="6">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="J72" s="6">
-        <v>209</v>
+        <v>189</v>
       </c>
       <c r="K72" s="6">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="L72" s="7">
-        <v>5303.37</v>
+        <v>5088.27</v>
       </c>
       <c r="M72" s="8" t="s">
         <v>18</v>
@@ -4772,10 +4772,10 @@
         <v>500</v>
       </c>
       <c r="F73" s="11">
-        <v>20000</v>
+        <v>32500</v>
       </c>
       <c r="G73" s="11">
-        <v>20000</v>
+        <v>32500</v>
       </c>
       <c r="H73" s="11">
         <v>0</v>
@@ -4784,13 +4784,13 @@
         <v>9</v>
       </c>
       <c r="J73" s="12">
-        <v>255</v>
+        <v>178</v>
       </c>
       <c r="K73" s="12">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="L73" s="13">
-        <v>5649.72</v>
+        <v>6572.3</v>
       </c>
       <c r="M73" s="14" t="s">
         <v>18</v>
@@ -4816,10 +4816,10 @@
         <v>10</v>
       </c>
       <c r="F74" s="5">
-        <v>380</v>
+        <v>540</v>
       </c>
       <c r="G74" s="5">
-        <v>380</v>
+        <v>540</v>
       </c>
       <c r="H74" s="5">
         <v>0</v>
@@ -4828,13 +4828,13 @@
         <v>10</v>
       </c>
       <c r="J74" s="6">
-        <v>115</v>
+        <v>143</v>
       </c>
       <c r="K74" s="6">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="L74" s="7">
-        <v>141.9</v>
+        <v>176.13</v>
       </c>
       <c r="M74" s="8" t="s">
         <v>18</v>
@@ -4860,10 +4860,10 @@
         <v>25</v>
       </c>
       <c r="F75" s="11">
-        <v>700</v>
+        <v>1250</v>
       </c>
       <c r="G75" s="11">
-        <v>700</v>
+        <v>1250</v>
       </c>
       <c r="H75" s="11">
         <v>0</v>
@@ -4872,13 +4872,13 @@
         <v>10</v>
       </c>
       <c r="J75" s="12">
-        <v>104</v>
+        <v>143</v>
       </c>
       <c r="K75" s="12">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="L75" s="13">
-        <v>295.61</v>
+        <v>403.23</v>
       </c>
       <c r="M75" s="14" t="s">
         <v>18</v>
@@ -4904,25 +4904,25 @@
         <v>50</v>
       </c>
       <c r="F76" s="5">
-        <v>2800</v>
+        <v>1050</v>
       </c>
       <c r="G76" s="5">
-        <v>2800</v>
+        <v>1050</v>
       </c>
       <c r="H76" s="5">
         <v>0</v>
       </c>
       <c r="I76" s="6">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="J76" s="6">
-        <v>569</v>
+        <v>817</v>
       </c>
       <c r="K76" s="6">
-        <v>116</v>
+        <v>122</v>
       </c>
       <c r="L76" s="7">
-        <v>350.18</v>
+        <v>258.49</v>
       </c>
       <c r="M76" s="8" t="s">
         <v>18</v>
@@ -4948,25 +4948,25 @@
         <v>100</v>
       </c>
       <c r="F77" s="11">
-        <v>6500</v>
+        <v>5400</v>
       </c>
       <c r="G77" s="11">
-        <v>6500</v>
+        <v>5400</v>
       </c>
       <c r="H77" s="11">
         <v>0</v>
       </c>
       <c r="I77" s="12">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="J77" s="12">
-        <v>157</v>
+        <v>138</v>
       </c>
       <c r="K77" s="12">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="L77" s="13">
-        <v>1752.02</v>
+        <v>1592.92</v>
       </c>
       <c r="M77" s="14" t="s">
         <v>18</v>
@@ -4992,25 +4992,25 @@
         <v>150</v>
       </c>
       <c r="F78" s="5">
-        <v>10200</v>
+        <v>9300</v>
       </c>
       <c r="G78" s="5">
-        <v>10200</v>
+        <v>9300</v>
       </c>
       <c r="H78" s="5">
         <v>0</v>
       </c>
       <c r="I78" s="6">
-        <v>127</v>
+        <v>115</v>
       </c>
       <c r="J78" s="6">
-        <v>1972</v>
+        <v>1891</v>
       </c>
       <c r="K78" s="6">
-        <v>400</v>
+        <v>396</v>
       </c>
       <c r="L78" s="7">
-        <v>355.4</v>
+        <v>356.98</v>
       </c>
       <c r="M78" s="8" t="s">
         <v>18</v>
@@ -5036,10 +5036,10 @@
         <v>200</v>
       </c>
       <c r="F79" s="11">
-        <v>13400</v>
+        <v>13800</v>
       </c>
       <c r="G79" s="11">
-        <v>13400</v>
+        <v>13800</v>
       </c>
       <c r="H79" s="11">
         <v>0</v>
@@ -5048,13 +5048,13 @@
         <v>9</v>
       </c>
       <c r="J79" s="12">
-        <v>146</v>
+        <v>170</v>
       </c>
       <c r="K79" s="12">
         <v>40</v>
       </c>
       <c r="L79" s="13">
-        <v>3205.74</v>
+        <v>3239.44</v>
       </c>
       <c r="M79" s="14" t="s">
         <v>18</v>
@@ -5080,25 +5080,25 @@
         <v>300</v>
       </c>
       <c r="F80" s="5">
-        <v>16800</v>
+        <v>17700</v>
       </c>
       <c r="G80" s="5">
-        <v>16800</v>
+        <v>17700</v>
       </c>
       <c r="H80" s="5">
         <v>0</v>
       </c>
       <c r="I80" s="6">
-        <v>38</v>
+        <v>41</v>
       </c>
       <c r="J80" s="6">
-        <v>798</v>
+        <v>1114</v>
       </c>
       <c r="K80" s="6">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="L80" s="7">
-        <v>1606.12</v>
+        <v>1609.24</v>
       </c>
       <c r="M80" s="8" t="s">
         <v>18</v>
@@ -5124,25 +5124,25 @@
         <v>400</v>
       </c>
       <c r="F81" s="11">
-        <v>22400</v>
+        <v>19600</v>
       </c>
       <c r="G81" s="11">
-        <v>22400</v>
+        <v>19600</v>
       </c>
       <c r="H81" s="11">
         <v>0</v>
       </c>
       <c r="I81" s="12">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="J81" s="12">
-        <v>219</v>
+        <v>214</v>
       </c>
       <c r="K81" s="12">
-        <v>50</v>
+        <v>47</v>
       </c>
       <c r="L81" s="13">
-        <v>5209.3</v>
+        <v>5153.83</v>
       </c>
       <c r="M81" s="14" t="s">
         <v>18</v>
@@ -5168,10 +5168,10 @@
         <v>500</v>
       </c>
       <c r="F82" s="5">
-        <v>32500</v>
+        <v>16500</v>
       </c>
       <c r="G82" s="5">
-        <v>32500</v>
+        <v>16500</v>
       </c>
       <c r="H82" s="5">
         <v>0</v>
@@ -5180,13 +5180,13 @@
         <v>10</v>
       </c>
       <c r="J82" s="6">
-        <v>226</v>
+        <v>181</v>
       </c>
       <c r="K82" s="6">
-        <v>51</v>
+        <v>56</v>
       </c>
       <c r="L82" s="7">
-        <v>6749.74</v>
+        <v>4928.32</v>
       </c>
       <c r="M82" s="8" t="s">
         <v>18</v>
@@ -5212,25 +5212,25 @@
         <v>10</v>
       </c>
       <c r="F83" s="11">
-        <v>380</v>
+        <v>250</v>
       </c>
       <c r="G83" s="11">
-        <v>380</v>
+        <v>250</v>
       </c>
       <c r="H83" s="11">
         <v>0</v>
       </c>
       <c r="I83" s="12">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="J83" s="12">
-        <v>113</v>
+        <v>117</v>
       </c>
       <c r="K83" s="12">
         <v>30</v>
       </c>
       <c r="L83" s="13">
-        <v>143.94</v>
+        <v>111.11</v>
       </c>
       <c r="M83" s="14" t="s">
         <v>18</v>
@@ -5256,25 +5256,25 @@
         <v>25</v>
       </c>
       <c r="F84" s="5">
-        <v>1050</v>
+        <v>825</v>
       </c>
       <c r="G84" s="5">
-        <v>1050</v>
+        <v>825</v>
       </c>
       <c r="H84" s="5">
         <v>0</v>
       </c>
       <c r="I84" s="6">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="J84" s="6">
-        <v>134</v>
+        <v>104</v>
       </c>
       <c r="K84" s="6">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="L84" s="7">
-        <v>374.73</v>
+        <v>331.33</v>
       </c>
       <c r="M84" s="8" t="s">
         <v>18</v>
@@ -5300,10 +5300,10 @@
         <v>50</v>
       </c>
       <c r="F85" s="11">
-        <v>1150</v>
+        <v>2650</v>
       </c>
       <c r="G85" s="11">
-        <v>1150</v>
+        <v>2650</v>
       </c>
       <c r="H85" s="11">
         <v>0</v>
@@ -5312,13 +5312,13 @@
         <v>9</v>
       </c>
       <c r="J85" s="12">
-        <v>135</v>
+        <v>114</v>
       </c>
       <c r="K85" s="12">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="L85" s="13">
-        <v>519.66</v>
+        <v>815.64</v>
       </c>
       <c r="M85" s="14" t="s">
         <v>18</v>
@@ -5353,16 +5353,16 @@
         <v>0</v>
       </c>
       <c r="I86" s="6">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="J86" s="6">
-        <v>127</v>
+        <v>132</v>
       </c>
       <c r="K86" s="6">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="L86" s="7">
-        <v>1078.84</v>
+        <v>1102.63</v>
       </c>
       <c r="M86" s="8" t="s">
         <v>18</v>
@@ -5388,25 +5388,25 @@
         <v>150</v>
       </c>
       <c r="F87" s="11">
-        <v>9900</v>
+        <v>10350</v>
       </c>
       <c r="G87" s="11">
-        <v>9900</v>
+        <v>10350</v>
       </c>
       <c r="H87" s="11">
         <v>0</v>
       </c>
       <c r="I87" s="12">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="J87" s="12">
-        <v>762</v>
+        <v>736</v>
       </c>
       <c r="K87" s="12">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="L87" s="13">
-        <v>945.02</v>
+        <v>944.95</v>
       </c>
       <c r="M87" s="14" t="s">
         <v>18</v>
@@ -5432,25 +5432,25 @@
         <v>200</v>
       </c>
       <c r="F88" s="5">
-        <v>6600</v>
+        <v>5800</v>
       </c>
       <c r="G88" s="5">
-        <v>6600</v>
+        <v>5800</v>
       </c>
       <c r="H88" s="5">
         <v>0</v>
       </c>
       <c r="I88" s="6">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="J88" s="6">
-        <v>183</v>
+        <v>152</v>
       </c>
       <c r="K88" s="6">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="L88" s="7">
-        <v>2340.43</v>
+        <v>2229.05</v>
       </c>
       <c r="M88" s="8" t="s">
         <v>18</v>
@@ -5476,25 +5476,25 @@
         <v>300</v>
       </c>
       <c r="F89" s="11">
-        <v>17700</v>
+        <v>14700</v>
       </c>
       <c r="G89" s="11">
-        <v>17700</v>
+        <v>14700</v>
       </c>
       <c r="H89" s="11">
         <v>0</v>
       </c>
       <c r="I89" s="12">
-        <v>124</v>
+        <v>117</v>
       </c>
       <c r="J89" s="12">
-        <v>2716</v>
+        <v>3021</v>
       </c>
       <c r="K89" s="12">
-        <v>471</v>
+        <v>480</v>
       </c>
       <c r="L89" s="13">
-        <v>604.32</v>
+        <v>587.53</v>
       </c>
       <c r="M89" s="14" t="s">
         <v>18</v>
@@ -5520,10 +5520,10 @@
         <v>400</v>
       </c>
       <c r="F90" s="5">
-        <v>13600</v>
+        <v>27600</v>
       </c>
       <c r="G90" s="5">
-        <v>13600</v>
+        <v>27600</v>
       </c>
       <c r="H90" s="5">
         <v>0</v>
@@ -5532,13 +5532,13 @@
         <v>10</v>
       </c>
       <c r="J90" s="6">
-        <v>211</v>
+        <v>160</v>
       </c>
       <c r="K90" s="6">
-        <v>49</v>
+        <v>46</v>
       </c>
       <c r="L90" s="7">
-        <v>4295.64</v>
+        <v>5905.01</v>
       </c>
       <c r="M90" s="8" t="s">
         <v>18</v>
@@ -5564,10 +5564,10 @@
         <v>500</v>
       </c>
       <c r="F91" s="11">
-        <v>19500</v>
+        <v>32500</v>
       </c>
       <c r="G91" s="11">
-        <v>19500</v>
+        <v>32500</v>
       </c>
       <c r="H91" s="11">
         <v>0</v>
@@ -5576,13 +5576,13 @@
         <v>39</v>
       </c>
       <c r="J91" s="12">
-        <v>1041</v>
+        <v>1151</v>
       </c>
       <c r="K91" s="12">
-        <v>203</v>
+        <v>205</v>
       </c>
       <c r="L91" s="13">
-        <v>2070.72</v>
+        <v>2192.24</v>
       </c>
       <c r="M91" s="14" t="s">
         <v>18</v>
@@ -5608,25 +5608,25 @@
         <v>10</v>
       </c>
       <c r="F92" s="5">
-        <v>270</v>
+        <v>400</v>
       </c>
       <c r="G92" s="5">
-        <v>270</v>
+        <v>400</v>
       </c>
       <c r="H92" s="5">
         <v>0</v>
       </c>
       <c r="I92" s="6">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="J92" s="6">
-        <v>102</v>
+        <v>99</v>
       </c>
       <c r="K92" s="6">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="L92" s="7">
-        <v>116.88</v>
+        <v>145.99</v>
       </c>
       <c r="M92" s="8" t="s">
         <v>18</v>
@@ -5652,25 +5652,25 @@
         <v>25</v>
       </c>
       <c r="F93" s="11">
-        <v>1675</v>
+        <v>775</v>
       </c>
       <c r="G93" s="11">
-        <v>1675</v>
+        <v>775</v>
       </c>
       <c r="H93" s="11">
         <v>0</v>
       </c>
       <c r="I93" s="12">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="J93" s="12">
-        <v>129</v>
+        <v>133</v>
       </c>
       <c r="K93" s="12">
         <v>31</v>
       </c>
       <c r="L93" s="13">
-        <v>468.27</v>
+        <v>314.91</v>
       </c>
       <c r="M93" s="14" t="s">
         <v>18</v>
@@ -5696,10 +5696,10 @@
         <v>50</v>
       </c>
       <c r="F94" s="5">
-        <v>3050</v>
+        <v>2600</v>
       </c>
       <c r="G94" s="5">
-        <v>3050</v>
+        <v>2600</v>
       </c>
       <c r="H94" s="5">
         <v>0</v>
@@ -5708,13 +5708,13 @@
         <v>9</v>
       </c>
       <c r="J94" s="6">
-        <v>149</v>
+        <v>118</v>
       </c>
       <c r="K94" s="6">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="L94" s="7">
-        <v>868.2</v>
+        <v>835.48</v>
       </c>
       <c r="M94" s="8" t="s">
         <v>18</v>
@@ -5740,25 +5740,25 @@
         <v>100</v>
       </c>
       <c r="F95" s="11">
-        <v>5000</v>
+        <v>6200</v>
       </c>
       <c r="G95" s="11">
-        <v>5000</v>
+        <v>6200</v>
       </c>
       <c r="H95" s="11">
         <v>0</v>
       </c>
       <c r="I95" s="12">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="J95" s="12">
-        <v>118</v>
+        <v>121</v>
       </c>
       <c r="K95" s="12">
         <v>33</v>
       </c>
       <c r="L95" s="13">
-        <v>1587.3</v>
+        <v>1748.45</v>
       </c>
       <c r="M95" s="14" t="s">
         <v>18</v>
@@ -5784,25 +5784,25 @@
         <v>150</v>
       </c>
       <c r="F96" s="5">
-        <v>3750</v>
+        <v>9600</v>
       </c>
       <c r="G96" s="5">
-        <v>3750</v>
+        <v>9600</v>
       </c>
       <c r="H96" s="5">
         <v>0</v>
       </c>
       <c r="I96" s="6">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="J96" s="6">
-        <v>131</v>
+        <v>124</v>
       </c>
       <c r="K96" s="6">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="L96" s="7">
-        <v>1562.5</v>
+        <v>2566.84</v>
       </c>
       <c r="M96" s="8" t="s">
         <v>18</v>
@@ -5828,25 +5828,25 @@
         <v>200</v>
       </c>
       <c r="F97" s="11">
-        <v>6600</v>
+        <v>12200</v>
       </c>
       <c r="G97" s="11">
-        <v>6600</v>
+        <v>12200</v>
       </c>
       <c r="H97" s="11">
         <v>0</v>
       </c>
       <c r="I97" s="12">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="J97" s="12">
-        <v>135</v>
+        <v>161</v>
       </c>
       <c r="K97" s="12">
         <v>38</v>
       </c>
       <c r="L97" s="13">
-        <v>2396.51</v>
+        <v>3195.39</v>
       </c>
       <c r="M97" s="14" t="s">
         <v>18</v>
@@ -5872,25 +5872,25 @@
         <v>300</v>
       </c>
       <c r="F98" s="5">
-        <v>13200</v>
+        <v>16200</v>
       </c>
       <c r="G98" s="5">
-        <v>13200</v>
+        <v>16200</v>
       </c>
       <c r="H98" s="5">
         <v>0</v>
       </c>
       <c r="I98" s="6">
-        <v>38</v>
+        <v>43</v>
       </c>
       <c r="J98" s="6">
-        <v>835</v>
+        <v>781</v>
       </c>
       <c r="K98" s="6">
-        <v>158</v>
+        <v>163</v>
       </c>
       <c r="L98" s="7">
-        <v>1561.76</v>
+        <v>1572.51</v>
       </c>
       <c r="M98" s="8" t="s">
         <v>18</v>
@@ -5916,10 +5916,10 @@
         <v>400</v>
       </c>
       <c r="F99" s="11">
-        <v>23600</v>
+        <v>8800</v>
       </c>
       <c r="G99" s="11">
-        <v>23600</v>
+        <v>8800</v>
       </c>
       <c r="H99" s="11">
         <v>0</v>
@@ -5928,13 +5928,13 @@
         <v>10</v>
       </c>
       <c r="J99" s="12">
-        <v>204</v>
+        <v>191</v>
       </c>
       <c r="K99" s="12">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="L99" s="13">
-        <v>5447.83</v>
+        <v>3503.18</v>
       </c>
       <c r="M99" s="14" t="s">
         <v>18</v>
@@ -5960,25 +5960,25 @@
         <v>500</v>
       </c>
       <c r="F100" s="5">
-        <v>10500</v>
+        <v>22500</v>
       </c>
       <c r="G100" s="5">
-        <v>10500</v>
+        <v>22500</v>
       </c>
       <c r="H100" s="5">
         <v>0</v>
       </c>
       <c r="I100" s="6">
-        <v>120</v>
+        <v>115</v>
       </c>
       <c r="J100" s="6">
-        <v>3863</v>
+        <v>3295</v>
       </c>
       <c r="K100" s="6">
-        <v>547</v>
+        <v>596</v>
       </c>
       <c r="L100" s="7">
-        <v>808.5</v>
+        <v>794.49</v>
       </c>
       <c r="M100" s="8" t="s">
         <v>18</v>
@@ -6004,10 +6004,10 @@
         <v>10</v>
       </c>
       <c r="F101" s="11">
-        <v>600</v>
+        <v>470</v>
       </c>
       <c r="G101" s="11">
-        <v>600</v>
+        <v>470</v>
       </c>
       <c r="H101" s="11">
         <v>0</v>
@@ -6016,13 +6016,13 @@
         <v>9</v>
       </c>
       <c r="J101" s="12">
-        <v>114</v>
+        <v>132</v>
       </c>
       <c r="K101" s="12">
         <v>31</v>
       </c>
       <c r="L101" s="13">
-        <v>178.57</v>
+        <v>158.94</v>
       </c>
       <c r="M101" s="14" t="s">
         <v>18</v>
@@ -6048,25 +6048,25 @@
         <v>25</v>
       </c>
       <c r="F102" s="5">
-        <v>1125</v>
+        <v>1650</v>
       </c>
       <c r="G102" s="5">
-        <v>1125</v>
+        <v>1650</v>
       </c>
       <c r="H102" s="5">
         <v>0</v>
       </c>
       <c r="I102" s="6">
-        <v>42</v>
+        <v>39</v>
       </c>
       <c r="J102" s="6">
-        <v>618</v>
+        <v>570</v>
       </c>
       <c r="K102" s="6">
-        <v>115</v>
+        <v>118</v>
       </c>
       <c r="L102" s="7">
-        <v>168.54</v>
+        <v>177.65</v>
       </c>
       <c r="M102" s="8" t="s">
         <v>18</v>
@@ -6092,25 +6092,25 @@
         <v>50</v>
       </c>
       <c r="F103" s="11">
-        <v>1250</v>
+        <v>2600</v>
       </c>
       <c r="G103" s="11">
-        <v>1250</v>
+        <v>2600</v>
       </c>
       <c r="H103" s="11">
         <v>0</v>
       </c>
       <c r="I103" s="12">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="J103" s="12">
-        <v>145</v>
+        <v>148</v>
       </c>
       <c r="K103" s="12">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="L103" s="13">
-        <v>537.63</v>
+        <v>821.74</v>
       </c>
       <c r="M103" s="14" t="s">
         <v>18</v>
@@ -6136,25 +6136,25 @@
         <v>100</v>
       </c>
       <c r="F104" s="5">
-        <v>4700</v>
+        <v>3400</v>
       </c>
       <c r="G104" s="5">
-        <v>4700</v>
+        <v>3400</v>
       </c>
       <c r="H104" s="5">
         <v>0</v>
       </c>
       <c r="I104" s="6">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="J104" s="6">
-        <v>142</v>
+        <v>147</v>
       </c>
       <c r="K104" s="6">
         <v>33</v>
       </c>
       <c r="L104" s="7">
-        <v>1540.48</v>
+        <v>1296.72</v>
       </c>
       <c r="M104" s="8" t="s">
         <v>18</v>
@@ -6180,16 +6180,16 @@
         <v>150</v>
       </c>
       <c r="F105" s="11">
-        <v>7050</v>
+        <v>3900</v>
       </c>
       <c r="G105" s="11">
-        <v>7050</v>
+        <v>3900</v>
       </c>
       <c r="H105" s="11">
         <v>0</v>
       </c>
       <c r="I105" s="12">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="J105" s="12">
         <v>148</v>
@@ -6198,7 +6198,7 @@
         <v>36</v>
       </c>
       <c r="L105" s="13">
-        <v>2208.65</v>
+        <v>1600.99</v>
       </c>
       <c r="M105" s="14" t="s">
         <v>18</v>
@@ -6224,25 +6224,25 @@
         <v>200</v>
       </c>
       <c r="F106" s="5">
-        <v>10800</v>
+        <v>6600</v>
       </c>
       <c r="G106" s="5">
-        <v>10800</v>
+        <v>6600</v>
       </c>
       <c r="H106" s="5">
         <v>0</v>
       </c>
       <c r="I106" s="6">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="J106" s="6">
-        <v>150</v>
+        <v>152</v>
       </c>
       <c r="K106" s="6">
-        <v>38</v>
+        <v>41</v>
       </c>
       <c r="L106" s="7">
-        <v>3040.54</v>
+        <v>2313.35</v>
       </c>
       <c r="M106" s="8" t="s">
         <v>18</v>
@@ -6268,10 +6268,10 @@
         <v>300</v>
       </c>
       <c r="F107" s="11">
-        <v>8100</v>
+        <v>6000</v>
       </c>
       <c r="G107" s="11">
-        <v>8100</v>
+        <v>6000</v>
       </c>
       <c r="H107" s="11">
         <v>0</v>
@@ -6286,7 +6286,7 @@
         <v>45</v>
       </c>
       <c r="L107" s="13">
-        <v>2983.43</v>
+        <v>2500</v>
       </c>
       <c r="M107" s="14" t="s">
         <v>18</v>
@@ -6312,10 +6312,10 @@
         <v>400</v>
       </c>
       <c r="F108" s="5">
-        <v>20000</v>
+        <v>26800</v>
       </c>
       <c r="G108" s="5">
-        <v>20000</v>
+        <v>26800</v>
       </c>
       <c r="H108" s="5">
         <v>0</v>
@@ -6324,13 +6324,13 @@
         <v>9</v>
       </c>
       <c r="J108" s="6">
-        <v>165</v>
+        <v>171</v>
       </c>
       <c r="K108" s="6">
         <v>50</v>
       </c>
       <c r="L108" s="7">
-        <v>5000</v>
+        <v>5525.77</v>
       </c>
       <c r="M108" s="8" t="s">
         <v>18</v>
@@ -6356,10 +6356,10 @@
         <v>500</v>
       </c>
       <c r="F109" s="11">
-        <v>11000</v>
+        <v>19000</v>
       </c>
       <c r="G109" s="11">
-        <v>11000</v>
+        <v>19000</v>
       </c>
       <c r="H109" s="11">
         <v>0</v>
@@ -6368,13 +6368,13 @@
         <v>42</v>
       </c>
       <c r="J109" s="12">
-        <v>1051</v>
+        <v>1202</v>
       </c>
       <c r="K109" s="12">
-        <v>188</v>
+        <v>202</v>
       </c>
       <c r="L109" s="13">
-        <v>1951.74</v>
+        <v>2070.62</v>
       </c>
       <c r="M109" s="14" t="s">
         <v>18</v>
@@ -6400,10 +6400,10 @@
         <v>10</v>
       </c>
       <c r="F110" s="5">
-        <v>210</v>
+        <v>620</v>
       </c>
       <c r="G110" s="5">
-        <v>210</v>
+        <v>620</v>
       </c>
       <c r="H110" s="5">
         <v>0</v>
@@ -6412,13 +6412,13 @@
         <v>10</v>
       </c>
       <c r="J110" s="6">
-        <v>137</v>
+        <v>98</v>
       </c>
       <c r="K110" s="6">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="L110" s="7">
-        <v>99.57</v>
+        <v>191.59</v>
       </c>
       <c r="M110" s="8" t="s">
         <v>18</v>
@@ -6444,25 +6444,25 @@
         <v>25</v>
       </c>
       <c r="F111" s="11">
-        <v>625</v>
+        <v>1175</v>
       </c>
       <c r="G111" s="11">
-        <v>625</v>
+        <v>1175</v>
       </c>
       <c r="H111" s="11">
         <v>0</v>
       </c>
       <c r="I111" s="12">
-        <v>119</v>
+        <v>126</v>
       </c>
       <c r="J111" s="12">
-        <v>1895</v>
+        <v>2203</v>
       </c>
       <c r="K111" s="12">
-        <v>349</v>
+        <v>318</v>
       </c>
       <c r="L111" s="13">
-        <v>61.12</v>
+        <v>71.45</v>
       </c>
       <c r="M111" s="14" t="s">
         <v>18</v>
@@ -6488,10 +6488,10 @@
         <v>50</v>
       </c>
       <c r="F112" s="5">
-        <v>2700</v>
+        <v>2750</v>
       </c>
       <c r="G112" s="5">
-        <v>2700</v>
+        <v>2750</v>
       </c>
       <c r="H112" s="5">
         <v>0</v>
@@ -6500,13 +6500,13 @@
         <v>10</v>
       </c>
       <c r="J112" s="6">
-        <v>137</v>
+        <v>129</v>
       </c>
       <c r="K112" s="6">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="L112" s="7">
-        <v>822.67</v>
+        <v>858.03</v>
       </c>
       <c r="M112" s="8" t="s">
         <v>18</v>
@@ -6532,10 +6532,10 @@
         <v>100</v>
       </c>
       <c r="F113" s="11">
-        <v>6700</v>
+        <v>3800</v>
       </c>
       <c r="G113" s="11">
-        <v>6700</v>
+        <v>3800</v>
       </c>
       <c r="H113" s="11">
         <v>0</v>
@@ -6544,13 +6544,13 @@
         <v>39</v>
       </c>
       <c r="J113" s="12">
-        <v>764</v>
+        <v>665</v>
       </c>
       <c r="K113" s="12">
-        <v>129</v>
+        <v>131</v>
       </c>
       <c r="L113" s="13">
-        <v>660.55</v>
+        <v>586.6</v>
       </c>
       <c r="M113" s="14" t="s">
         <v>18</v>
@@ -6576,25 +6576,25 @@
         <v>150</v>
       </c>
       <c r="F114" s="5">
-        <v>5100</v>
+        <v>3000</v>
       </c>
       <c r="G114" s="5">
-        <v>5100</v>
+        <v>3000</v>
       </c>
       <c r="H114" s="5">
         <v>0</v>
       </c>
       <c r="I114" s="6">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="J114" s="6">
-        <v>154</v>
+        <v>146</v>
       </c>
       <c r="K114" s="6">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="L114" s="7">
-        <v>1849.17</v>
+        <v>1351.35</v>
       </c>
       <c r="M114" s="8" t="s">
         <v>18</v>
@@ -6620,25 +6620,25 @@
         <v>200</v>
       </c>
       <c r="F115" s="11">
-        <v>8800</v>
+        <v>10800</v>
       </c>
       <c r="G115" s="11">
-        <v>8800</v>
+        <v>10800</v>
       </c>
       <c r="H115" s="11">
         <v>0</v>
       </c>
       <c r="I115" s="12">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="J115" s="12">
-        <v>147</v>
+        <v>158</v>
       </c>
       <c r="K115" s="12">
-        <v>38</v>
+        <v>41</v>
       </c>
       <c r="L115" s="13">
-        <v>2774.27</v>
+        <v>2907.92</v>
       </c>
       <c r="M115" s="14" t="s">
         <v>18</v>
@@ -6676,13 +6676,13 @@
         <v>10</v>
       </c>
       <c r="J116" s="6">
-        <v>203</v>
+        <v>146</v>
       </c>
       <c r="K116" s="6">
-        <v>45</v>
+        <v>42</v>
       </c>
       <c r="L116" s="7">
-        <v>3677.13</v>
+        <v>3817.5</v>
       </c>
       <c r="M116" s="8" t="s">
         <v>18</v>
@@ -6708,25 +6708,25 @@
         <v>400</v>
       </c>
       <c r="F117" s="11">
-        <v>22800</v>
+        <v>21200</v>
       </c>
       <c r="G117" s="11">
-        <v>22800</v>
+        <v>21200</v>
       </c>
       <c r="H117" s="11">
         <v>0</v>
       </c>
       <c r="I117" s="12">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="J117" s="12">
-        <v>226</v>
+        <v>222</v>
       </c>
       <c r="K117" s="12">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="L117" s="13">
-        <v>5241.38</v>
+        <v>5242.33</v>
       </c>
       <c r="M117" s="14" t="s">
         <v>18</v>
@@ -6752,25 +6752,25 @@
         <v>500</v>
       </c>
       <c r="F118" s="5">
-        <v>30500</v>
+        <v>11000</v>
       </c>
       <c r="G118" s="5">
-        <v>30500</v>
+        <v>11000</v>
       </c>
       <c r="H118" s="5">
         <v>0</v>
       </c>
       <c r="I118" s="6">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="J118" s="6">
-        <v>189</v>
+        <v>179</v>
       </c>
       <c r="K118" s="6">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="L118" s="7">
-        <v>6282.18</v>
+        <v>4092.26</v>
       </c>
       <c r="M118" s="8" t="s">
         <v>18</v>
@@ -6796,25 +6796,25 @@
         <v>10</v>
       </c>
       <c r="F119" s="11">
-        <v>370</v>
+        <v>410</v>
       </c>
       <c r="G119" s="11">
-        <v>370</v>
+        <v>410</v>
       </c>
       <c r="H119" s="11">
         <v>0</v>
       </c>
       <c r="I119" s="12">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="J119" s="12">
-        <v>123</v>
+        <v>97</v>
       </c>
       <c r="K119" s="12">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="L119" s="13">
-        <v>141.76</v>
+        <v>147.96</v>
       </c>
       <c r="M119" s="14" t="s">
         <v>18</v>
@@ -6840,10 +6840,10 @@
         <v>25</v>
       </c>
       <c r="F120" s="5">
-        <v>1450</v>
+        <v>1375</v>
       </c>
       <c r="G120" s="5">
-        <v>1450</v>
+        <v>1375</v>
       </c>
       <c r="H120" s="5">
         <v>0</v>
@@ -6852,13 +6852,13 @@
         <v>37</v>
       </c>
       <c r="J120" s="6">
-        <v>634</v>
+        <v>771</v>
       </c>
       <c r="K120" s="6">
-        <v>118</v>
+        <v>109</v>
       </c>
       <c r="L120" s="7">
-        <v>173.78</v>
+        <v>183.46</v>
       </c>
       <c r="M120" s="8" t="s">
         <v>18</v>
@@ -6884,10 +6884,10 @@
         <v>50</v>
       </c>
       <c r="F121" s="11">
-        <v>2350</v>
+        <v>1900</v>
       </c>
       <c r="G121" s="11">
-        <v>2350</v>
+        <v>1900</v>
       </c>
       <c r="H121" s="11">
         <v>0</v>
@@ -6896,13 +6896,13 @@
         <v>10</v>
       </c>
       <c r="J121" s="12">
-        <v>111</v>
+        <v>128</v>
       </c>
       <c r="K121" s="12">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="L121" s="13">
-        <v>794.72</v>
+        <v>719.7</v>
       </c>
       <c r="M121" s="14" t="s">
         <v>18</v>
@@ -6928,25 +6928,25 @@
         <v>100</v>
       </c>
       <c r="F122" s="5">
-        <v>5400</v>
+        <v>4100</v>
       </c>
       <c r="G122" s="5">
-        <v>5400</v>
+        <v>4100</v>
       </c>
       <c r="H122" s="5">
         <v>0</v>
       </c>
       <c r="I122" s="6">
-        <v>120</v>
+        <v>110</v>
       </c>
       <c r="J122" s="6">
-        <v>1718</v>
+        <v>1867</v>
       </c>
       <c r="K122" s="6">
-        <v>385</v>
+        <v>357</v>
       </c>
       <c r="L122" s="7">
-        <v>242.26</v>
+        <v>254.07</v>
       </c>
       <c r="M122" s="8" t="s">
         <v>18</v>
@@ -6972,25 +6972,25 @@
         <v>150</v>
       </c>
       <c r="F123" s="11">
-        <v>7050</v>
+        <v>5100</v>
       </c>
       <c r="G123" s="11">
-        <v>7050</v>
+        <v>5100</v>
       </c>
       <c r="H123" s="11">
         <v>0</v>
       </c>
       <c r="I123" s="12">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="J123" s="12">
-        <v>136</v>
+        <v>167</v>
       </c>
       <c r="K123" s="12">
-        <v>38</v>
+        <v>35</v>
       </c>
       <c r="L123" s="13">
-        <v>2145.47</v>
+        <v>1895.91</v>
       </c>
       <c r="M123" s="14" t="s">
         <v>18</v>
@@ -7016,25 +7016,25 @@
         <v>200</v>
       </c>
       <c r="F124" s="5">
-        <v>5000</v>
+        <v>6000</v>
       </c>
       <c r="G124" s="5">
-        <v>5000</v>
+        <v>6000</v>
       </c>
       <c r="H124" s="5">
         <v>0</v>
       </c>
       <c r="I124" s="6">
-        <v>39</v>
+        <v>36</v>
       </c>
       <c r="J124" s="6">
-        <v>938</v>
+        <v>765</v>
       </c>
       <c r="K124" s="6">
-        <v>143</v>
+        <v>148</v>
       </c>
       <c r="L124" s="7">
-        <v>985.22</v>
+        <v>1010.1</v>
       </c>
       <c r="M124" s="8" t="s">
         <v>18</v>
@@ -7060,25 +7060,25 @@
         <v>300</v>
       </c>
       <c r="F125" s="11">
-        <v>6900</v>
+        <v>10200</v>
       </c>
       <c r="G125" s="11">
-        <v>6900</v>
+        <v>10200</v>
       </c>
       <c r="H125" s="11">
         <v>0</v>
       </c>
       <c r="I125" s="12">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="J125" s="12">
-        <v>205</v>
+        <v>187</v>
       </c>
       <c r="K125" s="12">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="L125" s="13">
-        <v>2772.2</v>
+        <v>3404.54</v>
       </c>
       <c r="M125" s="14" t="s">
         <v>18</v>
@@ -7104,25 +7104,25 @@
         <v>400</v>
       </c>
       <c r="F126" s="5">
-        <v>10400</v>
+        <v>10800</v>
       </c>
       <c r="G126" s="5">
-        <v>10400</v>
+        <v>10800</v>
       </c>
       <c r="H126" s="5">
         <v>0</v>
       </c>
       <c r="I126" s="6">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="J126" s="6">
-        <v>194</v>
+        <v>226</v>
       </c>
       <c r="K126" s="6">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="L126" s="7">
-        <v>3714.29</v>
+        <v>3825.72</v>
       </c>
       <c r="M126" s="8" t="s">
         <v>18</v>
@@ -7148,25 +7148,25 @@
         <v>500</v>
       </c>
       <c r="F127" s="11">
-        <v>25000</v>
+        <v>23000</v>
       </c>
       <c r="G127" s="11">
-        <v>25000</v>
+        <v>23000</v>
       </c>
       <c r="H127" s="11">
         <v>0</v>
       </c>
       <c r="I127" s="12">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="J127" s="12">
-        <v>192</v>
+        <v>246</v>
       </c>
       <c r="K127" s="12">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="L127" s="13">
-        <v>6097.56</v>
+        <v>5980.24</v>
       </c>
       <c r="M127" s="14" t="s">
         <v>18</v>
@@ -7192,25 +7192,25 @@
         <v>10</v>
       </c>
       <c r="F128" s="5">
-        <v>690</v>
+        <v>580</v>
       </c>
       <c r="G128" s="5">
-        <v>690</v>
+        <v>580</v>
       </c>
       <c r="H128" s="5">
         <v>0</v>
       </c>
       <c r="I128" s="6">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="J128" s="6">
-        <v>100</v>
+        <v>133</v>
       </c>
       <c r="K128" s="6">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="L128" s="7">
-        <v>189.61</v>
+        <v>182.28</v>
       </c>
       <c r="M128" s="8" t="s">
         <v>18</v>
@@ -7236,10 +7236,10 @@
         <v>25</v>
       </c>
       <c r="F129" s="11">
-        <v>975</v>
+        <v>1225</v>
       </c>
       <c r="G129" s="11">
-        <v>975</v>
+        <v>1225</v>
       </c>
       <c r="H129" s="11">
         <v>0</v>
@@ -7248,13 +7248,13 @@
         <v>10</v>
       </c>
       <c r="J129" s="12">
-        <v>144</v>
+        <v>139</v>
       </c>
       <c r="K129" s="12">
-        <v>29</v>
+        <v>32</v>
       </c>
       <c r="L129" s="13">
-        <v>370.58</v>
+        <v>399.28</v>
       </c>
       <c r="M129" s="14" t="s">
         <v>18</v>
@@ -7280,25 +7280,25 @@
         <v>50</v>
       </c>
       <c r="F130" s="5">
-        <v>2700</v>
+        <v>2750</v>
       </c>
       <c r="G130" s="5">
-        <v>2700</v>
+        <v>2750</v>
       </c>
       <c r="H130" s="5">
         <v>0</v>
       </c>
       <c r="I130" s="6">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="J130" s="6">
         <v>140</v>
       </c>
       <c r="K130" s="6">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="L130" s="7">
-        <v>850.66</v>
+        <v>829.56</v>
       </c>
       <c r="M130" s="8" t="s">
         <v>18</v>
@@ -7324,25 +7324,25 @@
         <v>100</v>
       </c>
       <c r="F131" s="11">
-        <v>4500</v>
+        <v>3100</v>
       </c>
       <c r="G131" s="11">
-        <v>4500</v>
+        <v>3100</v>
       </c>
       <c r="H131" s="11">
         <v>0</v>
       </c>
       <c r="I131" s="12">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="J131" s="12">
-        <v>745</v>
+        <v>849</v>
       </c>
       <c r="K131" s="12">
-        <v>127</v>
+        <v>133</v>
       </c>
       <c r="L131" s="13">
-        <v>623.7</v>
+        <v>551.31</v>
       </c>
       <c r="M131" s="14" t="s">
         <v>18</v>
@@ -7368,10 +7368,10 @@
         <v>150</v>
       </c>
       <c r="F132" s="5">
-        <v>3300</v>
+        <v>10200</v>
       </c>
       <c r="G132" s="5">
-        <v>3300</v>
+        <v>10200</v>
       </c>
       <c r="H132" s="5">
         <v>0</v>
@@ -7380,13 +7380,13 @@
         <v>9</v>
       </c>
       <c r="J132" s="6">
-        <v>119</v>
+        <v>170</v>
       </c>
       <c r="K132" s="6">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="L132" s="7">
-        <v>1412.67</v>
+        <v>2539.84</v>
       </c>
       <c r="M132" s="8" t="s">
         <v>18</v>
@@ -7412,25 +7412,25 @@
         <v>200</v>
       </c>
       <c r="F133" s="11">
-        <v>10400</v>
+        <v>8600</v>
       </c>
       <c r="G133" s="11">
-        <v>10400</v>
+        <v>8600</v>
       </c>
       <c r="H133" s="11">
         <v>0</v>
       </c>
       <c r="I133" s="12">
-        <v>118</v>
+        <v>110</v>
       </c>
       <c r="J133" s="12">
-        <v>2701</v>
+        <v>2612</v>
       </c>
       <c r="K133" s="12">
-        <v>423</v>
+        <v>412</v>
       </c>
       <c r="L133" s="13">
-        <v>442.63</v>
+        <v>447.54</v>
       </c>
       <c r="M133" s="14" t="s">
         <v>18</v>
@@ -7456,10 +7456,10 @@
         <v>300</v>
       </c>
       <c r="F134" s="5">
-        <v>20400</v>
+        <v>12900</v>
       </c>
       <c r="G134" s="5">
-        <v>20400</v>
+        <v>12900</v>
       </c>
       <c r="H134" s="5">
         <v>0</v>
@@ -7468,13 +7468,13 @@
         <v>9</v>
       </c>
       <c r="J134" s="6">
-        <v>145</v>
+        <v>180</v>
       </c>
       <c r="K134" s="6">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="L134" s="7">
-        <v>4611.21</v>
+        <v>3755.46</v>
       </c>
       <c r="M134" s="8" t="s">
         <v>18</v>
@@ -7500,25 +7500,25 @@
         <v>400</v>
       </c>
       <c r="F135" s="11">
-        <v>14000</v>
+        <v>21200</v>
       </c>
       <c r="G135" s="11">
-        <v>14000</v>
+        <v>21200</v>
       </c>
       <c r="H135" s="11">
         <v>0</v>
       </c>
       <c r="I135" s="12">
-        <v>36</v>
+        <v>42</v>
       </c>
       <c r="J135" s="12">
-        <v>1140</v>
+        <v>1148</v>
       </c>
       <c r="K135" s="12">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="L135" s="13">
-        <v>1740.21</v>
+        <v>1849.27</v>
       </c>
       <c r="M135" s="14" t="s">
         <v>18</v>
@@ -7544,10 +7544,10 @@
         <v>500</v>
       </c>
       <c r="F136" s="5">
-        <v>21000</v>
+        <v>17000</v>
       </c>
       <c r="G136" s="5">
-        <v>21000</v>
+        <v>17000</v>
       </c>
       <c r="H136" s="5">
         <v>0</v>
@@ -7556,13 +7556,13 @@
         <v>9</v>
       </c>
       <c r="J136" s="6">
-        <v>199</v>
+        <v>182</v>
       </c>
       <c r="K136" s="6">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="L136" s="7">
-        <v>5451.71</v>
+        <v>5044.51</v>
       </c>
       <c r="M136" s="8" t="s">
         <v>18</v>
@@ -7588,25 +7588,25 @@
         <v>10</v>
       </c>
       <c r="F137" s="11">
-        <v>550</v>
+        <v>600</v>
       </c>
       <c r="G137" s="11">
-        <v>550</v>
+        <v>600</v>
       </c>
       <c r="H137" s="11">
         <v>0</v>
       </c>
       <c r="I137" s="12">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="J137" s="12">
-        <v>105</v>
+        <v>142</v>
       </c>
       <c r="K137" s="12">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="L137" s="13">
-        <v>174.6</v>
+        <v>185.19</v>
       </c>
       <c r="M137" s="14" t="s">
         <v>18</v>
@@ -7632,25 +7632,25 @@
         <v>25</v>
       </c>
       <c r="F138" s="5">
-        <v>1050</v>
+        <v>800</v>
       </c>
       <c r="G138" s="5">
-        <v>1050</v>
+        <v>800</v>
       </c>
       <c r="H138" s="5">
         <v>0</v>
       </c>
       <c r="I138" s="6">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="J138" s="6">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="K138" s="6">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="L138" s="7">
-        <v>374.73</v>
+        <v>325.2</v>
       </c>
       <c r="M138" s="8" t="s">
         <v>18</v>
@@ -7676,10 +7676,10 @@
         <v>50</v>
       </c>
       <c r="F139" s="11">
-        <v>2900</v>
+        <v>1850</v>
       </c>
       <c r="G139" s="11">
-        <v>2900</v>
+        <v>1850</v>
       </c>
       <c r="H139" s="11">
         <v>0</v>
@@ -7688,13 +7688,13 @@
         <v>10</v>
       </c>
       <c r="J139" s="12">
-        <v>137</v>
+        <v>146</v>
       </c>
       <c r="K139" s="12">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="L139" s="13">
-        <v>879.32</v>
+        <v>689.27</v>
       </c>
       <c r="M139" s="14" t="s">
         <v>18</v>
@@ -7720,25 +7720,25 @@
         <v>100</v>
       </c>
       <c r="F140" s="5">
-        <v>4300</v>
+        <v>5900</v>
       </c>
       <c r="G140" s="5">
-        <v>4300</v>
+        <v>5900</v>
       </c>
       <c r="H140" s="5">
         <v>0</v>
       </c>
       <c r="I140" s="6">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="J140" s="6">
         <v>158</v>
       </c>
       <c r="K140" s="6">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="L140" s="7">
-        <v>1430.95</v>
+        <v>1682.83</v>
       </c>
       <c r="M140" s="8" t="s">
         <v>18</v>
@@ -7764,25 +7764,25 @@
         <v>150</v>
       </c>
       <c r="F141" s="11">
-        <v>9300</v>
+        <v>4950</v>
       </c>
       <c r="G141" s="11">
-        <v>9300</v>
+        <v>4950</v>
       </c>
       <c r="H141" s="11">
         <v>0</v>
       </c>
       <c r="I141" s="12">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="J141" s="12">
-        <v>120</v>
+        <v>135</v>
       </c>
       <c r="K141" s="12">
-        <v>38</v>
+        <v>35</v>
       </c>
       <c r="L141" s="13">
-        <v>2411.83</v>
+        <v>1864.41</v>
       </c>
       <c r="M141" s="14" t="s">
         <v>18</v>
@@ -7808,25 +7808,25 @@
         <v>200</v>
       </c>
       <c r="F142" s="5">
-        <v>6000</v>
+        <v>4400</v>
       </c>
       <c r="G142" s="5">
-        <v>6000</v>
+        <v>4400</v>
       </c>
       <c r="H142" s="5">
         <v>0</v>
       </c>
       <c r="I142" s="6">
-        <v>38</v>
+        <v>42</v>
       </c>
       <c r="J142" s="6">
-        <v>780</v>
+        <v>754</v>
       </c>
       <c r="K142" s="6">
-        <v>150</v>
+        <v>139</v>
       </c>
       <c r="L142" s="7">
-        <v>1000</v>
+        <v>965.34</v>
       </c>
       <c r="M142" s="8" t="s">
         <v>18</v>
@@ -7852,10 +7852,10 @@
         <v>300</v>
       </c>
       <c r="F143" s="11">
-        <v>19200</v>
+        <v>17400</v>
       </c>
       <c r="G143" s="11">
-        <v>19200</v>
+        <v>17400</v>
       </c>
       <c r="H143" s="11">
         <v>0</v>
@@ -7864,13 +7864,13 @@
         <v>9</v>
       </c>
       <c r="J143" s="12">
-        <v>175</v>
+        <v>206</v>
       </c>
       <c r="K143" s="12">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="L143" s="13">
-        <v>4320.43</v>
+        <v>4233.58</v>
       </c>
       <c r="M143" s="14" t="s">
         <v>18</v>
@@ -7896,25 +7896,25 @@
         <v>400</v>
       </c>
       <c r="F144" s="5">
-        <v>18800</v>
+        <v>12000</v>
       </c>
       <c r="G144" s="5">
-        <v>18800</v>
+        <v>12000</v>
       </c>
       <c r="H144" s="5">
         <v>0</v>
       </c>
       <c r="I144" s="6">
-        <v>109</v>
+        <v>126</v>
       </c>
       <c r="J144" s="6">
-        <v>3344</v>
+        <v>2404</v>
       </c>
       <c r="K144" s="6">
-        <v>523</v>
+        <v>539</v>
       </c>
       <c r="L144" s="7">
-        <v>720.83</v>
+        <v>679.12</v>
       </c>
       <c r="M144" s="8" t="s">
         <v>18</v>
@@ -7940,10 +7940,10 @@
         <v>500</v>
       </c>
       <c r="F145" s="11">
-        <v>22000</v>
+        <v>13000</v>
       </c>
       <c r="G145" s="11">
-        <v>22000</v>
+        <v>13000</v>
       </c>
       <c r="H145" s="11">
         <v>0</v>
@@ -7952,13 +7952,13 @@
         <v>9</v>
       </c>
       <c r="J145" s="12">
-        <v>213</v>
+        <v>246</v>
       </c>
       <c r="K145" s="12">
-        <v>55</v>
+        <v>53</v>
       </c>
       <c r="L145" s="13">
-        <v>5612.24</v>
+        <v>4517.03</v>
       </c>
       <c r="M145" s="14" t="s">
         <v>18</v>
@@ -7984,25 +7984,25 @@
         <v>10</v>
       </c>
       <c r="F146" s="5">
-        <v>550</v>
+        <v>260</v>
       </c>
       <c r="G146" s="5">
-        <v>550</v>
+        <v>260</v>
       </c>
       <c r="H146" s="5">
         <v>0</v>
       </c>
       <c r="I146" s="6">
-        <v>40</v>
+        <v>36</v>
       </c>
       <c r="J146" s="6">
-        <v>761</v>
+        <v>710</v>
       </c>
       <c r="K146" s="6">
-        <v>115</v>
+        <v>112</v>
       </c>
       <c r="L146" s="7">
-        <v>70.29</v>
+        <v>58.93</v>
       </c>
       <c r="M146" s="8" t="s">
         <v>18</v>
@@ -8028,10 +8028,10 @@
         <v>25</v>
       </c>
       <c r="F147" s="11">
-        <v>1250</v>
+        <v>775</v>
       </c>
       <c r="G147" s="11">
-        <v>1250</v>
+        <v>775</v>
       </c>
       <c r="H147" s="11">
         <v>0</v>
@@ -8043,10 +8043,10 @@
         <v>130</v>
       </c>
       <c r="K147" s="12">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="L147" s="13">
-        <v>403.23</v>
+        <v>318.93</v>
       </c>
       <c r="M147" s="14" t="s">
         <v>18</v>
@@ -8072,25 +8072,25 @@
         <v>50</v>
       </c>
       <c r="F148" s="5">
-        <v>1550</v>
+        <v>1350</v>
       </c>
       <c r="G148" s="5">
-        <v>1550</v>
+        <v>1350</v>
       </c>
       <c r="H148" s="5">
         <v>0</v>
       </c>
       <c r="I148" s="6">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="J148" s="6">
-        <v>110</v>
+        <v>139</v>
       </c>
       <c r="K148" s="6">
         <v>31</v>
       </c>
       <c r="L148" s="7">
-        <v>629.83</v>
+        <v>577.66</v>
       </c>
       <c r="M148" s="8" t="s">
         <v>18</v>
@@ -8116,10 +8116,10 @@
         <v>100</v>
       </c>
       <c r="F149" s="11">
-        <v>5300</v>
+        <v>6700</v>
       </c>
       <c r="G149" s="11">
-        <v>5300</v>
+        <v>6700</v>
       </c>
       <c r="H149" s="11">
         <v>0</v>
@@ -8128,13 +8128,13 @@
         <v>9</v>
       </c>
       <c r="J149" s="12">
-        <v>153</v>
+        <v>160</v>
       </c>
       <c r="K149" s="12">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="L149" s="13">
-        <v>1579.73</v>
+        <v>1805.44</v>
       </c>
       <c r="M149" s="14" t="s">
         <v>18</v>
@@ -8160,25 +8160,25 @@
         <v>150</v>
       </c>
       <c r="F150" s="5">
-        <v>5250</v>
+        <v>6900</v>
       </c>
       <c r="G150" s="5">
-        <v>5250</v>
+        <v>6900</v>
       </c>
       <c r="H150" s="5">
         <v>0</v>
       </c>
       <c r="I150" s="6">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="J150" s="6">
-        <v>178</v>
+        <v>123</v>
       </c>
       <c r="K150" s="6">
         <v>36</v>
       </c>
       <c r="L150" s="7">
-        <v>1902.17</v>
+        <v>2186.31</v>
       </c>
       <c r="M150" s="8" t="s">
         <v>18</v>
@@ -8204,10 +8204,10 @@
         <v>200</v>
       </c>
       <c r="F151" s="11">
-        <v>8000</v>
+        <v>8800</v>
       </c>
       <c r="G151" s="11">
-        <v>8000</v>
+        <v>8800</v>
       </c>
       <c r="H151" s="11">
         <v>0</v>
@@ -8216,13 +8216,13 @@
         <v>10</v>
       </c>
       <c r="J151" s="12">
-        <v>168</v>
+        <v>184</v>
       </c>
       <c r="K151" s="12">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="L151" s="13">
-        <v>2580.65</v>
+        <v>2774.27</v>
       </c>
       <c r="M151" s="14" t="s">
         <v>18</v>
@@ -8248,10 +8248,10 @@
         <v>300</v>
       </c>
       <c r="F152" s="5">
-        <v>16200</v>
+        <v>18000</v>
       </c>
       <c r="G152" s="5">
-        <v>16200</v>
+        <v>18000</v>
       </c>
       <c r="H152" s="5">
         <v>0</v>
@@ -8260,13 +8260,13 @@
         <v>9</v>
       </c>
       <c r="J152" s="6">
-        <v>203</v>
+        <v>200</v>
       </c>
       <c r="K152" s="6">
-        <v>46</v>
+        <v>42</v>
       </c>
       <c r="L152" s="7">
-        <v>4066.27</v>
+        <v>4477.61</v>
       </c>
       <c r="M152" s="8" t="s">
         <v>18</v>
@@ -8292,10 +8292,10 @@
         <v>400</v>
       </c>
       <c r="F153" s="11">
-        <v>17600</v>
+        <v>22800</v>
       </c>
       <c r="G153" s="11">
-        <v>17600</v>
+        <v>22800</v>
       </c>
       <c r="H153" s="11">
         <v>0</v>
@@ -8304,13 +8304,13 @@
         <v>36</v>
       </c>
       <c r="J153" s="12">
-        <v>877</v>
+        <v>889</v>
       </c>
       <c r="K153" s="12">
-        <v>171</v>
+        <v>175</v>
       </c>
       <c r="L153" s="13">
-        <v>1950.35</v>
+        <v>1986.93</v>
       </c>
       <c r="M153" s="14" t="s">
         <v>18</v>
@@ -8336,10 +8336,10 @@
         <v>500</v>
       </c>
       <c r="F154" s="5">
-        <v>30000</v>
+        <v>14500</v>
       </c>
       <c r="G154" s="5">
-        <v>30000</v>
+        <v>14500</v>
       </c>
       <c r="H154" s="5">
         <v>0</v>
@@ -8348,13 +8348,13 @@
         <v>9</v>
       </c>
       <c r="J154" s="6">
-        <v>239</v>
+        <v>219</v>
       </c>
       <c r="K154" s="6">
         <v>52</v>
       </c>
       <c r="L154" s="7">
-        <v>6493.51</v>
+        <v>4820.48</v>
       </c>
       <c r="M154" s="8" t="s">
         <v>18</v>
@@ -8380,25 +8380,25 @@
         <v>10</v>
       </c>
       <c r="F155" s="11">
-        <v>330</v>
+        <v>420</v>
       </c>
       <c r="G155" s="11">
-        <v>330</v>
+        <v>420</v>
       </c>
       <c r="H155" s="11">
         <v>0</v>
       </c>
       <c r="I155" s="12">
-        <v>110</v>
+        <v>123</v>
       </c>
       <c r="J155" s="12">
-        <v>1942</v>
+        <v>1891</v>
       </c>
       <c r="K155" s="12">
-        <v>317</v>
+        <v>316</v>
       </c>
       <c r="L155" s="13">
-        <v>27.59</v>
+        <v>28.43</v>
       </c>
       <c r="M155" s="14" t="s">
         <v>18</v>
@@ -8424,25 +8424,25 @@
         <v>25</v>
       </c>
       <c r="F156" s="5">
-        <v>1025</v>
+        <v>625</v>
       </c>
       <c r="G156" s="5">
-        <v>1025</v>
+        <v>625</v>
       </c>
       <c r="H156" s="5">
         <v>0</v>
       </c>
       <c r="I156" s="6">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="J156" s="6">
-        <v>114</v>
+        <v>122</v>
       </c>
       <c r="K156" s="6">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="L156" s="7">
-        <v>364.51</v>
+        <v>277.78</v>
       </c>
       <c r="M156" s="8" t="s">
         <v>18</v>
@@ -8468,25 +8468,25 @@
         <v>50</v>
       </c>
       <c r="F157" s="11">
-        <v>3450</v>
+        <v>3000</v>
       </c>
       <c r="G157" s="11">
-        <v>3450</v>
+        <v>3000</v>
       </c>
       <c r="H157" s="11">
         <v>0</v>
       </c>
       <c r="I157" s="12">
-        <v>38</v>
+        <v>42</v>
       </c>
       <c r="J157" s="12">
-        <v>800</v>
+        <v>773</v>
       </c>
       <c r="K157" s="12">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="L157" s="13">
-        <v>360.39</v>
+        <v>354.61</v>
       </c>
       <c r="M157" s="14" t="s">
         <v>18</v>
@@ -8512,25 +8512,25 @@
         <v>100</v>
       </c>
       <c r="F158" s="5">
-        <v>6100</v>
+        <v>5100</v>
       </c>
       <c r="G158" s="5">
-        <v>6100</v>
+        <v>5100</v>
       </c>
       <c r="H158" s="5">
         <v>0</v>
       </c>
       <c r="I158" s="6">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="J158" s="6">
-        <v>121</v>
+        <v>152</v>
       </c>
       <c r="K158" s="6">
         <v>33</v>
       </c>
       <c r="L158" s="7">
-        <v>1736.41</v>
+        <v>1602.26</v>
       </c>
       <c r="M158" s="8" t="s">
         <v>18</v>
@@ -8556,25 +8556,25 @@
         <v>150</v>
       </c>
       <c r="F159" s="11">
-        <v>3600</v>
+        <v>8700</v>
       </c>
       <c r="G159" s="11">
-        <v>3600</v>
+        <v>8700</v>
       </c>
       <c r="H159" s="11">
         <v>0</v>
       </c>
       <c r="I159" s="12">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="J159" s="12">
-        <v>152</v>
+        <v>122</v>
       </c>
       <c r="K159" s="12">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="L159" s="13">
-        <v>1522.84</v>
+        <v>2386.18</v>
       </c>
       <c r="M159" s="14" t="s">
         <v>18</v>
@@ -8600,25 +8600,25 @@
         <v>200</v>
       </c>
       <c r="F160" s="5">
-        <v>8600</v>
+        <v>8000</v>
       </c>
       <c r="G160" s="5">
-        <v>8600</v>
+        <v>8000</v>
       </c>
       <c r="H160" s="5">
         <v>0</v>
       </c>
       <c r="I160" s="6">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="J160" s="6">
-        <v>127</v>
+        <v>170</v>
       </c>
       <c r="K160" s="6">
         <v>40</v>
       </c>
       <c r="L160" s="7">
-        <v>2670.81</v>
+        <v>2580.65</v>
       </c>
       <c r="M160" s="8" t="s">
         <v>18</v>
@@ -8644,25 +8644,25 @@
         <v>300</v>
       </c>
       <c r="F161" s="11">
-        <v>6000</v>
+        <v>6300</v>
       </c>
       <c r="G161" s="11">
-        <v>6000</v>
+        <v>6300</v>
       </c>
       <c r="H161" s="11">
         <v>0</v>
       </c>
       <c r="I161" s="12">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="J161" s="12">
-        <v>206</v>
+        <v>177</v>
       </c>
       <c r="K161" s="12">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="L161" s="13">
-        <v>2564.1</v>
+        <v>2599.01</v>
       </c>
       <c r="M161" s="14" t="s">
         <v>18</v>
@@ -8688,25 +8688,25 @@
         <v>400</v>
       </c>
       <c r="F162" s="5">
-        <v>16400</v>
+        <v>11200</v>
       </c>
       <c r="G162" s="5">
-        <v>16400</v>
+        <v>11200</v>
       </c>
       <c r="H162" s="5">
         <v>0</v>
       </c>
       <c r="I162" s="6">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="J162" s="6">
-        <v>188</v>
+        <v>215</v>
       </c>
       <c r="K162" s="6">
-        <v>50</v>
+        <v>47</v>
       </c>
       <c r="L162" s="7">
-        <v>4619.72</v>
+        <v>3977.27</v>
       </c>
       <c r="M162" s="8" t="s">
         <v>18</v>
@@ -8732,10 +8732,10 @@
         <v>500</v>
       </c>
       <c r="F163" s="11">
-        <v>18500</v>
+        <v>27000</v>
       </c>
       <c r="G163" s="11">
-        <v>18500</v>
+        <v>27000</v>
       </c>
       <c r="H163" s="11">
         <v>0</v>
@@ -8744,13 +8744,13 @@
         <v>10</v>
       </c>
       <c r="J163" s="12">
-        <v>217</v>
+        <v>213</v>
       </c>
       <c r="K163" s="12">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="L163" s="13">
-        <v>5462.06</v>
+        <v>6189.82</v>
       </c>
       <c r="M163" s="14" t="s">
         <v>18</v>
@@ -8776,25 +8776,25 @@
         <v>10</v>
       </c>
       <c r="F164" s="5">
-        <v>450</v>
+        <v>270</v>
       </c>
       <c r="G164" s="5">
-        <v>450</v>
+        <v>270</v>
       </c>
       <c r="H164" s="5">
         <v>0</v>
       </c>
       <c r="I164" s="6">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="J164" s="6">
-        <v>612</v>
+        <v>606</v>
       </c>
       <c r="K164" s="6">
-        <v>116</v>
+        <v>110</v>
       </c>
       <c r="L164" s="7">
-        <v>66.96</v>
+        <v>60.4</v>
       </c>
       <c r="M164" s="8" t="s">
         <v>18</v>
@@ -8820,25 +8820,25 @@
         <v>25</v>
       </c>
       <c r="F165" s="11">
-        <v>975</v>
+        <v>725</v>
       </c>
       <c r="G165" s="11">
-        <v>975</v>
+        <v>725</v>
       </c>
       <c r="H165" s="11">
         <v>0</v>
       </c>
       <c r="I165" s="12">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="J165" s="12">
-        <v>117</v>
+        <v>138</v>
       </c>
       <c r="K165" s="12">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="L165" s="13">
-        <v>354.8</v>
+        <v>305.91</v>
       </c>
       <c r="M165" s="14" t="s">
         <v>18</v>
@@ -8864,25 +8864,25 @@
         <v>50</v>
       </c>
       <c r="F166" s="5">
-        <v>1850</v>
+        <v>2650</v>
       </c>
       <c r="G166" s="5">
-        <v>1850</v>
+        <v>2650</v>
       </c>
       <c r="H166" s="5">
         <v>0</v>
       </c>
       <c r="I166" s="6">
-        <v>117</v>
+        <v>122</v>
       </c>
       <c r="J166" s="6">
-        <v>1890</v>
+        <v>2004</v>
       </c>
       <c r="K166" s="6">
-        <v>333</v>
+        <v>357</v>
       </c>
       <c r="L166" s="7">
-        <v>133.85</v>
+        <v>129.77</v>
       </c>
       <c r="M166" s="8" t="s">
         <v>18</v>
@@ -8908,25 +8908,25 @@
         <v>100</v>
       </c>
       <c r="F167" s="11">
-        <v>3600</v>
+        <v>5700</v>
       </c>
       <c r="G167" s="11">
-        <v>3600</v>
+        <v>5700</v>
       </c>
       <c r="H167" s="11">
         <v>0</v>
       </c>
       <c r="I167" s="12">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="J167" s="12">
-        <v>126</v>
+        <v>155</v>
       </c>
       <c r="K167" s="12">
         <v>36</v>
       </c>
       <c r="L167" s="13">
-        <v>1287.55</v>
+        <v>1604.73</v>
       </c>
       <c r="M167" s="14" t="s">
         <v>18</v>
@@ -8952,25 +8952,25 @@
         <v>150</v>
       </c>
       <c r="F168" s="5">
-        <v>3750</v>
+        <v>4800</v>
       </c>
       <c r="G168" s="5">
-        <v>3750</v>
+        <v>4800</v>
       </c>
       <c r="H168" s="5">
         <v>0</v>
       </c>
       <c r="I168" s="6">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="J168" s="6">
-        <v>899</v>
+        <v>958</v>
       </c>
       <c r="K168" s="6">
-        <v>135</v>
+        <v>129</v>
       </c>
       <c r="L168" s="7">
-        <v>769.23</v>
+        <v>852.88</v>
       </c>
       <c r="M168" s="8" t="s">
         <v>18</v>
@@ -8996,10 +8996,10 @@
         <v>200</v>
       </c>
       <c r="F169" s="11">
-        <v>7000</v>
+        <v>7600</v>
       </c>
       <c r="G169" s="11">
-        <v>7000</v>
+        <v>7600</v>
       </c>
       <c r="H169" s="11">
         <v>0</v>
@@ -9008,13 +9008,13 @@
         <v>10</v>
       </c>
       <c r="J169" s="12">
-        <v>183</v>
+        <v>175</v>
       </c>
       <c r="K169" s="12">
         <v>40</v>
       </c>
       <c r="L169" s="13">
-        <v>2413.79</v>
+        <v>2516.56</v>
       </c>
       <c r="M169" s="14" t="s">
         <v>18</v>
@@ -9040,10 +9040,10 @@
         <v>300</v>
       </c>
       <c r="F170" s="5">
-        <v>20400</v>
+        <v>6600</v>
       </c>
       <c r="G170" s="5">
-        <v>20400</v>
+        <v>6600</v>
       </c>
       <c r="H170" s="5">
         <v>0</v>
@@ -9052,13 +9052,13 @@
         <v>9</v>
       </c>
       <c r="J170" s="6">
-        <v>191</v>
+        <v>200</v>
       </c>
       <c r="K170" s="6">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="L170" s="7">
-        <v>4683.2</v>
+        <v>2674.23</v>
       </c>
       <c r="M170" s="8" t="s">
         <v>18</v>
@@ -9084,25 +9084,25 @@
         <v>400</v>
       </c>
       <c r="F171" s="11">
-        <v>24000</v>
+        <v>20800</v>
       </c>
       <c r="G171" s="11">
-        <v>24000</v>
+        <v>20800</v>
       </c>
       <c r="H171" s="11">
         <v>0</v>
       </c>
       <c r="I171" s="12">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="J171" s="12">
-        <v>227</v>
+        <v>232</v>
       </c>
       <c r="K171" s="12">
-        <v>47</v>
+        <v>51</v>
       </c>
       <c r="L171" s="13">
-        <v>5555.56</v>
+        <v>5009.63</v>
       </c>
       <c r="M171" s="14" t="s">
         <v>18</v>
@@ -9128,10 +9128,10 @@
         <v>500</v>
       </c>
       <c r="F172" s="5">
-        <v>23000</v>
+        <v>10500</v>
       </c>
       <c r="G172" s="5">
-        <v>23000</v>
+        <v>10500</v>
       </c>
       <c r="H172" s="5">
         <v>0</v>
@@ -9140,13 +9140,13 @@
         <v>9</v>
       </c>
       <c r="J172" s="6">
-        <v>198</v>
+        <v>239</v>
       </c>
       <c r="K172" s="6">
-        <v>55</v>
+        <v>53</v>
       </c>
       <c r="L172" s="7">
-        <v>5707.2</v>
+        <v>4018.37</v>
       </c>
       <c r="M172" s="8" t="s">
         <v>18</v>
@@ -9172,10 +9172,10 @@
         <v>10</v>
       </c>
       <c r="F173" s="11">
-        <v>490</v>
+        <v>670</v>
       </c>
       <c r="G173" s="11">
-        <v>490</v>
+        <v>670</v>
       </c>
       <c r="H173" s="11">
         <v>0</v>
@@ -9184,13 +9184,13 @@
         <v>9</v>
       </c>
       <c r="J173" s="12">
-        <v>145</v>
+        <v>111</v>
       </c>
       <c r="K173" s="12">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="L173" s="13">
-        <v>167.75</v>
+        <v>190.88</v>
       </c>
       <c r="M173" s="14" t="s">
         <v>18</v>
@@ -9216,10 +9216,10 @@
         <v>25</v>
       </c>
       <c r="F174" s="5">
-        <v>1550</v>
+        <v>525</v>
       </c>
       <c r="G174" s="5">
-        <v>1550</v>
+        <v>525</v>
       </c>
       <c r="H174" s="5">
         <v>0</v>
@@ -9228,13 +9228,13 @@
         <v>9</v>
       </c>
       <c r="J174" s="6">
-        <v>135</v>
+        <v>130</v>
       </c>
       <c r="K174" s="6">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="L174" s="7">
-        <v>452.95</v>
+        <v>241.71</v>
       </c>
       <c r="M174" s="8" t="s">
         <v>18</v>
@@ -9260,10 +9260,10 @@
         <v>50</v>
       </c>
       <c r="F175" s="11">
-        <v>2300</v>
+        <v>2250</v>
       </c>
       <c r="G175" s="11">
-        <v>2300</v>
+        <v>2250</v>
       </c>
       <c r="H175" s="11">
         <v>0</v>
@@ -9272,13 +9272,13 @@
         <v>37</v>
       </c>
       <c r="J175" s="12">
-        <v>734</v>
+        <v>642</v>
       </c>
       <c r="K175" s="12">
-        <v>124</v>
+        <v>114</v>
       </c>
       <c r="L175" s="13">
-        <v>319.27</v>
+        <v>339.37</v>
       </c>
       <c r="M175" s="14" t="s">
         <v>18</v>
@@ -9304,10 +9304,10 @@
         <v>100</v>
       </c>
       <c r="F176" s="5">
-        <v>5300</v>
+        <v>2400</v>
       </c>
       <c r="G176" s="5">
-        <v>5300</v>
+        <v>2400</v>
       </c>
       <c r="H176" s="5">
         <v>0</v>
@@ -9316,13 +9316,13 @@
         <v>10</v>
       </c>
       <c r="J176" s="6">
-        <v>152</v>
+        <v>157</v>
       </c>
       <c r="K176" s="6">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="L176" s="7">
-        <v>1579.73</v>
+        <v>1015.23</v>
       </c>
       <c r="M176" s="8" t="s">
         <v>18</v>
@@ -9348,25 +9348,25 @@
         <v>150</v>
       </c>
       <c r="F177" s="11">
-        <v>5250</v>
+        <v>8250</v>
       </c>
       <c r="G177" s="11">
-        <v>5250</v>
+        <v>8250</v>
       </c>
       <c r="H177" s="11">
         <v>0</v>
       </c>
       <c r="I177" s="12">
-        <v>118</v>
+        <v>130</v>
       </c>
       <c r="J177" s="12">
-        <v>2589</v>
+        <v>2029</v>
       </c>
       <c r="K177" s="12">
-        <v>378</v>
+        <v>415</v>
       </c>
       <c r="L177" s="13">
-        <v>356.42</v>
+        <v>339.16</v>
       </c>
       <c r="M177" s="14" t="s">
         <v>18</v>
@@ -9392,10 +9392,10 @@
         <v>200</v>
       </c>
       <c r="F178" s="5">
-        <v>5400</v>
+        <v>7400</v>
       </c>
       <c r="G178" s="5">
-        <v>5400</v>
+        <v>7400</v>
       </c>
       <c r="H178" s="5">
         <v>0</v>
@@ -9404,13 +9404,13 @@
         <v>9</v>
       </c>
       <c r="J178" s="6">
-        <v>168</v>
+        <v>137</v>
       </c>
       <c r="K178" s="6">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="L178" s="7">
-        <v>2093.02</v>
+        <v>2452.77</v>
       </c>
       <c r="M178" s="8" t="s">
         <v>18</v>
@@ -9436,25 +9436,25 @@
         <v>300</v>
       </c>
       <c r="F179" s="11">
-        <v>16800</v>
+        <v>8400</v>
       </c>
       <c r="G179" s="11">
-        <v>16800</v>
+        <v>8400</v>
       </c>
       <c r="H179" s="11">
         <v>0</v>
       </c>
       <c r="I179" s="12">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="J179" s="12">
-        <v>1008</v>
+        <v>1076</v>
       </c>
       <c r="K179" s="12">
-        <v>169</v>
+        <v>158</v>
       </c>
       <c r="L179" s="13">
-        <v>1532.29</v>
+        <v>1417.96</v>
       </c>
       <c r="M179" s="14" t="s">
         <v>18</v>
@@ -9480,10 +9480,10 @@
         <v>400</v>
       </c>
       <c r="F180" s="5">
-        <v>14000</v>
+        <v>12000</v>
       </c>
       <c r="G180" s="5">
-        <v>14000</v>
+        <v>12000</v>
       </c>
       <c r="H180" s="5">
         <v>0</v>
@@ -9495,10 +9495,10 @@
         <v>222</v>
       </c>
       <c r="K180" s="6">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="L180" s="7">
-        <v>4307.69</v>
+        <v>4081.63</v>
       </c>
       <c r="M180" s="8" t="s">
         <v>18</v>
@@ -9533,16 +9533,16 @@
         <v>0</v>
       </c>
       <c r="I181" s="12">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="J181" s="12">
-        <v>245</v>
+        <v>175</v>
       </c>
       <c r="K181" s="12">
-        <v>55</v>
+        <v>52</v>
       </c>
       <c r="L181" s="13">
-        <v>4522.61</v>
+        <v>4648.76</v>
       </c>
       <c r="M181" s="14" t="s">
         <v>18</v>
@@ -9568,25 +9568,25 @@
         <v>10</v>
       </c>
       <c r="F182" s="5">
-        <v>520</v>
+        <v>320</v>
       </c>
       <c r="G182" s="5">
-        <v>520</v>
+        <v>320</v>
       </c>
       <c r="H182" s="5">
         <v>0</v>
       </c>
       <c r="I182" s="6">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="J182" s="6">
-        <v>125</v>
+        <v>98</v>
       </c>
       <c r="K182" s="6">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="L182" s="7">
-        <v>169.93</v>
+        <v>133.56</v>
       </c>
       <c r="M182" s="8" t="s">
         <v>18</v>
@@ -9624,13 +9624,13 @@
         <v>10</v>
       </c>
       <c r="J183" s="12">
-        <v>116</v>
+        <v>121</v>
       </c>
       <c r="K183" s="12">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="L183" s="13">
-        <v>446.43</v>
+        <v>454.55</v>
       </c>
       <c r="M183" s="14" t="s">
         <v>18</v>
@@ -9656,10 +9656,10 @@
         <v>50</v>
       </c>
       <c r="F184" s="5">
-        <v>3200</v>
+        <v>3100</v>
       </c>
       <c r="G184" s="5">
-        <v>3200</v>
+        <v>3100</v>
       </c>
       <c r="H184" s="5">
         <v>0</v>
@@ -9668,13 +9668,13 @@
         <v>10</v>
       </c>
       <c r="J184" s="6">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="K184" s="6">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="L184" s="7">
-        <v>901.92</v>
+        <v>874.22</v>
       </c>
       <c r="M184" s="8" t="s">
         <v>18</v>
@@ -9700,25 +9700,25 @@
         <v>100</v>
       </c>
       <c r="F185" s="11">
-        <v>6400</v>
+        <v>2600</v>
       </c>
       <c r="G185" s="11">
-        <v>6400</v>
+        <v>2600</v>
       </c>
       <c r="H185" s="11">
         <v>0</v>
       </c>
       <c r="I185" s="12">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="J185" s="12">
-        <v>135</v>
+        <v>114</v>
       </c>
       <c r="K185" s="12">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="L185" s="13">
-        <v>1771.87</v>
+        <v>1078.84</v>
       </c>
       <c r="M185" s="14" t="s">
         <v>18</v>
@@ -9744,25 +9744,25 @@
         <v>150</v>
       </c>
       <c r="F186" s="5">
-        <v>4200</v>
+        <v>3750</v>
       </c>
       <c r="G186" s="5">
-        <v>4200</v>
+        <v>3750</v>
       </c>
       <c r="H186" s="5">
         <v>0</v>
       </c>
       <c r="I186" s="6">
-        <v>42</v>
+        <v>39</v>
       </c>
       <c r="J186" s="6">
-        <v>913</v>
+        <v>860</v>
       </c>
       <c r="K186" s="6">
-        <v>130</v>
+        <v>138</v>
       </c>
       <c r="L186" s="7">
-        <v>817.12</v>
+        <v>757.58</v>
       </c>
       <c r="M186" s="8" t="s">
         <v>18</v>
@@ -9788,10 +9788,10 @@
         <v>200</v>
       </c>
       <c r="F187" s="11">
-        <v>12800</v>
+        <v>13800</v>
       </c>
       <c r="G187" s="11">
-        <v>12800</v>
+        <v>13800</v>
       </c>
       <c r="H187" s="11">
         <v>0</v>
@@ -9800,13 +9800,13 @@
         <v>10</v>
       </c>
       <c r="J187" s="12">
-        <v>159</v>
+        <v>178</v>
       </c>
       <c r="K187" s="12">
-        <v>41</v>
+        <v>37</v>
       </c>
       <c r="L187" s="13">
-        <v>3103.78</v>
+        <v>3404.89</v>
       </c>
       <c r="M187" s="14" t="s">
         <v>18</v>
@@ -9832,25 +9832,25 @@
         <v>300</v>
       </c>
       <c r="F188" s="5">
-        <v>11400</v>
+        <v>15000</v>
       </c>
       <c r="G188" s="5">
-        <v>11400</v>
+        <v>15000</v>
       </c>
       <c r="H188" s="5">
         <v>0</v>
       </c>
       <c r="I188" s="6">
-        <v>114</v>
+        <v>130</v>
       </c>
       <c r="J188" s="6">
-        <v>2436</v>
+        <v>3011</v>
       </c>
       <c r="K188" s="6">
-        <v>471</v>
+        <v>492</v>
       </c>
       <c r="L188" s="7">
-        <v>587.69</v>
+        <v>574.71</v>
       </c>
       <c r="M188" s="8" t="s">
         <v>18</v>
@@ -9876,25 +9876,25 @@
         <v>400</v>
       </c>
       <c r="F189" s="11">
-        <v>8000</v>
+        <v>12400</v>
       </c>
       <c r="G189" s="11">
-        <v>8000</v>
+        <v>12400</v>
       </c>
       <c r="H189" s="11">
         <v>0</v>
       </c>
       <c r="I189" s="12">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="J189" s="12">
-        <v>184</v>
+        <v>182</v>
       </c>
       <c r="K189" s="12">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="L189" s="13">
-        <v>3252.03</v>
+        <v>4065.57</v>
       </c>
       <c r="M189" s="14" t="s">
         <v>18</v>
@@ -9920,25 +9920,25 @@
         <v>500</v>
       </c>
       <c r="F190" s="5">
-        <v>20000</v>
+        <v>19000</v>
       </c>
       <c r="G190" s="5">
-        <v>20000</v>
+        <v>19000</v>
       </c>
       <c r="H190" s="5">
         <v>0</v>
       </c>
       <c r="I190" s="6">
-        <v>37</v>
+        <v>42</v>
       </c>
       <c r="J190" s="6">
-        <v>955</v>
+        <v>1162</v>
       </c>
       <c r="K190" s="6">
-        <v>201</v>
+        <v>190</v>
       </c>
       <c r="L190" s="7">
-        <v>2096.44</v>
+        <v>2178.9</v>
       </c>
       <c r="M190" s="8" t="s">
         <v>18</v>
@@ -9964,10 +9964,10 @@
         <v>10</v>
       </c>
       <c r="F191" s="11">
-        <v>560</v>
+        <v>650</v>
       </c>
       <c r="G191" s="11">
-        <v>560</v>
+        <v>650</v>
       </c>
       <c r="H191" s="11">
         <v>0</v>
@@ -9976,13 +9976,13 @@
         <v>10</v>
       </c>
       <c r="J191" s="12">
-        <v>118</v>
+        <v>126</v>
       </c>
       <c r="K191" s="12">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="L191" s="13">
-        <v>173.05</v>
+        <v>192.02</v>
       </c>
       <c r="M191" s="14" t="s">
         <v>18</v>
@@ -10008,25 +10008,25 @@
         <v>25</v>
       </c>
       <c r="F192" s="5">
-        <v>1075</v>
+        <v>1150</v>
       </c>
       <c r="G192" s="5">
-        <v>1075</v>
+        <v>1150</v>
       </c>
       <c r="H192" s="5">
         <v>0</v>
       </c>
       <c r="I192" s="6">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="J192" s="6">
-        <v>123</v>
+        <v>139</v>
       </c>
       <c r="K192" s="6">
         <v>32</v>
       </c>
       <c r="L192" s="7">
-        <v>373.78</v>
+        <v>386.94</v>
       </c>
       <c r="M192" s="8" t="s">
         <v>18</v>
@@ -10052,25 +10052,25 @@
         <v>50</v>
       </c>
       <c r="F193" s="11">
-        <v>1450</v>
+        <v>3000</v>
       </c>
       <c r="G193" s="11">
-        <v>1450</v>
+        <v>3000</v>
       </c>
       <c r="H193" s="11">
         <v>0</v>
       </c>
       <c r="I193" s="12">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="J193" s="12">
-        <v>135</v>
+        <v>108</v>
       </c>
       <c r="K193" s="12">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="L193" s="13">
-        <v>590.15</v>
+        <v>877.19</v>
       </c>
       <c r="M193" s="14" t="s">
         <v>18</v>
@@ -10096,25 +10096,25 @@
         <v>100</v>
       </c>
       <c r="F194" s="5">
-        <v>4000</v>
+        <v>4100</v>
       </c>
       <c r="G194" s="5">
-        <v>4000</v>
+        <v>4100</v>
       </c>
       <c r="H194" s="5">
         <v>0</v>
       </c>
       <c r="I194" s="6">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="J194" s="6">
-        <v>115</v>
+        <v>144</v>
       </c>
       <c r="K194" s="6">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="L194" s="7">
-        <v>1398.6</v>
+        <v>1437.08</v>
       </c>
       <c r="M194" s="8" t="s">
         <v>18</v>
@@ -10140,10 +10140,10 @@
         <v>150</v>
       </c>
       <c r="F195" s="11">
-        <v>8400</v>
+        <v>3300</v>
       </c>
       <c r="G195" s="11">
-        <v>8400</v>
+        <v>3300</v>
       </c>
       <c r="H195" s="11">
         <v>0</v>
@@ -10158,7 +10158,7 @@
         <v>35</v>
       </c>
       <c r="L195" s="13">
-        <v>2427.75</v>
+        <v>1453.74</v>
       </c>
       <c r="M195" s="14" t="s">
         <v>18</v>
@@ -10184,10 +10184,10 @@
         <v>200</v>
       </c>
       <c r="F196" s="5">
-        <v>4800</v>
+        <v>13200</v>
       </c>
       <c r="G196" s="5">
-        <v>4800</v>
+        <v>13200</v>
       </c>
       <c r="H196" s="5">
         <v>0</v>
@@ -10196,13 +10196,13 @@
         <v>10</v>
       </c>
       <c r="J196" s="6">
-        <v>162</v>
+        <v>174</v>
       </c>
       <c r="K196" s="6">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="L196" s="7">
-        <v>1990.05</v>
+        <v>3188.41</v>
       </c>
       <c r="M196" s="8" t="s">
         <v>18</v>
@@ -10228,25 +10228,25 @@
         <v>300</v>
       </c>
       <c r="F197" s="11">
-        <v>13200</v>
+        <v>11700</v>
       </c>
       <c r="G197" s="11">
-        <v>13200</v>
+        <v>11700</v>
       </c>
       <c r="H197" s="11">
         <v>0</v>
       </c>
       <c r="I197" s="12">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="J197" s="12">
-        <v>782</v>
+        <v>1146</v>
       </c>
       <c r="K197" s="12">
         <v>155</v>
       </c>
       <c r="L197" s="13">
-        <v>1586.54</v>
+        <v>1550.7</v>
       </c>
       <c r="M197" s="14" t="s">
         <v>18</v>
@@ -10272,25 +10272,25 @@
         <v>400</v>
       </c>
       <c r="F198" s="5">
-        <v>18000</v>
+        <v>24000</v>
       </c>
       <c r="G198" s="5">
-        <v>18000</v>
+        <v>24000</v>
       </c>
       <c r="H198" s="5">
         <v>0</v>
       </c>
       <c r="I198" s="6">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="J198" s="6">
-        <v>229</v>
+        <v>208</v>
       </c>
       <c r="K198" s="6">
-        <v>49</v>
+        <v>46</v>
       </c>
       <c r="L198" s="7">
-        <v>4858.3</v>
+        <v>5633.8</v>
       </c>
       <c r="M198" s="8" t="s">
         <v>18</v>
@@ -10316,25 +10316,25 @@
         <v>500</v>
       </c>
       <c r="F199" s="11">
-        <v>18500</v>
+        <v>34500</v>
       </c>
       <c r="G199" s="11">
-        <v>18500</v>
+        <v>34500</v>
       </c>
       <c r="H199" s="11">
         <v>0</v>
       </c>
       <c r="I199" s="12">
-        <v>110</v>
+        <v>116</v>
       </c>
       <c r="J199" s="12">
-        <v>3815</v>
+        <v>3303</v>
       </c>
       <c r="K199" s="12">
-        <v>572</v>
+        <v>587</v>
       </c>
       <c r="L199" s="13">
-        <v>816.27</v>
+        <v>821.37</v>
       </c>
       <c r="M199" s="14" t="s">
         <v>18</v>
@@ -10360,10 +10360,10 @@
         <v>10</v>
       </c>
       <c r="F200" s="5">
-        <v>480</v>
+        <v>630</v>
       </c>
       <c r="G200" s="5">
-        <v>480</v>
+        <v>630</v>
       </c>
       <c r="H200" s="5">
         <v>0</v>
@@ -10372,13 +10372,13 @@
         <v>9</v>
       </c>
       <c r="J200" s="6">
-        <v>116</v>
+        <v>101</v>
       </c>
       <c r="K200" s="6">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="L200" s="7">
-        <v>165.98</v>
+        <v>185.84</v>
       </c>
       <c r="M200" s="8" t="s">
         <v>18</v>
@@ -10404,25 +10404,25 @@
         <v>25</v>
       </c>
       <c r="F201" s="11">
-        <v>775</v>
+        <v>1600</v>
       </c>
       <c r="G201" s="11">
-        <v>775</v>
+        <v>1600</v>
       </c>
       <c r="H201" s="11">
         <v>0</v>
       </c>
       <c r="I201" s="12">
-        <v>37</v>
+        <v>41</v>
       </c>
       <c r="J201" s="12">
-        <v>807</v>
+        <v>788</v>
       </c>
       <c r="K201" s="12">
-        <v>117</v>
+        <v>111</v>
       </c>
       <c r="L201" s="13">
-        <v>151.16</v>
+        <v>185.96</v>
       </c>
       <c r="M201" s="14" t="s">
         <v>18</v>
@@ -10448,10 +10448,10 @@
         <v>50</v>
       </c>
       <c r="F202" s="5">
-        <v>2500</v>
+        <v>1950</v>
       </c>
       <c r="G202" s="5">
-        <v>2500</v>
+        <v>1950</v>
       </c>
       <c r="H202" s="5">
         <v>0</v>
@@ -10460,13 +10460,13 @@
         <v>10</v>
       </c>
       <c r="J202" s="6">
-        <v>138</v>
+        <v>115</v>
       </c>
       <c r="K202" s="6">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="L202" s="7">
-        <v>806.45</v>
+        <v>719.82</v>
       </c>
       <c r="M202" s="8" t="s">
         <v>18</v>
@@ -10492,10 +10492,10 @@
         <v>100</v>
       </c>
       <c r="F203" s="11">
-        <v>4500</v>
+        <v>6500</v>
       </c>
       <c r="G203" s="11">
-        <v>4500</v>
+        <v>6500</v>
       </c>
       <c r="H203" s="11">
         <v>0</v>
@@ -10504,13 +10504,13 @@
         <v>9</v>
       </c>
       <c r="J203" s="12">
-        <v>135</v>
+        <v>166</v>
       </c>
       <c r="K203" s="12">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="L203" s="13">
-        <v>1442.31</v>
+        <v>1721.85</v>
       </c>
       <c r="M203" s="14" t="s">
         <v>18</v>
@@ -10536,25 +10536,25 @@
         <v>150</v>
       </c>
       <c r="F204" s="5">
-        <v>6900</v>
+        <v>5400</v>
       </c>
       <c r="G204" s="5">
-        <v>6900</v>
+        <v>5400</v>
       </c>
       <c r="H204" s="5">
         <v>0</v>
       </c>
       <c r="I204" s="6">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="J204" s="6">
-        <v>162</v>
+        <v>137</v>
       </c>
       <c r="K204" s="6">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="L204" s="7">
-        <v>2154.9</v>
+        <v>1956.52</v>
       </c>
       <c r="M204" s="8" t="s">
         <v>18</v>
@@ -10580,10 +10580,10 @@
         <v>200</v>
       </c>
       <c r="F205" s="11">
-        <v>4800</v>
+        <v>12000</v>
       </c>
       <c r="G205" s="11">
-        <v>4800</v>
+        <v>12000</v>
       </c>
       <c r="H205" s="11">
         <v>0</v>
@@ -10592,13 +10592,13 @@
         <v>9</v>
       </c>
       <c r="J205" s="12">
-        <v>178</v>
+        <v>171</v>
       </c>
       <c r="K205" s="12">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="L205" s="13">
-        <v>1951.22</v>
+        <v>3030.3</v>
       </c>
       <c r="M205" s="14" t="s">
         <v>18</v>
@@ -10624,25 +10624,25 @@
         <v>300</v>
       </c>
       <c r="F206" s="5">
-        <v>6600</v>
+        <v>15600</v>
       </c>
       <c r="G206" s="5">
-        <v>6600</v>
+        <v>15600</v>
       </c>
       <c r="H206" s="5">
         <v>0</v>
       </c>
       <c r="I206" s="6">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="J206" s="6">
-        <v>148</v>
+        <v>161</v>
       </c>
       <c r="K206" s="6">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="L206" s="7">
-        <v>2674.23</v>
+        <v>4175.59</v>
       </c>
       <c r="M206" s="8" t="s">
         <v>18</v>
@@ -10668,10 +10668,10 @@
         <v>400</v>
       </c>
       <c r="F207" s="11">
-        <v>27200</v>
+        <v>19200</v>
       </c>
       <c r="G207" s="11">
-        <v>27200</v>
+        <v>19200</v>
       </c>
       <c r="H207" s="11">
         <v>0</v>
@@ -10680,13 +10680,13 @@
         <v>9</v>
       </c>
       <c r="J207" s="12">
-        <v>171</v>
+        <v>161</v>
       </c>
       <c r="K207" s="12">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="L207" s="13">
-        <v>5629.14</v>
+        <v>4923.08</v>
       </c>
       <c r="M207" s="14" t="s">
         <v>18</v>
@@ -10712,25 +10712,25 @@
         <v>500</v>
       </c>
       <c r="F208" s="5">
-        <v>19500</v>
+        <v>27000</v>
       </c>
       <c r="G208" s="5">
-        <v>19500</v>
+        <v>27000</v>
       </c>
       <c r="H208" s="5">
         <v>0</v>
       </c>
       <c r="I208" s="6">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="J208" s="6">
-        <v>1394</v>
+        <v>1247</v>
       </c>
       <c r="K208" s="6">
         <v>193</v>
       </c>
       <c r="L208" s="7">
-        <v>2160.19</v>
+        <v>2264.72</v>
       </c>
       <c r="M208" s="8" t="s">
         <v>18</v>
@@ -10756,25 +10756,25 @@
         <v>10</v>
       </c>
       <c r="F209" s="11">
-        <v>280</v>
+        <v>380</v>
       </c>
       <c r="G209" s="11">
-        <v>280</v>
+        <v>380</v>
       </c>
       <c r="H209" s="11">
         <v>0</v>
       </c>
       <c r="I209" s="12">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="J209" s="12">
-        <v>108</v>
+        <v>126</v>
       </c>
       <c r="K209" s="12">
         <v>29</v>
       </c>
       <c r="L209" s="13">
-        <v>121.11</v>
+        <v>146.04</v>
       </c>
       <c r="M209" s="14" t="s">
         <v>18</v>
@@ -10809,16 +10809,16 @@
         <v>0</v>
       </c>
       <c r="I210" s="6">
-        <v>108</v>
+        <v>126</v>
       </c>
       <c r="J210" s="6">
-        <v>1917</v>
+        <v>1724</v>
       </c>
       <c r="K210" s="6">
-        <v>325</v>
+        <v>338</v>
       </c>
       <c r="L210" s="7">
-        <v>65.69</v>
+        <v>63.52</v>
       </c>
       <c r="M210" s="8" t="s">
         <v>18</v>
@@ -10844,25 +10844,25 @@
         <v>50</v>
       </c>
       <c r="F211" s="11">
-        <v>2150</v>
+        <v>1250</v>
       </c>
       <c r="G211" s="11">
-        <v>2150</v>
+        <v>1250</v>
       </c>
       <c r="H211" s="11">
         <v>0</v>
       </c>
       <c r="I211" s="12">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="J211" s="12">
-        <v>110</v>
+        <v>135</v>
       </c>
       <c r="K211" s="12">
         <v>32</v>
       </c>
       <c r="L211" s="13">
-        <v>747.57</v>
+        <v>543.48</v>
       </c>
       <c r="M211" s="14" t="s">
         <v>18</v>
@@ -10888,10 +10888,10 @@
         <v>100</v>
       </c>
       <c r="F212" s="5">
-        <v>4600</v>
+        <v>6700</v>
       </c>
       <c r="G212" s="5">
-        <v>4600</v>
+        <v>6700</v>
       </c>
       <c r="H212" s="5">
         <v>0</v>
@@ -10900,13 +10900,13 @@
         <v>41</v>
       </c>
       <c r="J212" s="6">
-        <v>675</v>
+        <v>655</v>
       </c>
       <c r="K212" s="6">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="L212" s="7">
-        <v>614.97</v>
+        <v>660.55</v>
       </c>
       <c r="M212" s="8" t="s">
         <v>18</v>
@@ -10932,10 +10932,10 @@
         <v>150</v>
       </c>
       <c r="F213" s="11">
-        <v>9750</v>
+        <v>6600</v>
       </c>
       <c r="G213" s="11">
-        <v>9750</v>
+        <v>6600</v>
       </c>
       <c r="H213" s="11">
         <v>0</v>
@@ -10944,13 +10944,13 @@
         <v>9</v>
       </c>
       <c r="J213" s="12">
-        <v>138</v>
+        <v>127</v>
       </c>
       <c r="K213" s="12">
         <v>37</v>
       </c>
       <c r="L213" s="13">
-        <v>2496.8</v>
+        <v>2109.97</v>
       </c>
       <c r="M213" s="14" t="s">
         <v>18</v>
@@ -10976,10 +10976,10 @@
         <v>200</v>
       </c>
       <c r="F214" s="5">
-        <v>13600</v>
+        <v>11000</v>
       </c>
       <c r="G214" s="5">
-        <v>13600</v>
+        <v>11000</v>
       </c>
       <c r="H214" s="5">
         <v>0</v>
@@ -10988,13 +10988,13 @@
         <v>9</v>
       </c>
       <c r="J214" s="6">
-        <v>166</v>
+        <v>173</v>
       </c>
       <c r="K214" s="6">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="L214" s="7">
-        <v>3275.53</v>
+        <v>2929.43</v>
       </c>
       <c r="M214" s="8" t="s">
         <v>18</v>
@@ -11020,25 +11020,25 @@
         <v>300</v>
       </c>
       <c r="F215" s="11">
-        <v>14100</v>
+        <v>15300</v>
       </c>
       <c r="G215" s="11">
-        <v>14100</v>
+        <v>15300</v>
       </c>
       <c r="H215" s="11">
         <v>0</v>
       </c>
       <c r="I215" s="12">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="J215" s="12">
-        <v>156</v>
+        <v>187</v>
       </c>
       <c r="K215" s="12">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="L215" s="13">
-        <v>3900.41</v>
+        <v>4086.54</v>
       </c>
       <c r="M215" s="14" t="s">
         <v>18</v>
@@ -11064,25 +11064,25 @@
         <v>400</v>
       </c>
       <c r="F216" s="5">
-        <v>19200</v>
+        <v>16800</v>
       </c>
       <c r="G216" s="5">
-        <v>19200</v>
+        <v>16800</v>
       </c>
       <c r="H216" s="5">
         <v>0</v>
       </c>
       <c r="I216" s="6">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="J216" s="6">
-        <v>174</v>
+        <v>210</v>
       </c>
       <c r="K216" s="6">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="L216" s="7">
-        <v>5111.82</v>
+        <v>4895.1</v>
       </c>
       <c r="M216" s="8" t="s">
         <v>18</v>
@@ -11108,25 +11108,25 @@
         <v>500</v>
       </c>
       <c r="F217" s="11">
-        <v>14500</v>
+        <v>26000</v>
       </c>
       <c r="G217" s="11">
-        <v>14500</v>
+        <v>26000</v>
       </c>
       <c r="H217" s="11">
         <v>0</v>
       </c>
       <c r="I217" s="12">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="J217" s="12">
-        <v>247</v>
+        <v>185</v>
       </c>
       <c r="K217" s="12">
-        <v>52</v>
+        <v>55</v>
       </c>
       <c r="L217" s="13">
-        <v>4820.48</v>
+        <v>5963.3</v>
       </c>
       <c r="M217" s="14" t="s">
         <v>18</v>
@@ -11152,10 +11152,10 @@
         <v>10</v>
       </c>
       <c r="F218" s="5">
-        <v>410</v>
+        <v>510</v>
       </c>
       <c r="G218" s="5">
-        <v>410</v>
+        <v>510</v>
       </c>
       <c r="H218" s="5">
         <v>0</v>
@@ -11164,13 +11164,13 @@
         <v>10</v>
       </c>
       <c r="J218" s="6">
-        <v>108</v>
+        <v>121</v>
       </c>
       <c r="K218" s="6">
         <v>29</v>
       </c>
       <c r="L218" s="7">
-        <v>152.47</v>
+        <v>171.2</v>
       </c>
       <c r="M218" s="8" t="s">
         <v>18</v>
@@ -11196,25 +11196,25 @@
         <v>25</v>
       </c>
       <c r="F219" s="11">
-        <v>625</v>
+        <v>1225</v>
       </c>
       <c r="G219" s="11">
-        <v>625</v>
+        <v>1225</v>
       </c>
       <c r="H219" s="11">
         <v>0</v>
       </c>
       <c r="I219" s="12">
-        <v>43</v>
+        <v>37</v>
       </c>
       <c r="J219" s="12">
-        <v>801</v>
+        <v>618</v>
       </c>
       <c r="K219" s="12">
-        <v>110</v>
+        <v>117</v>
       </c>
       <c r="L219" s="13">
-        <v>147.06</v>
+        <v>169.36</v>
       </c>
       <c r="M219" s="14" t="s">
         <v>18</v>
@@ -11240,10 +11240,10 @@
         <v>50</v>
       </c>
       <c r="F220" s="5">
-        <v>1950</v>
+        <v>2400</v>
       </c>
       <c r="G220" s="5">
-        <v>1950</v>
+        <v>2400</v>
       </c>
       <c r="H220" s="5">
         <v>0</v>
@@ -11252,13 +11252,13 @@
         <v>10</v>
       </c>
       <c r="J220" s="6">
-        <v>107</v>
+        <v>153</v>
       </c>
       <c r="K220" s="6">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="L220" s="7">
-        <v>699.68</v>
+        <v>803.21</v>
       </c>
       <c r="M220" s="8" t="s">
         <v>18</v>
@@ -11284,25 +11284,25 @@
         <v>100</v>
       </c>
       <c r="F221" s="11">
-        <v>5300</v>
+        <v>4400</v>
       </c>
       <c r="G221" s="11">
-        <v>5300</v>
+        <v>4400</v>
       </c>
       <c r="H221" s="11">
         <v>0</v>
       </c>
       <c r="I221" s="12">
-        <v>121</v>
+        <v>109</v>
       </c>
       <c r="J221" s="12">
-        <v>1803</v>
+        <v>2278</v>
       </c>
       <c r="K221" s="12">
-        <v>383</v>
+        <v>356</v>
       </c>
       <c r="L221" s="13">
-        <v>243.13</v>
+        <v>256.35</v>
       </c>
       <c r="M221" s="14" t="s">
         <v>18</v>
@@ -11328,25 +11328,25 @@
         <v>150</v>
       </c>
       <c r="F222" s="5">
-        <v>5400</v>
+        <v>8700</v>
       </c>
       <c r="G222" s="5">
-        <v>5400</v>
+        <v>8700</v>
       </c>
       <c r="H222" s="5">
         <v>0</v>
       </c>
       <c r="I222" s="6">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="J222" s="6">
-        <v>166</v>
+        <v>142</v>
       </c>
       <c r="K222" s="6">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="L222" s="7">
-        <v>1906.78</v>
+        <v>2348.81</v>
       </c>
       <c r="M222" s="8" t="s">
         <v>18</v>
@@ -11372,25 +11372,25 @@
         <v>200</v>
       </c>
       <c r="F223" s="11">
-        <v>10600</v>
+        <v>7400</v>
       </c>
       <c r="G223" s="11">
-        <v>10600</v>
+        <v>7400</v>
       </c>
       <c r="H223" s="11">
         <v>0</v>
       </c>
       <c r="I223" s="12">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="J223" s="12">
-        <v>837</v>
+        <v>809</v>
       </c>
       <c r="K223" s="12">
-        <v>152</v>
+        <v>143</v>
       </c>
       <c r="L223" s="13">
-        <v>1109.25</v>
+        <v>1089.68</v>
       </c>
       <c r="M223" s="14" t="s">
         <v>18</v>
@@ -11416,25 +11416,25 @@
         <v>300</v>
       </c>
       <c r="F224" s="5">
-        <v>13200</v>
+        <v>13800</v>
       </c>
       <c r="G224" s="5">
-        <v>13200</v>
+        <v>13800</v>
       </c>
       <c r="H224" s="5">
         <v>0</v>
       </c>
       <c r="I224" s="6">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="J224" s="6">
-        <v>206</v>
+        <v>144</v>
       </c>
       <c r="K224" s="6">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="L224" s="7">
-        <v>3891.51</v>
+        <v>4020.98</v>
       </c>
       <c r="M224" s="8" t="s">
         <v>18</v>
@@ -11460,10 +11460,10 @@
         <v>400</v>
       </c>
       <c r="F225" s="11">
-        <v>11200</v>
+        <v>13600</v>
       </c>
       <c r="G225" s="11">
-        <v>11200</v>
+        <v>13600</v>
       </c>
       <c r="H225" s="11">
         <v>0</v>
@@ -11472,13 +11472,13 @@
         <v>9</v>
       </c>
       <c r="J225" s="12">
-        <v>205</v>
+        <v>211</v>
       </c>
       <c r="K225" s="12">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="L225" s="13">
-        <v>3862.07</v>
+        <v>4295.64</v>
       </c>
       <c r="M225" s="14" t="s">
         <v>18</v>
@@ -11504,10 +11504,10 @@
         <v>500</v>
       </c>
       <c r="F226" s="5">
-        <v>15500</v>
+        <v>18000</v>
       </c>
       <c r="G226" s="5">
-        <v>15500</v>
+        <v>18000</v>
       </c>
       <c r="H226" s="5">
         <v>0</v>
@@ -11516,13 +11516,13 @@
         <v>9</v>
       </c>
       <c r="J226" s="6">
-        <v>220</v>
+        <v>240</v>
       </c>
       <c r="K226" s="6">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="L226" s="7">
-        <v>4980.72</v>
+        <v>5226.48</v>
       </c>
       <c r="M226" s="8" t="s">
         <v>18</v>
@@ -11548,10 +11548,10 @@
         <v>10</v>
       </c>
       <c r="F227" s="11">
-        <v>480</v>
+        <v>600</v>
       </c>
       <c r="G227" s="11">
-        <v>480</v>
+        <v>600</v>
       </c>
       <c r="H227" s="11">
         <v>0</v>
@@ -11560,13 +11560,13 @@
         <v>10</v>
       </c>
       <c r="J227" s="12">
-        <v>113</v>
+        <v>102</v>
       </c>
       <c r="K227" s="12">
         <v>29</v>
       </c>
       <c r="L227" s="13">
-        <v>165.98</v>
+        <v>185.19</v>
       </c>
       <c r="M227" s="14" t="s">
         <v>18</v>
@@ -11592,10 +11592,10 @@
         <v>25</v>
       </c>
       <c r="F228" s="5">
-        <v>500</v>
+        <v>1425</v>
       </c>
       <c r="G228" s="5">
-        <v>500</v>
+        <v>1425</v>
       </c>
       <c r="H228" s="5">
         <v>0</v>
@@ -11604,13 +11604,13 @@
         <v>9</v>
       </c>
       <c r="J228" s="6">
-        <v>124</v>
+        <v>143</v>
       </c>
       <c r="K228" s="6">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="L228" s="7">
-        <v>235.85</v>
+        <v>428.7</v>
       </c>
       <c r="M228" s="8" t="s">
         <v>18</v>
@@ -11636,25 +11636,25 @@
         <v>50</v>
       </c>
       <c r="F229" s="11">
-        <v>2750</v>
+        <v>1350</v>
       </c>
       <c r="G229" s="11">
-        <v>2750</v>
+        <v>1350</v>
       </c>
       <c r="H229" s="11">
         <v>0</v>
       </c>
       <c r="I229" s="12">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="J229" s="12">
-        <v>151</v>
+        <v>135</v>
       </c>
       <c r="K229" s="12">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="L229" s="13">
-        <v>843.56</v>
+        <v>577.66</v>
       </c>
       <c r="M229" s="14" t="s">
         <v>18</v>
@@ -11680,10 +11680,10 @@
         <v>100</v>
       </c>
       <c r="F230" s="5">
-        <v>3300</v>
+        <v>4700</v>
       </c>
       <c r="G230" s="5">
-        <v>3300</v>
+        <v>4700</v>
       </c>
       <c r="H230" s="5">
         <v>0</v>
@@ -11692,13 +11692,13 @@
         <v>42</v>
       </c>
       <c r="J230" s="6">
-        <v>742</v>
+        <v>853</v>
       </c>
       <c r="K230" s="6">
-        <v>126</v>
+        <v>129</v>
       </c>
       <c r="L230" s="7">
-        <v>583.24</v>
+        <v>621.45</v>
       </c>
       <c r="M230" s="8" t="s">
         <v>18</v>
@@ -11724,10 +11724,10 @@
         <v>150</v>
       </c>
       <c r="F231" s="11">
-        <v>4650</v>
+        <v>3150</v>
       </c>
       <c r="G231" s="11">
-        <v>4650</v>
+        <v>3150</v>
       </c>
       <c r="H231" s="11">
         <v>0</v>
@@ -11736,13 +11736,13 @@
         <v>10</v>
       </c>
       <c r="J231" s="12">
-        <v>148</v>
+        <v>145</v>
       </c>
       <c r="K231" s="12">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="L231" s="13">
-        <v>1756.71</v>
+        <v>1370.76</v>
       </c>
       <c r="M231" s="14" t="s">
         <v>18</v>
@@ -11768,25 +11768,25 @@
         <v>200</v>
       </c>
       <c r="F232" s="5">
-        <v>7400</v>
+        <v>12600</v>
       </c>
       <c r="G232" s="5">
-        <v>7400</v>
+        <v>12600</v>
       </c>
       <c r="H232" s="5">
         <v>0</v>
       </c>
       <c r="I232" s="6">
-        <v>129</v>
+        <v>114</v>
       </c>
       <c r="J232" s="6">
-        <v>2235</v>
+        <v>2021</v>
       </c>
       <c r="K232" s="6">
-        <v>433</v>
+        <v>439</v>
       </c>
       <c r="L232" s="7">
-        <v>422.35</v>
+        <v>432.14</v>
       </c>
       <c r="M232" s="8" t="s">
         <v>18</v>
@@ -11812,10 +11812,10 @@
         <v>300</v>
       </c>
       <c r="F233" s="11">
-        <v>6000</v>
+        <v>17100</v>
       </c>
       <c r="G233" s="11">
-        <v>6000</v>
+        <v>17100</v>
       </c>
       <c r="H233" s="11">
         <v>0</v>
@@ -11824,13 +11824,13 @@
         <v>9</v>
       </c>
       <c r="J233" s="12">
-        <v>166</v>
+        <v>161</v>
       </c>
       <c r="K233" s="12">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="L233" s="13">
-        <v>2500</v>
+        <v>4266.47</v>
       </c>
       <c r="M233" s="14" t="s">
         <v>18</v>
@@ -11865,16 +11865,16 @@
         <v>0</v>
       </c>
       <c r="I234" s="6">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="J234" s="6">
-        <v>1018</v>
+        <v>897</v>
       </c>
       <c r="K234" s="6">
-        <v>173</v>
+        <v>176</v>
       </c>
       <c r="L234" s="7">
-        <v>2050.66</v>
+        <v>2019.6</v>
       </c>
       <c r="M234" s="8" t="s">
         <v>18</v>
@@ -11900,25 +11900,25 @@
         <v>500</v>
       </c>
       <c r="F235" s="11">
-        <v>13000</v>
+        <v>10000</v>
       </c>
       <c r="G235" s="11">
-        <v>13000</v>
+        <v>10000</v>
       </c>
       <c r="H235" s="11">
         <v>0</v>
       </c>
       <c r="I235" s="12">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="J235" s="12">
-        <v>184</v>
+        <v>210</v>
       </c>
       <c r="K235" s="12">
-        <v>51</v>
+        <v>56</v>
       </c>
       <c r="L235" s="13">
-        <v>4600.14</v>
+        <v>3816.79</v>
       </c>
       <c r="M235" s="14" t="s">
         <v>18</v>
@@ -11944,25 +11944,25 @@
         <v>10</v>
       </c>
       <c r="F236" s="5">
-        <v>610</v>
+        <v>310</v>
       </c>
       <c r="G236" s="5">
-        <v>610</v>
+        <v>310</v>
       </c>
       <c r="H236" s="5">
         <v>0</v>
       </c>
       <c r="I236" s="6">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="J236" s="6">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="K236" s="6">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="L236" s="7">
-        <v>186.6</v>
+        <v>127.57</v>
       </c>
       <c r="M236" s="8" t="s">
         <v>18</v>
@@ -11988,25 +11988,25 @@
         <v>25</v>
       </c>
       <c r="F237" s="11">
-        <v>1450</v>
+        <v>1525</v>
       </c>
       <c r="G237" s="11">
-        <v>1450</v>
+        <v>1525</v>
       </c>
       <c r="H237" s="11">
         <v>0</v>
       </c>
       <c r="I237" s="12">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="J237" s="12">
-        <v>140</v>
+        <v>109</v>
       </c>
       <c r="K237" s="12">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="L237" s="13">
-        <v>432.06</v>
+        <v>449.72</v>
       </c>
       <c r="M237" s="14" t="s">
         <v>18</v>
@@ -12032,10 +12032,10 @@
         <v>50</v>
       </c>
       <c r="F238" s="5">
-        <v>2300</v>
+        <v>2650</v>
       </c>
       <c r="G238" s="5">
-        <v>2300</v>
+        <v>2650</v>
       </c>
       <c r="H238" s="5">
         <v>0</v>
@@ -12044,13 +12044,13 @@
         <v>10</v>
       </c>
       <c r="J238" s="6">
-        <v>111</v>
+        <v>130</v>
       </c>
       <c r="K238" s="6">
         <v>33</v>
       </c>
       <c r="L238" s="7">
-        <v>762.09</v>
+        <v>815.64</v>
       </c>
       <c r="M238" s="8" t="s">
         <v>18</v>
@@ -12076,10 +12076,10 @@
         <v>100</v>
       </c>
       <c r="F239" s="11">
-        <v>4300</v>
+        <v>5400</v>
       </c>
       <c r="G239" s="11">
-        <v>4300</v>
+        <v>5400</v>
       </c>
       <c r="H239" s="11">
         <v>0</v>
@@ -12088,13 +12088,13 @@
         <v>10</v>
       </c>
       <c r="J239" s="12">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="K239" s="12">
         <v>34</v>
       </c>
       <c r="L239" s="13">
-        <v>1451.72</v>
+        <v>1618.71</v>
       </c>
       <c r="M239" s="14" t="s">
         <v>18</v>
@@ -12120,10 +12120,10 @@
         <v>150</v>
       </c>
       <c r="F240" s="5">
-        <v>6750</v>
+        <v>4500</v>
       </c>
       <c r="G240" s="5">
-        <v>6750</v>
+        <v>4500</v>
       </c>
       <c r="H240" s="5">
         <v>0</v>
@@ -12132,13 +12132,13 @@
         <v>10</v>
       </c>
       <c r="J240" s="6">
-        <v>142</v>
+        <v>136</v>
       </c>
       <c r="K240" s="6">
         <v>38</v>
       </c>
       <c r="L240" s="7">
-        <v>2102.8</v>
+        <v>1704.55</v>
       </c>
       <c r="M240" s="8" t="s">
         <v>18</v>
@@ -12164,25 +12164,25 @@
         <v>200</v>
       </c>
       <c r="F241" s="11">
-        <v>7000</v>
+        <v>9600</v>
       </c>
       <c r="G241" s="11">
-        <v>7000</v>
+        <v>9600</v>
       </c>
       <c r="H241" s="11">
         <v>0</v>
       </c>
       <c r="I241" s="12">
-        <v>38</v>
+        <v>43</v>
       </c>
       <c r="J241" s="12">
-        <v>950</v>
+        <v>893</v>
       </c>
       <c r="K241" s="12">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="L241" s="13">
-        <v>1064.64</v>
+        <v>1141.23</v>
       </c>
       <c r="M241" s="14" t="s">
         <v>18</v>
@@ -12208,25 +12208,25 @@
         <v>300</v>
       </c>
       <c r="F242" s="5">
-        <v>19200</v>
+        <v>17700</v>
       </c>
       <c r="G242" s="5">
-        <v>19200</v>
+        <v>17700</v>
       </c>
       <c r="H242" s="5">
         <v>0</v>
       </c>
       <c r="I242" s="6">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="J242" s="6">
-        <v>205</v>
+        <v>181</v>
       </c>
       <c r="K242" s="6">
-        <v>42</v>
+        <v>45</v>
       </c>
       <c r="L242" s="7">
-        <v>4584.53</v>
+        <v>4259.93</v>
       </c>
       <c r="M242" s="8" t="s">
         <v>18</v>
@@ -12252,25 +12252,25 @@
         <v>400</v>
       </c>
       <c r="F243" s="11">
-        <v>20800</v>
+        <v>12800</v>
       </c>
       <c r="G243" s="11">
-        <v>20800</v>
+        <v>12800</v>
       </c>
       <c r="H243" s="11">
         <v>0</v>
       </c>
       <c r="I243" s="12">
-        <v>114</v>
+        <v>116</v>
       </c>
       <c r="J243" s="12">
-        <v>2878</v>
+        <v>2518</v>
       </c>
       <c r="K243" s="12">
-        <v>531</v>
+        <v>532</v>
       </c>
       <c r="L243" s="13">
-        <v>714.48</v>
+        <v>691</v>
       </c>
       <c r="M243" s="14" t="s">
         <v>18</v>
@@ -12296,10 +12296,10 @@
         <v>500</v>
       </c>
       <c r="F244" s="5">
-        <v>27500</v>
+        <v>12500</v>
       </c>
       <c r="G244" s="5">
-        <v>27500</v>
+        <v>12500</v>
       </c>
       <c r="H244" s="5">
         <v>0</v>
@@ -12308,13 +12308,13 @@
         <v>9</v>
       </c>
       <c r="J244" s="6">
-        <v>234</v>
+        <v>223</v>
       </c>
       <c r="K244" s="6">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="L244" s="7">
-        <v>6228.77</v>
+        <v>4347.83</v>
       </c>
       <c r="M244" s="8" t="s">
         <v>18</v>
@@ -12340,25 +12340,25 @@
         <v>10</v>
       </c>
       <c r="F245" s="11">
-        <v>300</v>
+        <v>270</v>
       </c>
       <c r="G245" s="11">
-        <v>300</v>
+        <v>270</v>
       </c>
       <c r="H245" s="11">
         <v>0</v>
       </c>
       <c r="I245" s="12">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="J245" s="12">
-        <v>791</v>
+        <v>683</v>
       </c>
       <c r="K245" s="12">
         <v>108</v>
       </c>
       <c r="L245" s="13">
-        <v>63.29</v>
+        <v>61.14</v>
       </c>
       <c r="M245" s="14" t="s">
         <v>18</v>
@@ -12384,10 +12384,10 @@
         <v>25</v>
       </c>
       <c r="F246" s="5">
-        <v>625</v>
+        <v>1075</v>
       </c>
       <c r="G246" s="5">
-        <v>625</v>
+        <v>1075</v>
       </c>
       <c r="H246" s="5">
         <v>0</v>
@@ -12396,13 +12396,13 @@
         <v>10</v>
       </c>
       <c r="J246" s="6">
-        <v>137</v>
+        <v>115</v>
       </c>
       <c r="K246" s="6">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="L246" s="7">
-        <v>277.78</v>
+        <v>391.34</v>
       </c>
       <c r="M246" s="8" t="s">
         <v>18</v>
@@ -12428,25 +12428,25 @@
         <v>50</v>
       </c>
       <c r="F247" s="11">
-        <v>2600</v>
+        <v>2750</v>
       </c>
       <c r="G247" s="11">
-        <v>2600</v>
+        <v>2750</v>
       </c>
       <c r="H247" s="11">
         <v>0</v>
       </c>
       <c r="I247" s="12">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="J247" s="12">
-        <v>110</v>
+        <v>148</v>
       </c>
       <c r="K247" s="12">
         <v>33</v>
       </c>
       <c r="L247" s="13">
-        <v>808.46</v>
+        <v>829.56</v>
       </c>
       <c r="M247" s="14" t="s">
         <v>18</v>
@@ -12472,25 +12472,25 @@
         <v>100</v>
       </c>
       <c r="F248" s="5">
-        <v>6600</v>
+        <v>6000</v>
       </c>
       <c r="G248" s="5">
-        <v>6600</v>
+        <v>6000</v>
       </c>
       <c r="H248" s="5">
         <v>0</v>
       </c>
       <c r="I248" s="6">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="J248" s="6">
-        <v>154</v>
+        <v>111</v>
       </c>
       <c r="K248" s="6">
         <v>35</v>
       </c>
       <c r="L248" s="7">
-        <v>1732.28</v>
+        <v>1666.67</v>
       </c>
       <c r="M248" s="8" t="s">
         <v>18</v>
@@ -12516,25 +12516,25 @@
         <v>150</v>
       </c>
       <c r="F249" s="11">
-        <v>9900</v>
+        <v>5100</v>
       </c>
       <c r="G249" s="11">
-        <v>9900</v>
+        <v>5100</v>
       </c>
       <c r="H249" s="11">
         <v>0</v>
       </c>
       <c r="I249" s="12">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="J249" s="12">
-        <v>137</v>
+        <v>177</v>
       </c>
       <c r="K249" s="12">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="L249" s="13">
-        <v>2511.42</v>
+        <v>1872.25</v>
       </c>
       <c r="M249" s="14" t="s">
         <v>18</v>
@@ -12560,25 +12560,25 @@
         <v>200</v>
       </c>
       <c r="F250" s="5">
-        <v>13000</v>
+        <v>7600</v>
       </c>
       <c r="G250" s="5">
-        <v>13000</v>
+        <v>7600</v>
       </c>
       <c r="H250" s="5">
         <v>0</v>
       </c>
       <c r="I250" s="6">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="J250" s="6">
-        <v>134</v>
+        <v>128</v>
       </c>
       <c r="K250" s="6">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="L250" s="7">
-        <v>3221.81</v>
+        <v>2581.52</v>
       </c>
       <c r="M250" s="8" t="s">
         <v>18</v>
@@ -12604,25 +12604,25 @@
         <v>300</v>
       </c>
       <c r="F251" s="11">
-        <v>9000</v>
+        <v>10500</v>
       </c>
       <c r="G251" s="11">
-        <v>9000</v>
+        <v>10500</v>
       </c>
       <c r="H251" s="11">
         <v>0</v>
       </c>
       <c r="I251" s="12">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="J251" s="12">
-        <v>190</v>
+        <v>154</v>
       </c>
       <c r="K251" s="12">
-        <v>45</v>
+        <v>42</v>
       </c>
       <c r="L251" s="13">
-        <v>3157.89</v>
+        <v>3535.35</v>
       </c>
       <c r="M251" s="14" t="s">
         <v>18</v>
@@ -12648,10 +12648,10 @@
         <v>400</v>
       </c>
       <c r="F252" s="5">
-        <v>10800</v>
+        <v>13600</v>
       </c>
       <c r="G252" s="5">
-        <v>10800</v>
+        <v>13600</v>
       </c>
       <c r="H252" s="5">
         <v>0</v>
@@ -12660,13 +12660,13 @@
         <v>37</v>
       </c>
       <c r="J252" s="6">
-        <v>902</v>
+        <v>854</v>
       </c>
       <c r="K252" s="6">
-        <v>179</v>
+        <v>181</v>
       </c>
       <c r="L252" s="7">
-        <v>1705.35</v>
+        <v>1776.85</v>
       </c>
       <c r="M252" s="8" t="s">
         <v>18</v>
@@ -12692,25 +12692,25 @@
         <v>500</v>
       </c>
       <c r="F253" s="11">
-        <v>27000</v>
+        <v>19500</v>
       </c>
       <c r="G253" s="11">
-        <v>27000</v>
+        <v>19500</v>
       </c>
       <c r="H253" s="11">
         <v>0</v>
       </c>
       <c r="I253" s="12">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="J253" s="12">
-        <v>188</v>
+        <v>256</v>
       </c>
       <c r="K253" s="12">
         <v>52</v>
       </c>
       <c r="L253" s="13">
-        <v>6267.41</v>
+        <v>5527.21</v>
       </c>
       <c r="M253" s="14" t="s">
         <v>18</v>
@@ -12736,25 +12736,25 @@
         <v>10</v>
       </c>
       <c r="F254" s="5">
-        <v>580</v>
+        <v>510</v>
       </c>
       <c r="G254" s="5">
-        <v>580</v>
+        <v>510</v>
       </c>
       <c r="H254" s="5">
         <v>0</v>
       </c>
       <c r="I254" s="6">
-        <v>119</v>
+        <v>115</v>
       </c>
       <c r="J254" s="6">
-        <v>1780</v>
+        <v>2114</v>
       </c>
       <c r="K254" s="6">
-        <v>330</v>
+        <v>310</v>
       </c>
       <c r="L254" s="7">
-        <v>28.1</v>
+        <v>29.46</v>
       </c>
       <c r="M254" s="8" t="s">
         <v>18</v>
@@ -12780,25 +12780,25 @@
         <v>25</v>
       </c>
       <c r="F255" s="11">
-        <v>1500</v>
+        <v>1000</v>
       </c>
       <c r="G255" s="11">
-        <v>1500</v>
+        <v>1000</v>
       </c>
       <c r="H255" s="11">
         <v>0</v>
       </c>
       <c r="I255" s="12">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="J255" s="12">
-        <v>142</v>
+        <v>119</v>
       </c>
       <c r="K255" s="12">
         <v>31</v>
       </c>
       <c r="L255" s="13">
-        <v>446.43</v>
+        <v>364.96</v>
       </c>
       <c r="M255" s="14" t="s">
         <v>18</v>
@@ -12824,25 +12824,25 @@
         <v>50</v>
       </c>
       <c r="F256" s="5">
-        <v>2250</v>
+        <v>3050</v>
       </c>
       <c r="G256" s="5">
-        <v>2250</v>
+        <v>3050</v>
       </c>
       <c r="H256" s="5">
         <v>0</v>
       </c>
       <c r="I256" s="6">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="J256" s="6">
-        <v>718</v>
+        <v>767</v>
       </c>
       <c r="K256" s="6">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="L256" s="7">
-        <v>332.59</v>
+        <v>355.64</v>
       </c>
       <c r="M256" s="8" t="s">
         <v>18</v>
@@ -12868,10 +12868,10 @@
         <v>100</v>
       </c>
       <c r="F257" s="11">
-        <v>2600</v>
+        <v>5400</v>
       </c>
       <c r="G257" s="11">
-        <v>2600</v>
+        <v>5400</v>
       </c>
       <c r="H257" s="11">
         <v>0</v>
@@ -12880,13 +12880,13 @@
         <v>10</v>
       </c>
       <c r="J257" s="12">
-        <v>126</v>
+        <v>121</v>
       </c>
       <c r="K257" s="12">
         <v>33</v>
       </c>
       <c r="L257" s="13">
-        <v>1102.63</v>
+        <v>1645.34</v>
       </c>
       <c r="M257" s="14" t="s">
         <v>18</v>
@@ -12912,25 +12912,25 @@
         <v>150</v>
       </c>
       <c r="F258" s="5">
-        <v>3600</v>
+        <v>4500</v>
       </c>
       <c r="G258" s="5">
-        <v>3600</v>
+        <v>4500</v>
       </c>
       <c r="H258" s="5">
         <v>0</v>
       </c>
       <c r="I258" s="6">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="J258" s="6">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="K258" s="6">
-        <v>35</v>
+        <v>38</v>
       </c>
       <c r="L258" s="7">
-        <v>1538.46</v>
+        <v>1704.55</v>
       </c>
       <c r="M258" s="8" t="s">
         <v>18</v>
@@ -12956,10 +12956,10 @@
         <v>200</v>
       </c>
       <c r="F259" s="11">
-        <v>10800</v>
+        <v>12000</v>
       </c>
       <c r="G259" s="11">
-        <v>10800</v>
+        <v>12000</v>
       </c>
       <c r="H259" s="11">
         <v>0</v>
@@ -12968,13 +12968,13 @@
         <v>10</v>
       </c>
       <c r="J259" s="12">
-        <v>152</v>
+        <v>134</v>
       </c>
       <c r="K259" s="12">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="L259" s="13">
-        <v>3040.54</v>
+        <v>3076.92</v>
       </c>
       <c r="M259" s="14" t="s">
         <v>18</v>
@@ -13000,10 +13000,10 @@
         <v>300</v>
       </c>
       <c r="F260" s="5">
-        <v>19200</v>
+        <v>10800</v>
       </c>
       <c r="G260" s="5">
-        <v>19200</v>
+        <v>10800</v>
       </c>
       <c r="H260" s="5">
         <v>0</v>
@@ -13012,13 +13012,13 @@
         <v>10</v>
       </c>
       <c r="J260" s="6">
-        <v>151</v>
+        <v>195</v>
       </c>
       <c r="K260" s="6">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="L260" s="7">
-        <v>4383.56</v>
+        <v>3543.31</v>
       </c>
       <c r="M260" s="8" t="s">
         <v>18</v>
@@ -13044,10 +13044,10 @@
         <v>400</v>
       </c>
       <c r="F261" s="11">
-        <v>12000</v>
+        <v>27600</v>
       </c>
       <c r="G261" s="11">
-        <v>12000</v>
+        <v>27600</v>
       </c>
       <c r="H261" s="11">
         <v>0</v>
@@ -13056,13 +13056,13 @@
         <v>10</v>
       </c>
       <c r="J261" s="12">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="K261" s="12">
-        <v>50</v>
+        <v>47</v>
       </c>
       <c r="L261" s="13">
-        <v>4000</v>
+        <v>5819.1</v>
       </c>
       <c r="M261" s="14" t="s">
         <v>18</v>
@@ -13088,10 +13088,10 @@
         <v>500</v>
       </c>
       <c r="F262" s="5">
-        <v>14500</v>
+        <v>13000</v>
       </c>
       <c r="G262" s="5">
-        <v>14500</v>
+        <v>13000</v>
       </c>
       <c r="H262" s="5">
         <v>0</v>
@@ -13100,13 +13100,13 @@
         <v>10</v>
       </c>
       <c r="J262" s="6">
-        <v>241</v>
+        <v>212</v>
       </c>
       <c r="K262" s="6">
         <v>52</v>
       </c>
       <c r="L262" s="7">
-        <v>4820.48</v>
+        <v>4558.2</v>
       </c>
       <c r="M262" s="8" t="s">
         <v>18</v>
@@ -13132,25 +13132,25 @@
         <v>10</v>
       </c>
       <c r="F263" s="11">
-        <v>630</v>
+        <v>440</v>
       </c>
       <c r="G263" s="11">
-        <v>630</v>
+        <v>440</v>
       </c>
       <c r="H263" s="11">
         <v>0</v>
       </c>
       <c r="I263" s="12">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="J263" s="12">
-        <v>772</v>
+        <v>595</v>
       </c>
       <c r="K263" s="12">
-        <v>110</v>
+        <v>115</v>
       </c>
       <c r="L263" s="13">
-        <v>74.73</v>
+        <v>67.07</v>
       </c>
       <c r="M263" s="14" t="s">
         <v>18</v>
@@ -13176,10 +13176,10 @@
         <v>25</v>
       </c>
       <c r="F264" s="5">
-        <v>975</v>
+        <v>1150</v>
       </c>
       <c r="G264" s="5">
-        <v>975</v>
+        <v>1150</v>
       </c>
       <c r="H264" s="5">
         <v>0</v>
@@ -13188,13 +13188,13 @@
         <v>9</v>
       </c>
       <c r="J264" s="6">
-        <v>137</v>
+        <v>144</v>
       </c>
       <c r="K264" s="6">
         <v>30</v>
       </c>
       <c r="L264" s="7">
-        <v>365.17</v>
+        <v>399.31</v>
       </c>
       <c r="M264" s="8" t="s">
         <v>18</v>
@@ -13220,25 +13220,25 @@
         <v>50</v>
       </c>
       <c r="F265" s="11">
-        <v>2700</v>
+        <v>3450</v>
       </c>
       <c r="G265" s="11">
-        <v>2700</v>
+        <v>3450</v>
       </c>
       <c r="H265" s="11">
         <v>0</v>
       </c>
       <c r="I265" s="12">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="J265" s="12">
-        <v>1557</v>
+        <v>2091</v>
       </c>
       <c r="K265" s="12">
-        <v>348</v>
+        <v>342</v>
       </c>
       <c r="L265" s="13">
-        <v>133.06</v>
+        <v>137.46</v>
       </c>
       <c r="M265" s="14" t="s">
         <v>18</v>
@@ -13264,25 +13264,25 @@
         <v>100</v>
       </c>
       <c r="F266" s="5">
-        <v>3400</v>
+        <v>3300</v>
       </c>
       <c r="G266" s="5">
-        <v>3400</v>
+        <v>3300</v>
       </c>
       <c r="H266" s="5">
         <v>0</v>
       </c>
       <c r="I266" s="6">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="J266" s="6">
-        <v>158</v>
+        <v>114</v>
       </c>
       <c r="K266" s="6">
         <v>34</v>
       </c>
       <c r="L266" s="7">
-        <v>1280.12</v>
+        <v>1258.58</v>
       </c>
       <c r="M266" s="8" t="s">
         <v>18</v>
@@ -13308,25 +13308,25 @@
         <v>150</v>
       </c>
       <c r="F267" s="11">
-        <v>3000</v>
+        <v>3750</v>
       </c>
       <c r="G267" s="11">
-        <v>3000</v>
+        <v>3750</v>
       </c>
       <c r="H267" s="11">
         <v>0</v>
       </c>
       <c r="I267" s="12">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="J267" s="12">
-        <v>755</v>
+        <v>893</v>
       </c>
       <c r="K267" s="12">
-        <v>139</v>
+        <v>133</v>
       </c>
       <c r="L267" s="13">
-        <v>700.93</v>
+        <v>777.2</v>
       </c>
       <c r="M267" s="14" t="s">
         <v>18</v>
@@ -13352,10 +13352,10 @@
         <v>200</v>
       </c>
       <c r="F268" s="5">
-        <v>11200</v>
+        <v>8000</v>
       </c>
       <c r="G268" s="5">
-        <v>11200</v>
+        <v>8000</v>
       </c>
       <c r="H268" s="5">
         <v>0</v>
@@ -13364,13 +13364,13 @@
         <v>9</v>
       </c>
       <c r="J268" s="6">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="K268" s="6">
         <v>39</v>
       </c>
       <c r="L268" s="7">
-        <v>3040.17</v>
+        <v>2614.38</v>
       </c>
       <c r="M268" s="8" t="s">
         <v>18</v>
@@ -13396,10 +13396,10 @@
         <v>300</v>
       </c>
       <c r="F269" s="11">
-        <v>19500</v>
+        <v>11400</v>
       </c>
       <c r="G269" s="11">
-        <v>19500</v>
+        <v>11400</v>
       </c>
       <c r="H269" s="11">
         <v>0</v>
@@ -13408,13 +13408,13 @@
         <v>10</v>
       </c>
       <c r="J269" s="12">
-        <v>192</v>
+        <v>178</v>
       </c>
       <c r="K269" s="12">
         <v>43</v>
       </c>
       <c r="L269" s="13">
-        <v>4540.16</v>
+        <v>3637.52</v>
       </c>
       <c r="M269" s="14" t="s">
         <v>18</v>
@@ -13440,10 +13440,10 @@
         <v>400</v>
       </c>
       <c r="F270" s="5">
-        <v>13200</v>
+        <v>12000</v>
       </c>
       <c r="G270" s="5">
-        <v>13200</v>
+        <v>12000</v>
       </c>
       <c r="H270" s="5">
         <v>0</v>
@@ -13452,13 +13452,13 @@
         <v>10</v>
       </c>
       <c r="J270" s="6">
-        <v>205</v>
+        <v>188</v>
       </c>
       <c r="K270" s="6">
-        <v>47</v>
+        <v>51</v>
       </c>
       <c r="L270" s="7">
-        <v>4326.45</v>
+        <v>3960.4</v>
       </c>
       <c r="M270" s="8" t="s">
         <v>18</v>
@@ -13484,10 +13484,10 @@
         <v>500</v>
       </c>
       <c r="F271" s="11">
-        <v>34000</v>
+        <v>32000</v>
       </c>
       <c r="G271" s="11">
-        <v>34000</v>
+        <v>32000</v>
       </c>
       <c r="H271" s="11">
         <v>0</v>
@@ -13496,13 +13496,13 @@
         <v>9</v>
       </c>
       <c r="J271" s="12">
-        <v>182</v>
+        <v>241</v>
       </c>
       <c r="K271" s="12">
         <v>51</v>
       </c>
       <c r="L271" s="13">
-        <v>6843.8</v>
+        <v>6717.04</v>
       </c>
       <c r="M271" s="14" t="s">
         <v>18</v>
@@ -13528,25 +13528,25 @@
         <v>10</v>
       </c>
       <c r="F272" s="5">
-        <v>420</v>
+        <v>220</v>
       </c>
       <c r="G272" s="5">
-        <v>420</v>
+        <v>220</v>
       </c>
       <c r="H272" s="5">
         <v>0</v>
       </c>
       <c r="I272" s="6">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="J272" s="6">
-        <v>145</v>
+        <v>126</v>
       </c>
       <c r="K272" s="6">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="L272" s="7">
-        <v>152.17</v>
+        <v>102.9</v>
       </c>
       <c r="M272" s="8" t="s">
         <v>18</v>
@@ -13572,25 +13572,25 @@
         <v>25</v>
       </c>
       <c r="F273" s="11">
-        <v>500</v>
+        <v>1600</v>
       </c>
       <c r="G273" s="11">
-        <v>500</v>
+        <v>1600</v>
       </c>
       <c r="H273" s="11">
         <v>0</v>
       </c>
       <c r="I273" s="12">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="J273" s="12">
-        <v>118</v>
+        <v>116</v>
       </c>
       <c r="K273" s="12">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="L273" s="13">
-        <v>233.64</v>
+        <v>467.84</v>
       </c>
       <c r="M273" s="14" t="s">
         <v>18</v>
@@ -13616,25 +13616,25 @@
         <v>50</v>
       </c>
       <c r="F274" s="5">
-        <v>3050</v>
+        <v>2150</v>
       </c>
       <c r="G274" s="5">
-        <v>3050</v>
+        <v>2150</v>
       </c>
       <c r="H274" s="5">
         <v>0</v>
       </c>
       <c r="I274" s="6">
-        <v>36</v>
+        <v>43</v>
       </c>
       <c r="J274" s="6">
-        <v>672</v>
+        <v>683</v>
       </c>
       <c r="K274" s="6">
-        <v>115</v>
+        <v>117</v>
       </c>
       <c r="L274" s="7">
-        <v>358.19</v>
+        <v>329.2</v>
       </c>
       <c r="M274" s="8" t="s">
         <v>18</v>
@@ -13660,25 +13660,25 @@
         <v>100</v>
       </c>
       <c r="F275" s="11">
-        <v>6100</v>
+        <v>3000</v>
       </c>
       <c r="G275" s="11">
-        <v>6100</v>
+        <v>3000</v>
       </c>
       <c r="H275" s="11">
         <v>0</v>
       </c>
       <c r="I275" s="12">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="J275" s="12">
-        <v>163</v>
+        <v>147</v>
       </c>
       <c r="K275" s="12">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="L275" s="13">
-        <v>1678.13</v>
+        <v>1190.48</v>
       </c>
       <c r="M275" s="14" t="s">
         <v>18</v>
@@ -13704,25 +13704,25 @@
         <v>150</v>
       </c>
       <c r="F276" s="5">
-        <v>9750</v>
+        <v>9150</v>
       </c>
       <c r="G276" s="5">
-        <v>9750</v>
+        <v>9150</v>
       </c>
       <c r="H276" s="5">
         <v>0</v>
       </c>
       <c r="I276" s="6">
-        <v>119</v>
+        <v>111</v>
       </c>
       <c r="J276" s="6">
-        <v>1821</v>
+        <v>2572</v>
       </c>
       <c r="K276" s="6">
-        <v>406</v>
+        <v>413</v>
       </c>
       <c r="L276" s="7">
-        <v>349.59</v>
+        <v>342.79</v>
       </c>
       <c r="M276" s="8" t="s">
         <v>18</v>
@@ -13748,25 +13748,25 @@
         <v>200</v>
       </c>
       <c r="F277" s="11">
-        <v>10200</v>
+        <v>13800</v>
       </c>
       <c r="G277" s="11">
-        <v>10200</v>
+        <v>13800</v>
       </c>
       <c r="H277" s="11">
         <v>0</v>
       </c>
       <c r="I277" s="12">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="J277" s="12">
-        <v>168</v>
+        <v>152</v>
       </c>
       <c r="K277" s="12">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="L277" s="13">
-        <v>2966.84</v>
+        <v>3239.44</v>
       </c>
       <c r="M277" s="14" t="s">
         <v>18</v>
@@ -13792,25 +13792,25 @@
         <v>300</v>
       </c>
       <c r="F278" s="5">
-        <v>15900</v>
+        <v>18600</v>
       </c>
       <c r="G278" s="5">
-        <v>15900</v>
+        <v>18600</v>
       </c>
       <c r="H278" s="5">
         <v>0</v>
       </c>
       <c r="I278" s="6">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="J278" s="6">
-        <v>848</v>
+        <v>1110</v>
       </c>
       <c r="K278" s="6">
         <v>163</v>
       </c>
       <c r="L278" s="7">
-        <v>1568.2</v>
+        <v>1602.62</v>
       </c>
       <c r="M278" s="8" t="s">
         <v>18</v>
@@ -13836,25 +13836,25 @@
         <v>400</v>
       </c>
       <c r="F279" s="11">
-        <v>19600</v>
+        <v>25600</v>
       </c>
       <c r="G279" s="11">
-        <v>19600</v>
+        <v>25600</v>
       </c>
       <c r="H279" s="11">
         <v>0</v>
       </c>
       <c r="I279" s="12">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="J279" s="12">
-        <v>204</v>
+        <v>221</v>
       </c>
       <c r="K279" s="12">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="L279" s="13">
-        <v>5153.83</v>
+        <v>5760.58</v>
       </c>
       <c r="M279" s="14" t="s">
         <v>18</v>
@@ -13880,25 +13880,25 @@
         <v>500</v>
       </c>
       <c r="F280" s="5">
-        <v>13500</v>
+        <v>18500</v>
       </c>
       <c r="G280" s="5">
-        <v>13500</v>
+        <v>18500</v>
       </c>
       <c r="H280" s="5">
         <v>0</v>
       </c>
       <c r="I280" s="6">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="J280" s="6">
-        <v>189</v>
+        <v>250</v>
       </c>
       <c r="K280" s="6">
-        <v>51</v>
+        <v>55</v>
       </c>
       <c r="L280" s="7">
-        <v>4692.39</v>
+        <v>5233.38</v>
       </c>
       <c r="M280" s="8" t="s">
         <v>18</v>
@@ -13924,25 +13924,25 @@
         <v>10</v>
       </c>
       <c r="F281" s="11">
-        <v>440</v>
+        <v>280</v>
       </c>
       <c r="G281" s="11">
-        <v>440</v>
+        <v>280</v>
       </c>
       <c r="H281" s="11">
         <v>0</v>
       </c>
       <c r="I281" s="12">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="J281" s="12">
-        <v>119</v>
+        <v>106</v>
       </c>
       <c r="K281" s="12">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="L281" s="13">
-        <v>153.63</v>
+        <v>119.66</v>
       </c>
       <c r="M281" s="14" t="s">
         <v>18</v>
@@ -13968,25 +13968,25 @@
         <v>25</v>
       </c>
       <c r="F282" s="5">
-        <v>1025</v>
+        <v>1675</v>
       </c>
       <c r="G282" s="5">
-        <v>1025</v>
+        <v>1675</v>
       </c>
       <c r="H282" s="5">
         <v>0</v>
       </c>
       <c r="I282" s="6">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="J282" s="6">
-        <v>120</v>
+        <v>123</v>
       </c>
       <c r="K282" s="6">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="L282" s="7">
-        <v>369.9</v>
+        <v>477.21</v>
       </c>
       <c r="M282" s="8" t="s">
         <v>18</v>
@@ -14012,10 +14012,10 @@
         <v>50</v>
       </c>
       <c r="F283" s="11">
-        <v>3250</v>
+        <v>3350</v>
       </c>
       <c r="G283" s="11">
-        <v>3250</v>
+        <v>3350</v>
       </c>
       <c r="H283" s="11">
         <v>0</v>
@@ -14024,13 +14024,13 @@
         <v>10</v>
       </c>
       <c r="J283" s="12">
-        <v>138</v>
+        <v>154</v>
       </c>
       <c r="K283" s="12">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="L283" s="13">
-        <v>924.61</v>
+        <v>954.42</v>
       </c>
       <c r="M283" s="14" t="s">
         <v>18</v>
@@ -14056,10 +14056,10 @@
         <v>100</v>
       </c>
       <c r="F284" s="5">
-        <v>2700</v>
+        <v>5500</v>
       </c>
       <c r="G284" s="5">
-        <v>2700</v>
+        <v>5500</v>
       </c>
       <c r="H284" s="5">
         <v>0</v>
@@ -14068,13 +14068,13 @@
         <v>10</v>
       </c>
       <c r="J284" s="6">
-        <v>147</v>
+        <v>162</v>
       </c>
       <c r="K284" s="6">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="L284" s="7">
-        <v>1129.23</v>
+        <v>1605.84</v>
       </c>
       <c r="M284" s="8" t="s">
         <v>18</v>
@@ -14100,25 +14100,25 @@
         <v>150</v>
       </c>
       <c r="F285" s="11">
-        <v>8400</v>
+        <v>3600</v>
       </c>
       <c r="G285" s="11">
-        <v>8400</v>
+        <v>3600</v>
       </c>
       <c r="H285" s="11">
         <v>0</v>
       </c>
       <c r="I285" s="12">
-        <v>36</v>
+        <v>42</v>
       </c>
       <c r="J285" s="12">
-        <v>840</v>
+        <v>706</v>
       </c>
       <c r="K285" s="12">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="L285" s="13">
-        <v>950.66</v>
+        <v>779.22</v>
       </c>
       <c r="M285" s="14" t="s">
         <v>18</v>
@@ -14144,25 +14144,25 @@
         <v>200</v>
       </c>
       <c r="F286" s="5">
-        <v>12000</v>
+        <v>13600</v>
       </c>
       <c r="G286" s="5">
-        <v>12000</v>
+        <v>13600</v>
       </c>
       <c r="H286" s="5">
         <v>0</v>
       </c>
       <c r="I286" s="6">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="J286" s="6">
-        <v>167</v>
+        <v>140</v>
       </c>
       <c r="K286" s="6">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="L286" s="7">
-        <v>3076.92</v>
+        <v>3275.53</v>
       </c>
       <c r="M286" s="8" t="s">
         <v>18</v>
@@ -14188,25 +14188,25 @@
         <v>300</v>
       </c>
       <c r="F287" s="11">
-        <v>17100</v>
+        <v>16500</v>
       </c>
       <c r="G287" s="11">
-        <v>17100</v>
+        <v>16500</v>
       </c>
       <c r="H287" s="11">
         <v>0</v>
       </c>
       <c r="I287" s="12">
-        <v>120</v>
+        <v>127</v>
       </c>
       <c r="J287" s="12">
-        <v>2876</v>
+        <v>2256</v>
       </c>
       <c r="K287" s="12">
-        <v>466</v>
+        <v>454</v>
       </c>
       <c r="L287" s="13">
-        <v>609.36</v>
+        <v>623.35</v>
       </c>
       <c r="M287" s="14" t="s">
         <v>18</v>
@@ -14232,25 +14232,25 @@
         <v>400</v>
       </c>
       <c r="F288" s="5">
-        <v>8000</v>
+        <v>9200</v>
       </c>
       <c r="G288" s="5">
-        <v>8000</v>
+        <v>9200</v>
       </c>
       <c r="H288" s="5">
         <v>0</v>
       </c>
       <c r="I288" s="6">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="J288" s="6">
-        <v>187</v>
+        <v>167</v>
       </c>
       <c r="K288" s="6">
-        <v>46</v>
+        <v>50</v>
       </c>
       <c r="L288" s="7">
-        <v>3305.79</v>
+        <v>3471.7</v>
       </c>
       <c r="M288" s="8" t="s">
         <v>18</v>
@@ -14276,25 +14276,25 @@
         <v>500</v>
       </c>
       <c r="F289" s="11">
-        <v>27500</v>
+        <v>17000</v>
       </c>
       <c r="G289" s="11">
-        <v>27500</v>
+        <v>17000</v>
       </c>
       <c r="H289" s="11">
         <v>0</v>
       </c>
       <c r="I289" s="12">
-        <v>38</v>
+        <v>43</v>
       </c>
       <c r="J289" s="12">
-        <v>1254</v>
+        <v>1051</v>
       </c>
       <c r="K289" s="12">
-        <v>188</v>
+        <v>207</v>
       </c>
       <c r="L289" s="13">
-        <v>2322.64</v>
+        <v>1991.1</v>
       </c>
       <c r="M289" s="14" t="s">
         <v>18</v>
@@ -14320,25 +14320,25 @@
         <v>10</v>
       </c>
       <c r="F290" s="5">
-        <v>490</v>
+        <v>450</v>
       </c>
       <c r="G290" s="5">
-        <v>490</v>
+        <v>450</v>
       </c>
       <c r="H290" s="5">
         <v>0</v>
       </c>
       <c r="I290" s="6">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="J290" s="6">
-        <v>143</v>
+        <v>98</v>
       </c>
       <c r="K290" s="6">
         <v>29</v>
       </c>
       <c r="L290" s="7">
-        <v>167.75</v>
+        <v>160.43</v>
       </c>
       <c r="M290" s="8" t="s">
         <v>18</v>
@@ -14376,7 +14376,7 @@
         <v>9</v>
       </c>
       <c r="J291" s="12">
-        <v>120</v>
+        <v>100</v>
       </c>
       <c r="K291" s="12">
         <v>31</v>
@@ -14408,10 +14408,10 @@
         <v>50</v>
       </c>
       <c r="F292" s="5">
-        <v>2700</v>
+        <v>3050</v>
       </c>
       <c r="G292" s="5">
-        <v>2700</v>
+        <v>3050</v>
       </c>
       <c r="H292" s="5">
         <v>0</v>
@@ -14420,13 +14420,13 @@
         <v>9</v>
       </c>
       <c r="J292" s="6">
-        <v>107</v>
+        <v>127</v>
       </c>
       <c r="K292" s="6">
         <v>33</v>
       </c>
       <c r="L292" s="7">
-        <v>822.67</v>
+        <v>868.2</v>
       </c>
       <c r="M292" s="8" t="s">
         <v>18</v>
@@ -14452,10 +14452,10 @@
         <v>100</v>
       </c>
       <c r="F293" s="11">
-        <v>2800</v>
+        <v>6200</v>
       </c>
       <c r="G293" s="11">
-        <v>2800</v>
+        <v>6200</v>
       </c>
       <c r="H293" s="11">
         <v>0</v>
@@ -14464,13 +14464,13 @@
         <v>10</v>
       </c>
       <c r="J293" s="12">
-        <v>146</v>
+        <v>160</v>
       </c>
       <c r="K293" s="12">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="L293" s="13">
-        <v>1141.92</v>
+        <v>1689.37</v>
       </c>
       <c r="M293" s="14" t="s">
         <v>18</v>
@@ -14496,25 +14496,25 @@
         <v>150</v>
       </c>
       <c r="F294" s="5">
-        <v>7800</v>
+        <v>3450</v>
       </c>
       <c r="G294" s="5">
-        <v>7800</v>
+        <v>3450</v>
       </c>
       <c r="H294" s="5">
         <v>0</v>
       </c>
       <c r="I294" s="6">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="J294" s="6">
-        <v>142</v>
+        <v>152</v>
       </c>
       <c r="K294" s="6">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="L294" s="7">
-        <v>2278.04</v>
+        <v>1453.24</v>
       </c>
       <c r="M294" s="8" t="s">
         <v>18</v>
@@ -14540,10 +14540,10 @@
         <v>200</v>
       </c>
       <c r="F295" s="11">
-        <v>9200</v>
+        <v>5600</v>
       </c>
       <c r="G295" s="11">
-        <v>9200</v>
+        <v>5600</v>
       </c>
       <c r="H295" s="11">
         <v>0</v>
@@ -14552,13 +14552,13 @@
         <v>9</v>
       </c>
       <c r="J295" s="12">
-        <v>145</v>
+        <v>132</v>
       </c>
       <c r="K295" s="12">
         <v>38</v>
       </c>
       <c r="L295" s="13">
-        <v>2832.51</v>
+        <v>2184.09</v>
       </c>
       <c r="M295" s="14" t="s">
         <v>18</v>
@@ -14596,13 +14596,13 @@
         <v>38</v>
       </c>
       <c r="J296" s="6">
-        <v>1097</v>
+        <v>825</v>
       </c>
       <c r="K296" s="6">
-        <v>154</v>
+        <v>157</v>
       </c>
       <c r="L296" s="7">
-        <v>1417.15</v>
+        <v>1397.35</v>
       </c>
       <c r="M296" s="8" t="s">
         <v>18</v>
@@ -14628,10 +14628,10 @@
         <v>400</v>
       </c>
       <c r="F297" s="11">
-        <v>24400</v>
+        <v>14400</v>
       </c>
       <c r="G297" s="11">
-        <v>24400</v>
+        <v>14400</v>
       </c>
       <c r="H297" s="11">
         <v>0</v>
@@ -14640,13 +14640,13 @@
         <v>10</v>
       </c>
       <c r="J297" s="12">
-        <v>198</v>
+        <v>180</v>
       </c>
       <c r="K297" s="12">
-        <v>47</v>
+        <v>51</v>
       </c>
       <c r="L297" s="13">
-        <v>5587.36</v>
+        <v>4316.55</v>
       </c>
       <c r="M297" s="14" t="s">
         <v>18</v>
@@ -14672,25 +14672,25 @@
         <v>500</v>
       </c>
       <c r="F298" s="5">
-        <v>34000</v>
+        <v>22500</v>
       </c>
       <c r="G298" s="5">
-        <v>34000</v>
+        <v>22500</v>
       </c>
       <c r="H298" s="5">
         <v>0</v>
       </c>
       <c r="I298" s="6">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="J298" s="6">
-        <v>2703</v>
+        <v>3312</v>
       </c>
       <c r="K298" s="6">
-        <v>586</v>
+        <v>595</v>
       </c>
       <c r="L298" s="7">
-        <v>822.29</v>
+        <v>795.76</v>
       </c>
       <c r="M298" s="8" t="s">
         <v>18</v>
@@ -14716,10 +14716,10 @@
         <v>10</v>
       </c>
       <c r="F299" s="11">
-        <v>210</v>
+        <v>440</v>
       </c>
       <c r="G299" s="11">
-        <v>210</v>
+        <v>440</v>
       </c>
       <c r="H299" s="11">
         <v>0</v>
@@ -14728,13 +14728,13 @@
         <v>9</v>
       </c>
       <c r="J299" s="12">
-        <v>133</v>
+        <v>144</v>
       </c>
       <c r="K299" s="12">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="L299" s="13">
-        <v>98.59</v>
+        <v>158.5</v>
       </c>
       <c r="M299" s="14" t="s">
         <v>18</v>
@@ -14760,25 +14760,25 @@
         <v>25</v>
       </c>
       <c r="F300" s="5">
-        <v>975</v>
+        <v>600</v>
       </c>
       <c r="G300" s="5">
-        <v>975</v>
+        <v>600</v>
       </c>
       <c r="H300" s="5">
         <v>0</v>
       </c>
       <c r="I300" s="6">
-        <v>41</v>
+        <v>36</v>
       </c>
       <c r="J300" s="6">
-        <v>746</v>
+        <v>622</v>
       </c>
       <c r="K300" s="6">
-        <v>111</v>
+        <v>119</v>
       </c>
       <c r="L300" s="7">
-        <v>167.27</v>
+        <v>137.74</v>
       </c>
       <c r="M300" s="8" t="s">
         <v>18</v>
@@ -14804,10 +14804,10 @@
         <v>50</v>
       </c>
       <c r="F301" s="11">
-        <v>2250</v>
+        <v>1750</v>
       </c>
       <c r="G301" s="11">
-        <v>2250</v>
+        <v>1750</v>
       </c>
       <c r="H301" s="11">
         <v>0</v>
@@ -14816,13 +14816,13 @@
         <v>9</v>
       </c>
       <c r="J301" s="12">
-        <v>144</v>
+        <v>122</v>
       </c>
       <c r="K301" s="12">
         <v>31</v>
       </c>
       <c r="L301" s="13">
-        <v>777.2</v>
+        <v>676.98</v>
       </c>
       <c r="M301" s="14" t="s">
         <v>18</v>
@@ -14848,25 +14848,25 @@
         <v>100</v>
       </c>
       <c r="F302" s="5">
-        <v>6500</v>
+        <v>6400</v>
       </c>
       <c r="G302" s="5">
-        <v>6500</v>
+        <v>6400</v>
       </c>
       <c r="H302" s="5">
         <v>0</v>
       </c>
       <c r="I302" s="6">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="J302" s="6">
-        <v>119</v>
+        <v>165</v>
       </c>
       <c r="K302" s="6">
-        <v>36</v>
+        <v>33</v>
       </c>
       <c r="L302" s="7">
-        <v>1692.71</v>
+        <v>1771.87</v>
       </c>
       <c r="M302" s="8" t="s">
         <v>18</v>
@@ -14892,25 +14892,25 @@
         <v>150</v>
       </c>
       <c r="F303" s="11">
-        <v>8100</v>
+        <v>7950</v>
       </c>
       <c r="G303" s="11">
-        <v>8100</v>
+        <v>7950</v>
       </c>
       <c r="H303" s="11">
         <v>0</v>
       </c>
       <c r="I303" s="12">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="J303" s="12">
-        <v>122</v>
+        <v>144</v>
       </c>
       <c r="K303" s="12">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="L303" s="13">
-        <v>2315.61</v>
+        <v>2228.76</v>
       </c>
       <c r="M303" s="14" t="s">
         <v>18</v>
@@ -14936,25 +14936,25 @@
         <v>200</v>
       </c>
       <c r="F304" s="5">
-        <v>6200</v>
+        <v>13600</v>
       </c>
       <c r="G304" s="5">
-        <v>6200</v>
+        <v>13600</v>
       </c>
       <c r="H304" s="5">
         <v>0</v>
       </c>
       <c r="I304" s="6">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="J304" s="6">
-        <v>169</v>
+        <v>174</v>
       </c>
       <c r="K304" s="6">
-        <v>40</v>
+        <v>37</v>
       </c>
       <c r="L304" s="7">
-        <v>2262.77</v>
+        <v>3386.45</v>
       </c>
       <c r="M304" s="8" t="s">
         <v>18</v>
@@ -14980,10 +14980,10 @@
         <v>300</v>
       </c>
       <c r="F305" s="11">
-        <v>6600</v>
+        <v>14400</v>
       </c>
       <c r="G305" s="11">
-        <v>6600</v>
+        <v>14400</v>
       </c>
       <c r="H305" s="11">
         <v>0</v>
@@ -14992,13 +14992,13 @@
         <v>10</v>
       </c>
       <c r="J305" s="12">
-        <v>173</v>
+        <v>186</v>
       </c>
       <c r="K305" s="12">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="L305" s="13">
-        <v>2650.6</v>
+        <v>3986.71</v>
       </c>
       <c r="M305" s="14" t="s">
         <v>18</v>
@@ -15024,25 +15024,25 @@
         <v>400</v>
       </c>
       <c r="F306" s="5">
-        <v>14800</v>
+        <v>21200</v>
       </c>
       <c r="G306" s="5">
-        <v>14800</v>
+        <v>21200</v>
       </c>
       <c r="H306" s="5">
         <v>0</v>
       </c>
       <c r="I306" s="6">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="J306" s="6">
-        <v>219</v>
+        <v>182</v>
       </c>
       <c r="K306" s="6">
         <v>48</v>
       </c>
       <c r="L306" s="7">
-        <v>4517.7</v>
+        <v>5242.33</v>
       </c>
       <c r="M306" s="8" t="s">
         <v>18</v>
@@ -15068,25 +15068,25 @@
         <v>500</v>
       </c>
       <c r="F307" s="11">
-        <v>11500</v>
+        <v>21500</v>
       </c>
       <c r="G307" s="11">
-        <v>11500</v>
+        <v>21500</v>
       </c>
       <c r="H307" s="11">
         <v>0</v>
       </c>
       <c r="I307" s="12">
-        <v>43</v>
+        <v>40</v>
       </c>
       <c r="J307" s="12">
-        <v>960</v>
+        <v>1316</v>
       </c>
       <c r="K307" s="12">
-        <v>204</v>
+        <v>196</v>
       </c>
       <c r="L307" s="13">
-        <v>1857.24</v>
+        <v>2165.59</v>
       </c>
       <c r="M307" s="14" t="s">
         <v>18</v>
@@ -15112,10 +15112,10 @@
         <v>10</v>
       </c>
       <c r="F308" s="5">
-        <v>240</v>
+        <v>380</v>
       </c>
       <c r="G308" s="5">
-        <v>240</v>
+        <v>380</v>
       </c>
       <c r="H308" s="5">
         <v>0</v>
@@ -15124,13 +15124,13 @@
         <v>9</v>
       </c>
       <c r="J308" s="6">
-        <v>129</v>
+        <v>112</v>
       </c>
       <c r="K308" s="6">
         <v>30</v>
       </c>
       <c r="L308" s="7">
-        <v>108.11</v>
+        <v>143.94</v>
       </c>
       <c r="M308" s="8" t="s">
         <v>18</v>
@@ -15156,25 +15156,25 @@
         <v>25</v>
       </c>
       <c r="F309" s="11">
-        <v>1375</v>
+        <v>1075</v>
       </c>
       <c r="G309" s="11">
-        <v>1375</v>
+        <v>1075</v>
       </c>
       <c r="H309" s="11">
         <v>0</v>
       </c>
       <c r="I309" s="12">
-        <v>128</v>
+        <v>118</v>
       </c>
       <c r="J309" s="12">
-        <v>1605</v>
+        <v>2103</v>
       </c>
       <c r="K309" s="12">
-        <v>328</v>
+        <v>324</v>
       </c>
       <c r="L309" s="13">
-        <v>70.37</v>
+        <v>69.66</v>
       </c>
       <c r="M309" s="14" t="s">
         <v>18</v>
@@ -15200,25 +15200,25 @@
         <v>50</v>
       </c>
       <c r="F310" s="5">
-        <v>2500</v>
+        <v>1000</v>
       </c>
       <c r="G310" s="5">
-        <v>2500</v>
+        <v>1000</v>
       </c>
       <c r="H310" s="5">
         <v>0</v>
       </c>
       <c r="I310" s="6">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="J310" s="6">
-        <v>145</v>
+        <v>131</v>
       </c>
       <c r="K310" s="6">
         <v>33</v>
       </c>
       <c r="L310" s="7">
-        <v>793.65</v>
+        <v>462.96</v>
       </c>
       <c r="M310" s="8" t="s">
         <v>18</v>
@@ -15244,25 +15244,25 @@
         <v>100</v>
       </c>
       <c r="F311" s="11">
-        <v>2400</v>
+        <v>4100</v>
       </c>
       <c r="G311" s="11">
-        <v>2400</v>
+        <v>4100</v>
       </c>
       <c r="H311" s="11">
         <v>0</v>
       </c>
       <c r="I311" s="12">
-        <v>37</v>
+        <v>40</v>
       </c>
       <c r="J311" s="12">
-        <v>738</v>
+        <v>867</v>
       </c>
       <c r="K311" s="12">
-        <v>130</v>
+        <v>133</v>
       </c>
       <c r="L311" s="13">
-        <v>519.48</v>
+        <v>589.67</v>
       </c>
       <c r="M311" s="14" t="s">
         <v>18</v>
@@ -15288,10 +15288,10 @@
         <v>150</v>
       </c>
       <c r="F312" s="5">
-        <v>4200</v>
+        <v>4800</v>
       </c>
       <c r="G312" s="5">
-        <v>4200</v>
+        <v>4800</v>
       </c>
       <c r="H312" s="5">
         <v>0</v>
@@ -15300,13 +15300,13 @@
         <v>10</v>
       </c>
       <c r="J312" s="6">
-        <v>162</v>
+        <v>144</v>
       </c>
       <c r="K312" s="6">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="L312" s="7">
-        <v>1674.64</v>
+        <v>1788.38</v>
       </c>
       <c r="M312" s="8" t="s">
         <v>18</v>
@@ -15332,25 +15332,25 @@
         <v>200</v>
       </c>
       <c r="F313" s="11">
-        <v>5200</v>
+        <v>13600</v>
       </c>
       <c r="G313" s="11">
-        <v>5200</v>
+        <v>13600</v>
       </c>
       <c r="H313" s="11">
         <v>0</v>
       </c>
       <c r="I313" s="12">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="J313" s="12">
-        <v>151</v>
+        <v>177</v>
       </c>
       <c r="K313" s="12">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="L313" s="13">
-        <v>2047.24</v>
+        <v>3330.07</v>
       </c>
       <c r="M313" s="14" t="s">
         <v>18</v>
@@ -15376,25 +15376,25 @@
         <v>300</v>
       </c>
       <c r="F314" s="5">
-        <v>12300</v>
+        <v>7500</v>
       </c>
       <c r="G314" s="5">
-        <v>12300</v>
+        <v>7500</v>
       </c>
       <c r="H314" s="5">
         <v>0</v>
       </c>
       <c r="I314" s="6">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="J314" s="6">
-        <v>178</v>
+        <v>172</v>
       </c>
       <c r="K314" s="6">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="L314" s="7">
-        <v>3817.5</v>
+        <v>2912.62</v>
       </c>
       <c r="M314" s="8" t="s">
         <v>18</v>
@@ -15420,25 +15420,25 @@
         <v>400</v>
       </c>
       <c r="F315" s="11">
-        <v>25600</v>
+        <v>21600</v>
       </c>
       <c r="G315" s="11">
-        <v>25600</v>
+        <v>21600</v>
       </c>
       <c r="H315" s="11">
         <v>0</v>
       </c>
       <c r="I315" s="12">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="J315" s="12">
-        <v>195</v>
+        <v>206</v>
       </c>
       <c r="K315" s="12">
         <v>51</v>
       </c>
       <c r="L315" s="13">
-        <v>5373.64</v>
+        <v>5077.57</v>
       </c>
       <c r="M315" s="14" t="s">
         <v>18</v>
@@ -15464,25 +15464,25 @@
         <v>500</v>
       </c>
       <c r="F316" s="5">
-        <v>10500</v>
+        <v>25000</v>
       </c>
       <c r="G316" s="5">
-        <v>10500</v>
+        <v>25000</v>
       </c>
       <c r="H316" s="5">
         <v>0</v>
       </c>
       <c r="I316" s="6">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="J316" s="6">
-        <v>194</v>
+        <v>237</v>
       </c>
       <c r="K316" s="6">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="L316" s="7">
-        <v>3986.33</v>
+        <v>6024.1</v>
       </c>
       <c r="M316" s="8" t="s">
         <v>18</v>
@@ -15508,25 +15508,25 @@
         <v>10</v>
       </c>
       <c r="F317" s="11">
-        <v>280</v>
+        <v>680</v>
       </c>
       <c r="G317" s="11">
-        <v>280</v>
+        <v>680</v>
       </c>
       <c r="H317" s="11">
         <v>0</v>
       </c>
       <c r="I317" s="12">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="J317" s="12">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="K317" s="12">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="L317" s="13">
-        <v>119.66</v>
+        <v>199.76</v>
       </c>
       <c r="M317" s="14" t="s">
         <v>18</v>
@@ -15552,25 +15552,25 @@
         <v>25</v>
       </c>
       <c r="F318" s="5">
-        <v>1650</v>
+        <v>775</v>
       </c>
       <c r="G318" s="5">
-        <v>1650</v>
+        <v>775</v>
       </c>
       <c r="H318" s="5">
         <v>0</v>
       </c>
       <c r="I318" s="6">
-        <v>38</v>
+        <v>42</v>
       </c>
       <c r="J318" s="6">
-        <v>712</v>
+        <v>615</v>
       </c>
       <c r="K318" s="6">
-        <v>118</v>
+        <v>114</v>
       </c>
       <c r="L318" s="7">
-        <v>177.65</v>
+        <v>153.95</v>
       </c>
       <c r="M318" s="8" t="s">
         <v>18</v>
@@ -15596,10 +15596,10 @@
         <v>50</v>
       </c>
       <c r="F319" s="11">
-        <v>2100</v>
+        <v>1250</v>
       </c>
       <c r="G319" s="11">
-        <v>2100</v>
+        <v>1250</v>
       </c>
       <c r="H319" s="11">
         <v>0</v>
@@ -15608,13 +15608,13 @@
         <v>9</v>
       </c>
       <c r="J319" s="12">
-        <v>139</v>
+        <v>132</v>
       </c>
       <c r="K319" s="12">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="L319" s="13">
-        <v>738.4</v>
+        <v>537.63</v>
       </c>
       <c r="M319" s="14" t="s">
         <v>18</v>
@@ -15640,25 +15640,25 @@
         <v>100</v>
       </c>
       <c r="F320" s="5">
-        <v>6900</v>
+        <v>5900</v>
       </c>
       <c r="G320" s="5">
-        <v>6900</v>
+        <v>5900</v>
       </c>
       <c r="H320" s="5">
         <v>0</v>
       </c>
       <c r="I320" s="6">
-        <v>122</v>
+        <v>124</v>
       </c>
       <c r="J320" s="6">
-        <v>1822</v>
+        <v>2346</v>
       </c>
       <c r="K320" s="6">
-        <v>359</v>
+        <v>363</v>
       </c>
       <c r="L320" s="7">
-        <v>262.65</v>
+        <v>257.45</v>
       </c>
       <c r="M320" s="8" t="s">
         <v>18</v>
@@ -15684,25 +15684,25 @@
         <v>150</v>
       </c>
       <c r="F321" s="11">
-        <v>8850</v>
+        <v>9000</v>
       </c>
       <c r="G321" s="11">
-        <v>8850</v>
+        <v>9000</v>
       </c>
       <c r="H321" s="11">
         <v>0</v>
       </c>
       <c r="I321" s="12">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="J321" s="12">
-        <v>164</v>
+        <v>173</v>
       </c>
       <c r="K321" s="12">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="L321" s="13">
-        <v>2365.05</v>
+        <v>2459.02</v>
       </c>
       <c r="M321" s="14" t="s">
         <v>18</v>

--- a/testing/load/load_report.xlsx
+++ b/testing/load/load_report.xlsx
@@ -1648,25 +1648,25 @@
         <v>10</v>
       </c>
       <c r="F2" s="5">
-        <v>330</v>
+        <v>220</v>
       </c>
       <c r="G2" s="5">
-        <v>330</v>
+        <v>220</v>
       </c>
       <c r="H2" s="5">
         <v>0</v>
       </c>
       <c r="I2" s="6">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="J2" s="6">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="K2" s="6">
         <v>31</v>
       </c>
       <c r="L2" s="7">
-        <v>130.8</v>
+        <v>100.82</v>
       </c>
       <c r="M2" s="8" t="s">
         <v>18</v>
@@ -1692,25 +1692,25 @@
         <v>25</v>
       </c>
       <c r="F3" s="11">
-        <v>925</v>
+        <v>1000</v>
       </c>
       <c r="G3" s="11">
-        <v>925</v>
+        <v>1000</v>
       </c>
       <c r="H3" s="11">
         <v>0</v>
       </c>
       <c r="I3" s="12">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="J3" s="12">
-        <v>692</v>
+        <v>686</v>
       </c>
       <c r="K3" s="12">
-        <v>120</v>
+        <v>113</v>
       </c>
       <c r="L3" s="13">
-        <v>155.72</v>
+        <v>166.11</v>
       </c>
       <c r="M3" s="14" t="s">
         <v>18</v>
@@ -1736,25 +1736,25 @@
         <v>50</v>
       </c>
       <c r="F4" s="5">
-        <v>3300</v>
+        <v>1800</v>
       </c>
       <c r="G4" s="5">
-        <v>3300</v>
+        <v>1800</v>
       </c>
       <c r="H4" s="5">
         <v>0</v>
       </c>
       <c r="I4" s="6">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="J4" s="6">
-        <v>134</v>
+        <v>151</v>
       </c>
       <c r="K4" s="6">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="L4" s="7">
-        <v>930.63</v>
+        <v>697.67</v>
       </c>
       <c r="M4" s="8" t="s">
         <v>18</v>
@@ -1780,25 +1780,25 @@
         <v>100</v>
       </c>
       <c r="F5" s="11">
-        <v>2900</v>
+        <v>2300</v>
       </c>
       <c r="G5" s="11">
-        <v>2900</v>
+        <v>2300</v>
       </c>
       <c r="H5" s="11">
         <v>0</v>
       </c>
       <c r="I5" s="12">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="J5" s="12">
-        <v>161</v>
+        <v>115</v>
       </c>
       <c r="K5" s="12">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="L5" s="13">
-        <v>1166.53</v>
+        <v>997.83</v>
       </c>
       <c r="M5" s="14" t="s">
         <v>18</v>
@@ -1824,10 +1824,10 @@
         <v>150</v>
       </c>
       <c r="F6" s="5">
-        <v>6150</v>
+        <v>7050</v>
       </c>
       <c r="G6" s="5">
-        <v>6150</v>
+        <v>7050</v>
       </c>
       <c r="H6" s="5">
         <v>0</v>
@@ -1836,13 +1836,13 @@
         <v>9</v>
       </c>
       <c r="J6" s="6">
-        <v>119</v>
+        <v>173</v>
       </c>
       <c r="K6" s="6">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="L6" s="7">
-        <v>2066.53</v>
+        <v>2241.65</v>
       </c>
       <c r="M6" s="8" t="s">
         <v>18</v>
@@ -1868,25 +1868,25 @@
         <v>200</v>
       </c>
       <c r="F7" s="11">
-        <v>12800</v>
+        <v>4600</v>
       </c>
       <c r="G7" s="11">
-        <v>12800</v>
+        <v>4600</v>
       </c>
       <c r="H7" s="11">
         <v>0</v>
       </c>
       <c r="I7" s="12">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="J7" s="12">
-        <v>133</v>
+        <v>155</v>
       </c>
       <c r="K7" s="12">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="L7" s="13">
-        <v>3152.71</v>
+        <v>1882.93</v>
       </c>
       <c r="M7" s="14" t="s">
         <v>18</v>
@@ -1912,10 +1912,10 @@
         <v>300</v>
       </c>
       <c r="F8" s="5">
-        <v>16200</v>
+        <v>13500</v>
       </c>
       <c r="G8" s="5">
-        <v>16200</v>
+        <v>13500</v>
       </c>
       <c r="H8" s="5">
         <v>0</v>
@@ -1927,10 +1927,10 @@
         <v>148</v>
       </c>
       <c r="K8" s="6">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="L8" s="7">
-        <v>4238.62</v>
+        <v>3879.31</v>
       </c>
       <c r="M8" s="8" t="s">
         <v>18</v>
@@ -1956,25 +1956,25 @@
         <v>400</v>
       </c>
       <c r="F9" s="11">
-        <v>22000</v>
+        <v>24000</v>
       </c>
       <c r="G9" s="11">
-        <v>22000</v>
+        <v>24000</v>
       </c>
       <c r="H9" s="11">
         <v>0</v>
       </c>
       <c r="I9" s="12">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="J9" s="12">
-        <v>234</v>
+        <v>216</v>
       </c>
       <c r="K9" s="12">
-        <v>51</v>
+        <v>48</v>
       </c>
       <c r="L9" s="13">
-        <v>5110.34</v>
+        <v>5479.45</v>
       </c>
       <c r="M9" s="14" t="s">
         <v>18</v>
@@ -2000,25 +2000,25 @@
         <v>500</v>
       </c>
       <c r="F10" s="5">
-        <v>28500</v>
+        <v>30500</v>
       </c>
       <c r="G10" s="5">
-        <v>28500</v>
+        <v>30500</v>
       </c>
       <c r="H10" s="5">
         <v>0</v>
       </c>
       <c r="I10" s="6">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="J10" s="6">
-        <v>1075</v>
+        <v>1064</v>
       </c>
       <c r="K10" s="6">
-        <v>198</v>
+        <v>189</v>
       </c>
       <c r="L10" s="7">
-        <v>2229</v>
+        <v>2340.93</v>
       </c>
       <c r="M10" s="8" t="s">
         <v>18</v>
@@ -2044,10 +2044,10 @@
         <v>10</v>
       </c>
       <c r="F11" s="11">
-        <v>490</v>
+        <v>380</v>
       </c>
       <c r="G11" s="11">
-        <v>490</v>
+        <v>380</v>
       </c>
       <c r="H11" s="11">
         <v>0</v>
@@ -2056,13 +2056,13 @@
         <v>9</v>
       </c>
       <c r="J11" s="12">
-        <v>108</v>
+        <v>144</v>
       </c>
       <c r="K11" s="12">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="L11" s="13">
-        <v>162.31</v>
+        <v>143.94</v>
       </c>
       <c r="M11" s="14" t="s">
         <v>18</v>
@@ -2088,25 +2088,25 @@
         <v>25</v>
       </c>
       <c r="F12" s="5">
-        <v>850</v>
+        <v>800</v>
       </c>
       <c r="G12" s="5">
-        <v>850</v>
+        <v>800</v>
       </c>
       <c r="H12" s="5">
         <v>0</v>
       </c>
       <c r="I12" s="6">
-        <v>109</v>
+        <v>124</v>
       </c>
       <c r="J12" s="6">
-        <v>1658</v>
+        <v>1680</v>
       </c>
       <c r="K12" s="6">
-        <v>344</v>
+        <v>343</v>
       </c>
       <c r="L12" s="7">
-        <v>64.41</v>
+        <v>64.12</v>
       </c>
       <c r="M12" s="8" t="s">
         <v>18</v>
@@ -2132,10 +2132,10 @@
         <v>50</v>
       </c>
       <c r="F13" s="11">
-        <v>2300</v>
+        <v>2850</v>
       </c>
       <c r="G13" s="11">
-        <v>2300</v>
+        <v>2850</v>
       </c>
       <c r="H13" s="11">
         <v>0</v>
@@ -2144,13 +2144,13 @@
         <v>10</v>
       </c>
       <c r="J13" s="12">
-        <v>137</v>
+        <v>153</v>
       </c>
       <c r="K13" s="12">
         <v>32</v>
       </c>
       <c r="L13" s="13">
-        <v>773.89</v>
+        <v>857.4</v>
       </c>
       <c r="M13" s="14" t="s">
         <v>18</v>
@@ -2176,10 +2176,10 @@
         <v>100</v>
       </c>
       <c r="F14" s="5">
-        <v>2800</v>
+        <v>2300</v>
       </c>
       <c r="G14" s="5">
-        <v>2800</v>
+        <v>2300</v>
       </c>
       <c r="H14" s="5">
         <v>0</v>
@@ -2188,13 +2188,13 @@
         <v>36</v>
       </c>
       <c r="J14" s="6">
-        <v>879</v>
+        <v>730</v>
       </c>
       <c r="K14" s="6">
-        <v>121</v>
+        <v>128</v>
       </c>
       <c r="L14" s="7">
-        <v>572.83</v>
+        <v>517.55</v>
       </c>
       <c r="M14" s="8" t="s">
         <v>18</v>
@@ -2220,25 +2220,25 @@
         <v>150</v>
       </c>
       <c r="F15" s="11">
-        <v>8250</v>
+        <v>6000</v>
       </c>
       <c r="G15" s="11">
-        <v>8250</v>
+        <v>6000</v>
       </c>
       <c r="H15" s="11">
         <v>0</v>
       </c>
       <c r="I15" s="12">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="J15" s="12">
-        <v>138</v>
+        <v>157</v>
       </c>
       <c r="K15" s="12">
         <v>36</v>
       </c>
       <c r="L15" s="13">
-        <v>2370.69</v>
+        <v>2040.82</v>
       </c>
       <c r="M15" s="14" t="s">
         <v>18</v>
@@ -2264,10 +2264,10 @@
         <v>200</v>
       </c>
       <c r="F16" s="5">
-        <v>5000</v>
+        <v>12200</v>
       </c>
       <c r="G16" s="5">
-        <v>5000</v>
+        <v>12200</v>
       </c>
       <c r="H16" s="5">
         <v>0</v>
@@ -2276,13 +2276,13 @@
         <v>10</v>
       </c>
       <c r="J16" s="6">
-        <v>142</v>
+        <v>128</v>
       </c>
       <c r="K16" s="6">
-        <v>41</v>
+        <v>38</v>
       </c>
       <c r="L16" s="7">
-        <v>1980.2</v>
+        <v>3195.39</v>
       </c>
       <c r="M16" s="8" t="s">
         <v>18</v>
@@ -2308,25 +2308,25 @@
         <v>300</v>
       </c>
       <c r="F17" s="11">
-        <v>9000</v>
+        <v>7800</v>
       </c>
       <c r="G17" s="11">
-        <v>9000</v>
+        <v>7800</v>
       </c>
       <c r="H17" s="11">
         <v>0</v>
       </c>
       <c r="I17" s="12">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="J17" s="12">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="K17" s="12">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="L17" s="13">
-        <v>3191.49</v>
+        <v>2979.37</v>
       </c>
       <c r="M17" s="14" t="s">
         <v>18</v>
@@ -2352,25 +2352,25 @@
         <v>400</v>
       </c>
       <c r="F18" s="5">
-        <v>23600</v>
+        <v>10400</v>
       </c>
       <c r="G18" s="5">
-        <v>23600</v>
+        <v>10400</v>
       </c>
       <c r="H18" s="5">
         <v>0</v>
       </c>
       <c r="I18" s="6">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="J18" s="6">
-        <v>162</v>
+        <v>171</v>
       </c>
       <c r="K18" s="6">
         <v>50</v>
       </c>
       <c r="L18" s="7">
-        <v>5303.37</v>
+        <v>3714.29</v>
       </c>
       <c r="M18" s="8" t="s">
         <v>18</v>
@@ -2396,25 +2396,25 @@
         <v>500</v>
       </c>
       <c r="F19" s="11">
-        <v>22500</v>
+        <v>20000</v>
       </c>
       <c r="G19" s="11">
-        <v>22500</v>
+        <v>20000</v>
       </c>
       <c r="H19" s="11">
         <v>0</v>
       </c>
       <c r="I19" s="12">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="J19" s="12">
-        <v>181</v>
+        <v>221</v>
       </c>
       <c r="K19" s="12">
-        <v>53</v>
+        <v>56</v>
       </c>
       <c r="L19" s="13">
-        <v>5791.51</v>
+        <v>5347.59</v>
       </c>
       <c r="M19" s="14" t="s">
         <v>18</v>
@@ -2440,25 +2440,25 @@
         <v>10</v>
       </c>
       <c r="F20" s="5">
-        <v>490</v>
+        <v>550</v>
       </c>
       <c r="G20" s="5">
-        <v>490</v>
+        <v>550</v>
       </c>
       <c r="H20" s="5">
         <v>0</v>
       </c>
       <c r="I20" s="6">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="J20" s="6">
-        <v>145</v>
+        <v>114</v>
       </c>
       <c r="K20" s="6">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="L20" s="7">
-        <v>162.31</v>
+        <v>174.6</v>
       </c>
       <c r="M20" s="8" t="s">
         <v>18</v>
@@ -2484,25 +2484,25 @@
         <v>25</v>
       </c>
       <c r="F21" s="11">
-        <v>725</v>
+        <v>1450</v>
       </c>
       <c r="G21" s="11">
-        <v>725</v>
+        <v>1450</v>
       </c>
       <c r="H21" s="11">
         <v>0</v>
       </c>
       <c r="I21" s="12">
-        <v>43</v>
+        <v>40</v>
       </c>
       <c r="J21" s="12">
-        <v>700</v>
+        <v>590</v>
       </c>
       <c r="K21" s="12">
-        <v>111</v>
+        <v>116</v>
       </c>
       <c r="L21" s="13">
-        <v>153.63</v>
+        <v>176.23</v>
       </c>
       <c r="M21" s="14" t="s">
         <v>18</v>
@@ -2528,10 +2528,10 @@
         <v>50</v>
       </c>
       <c r="F22" s="5">
-        <v>1750</v>
+        <v>2000</v>
       </c>
       <c r="G22" s="5">
-        <v>1750</v>
+        <v>2000</v>
       </c>
       <c r="H22" s="5">
         <v>0</v>
@@ -2540,13 +2540,13 @@
         <v>9</v>
       </c>
       <c r="J22" s="6">
-        <v>128</v>
+        <v>109</v>
       </c>
       <c r="K22" s="6">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="L22" s="7">
-        <v>686.27</v>
+        <v>719.42</v>
       </c>
       <c r="M22" s="8" t="s">
         <v>18</v>
@@ -2572,25 +2572,25 @@
         <v>100</v>
       </c>
       <c r="F23" s="11">
-        <v>4900</v>
+        <v>6400</v>
       </c>
       <c r="G23" s="11">
-        <v>4900</v>
+        <v>6400</v>
       </c>
       <c r="H23" s="11">
         <v>0</v>
       </c>
       <c r="I23" s="12">
-        <v>122</v>
+        <v>118</v>
       </c>
       <c r="J23" s="12">
-        <v>2021</v>
+        <v>2069</v>
       </c>
       <c r="K23" s="12">
-        <v>387</v>
+        <v>374</v>
       </c>
       <c r="L23" s="13">
-        <v>239.46</v>
+        <v>251.61</v>
       </c>
       <c r="M23" s="14" t="s">
         <v>18</v>
@@ -2616,10 +2616,10 @@
         <v>150</v>
       </c>
       <c r="F24" s="5">
-        <v>3600</v>
+        <v>9150</v>
       </c>
       <c r="G24" s="5">
-        <v>3600</v>
+        <v>9150</v>
       </c>
       <c r="H24" s="5">
         <v>0</v>
@@ -2628,13 +2628,13 @@
         <v>10</v>
       </c>
       <c r="J24" s="6">
-        <v>165</v>
+        <v>134</v>
       </c>
       <c r="K24" s="6">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="L24" s="7">
-        <v>1522.84</v>
+        <v>2435.45</v>
       </c>
       <c r="M24" s="8" t="s">
         <v>18</v>
@@ -2660,25 +2660,25 @@
         <v>200</v>
       </c>
       <c r="F25" s="11">
-        <v>13600</v>
+        <v>11800</v>
       </c>
       <c r="G25" s="11">
-        <v>13600</v>
+        <v>11800</v>
       </c>
       <c r="H25" s="11">
         <v>0</v>
       </c>
       <c r="I25" s="12">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="J25" s="12">
-        <v>702</v>
+        <v>839</v>
       </c>
       <c r="K25" s="12">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="L25" s="13">
-        <v>1219.07</v>
+        <v>1187.48</v>
       </c>
       <c r="M25" s="14" t="s">
         <v>18</v>
@@ -2704,10 +2704,10 @@
         <v>300</v>
       </c>
       <c r="F26" s="5">
-        <v>17400</v>
+        <v>13200</v>
       </c>
       <c r="G26" s="5">
-        <v>17400</v>
+        <v>13200</v>
       </c>
       <c r="H26" s="5">
         <v>0</v>
@@ -2716,13 +2716,13 @@
         <v>9</v>
       </c>
       <c r="J26" s="6">
-        <v>151</v>
+        <v>169</v>
       </c>
       <c r="K26" s="6">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="L26" s="7">
-        <v>4294.18</v>
+        <v>3891.51</v>
       </c>
       <c r="M26" s="8" t="s">
         <v>18</v>
@@ -2748,25 +2748,25 @@
         <v>400</v>
       </c>
       <c r="F27" s="11">
-        <v>24000</v>
+        <v>13600</v>
       </c>
       <c r="G27" s="11">
-        <v>24000</v>
+        <v>13600</v>
       </c>
       <c r="H27" s="11">
         <v>0</v>
       </c>
       <c r="I27" s="12">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="J27" s="12">
-        <v>158</v>
+        <v>224</v>
       </c>
       <c r="K27" s="12">
         <v>48</v>
       </c>
       <c r="L27" s="13">
-        <v>5479.45</v>
+        <v>4342.27</v>
       </c>
       <c r="M27" s="14" t="s">
         <v>18</v>
@@ -2792,10 +2792,10 @@
         <v>500</v>
       </c>
       <c r="F28" s="5">
-        <v>13500</v>
+        <v>31000</v>
       </c>
       <c r="G28" s="5">
-        <v>13500</v>
+        <v>31000</v>
       </c>
       <c r="H28" s="5">
         <v>0</v>
@@ -2804,13 +2804,13 @@
         <v>10</v>
       </c>
       <c r="J28" s="6">
-        <v>232</v>
+        <v>241</v>
       </c>
       <c r="K28" s="6">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="L28" s="7">
-        <v>4648.76</v>
+        <v>6394.39</v>
       </c>
       <c r="M28" s="8" t="s">
         <v>18</v>
@@ -2836,10 +2836,10 @@
         <v>10</v>
       </c>
       <c r="F29" s="11">
-        <v>380</v>
+        <v>590</v>
       </c>
       <c r="G29" s="11">
-        <v>380</v>
+        <v>590</v>
       </c>
       <c r="H29" s="11">
         <v>0</v>
@@ -2848,13 +2848,13 @@
         <v>9</v>
       </c>
       <c r="J29" s="12">
-        <v>144</v>
+        <v>112</v>
       </c>
       <c r="K29" s="12">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="L29" s="13">
-        <v>141.9</v>
+        <v>180.43</v>
       </c>
       <c r="M29" s="14" t="s">
         <v>18</v>
@@ -2880,25 +2880,25 @@
         <v>25</v>
       </c>
       <c r="F30" s="5">
-        <v>625</v>
+        <v>550</v>
       </c>
       <c r="G30" s="5">
-        <v>625</v>
+        <v>550</v>
       </c>
       <c r="H30" s="5">
         <v>0</v>
       </c>
       <c r="I30" s="6">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="J30" s="6">
-        <v>116</v>
+        <v>108</v>
       </c>
       <c r="K30" s="6">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="L30" s="7">
-        <v>271.74</v>
+        <v>252.06</v>
       </c>
       <c r="M30" s="8" t="s">
         <v>18</v>
@@ -2924,25 +2924,25 @@
         <v>50</v>
       </c>
       <c r="F31" s="11">
-        <v>3350</v>
+        <v>3300</v>
       </c>
       <c r="G31" s="11">
-        <v>3350</v>
+        <v>3300</v>
       </c>
       <c r="H31" s="11">
         <v>0</v>
       </c>
       <c r="I31" s="12">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="J31" s="12">
-        <v>143</v>
+        <v>131</v>
       </c>
       <c r="K31" s="12">
         <v>32</v>
       </c>
       <c r="L31" s="13">
-        <v>919.32</v>
+        <v>913.62</v>
       </c>
       <c r="M31" s="14" t="s">
         <v>18</v>
@@ -2968,25 +2968,25 @@
         <v>100</v>
       </c>
       <c r="F32" s="5">
-        <v>4600</v>
+        <v>2900</v>
       </c>
       <c r="G32" s="5">
-        <v>4600</v>
+        <v>2900</v>
       </c>
       <c r="H32" s="5">
         <v>0</v>
       </c>
       <c r="I32" s="6">
-        <v>37</v>
+        <v>41</v>
       </c>
       <c r="J32" s="6">
-        <v>773</v>
+        <v>846</v>
       </c>
       <c r="K32" s="6">
-        <v>131</v>
+        <v>126</v>
       </c>
       <c r="L32" s="7">
-        <v>611.21</v>
+        <v>562.67</v>
       </c>
       <c r="M32" s="8" t="s">
         <v>18</v>
@@ -3012,10 +3012,10 @@
         <v>150</v>
       </c>
       <c r="F33" s="11">
-        <v>5250</v>
+        <v>9300</v>
       </c>
       <c r="G33" s="11">
-        <v>5250</v>
+        <v>9300</v>
       </c>
       <c r="H33" s="11">
         <v>0</v>
@@ -3024,13 +3024,13 @@
         <v>9</v>
       </c>
       <c r="J33" s="12">
-        <v>155</v>
+        <v>152</v>
       </c>
       <c r="K33" s="12">
         <v>38</v>
       </c>
       <c r="L33" s="13">
-        <v>1855.12</v>
+        <v>2411.83</v>
       </c>
       <c r="M33" s="14" t="s">
         <v>18</v>
@@ -3056,25 +3056,25 @@
         <v>200</v>
       </c>
       <c r="F34" s="5">
-        <v>5800</v>
+        <v>10200</v>
       </c>
       <c r="G34" s="5">
-        <v>5800</v>
+        <v>10200</v>
       </c>
       <c r="H34" s="5">
         <v>0</v>
       </c>
       <c r="I34" s="6">
-        <v>119</v>
+        <v>116</v>
       </c>
       <c r="J34" s="6">
-        <v>1933</v>
+        <v>2768</v>
       </c>
       <c r="K34" s="6">
-        <v>401</v>
+        <v>425</v>
       </c>
       <c r="L34" s="7">
-        <v>441.77</v>
+        <v>440.13</v>
       </c>
       <c r="M34" s="8" t="s">
         <v>18</v>
@@ -3100,10 +3100,10 @@
         <v>300</v>
       </c>
       <c r="F35" s="11">
-        <v>15300</v>
+        <v>6000</v>
       </c>
       <c r="G35" s="11">
-        <v>15300</v>
+        <v>6000</v>
       </c>
       <c r="H35" s="11">
         <v>0</v>
@@ -3112,13 +3112,13 @@
         <v>10</v>
       </c>
       <c r="J35" s="12">
-        <v>186</v>
+        <v>153</v>
       </c>
       <c r="K35" s="12">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="L35" s="13">
-        <v>3978.16</v>
+        <v>2521.01</v>
       </c>
       <c r="M35" s="14" t="s">
         <v>18</v>
@@ -3144,25 +3144,25 @@
         <v>400</v>
       </c>
       <c r="F36" s="5">
-        <v>12400</v>
+        <v>23200</v>
       </c>
       <c r="G36" s="5">
-        <v>12400</v>
+        <v>23200</v>
       </c>
       <c r="H36" s="5">
         <v>0</v>
       </c>
       <c r="I36" s="6">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="J36" s="6">
-        <v>1145</v>
+        <v>984</v>
       </c>
       <c r="K36" s="6">
-        <v>175</v>
+        <v>178</v>
       </c>
       <c r="L36" s="7">
-        <v>1790.61</v>
+        <v>1962.11</v>
       </c>
       <c r="M36" s="8" t="s">
         <v>18</v>
@@ -3188,25 +3188,25 @@
         <v>500</v>
       </c>
       <c r="F37" s="11">
-        <v>34000</v>
+        <v>16500</v>
       </c>
       <c r="G37" s="11">
-        <v>34000</v>
+        <v>16500</v>
       </c>
       <c r="H37" s="11">
         <v>0</v>
       </c>
       <c r="I37" s="12">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="J37" s="12">
-        <v>207</v>
+        <v>178</v>
       </c>
       <c r="K37" s="12">
-        <v>52</v>
+        <v>55</v>
       </c>
       <c r="L37" s="13">
-        <v>6751.39</v>
+        <v>4977.38</v>
       </c>
       <c r="M37" s="14" t="s">
         <v>18</v>
@@ -3232,10 +3232,10 @@
         <v>10</v>
       </c>
       <c r="F38" s="5">
-        <v>680</v>
+        <v>470</v>
       </c>
       <c r="G38" s="5">
-        <v>680</v>
+        <v>470</v>
       </c>
       <c r="H38" s="5">
         <v>0</v>
@@ -3244,13 +3244,13 @@
         <v>10</v>
       </c>
       <c r="J38" s="6">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="K38" s="6">
         <v>31</v>
       </c>
       <c r="L38" s="7">
-        <v>188.47</v>
+        <v>158.94</v>
       </c>
       <c r="M38" s="8" t="s">
         <v>18</v>
@@ -3276,25 +3276,25 @@
         <v>25</v>
       </c>
       <c r="F39" s="11">
-        <v>1450</v>
+        <v>650</v>
       </c>
       <c r="G39" s="11">
-        <v>1450</v>
+        <v>650</v>
       </c>
       <c r="H39" s="11">
         <v>0</v>
       </c>
       <c r="I39" s="12">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="J39" s="12">
-        <v>120</v>
+        <v>110</v>
       </c>
       <c r="K39" s="12">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="L39" s="13">
-        <v>447.53</v>
+        <v>278.73</v>
       </c>
       <c r="M39" s="14" t="s">
         <v>18</v>
@@ -3320,25 +3320,25 @@
         <v>50</v>
       </c>
       <c r="F40" s="5">
-        <v>1400</v>
+        <v>2750</v>
       </c>
       <c r="G40" s="5">
-        <v>1400</v>
+        <v>2750</v>
       </c>
       <c r="H40" s="5">
         <v>0</v>
       </c>
       <c r="I40" s="6">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="J40" s="6">
-        <v>147</v>
+        <v>111</v>
       </c>
       <c r="K40" s="6">
         <v>31</v>
       </c>
       <c r="L40" s="7">
-        <v>591.22</v>
+        <v>858.03</v>
       </c>
       <c r="M40" s="8" t="s">
         <v>18</v>
@@ -3364,10 +3364,10 @@
         <v>100</v>
       </c>
       <c r="F41" s="11">
-        <v>2600</v>
+        <v>4300</v>
       </c>
       <c r="G41" s="11">
-        <v>2600</v>
+        <v>4300</v>
       </c>
       <c r="H41" s="11">
         <v>0</v>
@@ -3376,13 +3376,13 @@
         <v>9</v>
       </c>
       <c r="J41" s="12">
-        <v>114</v>
+        <v>141</v>
       </c>
       <c r="K41" s="12">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="L41" s="13">
-        <v>1090.6</v>
+        <v>1473.11</v>
       </c>
       <c r="M41" s="14" t="s">
         <v>18</v>
@@ -3408,10 +3408,10 @@
         <v>150</v>
       </c>
       <c r="F42" s="5">
-        <v>4500</v>
+        <v>8550</v>
       </c>
       <c r="G42" s="5">
-        <v>4500</v>
+        <v>8550</v>
       </c>
       <c r="H42" s="5">
         <v>0</v>
@@ -3420,13 +3420,13 @@
         <v>9</v>
       </c>
       <c r="J42" s="6">
-        <v>147</v>
+        <v>139</v>
       </c>
       <c r="K42" s="6">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="L42" s="7">
-        <v>1744.19</v>
+        <v>2446.35</v>
       </c>
       <c r="M42" s="8" t="s">
         <v>18</v>
@@ -3452,25 +3452,25 @@
         <v>200</v>
       </c>
       <c r="F43" s="11">
-        <v>11200</v>
+        <v>4800</v>
       </c>
       <c r="G43" s="11">
-        <v>11200</v>
+        <v>4800</v>
       </c>
       <c r="H43" s="11">
         <v>0</v>
       </c>
       <c r="I43" s="12">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="J43" s="12">
-        <v>899</v>
+        <v>888</v>
       </c>
       <c r="K43" s="12">
-        <v>138</v>
+        <v>152</v>
       </c>
       <c r="L43" s="13">
-        <v>1213.7</v>
+        <v>932.4</v>
       </c>
       <c r="M43" s="14" t="s">
         <v>18</v>
@@ -3496,10 +3496,10 @@
         <v>300</v>
       </c>
       <c r="F44" s="5">
-        <v>15000</v>
+        <v>15300</v>
       </c>
       <c r="G44" s="5">
-        <v>15000</v>
+        <v>15300</v>
       </c>
       <c r="H44" s="5">
         <v>0</v>
@@ -3508,13 +3508,13 @@
         <v>10</v>
       </c>
       <c r="J44" s="6">
-        <v>183</v>
+        <v>196</v>
       </c>
       <c r="K44" s="6">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="L44" s="7">
-        <v>4054.05</v>
+        <v>4142.97</v>
       </c>
       <c r="M44" s="8" t="s">
         <v>18</v>
@@ -3540,25 +3540,25 @@
         <v>400</v>
       </c>
       <c r="F45" s="11">
-        <v>26000</v>
+        <v>24400</v>
       </c>
       <c r="G45" s="11">
-        <v>26000</v>
+        <v>24400</v>
       </c>
       <c r="H45" s="11">
         <v>0</v>
       </c>
       <c r="I45" s="12">
-        <v>121</v>
+        <v>128</v>
       </c>
       <c r="J45" s="12">
-        <v>3301</v>
+        <v>3037</v>
       </c>
       <c r="K45" s="12">
-        <v>499</v>
+        <v>507</v>
       </c>
       <c r="L45" s="13">
-        <v>766.17</v>
+        <v>752.46</v>
       </c>
       <c r="M45" s="14" t="s">
         <v>18</v>
@@ -3584,10 +3584,10 @@
         <v>500</v>
       </c>
       <c r="F46" s="5">
-        <v>24000</v>
+        <v>28500</v>
       </c>
       <c r="G46" s="5">
-        <v>24000</v>
+        <v>28500</v>
       </c>
       <c r="H46" s="5">
         <v>0</v>
@@ -3596,13 +3596,13 @@
         <v>10</v>
       </c>
       <c r="J46" s="6">
-        <v>239</v>
+        <v>233</v>
       </c>
       <c r="K46" s="6">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="L46" s="7">
-        <v>5865.1</v>
+        <v>6303.92</v>
       </c>
       <c r="M46" s="8" t="s">
         <v>18</v>
@@ -3628,25 +3628,25 @@
         <v>10</v>
       </c>
       <c r="F47" s="11">
-        <v>680</v>
+        <v>230</v>
       </c>
       <c r="G47" s="11">
-        <v>680</v>
+        <v>230</v>
       </c>
       <c r="H47" s="11">
         <v>0</v>
       </c>
       <c r="I47" s="12">
-        <v>38</v>
+        <v>43</v>
       </c>
       <c r="J47" s="12">
-        <v>578</v>
+        <v>556</v>
       </c>
       <c r="K47" s="12">
-        <v>115</v>
+        <v>110</v>
       </c>
       <c r="L47" s="13">
-        <v>72.96</v>
+        <v>57.07</v>
       </c>
       <c r="M47" s="14" t="s">
         <v>18</v>
@@ -3672,25 +3672,25 @@
         <v>25</v>
       </c>
       <c r="F48" s="5">
-        <v>950</v>
+        <v>1625</v>
       </c>
       <c r="G48" s="5">
-        <v>950</v>
+        <v>1625</v>
       </c>
       <c r="H48" s="5">
         <v>0</v>
       </c>
       <c r="I48" s="6">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="J48" s="6">
-        <v>117</v>
+        <v>125</v>
       </c>
       <c r="K48" s="6">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="L48" s="7">
-        <v>359.85</v>
+        <v>480.06</v>
       </c>
       <c r="M48" s="8" t="s">
         <v>18</v>
@@ -3716,10 +3716,10 @@
         <v>50</v>
       </c>
       <c r="F49" s="11">
-        <v>2300</v>
+        <v>2000</v>
       </c>
       <c r="G49" s="11">
-        <v>2300</v>
+        <v>2000</v>
       </c>
       <c r="H49" s="11">
         <v>0</v>
@@ -3728,13 +3728,13 @@
         <v>9</v>
       </c>
       <c r="J49" s="12">
-        <v>118</v>
+        <v>140</v>
       </c>
       <c r="K49" s="12">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="L49" s="13">
-        <v>786.06</v>
+        <v>740.74</v>
       </c>
       <c r="M49" s="14" t="s">
         <v>18</v>
@@ -3760,25 +3760,25 @@
         <v>100</v>
       </c>
       <c r="F50" s="5">
-        <v>3200</v>
+        <v>3300</v>
       </c>
       <c r="G50" s="5">
-        <v>3200</v>
+        <v>3300</v>
       </c>
       <c r="H50" s="5">
         <v>0</v>
       </c>
       <c r="I50" s="6">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="J50" s="6">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="K50" s="6">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="L50" s="7">
-        <v>1251.96</v>
+        <v>1258.58</v>
       </c>
       <c r="M50" s="8" t="s">
         <v>18</v>
@@ -3804,10 +3804,10 @@
         <v>150</v>
       </c>
       <c r="F51" s="11">
-        <v>8550</v>
+        <v>9450</v>
       </c>
       <c r="G51" s="11">
-        <v>8550</v>
+        <v>9450</v>
       </c>
       <c r="H51" s="11">
         <v>0</v>
@@ -3816,13 +3816,13 @@
         <v>9</v>
       </c>
       <c r="J51" s="12">
-        <v>119</v>
+        <v>137</v>
       </c>
       <c r="K51" s="12">
         <v>38</v>
       </c>
       <c r="L51" s="13">
-        <v>2332.24</v>
+        <v>2426.81</v>
       </c>
       <c r="M51" s="14" t="s">
         <v>18</v>
@@ -3848,25 +3848,25 @@
         <v>200</v>
       </c>
       <c r="F52" s="5">
-        <v>13000</v>
+        <v>13200</v>
       </c>
       <c r="G52" s="5">
-        <v>13000</v>
+        <v>13200</v>
       </c>
       <c r="H52" s="5">
         <v>0</v>
       </c>
       <c r="I52" s="6">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="J52" s="6">
-        <v>168</v>
+        <v>163</v>
       </c>
       <c r="K52" s="6">
-        <v>40</v>
+        <v>37</v>
       </c>
       <c r="L52" s="7">
-        <v>3170.73</v>
+        <v>3348.55</v>
       </c>
       <c r="M52" s="8" t="s">
         <v>18</v>
@@ -3892,25 +3892,25 @@
         <v>300</v>
       </c>
       <c r="F53" s="11">
-        <v>10800</v>
+        <v>14400</v>
       </c>
       <c r="G53" s="11">
-        <v>10800</v>
+        <v>14400</v>
       </c>
       <c r="H53" s="11">
         <v>0</v>
       </c>
       <c r="I53" s="12">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="J53" s="12">
-        <v>204</v>
+        <v>142</v>
       </c>
       <c r="K53" s="12">
-        <v>46</v>
+        <v>42</v>
       </c>
       <c r="L53" s="13">
-        <v>3422.05</v>
+        <v>4095.56</v>
       </c>
       <c r="M53" s="14" t="s">
         <v>18</v>
@@ -3936,25 +3936,25 @@
         <v>400</v>
       </c>
       <c r="F54" s="5">
-        <v>11200</v>
+        <v>27200</v>
       </c>
       <c r="G54" s="5">
-        <v>11200</v>
+        <v>27200</v>
       </c>
       <c r="H54" s="5">
         <v>0</v>
       </c>
       <c r="I54" s="6">
-        <v>43</v>
+        <v>36</v>
       </c>
       <c r="J54" s="6">
-        <v>953</v>
+        <v>1065</v>
       </c>
       <c r="K54" s="6">
-        <v>181</v>
+        <v>187</v>
       </c>
       <c r="L54" s="7">
-        <v>1705.24</v>
+        <v>1913.34</v>
       </c>
       <c r="M54" s="8" t="s">
         <v>18</v>
@@ -3980,10 +3980,10 @@
         <v>500</v>
       </c>
       <c r="F55" s="11">
-        <v>27500</v>
+        <v>26000</v>
       </c>
       <c r="G55" s="11">
-        <v>27500</v>
+        <v>26000</v>
       </c>
       <c r="H55" s="11">
         <v>0</v>
@@ -3992,13 +3992,13 @@
         <v>10</v>
       </c>
       <c r="J55" s="12">
-        <v>233</v>
+        <v>189</v>
       </c>
       <c r="K55" s="12">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="L55" s="13">
-        <v>6387.92</v>
+        <v>6109.02</v>
       </c>
       <c r="M55" s="14" t="s">
         <v>18</v>
@@ -4024,25 +4024,25 @@
         <v>10</v>
       </c>
       <c r="F56" s="5">
-        <v>510</v>
+        <v>230</v>
       </c>
       <c r="G56" s="5">
-        <v>510</v>
+        <v>230</v>
       </c>
       <c r="H56" s="5">
         <v>0</v>
       </c>
       <c r="I56" s="6">
-        <v>111</v>
+        <v>122</v>
       </c>
       <c r="J56" s="6">
-        <v>2016</v>
+        <v>1812</v>
       </c>
       <c r="K56" s="6">
-        <v>311</v>
+        <v>325</v>
       </c>
       <c r="L56" s="7">
-        <v>29.38</v>
+        <v>25.63</v>
       </c>
       <c r="M56" s="8" t="s">
         <v>18</v>
@@ -4068,10 +4068,10 @@
         <v>25</v>
       </c>
       <c r="F57" s="11">
-        <v>1050</v>
+        <v>1475</v>
       </c>
       <c r="G57" s="11">
-        <v>1050</v>
+        <v>1475</v>
       </c>
       <c r="H57" s="11">
         <v>0</v>
@@ -4080,13 +4080,13 @@
         <v>10</v>
       </c>
       <c r="J57" s="12">
-        <v>148</v>
+        <v>125</v>
       </c>
       <c r="K57" s="12">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="L57" s="13">
-        <v>374.73</v>
+        <v>435.36</v>
       </c>
       <c r="M57" s="14" t="s">
         <v>18</v>
@@ -4112,25 +4112,25 @@
         <v>50</v>
       </c>
       <c r="F58" s="5">
-        <v>1400</v>
+        <v>1750</v>
       </c>
       <c r="G58" s="5">
-        <v>1400</v>
+        <v>1750</v>
       </c>
       <c r="H58" s="5">
         <v>0</v>
       </c>
       <c r="I58" s="6">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="J58" s="6">
-        <v>767</v>
+        <v>705</v>
       </c>
       <c r="K58" s="6">
-        <v>120</v>
+        <v>116</v>
       </c>
       <c r="L58" s="7">
-        <v>288.07</v>
+        <v>314.75</v>
       </c>
       <c r="M58" s="8" t="s">
         <v>18</v>
@@ -4156,10 +4156,10 @@
         <v>100</v>
       </c>
       <c r="F59" s="11">
-        <v>5400</v>
+        <v>4900</v>
       </c>
       <c r="G59" s="11">
-        <v>5400</v>
+        <v>4900</v>
       </c>
       <c r="H59" s="11">
         <v>0</v>
@@ -4168,13 +4168,13 @@
         <v>9</v>
       </c>
       <c r="J59" s="12">
-        <v>142</v>
+        <v>163</v>
       </c>
       <c r="K59" s="12">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="L59" s="13">
-        <v>1567.94</v>
+        <v>1524.11</v>
       </c>
       <c r="M59" s="14" t="s">
         <v>18</v>
@@ -4200,25 +4200,25 @@
         <v>150</v>
       </c>
       <c r="F60" s="5">
-        <v>3150</v>
+        <v>4950</v>
       </c>
       <c r="G60" s="5">
-        <v>3150</v>
+        <v>4950</v>
       </c>
       <c r="H60" s="5">
         <v>0</v>
       </c>
       <c r="I60" s="6">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="J60" s="6">
-        <v>127</v>
+        <v>149</v>
       </c>
       <c r="K60" s="6">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="L60" s="7">
-        <v>1383.4</v>
+        <v>1864.41</v>
       </c>
       <c r="M60" s="8" t="s">
         <v>18</v>
@@ -4244,10 +4244,10 @@
         <v>200</v>
       </c>
       <c r="F61" s="11">
-        <v>9600</v>
+        <v>9400</v>
       </c>
       <c r="G61" s="11">
-        <v>9600</v>
+        <v>9400</v>
       </c>
       <c r="H61" s="11">
         <v>0</v>
@@ -4256,13 +4256,13 @@
         <v>9</v>
       </c>
       <c r="J61" s="12">
-        <v>164</v>
+        <v>127</v>
       </c>
       <c r="K61" s="12">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="L61" s="13">
-        <v>2846.98</v>
+        <v>2860.62</v>
       </c>
       <c r="M61" s="14" t="s">
         <v>18</v>
@@ -4288,10 +4288,10 @@
         <v>300</v>
       </c>
       <c r="F62" s="5">
-        <v>15000</v>
+        <v>20100</v>
       </c>
       <c r="G62" s="5">
-        <v>15000</v>
+        <v>20100</v>
       </c>
       <c r="H62" s="5">
         <v>0</v>
@@ -4300,13 +4300,13 @@
         <v>10</v>
       </c>
       <c r="J62" s="6">
-        <v>161</v>
+        <v>196</v>
       </c>
       <c r="K62" s="6">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="L62" s="7">
-        <v>3947.37</v>
+        <v>4451.83</v>
       </c>
       <c r="M62" s="8" t="s">
         <v>18</v>
@@ -4332,10 +4332,10 @@
         <v>400</v>
       </c>
       <c r="F63" s="11">
-        <v>24400</v>
+        <v>27600</v>
       </c>
       <c r="G63" s="11">
-        <v>24400</v>
+        <v>27600</v>
       </c>
       <c r="H63" s="11">
         <v>0</v>
@@ -4344,13 +4344,13 @@
         <v>9</v>
       </c>
       <c r="J63" s="12">
-        <v>158</v>
+        <v>218</v>
       </c>
       <c r="K63" s="12">
         <v>47</v>
       </c>
       <c r="L63" s="13">
-        <v>5587.36</v>
+        <v>5819.1</v>
       </c>
       <c r="M63" s="14" t="s">
         <v>18</v>
@@ -4376,25 +4376,25 @@
         <v>500</v>
       </c>
       <c r="F64" s="5">
-        <v>16000</v>
+        <v>25500</v>
       </c>
       <c r="G64" s="5">
-        <v>16000</v>
+        <v>25500</v>
       </c>
       <c r="H64" s="5">
         <v>0</v>
       </c>
       <c r="I64" s="6">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="J64" s="6">
-        <v>257</v>
+        <v>233</v>
       </c>
       <c r="K64" s="6">
         <v>52</v>
       </c>
       <c r="L64" s="7">
-        <v>5056.89</v>
+        <v>6141.62</v>
       </c>
       <c r="M64" s="8" t="s">
         <v>18</v>
@@ -4420,25 +4420,25 @@
         <v>10</v>
       </c>
       <c r="F65" s="11">
-        <v>220</v>
+        <v>690</v>
       </c>
       <c r="G65" s="11">
-        <v>220</v>
+        <v>690</v>
       </c>
       <c r="H65" s="11">
         <v>0</v>
       </c>
       <c r="I65" s="12">
-        <v>43</v>
+        <v>36</v>
       </c>
       <c r="J65" s="12">
         <v>734</v>
       </c>
       <c r="K65" s="12">
-        <v>114</v>
+        <v>108</v>
       </c>
       <c r="L65" s="13">
-        <v>54.89</v>
+        <v>77.08</v>
       </c>
       <c r="M65" s="14" t="s">
         <v>18</v>
@@ -4464,25 +4464,25 @@
         <v>25</v>
       </c>
       <c r="F66" s="5">
-        <v>1600</v>
+        <v>1425</v>
       </c>
       <c r="G66" s="5">
-        <v>1600</v>
+        <v>1425</v>
       </c>
       <c r="H66" s="5">
         <v>0</v>
       </c>
       <c r="I66" s="6">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="J66" s="6">
-        <v>119</v>
+        <v>130</v>
       </c>
       <c r="K66" s="6">
         <v>30</v>
       </c>
       <c r="L66" s="7">
-        <v>467.84</v>
+        <v>443.93</v>
       </c>
       <c r="M66" s="8" t="s">
         <v>18</v>
@@ -4508,25 +4508,25 @@
         <v>50</v>
       </c>
       <c r="F67" s="11">
-        <v>1500</v>
+        <v>2150</v>
       </c>
       <c r="G67" s="11">
-        <v>1500</v>
+        <v>2150</v>
       </c>
       <c r="H67" s="11">
         <v>0</v>
       </c>
       <c r="I67" s="12">
-        <v>108</v>
+        <v>131</v>
       </c>
       <c r="J67" s="12">
-        <v>1646</v>
+        <v>2007</v>
       </c>
       <c r="K67" s="12">
-        <v>334</v>
+        <v>335</v>
       </c>
       <c r="L67" s="13">
-        <v>130.21</v>
+        <v>135.18</v>
       </c>
       <c r="M67" s="14" t="s">
         <v>18</v>
@@ -4552,25 +4552,25 @@
         <v>100</v>
       </c>
       <c r="F68" s="5">
-        <v>6600</v>
+        <v>4500</v>
       </c>
       <c r="G68" s="5">
-        <v>6600</v>
+        <v>4500</v>
       </c>
       <c r="H68" s="5">
         <v>0</v>
       </c>
       <c r="I68" s="6">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="J68" s="6">
-        <v>114</v>
+        <v>154</v>
       </c>
       <c r="K68" s="6">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="L68" s="7">
-        <v>1794.45</v>
+        <v>1463.41</v>
       </c>
       <c r="M68" s="8" t="s">
         <v>18</v>
@@ -4596,25 +4596,25 @@
         <v>150</v>
       </c>
       <c r="F69" s="11">
-        <v>4500</v>
+        <v>7050</v>
       </c>
       <c r="G69" s="11">
-        <v>4500</v>
+        <v>7050</v>
       </c>
       <c r="H69" s="11">
         <v>0</v>
       </c>
       <c r="I69" s="12">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="J69" s="12">
-        <v>902</v>
+        <v>882</v>
       </c>
       <c r="K69" s="12">
-        <v>138</v>
+        <v>130</v>
       </c>
       <c r="L69" s="13">
-        <v>797.87</v>
+        <v>926.41</v>
       </c>
       <c r="M69" s="14" t="s">
         <v>18</v>
@@ -4640,10 +4640,10 @@
         <v>200</v>
       </c>
       <c r="F70" s="5">
-        <v>8600</v>
+        <v>5400</v>
       </c>
       <c r="G70" s="5">
-        <v>8600</v>
+        <v>5400</v>
       </c>
       <c r="H70" s="5">
         <v>0</v>
@@ -4652,13 +4652,13 @@
         <v>9</v>
       </c>
       <c r="J70" s="6">
-        <v>172</v>
+        <v>131</v>
       </c>
       <c r="K70" s="6">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="L70" s="7">
-        <v>2706.96</v>
+        <v>2137.77</v>
       </c>
       <c r="M70" s="8" t="s">
         <v>18</v>
@@ -4684,25 +4684,25 @@
         <v>300</v>
       </c>
       <c r="F71" s="11">
-        <v>9000</v>
+        <v>12900</v>
       </c>
       <c r="G71" s="11">
-        <v>9000</v>
+        <v>12900</v>
       </c>
       <c r="H71" s="11">
         <v>0</v>
       </c>
       <c r="I71" s="12">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="J71" s="12">
-        <v>206</v>
+        <v>144</v>
       </c>
       <c r="K71" s="12">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="L71" s="13">
-        <v>3157.89</v>
+        <v>3803.07</v>
       </c>
       <c r="M71" s="14" t="s">
         <v>18</v>
@@ -4728,10 +4728,10 @@
         <v>400</v>
       </c>
       <c r="F72" s="5">
-        <v>19600</v>
+        <v>8400</v>
       </c>
       <c r="G72" s="5">
-        <v>19600</v>
+        <v>8400</v>
       </c>
       <c r="H72" s="5">
         <v>0</v>
@@ -4740,13 +4740,13 @@
         <v>10</v>
       </c>
       <c r="J72" s="6">
-        <v>189</v>
+        <v>225</v>
       </c>
       <c r="K72" s="6">
         <v>48</v>
       </c>
       <c r="L72" s="7">
-        <v>5088.27</v>
+        <v>3349.28</v>
       </c>
       <c r="M72" s="8" t="s">
         <v>18</v>
@@ -4772,25 +4772,25 @@
         <v>500</v>
       </c>
       <c r="F73" s="11">
-        <v>32500</v>
+        <v>11500</v>
       </c>
       <c r="G73" s="11">
-        <v>32500</v>
+        <v>11500</v>
       </c>
       <c r="H73" s="11">
         <v>0</v>
       </c>
       <c r="I73" s="12">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="J73" s="12">
-        <v>178</v>
+        <v>225</v>
       </c>
       <c r="K73" s="12">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="L73" s="13">
-        <v>6572.3</v>
+        <v>4194.02</v>
       </c>
       <c r="M73" s="14" t="s">
         <v>18</v>
@@ -4816,10 +4816,10 @@
         <v>10</v>
       </c>
       <c r="F74" s="5">
-        <v>540</v>
+        <v>640</v>
       </c>
       <c r="G74" s="5">
-        <v>540</v>
+        <v>640</v>
       </c>
       <c r="H74" s="5">
         <v>0</v>
@@ -4828,13 +4828,13 @@
         <v>10</v>
       </c>
       <c r="J74" s="6">
-        <v>143</v>
+        <v>123</v>
       </c>
       <c r="K74" s="6">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="L74" s="7">
-        <v>176.13</v>
+        <v>183.7</v>
       </c>
       <c r="M74" s="8" t="s">
         <v>18</v>
@@ -4860,25 +4860,25 @@
         <v>25</v>
       </c>
       <c r="F75" s="11">
-        <v>1250</v>
+        <v>1675</v>
       </c>
       <c r="G75" s="11">
-        <v>1250</v>
+        <v>1675</v>
       </c>
       <c r="H75" s="11">
         <v>0</v>
       </c>
       <c r="I75" s="12">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="J75" s="12">
-        <v>143</v>
+        <v>145</v>
       </c>
       <c r="K75" s="12">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="L75" s="13">
-        <v>403.23</v>
+        <v>486.49</v>
       </c>
       <c r="M75" s="14" t="s">
         <v>18</v>
@@ -4904,25 +4904,25 @@
         <v>50</v>
       </c>
       <c r="F76" s="5">
-        <v>1050</v>
+        <v>2150</v>
       </c>
       <c r="G76" s="5">
-        <v>1050</v>
+        <v>2150</v>
       </c>
       <c r="H76" s="5">
         <v>0</v>
       </c>
       <c r="I76" s="6">
-        <v>41</v>
+        <v>37</v>
       </c>
       <c r="J76" s="6">
-        <v>817</v>
+        <v>768</v>
       </c>
       <c r="K76" s="6">
-        <v>122</v>
+        <v>114</v>
       </c>
       <c r="L76" s="7">
-        <v>258.49</v>
+        <v>335.83</v>
       </c>
       <c r="M76" s="8" t="s">
         <v>18</v>
@@ -4948,25 +4948,25 @@
         <v>100</v>
       </c>
       <c r="F77" s="11">
-        <v>5400</v>
+        <v>3700</v>
       </c>
       <c r="G77" s="11">
-        <v>5400</v>
+        <v>3700</v>
       </c>
       <c r="H77" s="11">
         <v>0</v>
       </c>
       <c r="I77" s="12">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="J77" s="12">
-        <v>138</v>
+        <v>163</v>
       </c>
       <c r="K77" s="12">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="L77" s="13">
-        <v>1592.92</v>
+        <v>1306.5</v>
       </c>
       <c r="M77" s="14" t="s">
         <v>18</v>
@@ -4992,25 +4992,25 @@
         <v>150</v>
       </c>
       <c r="F78" s="5">
-        <v>9300</v>
+        <v>3750</v>
       </c>
       <c r="G78" s="5">
-        <v>9300</v>
+        <v>3750</v>
       </c>
       <c r="H78" s="5">
         <v>0</v>
       </c>
       <c r="I78" s="6">
-        <v>115</v>
+        <v>113</v>
       </c>
       <c r="J78" s="6">
-        <v>1891</v>
+        <v>2292</v>
       </c>
       <c r="K78" s="6">
-        <v>396</v>
+        <v>389</v>
       </c>
       <c r="L78" s="7">
-        <v>356.98</v>
+        <v>334.08</v>
       </c>
       <c r="M78" s="8" t="s">
         <v>18</v>
@@ -5036,10 +5036,10 @@
         <v>200</v>
       </c>
       <c r="F79" s="11">
-        <v>13800</v>
+        <v>13400</v>
       </c>
       <c r="G79" s="11">
-        <v>13800</v>
+        <v>13400</v>
       </c>
       <c r="H79" s="11">
         <v>0</v>
@@ -5048,13 +5048,13 @@
         <v>9</v>
       </c>
       <c r="J79" s="12">
-        <v>170</v>
+        <v>175</v>
       </c>
       <c r="K79" s="12">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="L79" s="13">
-        <v>3239.44</v>
+        <v>3257.96</v>
       </c>
       <c r="M79" s="14" t="s">
         <v>18</v>
@@ -5080,25 +5080,25 @@
         <v>300</v>
       </c>
       <c r="F80" s="5">
-        <v>17700</v>
+        <v>17400</v>
       </c>
       <c r="G80" s="5">
-        <v>17700</v>
+        <v>17400</v>
       </c>
       <c r="H80" s="5">
         <v>0</v>
       </c>
       <c r="I80" s="6">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="J80" s="6">
-        <v>1114</v>
+        <v>1134</v>
       </c>
       <c r="K80" s="6">
-        <v>161</v>
+        <v>159</v>
       </c>
       <c r="L80" s="7">
-        <v>1609.24</v>
+        <v>1622.83</v>
       </c>
       <c r="M80" s="8" t="s">
         <v>18</v>
@@ -5124,25 +5124,25 @@
         <v>400</v>
       </c>
       <c r="F81" s="11">
-        <v>19600</v>
+        <v>9600</v>
       </c>
       <c r="G81" s="11">
-        <v>19600</v>
+        <v>9600</v>
       </c>
       <c r="H81" s="11">
         <v>0</v>
       </c>
       <c r="I81" s="12">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="J81" s="12">
-        <v>214</v>
+        <v>193</v>
       </c>
       <c r="K81" s="12">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="L81" s="13">
-        <v>5153.83</v>
+        <v>3619.91</v>
       </c>
       <c r="M81" s="14" t="s">
         <v>18</v>
@@ -5168,25 +5168,25 @@
         <v>500</v>
       </c>
       <c r="F82" s="5">
-        <v>16500</v>
+        <v>22000</v>
       </c>
       <c r="G82" s="5">
-        <v>16500</v>
+        <v>22000</v>
       </c>
       <c r="H82" s="5">
         <v>0</v>
       </c>
       <c r="I82" s="6">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="J82" s="6">
-        <v>181</v>
+        <v>242</v>
       </c>
       <c r="K82" s="6">
-        <v>56</v>
+        <v>51</v>
       </c>
       <c r="L82" s="7">
-        <v>4928.32</v>
+        <v>5876.07</v>
       </c>
       <c r="M82" s="8" t="s">
         <v>18</v>
@@ -5212,10 +5212,10 @@
         <v>10</v>
       </c>
       <c r="F83" s="11">
-        <v>250</v>
+        <v>260</v>
       </c>
       <c r="G83" s="11">
-        <v>250</v>
+        <v>260</v>
       </c>
       <c r="H83" s="11">
         <v>0</v>
@@ -5224,13 +5224,13 @@
         <v>10</v>
       </c>
       <c r="J83" s="12">
-        <v>117</v>
+        <v>107</v>
       </c>
       <c r="K83" s="12">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="L83" s="13">
-        <v>111.11</v>
+        <v>115.35</v>
       </c>
       <c r="M83" s="14" t="s">
         <v>18</v>
@@ -5256,10 +5256,10 @@
         <v>25</v>
       </c>
       <c r="F84" s="5">
-        <v>825</v>
+        <v>1475</v>
       </c>
       <c r="G84" s="5">
-        <v>825</v>
+        <v>1475</v>
       </c>
       <c r="H84" s="5">
         <v>0</v>
@@ -5268,13 +5268,13 @@
         <v>10</v>
       </c>
       <c r="J84" s="6">
-        <v>104</v>
+        <v>139</v>
       </c>
       <c r="K84" s="6">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="L84" s="7">
-        <v>331.33</v>
+        <v>443.08</v>
       </c>
       <c r="M84" s="8" t="s">
         <v>18</v>
@@ -5300,25 +5300,25 @@
         <v>50</v>
       </c>
       <c r="F85" s="11">
-        <v>2650</v>
+        <v>3350</v>
       </c>
       <c r="G85" s="11">
-        <v>2650</v>
+        <v>3350</v>
       </c>
       <c r="H85" s="11">
         <v>0</v>
       </c>
       <c r="I85" s="12">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="J85" s="12">
-        <v>114</v>
+        <v>109</v>
       </c>
       <c r="K85" s="12">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="L85" s="13">
-        <v>815.64</v>
+        <v>936.54</v>
       </c>
       <c r="M85" s="14" t="s">
         <v>18</v>
@@ -5344,10 +5344,10 @@
         <v>100</v>
       </c>
       <c r="F86" s="5">
-        <v>2600</v>
+        <v>6800</v>
       </c>
       <c r="G86" s="5">
-        <v>2600</v>
+        <v>6800</v>
       </c>
       <c r="H86" s="5">
         <v>0</v>
@@ -5356,13 +5356,13 @@
         <v>9</v>
       </c>
       <c r="J86" s="6">
-        <v>132</v>
+        <v>123</v>
       </c>
       <c r="K86" s="6">
         <v>33</v>
       </c>
       <c r="L86" s="7">
-        <v>1102.63</v>
+        <v>1816.24</v>
       </c>
       <c r="M86" s="8" t="s">
         <v>18</v>
@@ -5388,10 +5388,10 @@
         <v>150</v>
       </c>
       <c r="F87" s="11">
-        <v>10350</v>
+        <v>6600</v>
       </c>
       <c r="G87" s="11">
-        <v>10350</v>
+        <v>6600</v>
       </c>
       <c r="H87" s="11">
         <v>0</v>
@@ -5400,13 +5400,13 @@
         <v>39</v>
       </c>
       <c r="J87" s="12">
-        <v>736</v>
+        <v>701</v>
       </c>
       <c r="K87" s="12">
-        <v>137</v>
+        <v>140</v>
       </c>
       <c r="L87" s="13">
-        <v>944.95</v>
+        <v>861.62</v>
       </c>
       <c r="M87" s="14" t="s">
         <v>18</v>
@@ -5432,25 +5432,25 @@
         <v>200</v>
       </c>
       <c r="F88" s="5">
-        <v>5800</v>
+        <v>4200</v>
       </c>
       <c r="G88" s="5">
-        <v>5800</v>
+        <v>4200</v>
       </c>
       <c r="H88" s="5">
         <v>0</v>
       </c>
       <c r="I88" s="6">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="J88" s="6">
-        <v>152</v>
+        <v>143</v>
       </c>
       <c r="K88" s="6">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="L88" s="7">
-        <v>2229.05</v>
+        <v>1794.87</v>
       </c>
       <c r="M88" s="8" t="s">
         <v>18</v>
@@ -5476,25 +5476,25 @@
         <v>300</v>
       </c>
       <c r="F89" s="11">
-        <v>14700</v>
+        <v>9900</v>
       </c>
       <c r="G89" s="11">
-        <v>14700</v>
+        <v>9900</v>
       </c>
       <c r="H89" s="11">
         <v>0</v>
       </c>
       <c r="I89" s="12">
-        <v>117</v>
+        <v>128</v>
       </c>
       <c r="J89" s="12">
-        <v>3021</v>
+        <v>2993</v>
       </c>
       <c r="K89" s="12">
-        <v>480</v>
+        <v>489</v>
       </c>
       <c r="L89" s="13">
-        <v>587.53</v>
+        <v>561.32</v>
       </c>
       <c r="M89" s="14" t="s">
         <v>18</v>
@@ -5520,25 +5520,25 @@
         <v>400</v>
       </c>
       <c r="F90" s="5">
-        <v>27600</v>
+        <v>12000</v>
       </c>
       <c r="G90" s="5">
-        <v>27600</v>
+        <v>12000</v>
       </c>
       <c r="H90" s="5">
         <v>0</v>
       </c>
       <c r="I90" s="6">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="J90" s="6">
-        <v>160</v>
+        <v>191</v>
       </c>
       <c r="K90" s="6">
-        <v>46</v>
+        <v>49</v>
       </c>
       <c r="L90" s="7">
-        <v>5905.01</v>
+        <v>4040.4</v>
       </c>
       <c r="M90" s="8" t="s">
         <v>18</v>
@@ -5564,25 +5564,25 @@
         <v>500</v>
       </c>
       <c r="F91" s="11">
-        <v>32500</v>
+        <v>14500</v>
       </c>
       <c r="G91" s="11">
-        <v>32500</v>
+        <v>14500</v>
       </c>
       <c r="H91" s="11">
         <v>0</v>
       </c>
       <c r="I91" s="12">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="J91" s="12">
-        <v>1151</v>
+        <v>974</v>
       </c>
       <c r="K91" s="12">
-        <v>205</v>
+        <v>188</v>
       </c>
       <c r="L91" s="13">
-        <v>2192.24</v>
+        <v>2085.73</v>
       </c>
       <c r="M91" s="14" t="s">
         <v>18</v>
@@ -5608,10 +5608,10 @@
         <v>10</v>
       </c>
       <c r="F92" s="5">
-        <v>400</v>
+        <v>260</v>
       </c>
       <c r="G92" s="5">
-        <v>400</v>
+        <v>260</v>
       </c>
       <c r="H92" s="5">
         <v>0</v>
@@ -5623,10 +5623,10 @@
         <v>99</v>
       </c>
       <c r="K92" s="6">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="L92" s="7">
-        <v>145.99</v>
+        <v>114.04</v>
       </c>
       <c r="M92" s="8" t="s">
         <v>18</v>
@@ -5652,10 +5652,10 @@
         <v>25</v>
       </c>
       <c r="F93" s="11">
-        <v>775</v>
+        <v>1225</v>
       </c>
       <c r="G93" s="11">
-        <v>775</v>
+        <v>1225</v>
       </c>
       <c r="H93" s="11">
         <v>0</v>
@@ -5664,13 +5664,13 @@
         <v>9</v>
       </c>
       <c r="J93" s="12">
-        <v>133</v>
+        <v>144</v>
       </c>
       <c r="K93" s="12">
         <v>31</v>
       </c>
       <c r="L93" s="13">
-        <v>314.91</v>
+        <v>405.76</v>
       </c>
       <c r="M93" s="14" t="s">
         <v>18</v>
@@ -5696,25 +5696,25 @@
         <v>50</v>
       </c>
       <c r="F94" s="5">
-        <v>2600</v>
+        <v>1750</v>
       </c>
       <c r="G94" s="5">
-        <v>2600</v>
+        <v>1750</v>
       </c>
       <c r="H94" s="5">
         <v>0</v>
       </c>
       <c r="I94" s="6">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="J94" s="6">
-        <v>118</v>
+        <v>135</v>
       </c>
       <c r="K94" s="6">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="L94" s="7">
-        <v>835.48</v>
+        <v>686.27</v>
       </c>
       <c r="M94" s="8" t="s">
         <v>18</v>
@@ -5740,10 +5740,10 @@
         <v>100</v>
       </c>
       <c r="F95" s="11">
-        <v>6200</v>
+        <v>4200</v>
       </c>
       <c r="G95" s="11">
-        <v>6200</v>
+        <v>4200</v>
       </c>
       <c r="H95" s="11">
         <v>0</v>
@@ -5752,13 +5752,13 @@
         <v>9</v>
       </c>
       <c r="J95" s="12">
-        <v>121</v>
+        <v>143</v>
       </c>
       <c r="K95" s="12">
         <v>33</v>
       </c>
       <c r="L95" s="13">
-        <v>1748.45</v>
+        <v>1455.3</v>
       </c>
       <c r="M95" s="14" t="s">
         <v>18</v>
@@ -5784,25 +5784,25 @@
         <v>150</v>
       </c>
       <c r="F96" s="5">
-        <v>9600</v>
+        <v>3600</v>
       </c>
       <c r="G96" s="5">
-        <v>9600</v>
+        <v>3600</v>
       </c>
       <c r="H96" s="5">
         <v>0</v>
       </c>
       <c r="I96" s="6">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="J96" s="6">
-        <v>124</v>
+        <v>176</v>
       </c>
       <c r="K96" s="6">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="L96" s="7">
-        <v>2566.84</v>
+        <v>1522.84</v>
       </c>
       <c r="M96" s="8" t="s">
         <v>18</v>
@@ -5828,25 +5828,25 @@
         <v>200</v>
       </c>
       <c r="F97" s="11">
-        <v>12200</v>
+        <v>12400</v>
       </c>
       <c r="G97" s="11">
-        <v>12200</v>
+        <v>12400</v>
       </c>
       <c r="H97" s="11">
         <v>0</v>
       </c>
       <c r="I97" s="12">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="J97" s="12">
-        <v>161</v>
+        <v>170</v>
       </c>
       <c r="K97" s="12">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="L97" s="13">
-        <v>3195.39</v>
+        <v>3164.88</v>
       </c>
       <c r="M97" s="14" t="s">
         <v>18</v>
@@ -5872,25 +5872,25 @@
         <v>300</v>
       </c>
       <c r="F98" s="5">
-        <v>16200</v>
+        <v>8400</v>
       </c>
       <c r="G98" s="5">
-        <v>16200</v>
+        <v>8400</v>
       </c>
       <c r="H98" s="5">
         <v>0</v>
       </c>
       <c r="I98" s="6">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="J98" s="6">
-        <v>781</v>
+        <v>950</v>
       </c>
       <c r="K98" s="6">
-        <v>163</v>
+        <v>169</v>
       </c>
       <c r="L98" s="7">
-        <v>1572.51</v>
+        <v>1347.88</v>
       </c>
       <c r="M98" s="8" t="s">
         <v>18</v>
@@ -5916,25 +5916,25 @@
         <v>400</v>
       </c>
       <c r="F99" s="11">
-        <v>8800</v>
+        <v>10400</v>
       </c>
       <c r="G99" s="11">
-        <v>8800</v>
+        <v>10400</v>
       </c>
       <c r="H99" s="11">
         <v>0</v>
       </c>
       <c r="I99" s="12">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="J99" s="12">
-        <v>191</v>
+        <v>166</v>
       </c>
       <c r="K99" s="12">
-        <v>46</v>
+        <v>51</v>
       </c>
       <c r="L99" s="13">
-        <v>3503.18</v>
+        <v>3680.11</v>
       </c>
       <c r="M99" s="14" t="s">
         <v>18</v>
@@ -5960,25 +5960,25 @@
         <v>500</v>
       </c>
       <c r="F100" s="5">
-        <v>22500</v>
+        <v>29500</v>
       </c>
       <c r="G100" s="5">
-        <v>22500</v>
+        <v>29500</v>
       </c>
       <c r="H100" s="5">
         <v>0</v>
       </c>
       <c r="I100" s="6">
-        <v>115</v>
+        <v>111</v>
       </c>
       <c r="J100" s="6">
-        <v>3295</v>
+        <v>3647</v>
       </c>
       <c r="K100" s="6">
-        <v>596</v>
+        <v>555</v>
       </c>
       <c r="L100" s="7">
-        <v>794.49</v>
+        <v>861.44</v>
       </c>
       <c r="M100" s="8" t="s">
         <v>18</v>
@@ -6004,10 +6004,10 @@
         <v>10</v>
       </c>
       <c r="F101" s="11">
-        <v>470</v>
+        <v>240</v>
       </c>
       <c r="G101" s="11">
-        <v>470</v>
+        <v>240</v>
       </c>
       <c r="H101" s="11">
         <v>0</v>
@@ -6016,13 +6016,13 @@
         <v>9</v>
       </c>
       <c r="J101" s="12">
-        <v>132</v>
+        <v>123</v>
       </c>
       <c r="K101" s="12">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="L101" s="13">
-        <v>158.94</v>
+        <v>109.29</v>
       </c>
       <c r="M101" s="14" t="s">
         <v>18</v>
@@ -6048,25 +6048,25 @@
         <v>25</v>
       </c>
       <c r="F102" s="5">
-        <v>1650</v>
+        <v>725</v>
       </c>
       <c r="G102" s="5">
-        <v>1650</v>
+        <v>725</v>
       </c>
       <c r="H102" s="5">
         <v>0</v>
       </c>
       <c r="I102" s="6">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="J102" s="6">
-        <v>570</v>
+        <v>694</v>
       </c>
       <c r="K102" s="6">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="L102" s="7">
-        <v>177.65</v>
+        <v>148.17</v>
       </c>
       <c r="M102" s="8" t="s">
         <v>18</v>
@@ -6092,10 +6092,10 @@
         <v>50</v>
       </c>
       <c r="F103" s="11">
-        <v>2600</v>
+        <v>2700</v>
       </c>
       <c r="G103" s="11">
-        <v>2600</v>
+        <v>2700</v>
       </c>
       <c r="H103" s="11">
         <v>0</v>
@@ -6104,13 +6104,13 @@
         <v>9</v>
       </c>
       <c r="J103" s="12">
-        <v>148</v>
+        <v>105</v>
       </c>
       <c r="K103" s="12">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="L103" s="13">
-        <v>821.74</v>
+        <v>850.66</v>
       </c>
       <c r="M103" s="14" t="s">
         <v>18</v>
@@ -6136,25 +6136,25 @@
         <v>100</v>
       </c>
       <c r="F104" s="5">
-        <v>3400</v>
+        <v>3600</v>
       </c>
       <c r="G104" s="5">
-        <v>3400</v>
+        <v>3600</v>
       </c>
       <c r="H104" s="5">
         <v>0</v>
       </c>
       <c r="I104" s="6">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="J104" s="6">
-        <v>147</v>
+        <v>162</v>
       </c>
       <c r="K104" s="6">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="L104" s="7">
-        <v>1296.72</v>
+        <v>1304.35</v>
       </c>
       <c r="M104" s="8" t="s">
         <v>18</v>
@@ -6180,25 +6180,25 @@
         <v>150</v>
       </c>
       <c r="F105" s="11">
-        <v>3900</v>
+        <v>7950</v>
       </c>
       <c r="G105" s="11">
-        <v>3900</v>
+        <v>7950</v>
       </c>
       <c r="H105" s="11">
         <v>0</v>
       </c>
       <c r="I105" s="12">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="J105" s="12">
-        <v>148</v>
+        <v>123</v>
       </c>
       <c r="K105" s="12">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="L105" s="13">
-        <v>1600.99</v>
+        <v>2262.38</v>
       </c>
       <c r="M105" s="14" t="s">
         <v>18</v>
@@ -6224,25 +6224,25 @@
         <v>200</v>
       </c>
       <c r="F106" s="5">
-        <v>6600</v>
+        <v>12000</v>
       </c>
       <c r="G106" s="5">
-        <v>6600</v>
+        <v>12000</v>
       </c>
       <c r="H106" s="5">
         <v>0</v>
       </c>
       <c r="I106" s="6">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="J106" s="6">
-        <v>152</v>
+        <v>185</v>
       </c>
       <c r="K106" s="6">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="L106" s="7">
-        <v>2313.35</v>
+        <v>3125</v>
       </c>
       <c r="M106" s="8" t="s">
         <v>18</v>
@@ -6268,25 +6268,25 @@
         <v>300</v>
       </c>
       <c r="F107" s="11">
-        <v>6000</v>
+        <v>6900</v>
       </c>
       <c r="G107" s="11">
-        <v>6000</v>
+        <v>6900</v>
       </c>
       <c r="H107" s="11">
         <v>0</v>
       </c>
       <c r="I107" s="12">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="J107" s="12">
-        <v>179</v>
+        <v>171</v>
       </c>
       <c r="K107" s="12">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="L107" s="13">
-        <v>2500</v>
+        <v>2746.82</v>
       </c>
       <c r="M107" s="14" t="s">
         <v>18</v>
@@ -6312,25 +6312,25 @@
         <v>400</v>
       </c>
       <c r="F108" s="5">
-        <v>26800</v>
+        <v>27600</v>
       </c>
       <c r="G108" s="5">
-        <v>26800</v>
+        <v>27600</v>
       </c>
       <c r="H108" s="5">
         <v>0</v>
       </c>
       <c r="I108" s="6">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="J108" s="6">
-        <v>171</v>
+        <v>230</v>
       </c>
       <c r="K108" s="6">
-        <v>50</v>
+        <v>47</v>
       </c>
       <c r="L108" s="7">
-        <v>5525.77</v>
+        <v>5819.1</v>
       </c>
       <c r="M108" s="8" t="s">
         <v>18</v>
@@ -6356,10 +6356,10 @@
         <v>500</v>
       </c>
       <c r="F109" s="11">
-        <v>19000</v>
+        <v>16000</v>
       </c>
       <c r="G109" s="11">
-        <v>19000</v>
+        <v>16000</v>
       </c>
       <c r="H109" s="11">
         <v>0</v>
@@ -6368,13 +6368,13 @@
         <v>42</v>
       </c>
       <c r="J109" s="12">
-        <v>1202</v>
+        <v>1293</v>
       </c>
       <c r="K109" s="12">
-        <v>202</v>
+        <v>193</v>
       </c>
       <c r="L109" s="13">
-        <v>2070.62</v>
+        <v>2084.42</v>
       </c>
       <c r="M109" s="14" t="s">
         <v>18</v>
@@ -6400,25 +6400,25 @@
         <v>10</v>
       </c>
       <c r="F110" s="5">
-        <v>620</v>
+        <v>290</v>
       </c>
       <c r="G110" s="5">
-        <v>620</v>
+        <v>290</v>
       </c>
       <c r="H110" s="5">
         <v>0</v>
       </c>
       <c r="I110" s="6">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="J110" s="6">
-        <v>98</v>
+        <v>116</v>
       </c>
       <c r="K110" s="6">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="L110" s="7">
-        <v>191.59</v>
+        <v>123.88</v>
       </c>
       <c r="M110" s="8" t="s">
         <v>18</v>
@@ -6444,25 +6444,25 @@
         <v>25</v>
       </c>
       <c r="F111" s="11">
-        <v>1175</v>
+        <v>650</v>
       </c>
       <c r="G111" s="11">
-        <v>1175</v>
+        <v>650</v>
       </c>
       <c r="H111" s="11">
         <v>0</v>
       </c>
       <c r="I111" s="12">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="J111" s="12">
-        <v>2203</v>
+        <v>1872</v>
       </c>
       <c r="K111" s="12">
-        <v>318</v>
+        <v>324</v>
       </c>
       <c r="L111" s="13">
-        <v>71.45</v>
+        <v>65.5</v>
       </c>
       <c r="M111" s="14" t="s">
         <v>18</v>
@@ -6488,10 +6488,10 @@
         <v>50</v>
       </c>
       <c r="F112" s="5">
-        <v>2750</v>
+        <v>2000</v>
       </c>
       <c r="G112" s="5">
-        <v>2750</v>
+        <v>2000</v>
       </c>
       <c r="H112" s="5">
         <v>0</v>
@@ -6500,13 +6500,13 @@
         <v>10</v>
       </c>
       <c r="J112" s="6">
-        <v>129</v>
+        <v>145</v>
       </c>
       <c r="K112" s="6">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="L112" s="7">
-        <v>858.03</v>
+        <v>709.22</v>
       </c>
       <c r="M112" s="8" t="s">
         <v>18</v>
@@ -6532,25 +6532,25 @@
         <v>100</v>
       </c>
       <c r="F113" s="11">
-        <v>3800</v>
+        <v>5100</v>
       </c>
       <c r="G113" s="11">
-        <v>3800</v>
+        <v>5100</v>
       </c>
       <c r="H113" s="11">
         <v>0</v>
       </c>
       <c r="I113" s="12">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="J113" s="12">
-        <v>665</v>
+        <v>860</v>
       </c>
       <c r="K113" s="12">
-        <v>131</v>
+        <v>127</v>
       </c>
       <c r="L113" s="13">
-        <v>586.6</v>
+        <v>639.34</v>
       </c>
       <c r="M113" s="14" t="s">
         <v>18</v>
@@ -6576,25 +6576,25 @@
         <v>150</v>
       </c>
       <c r="F114" s="5">
-        <v>3000</v>
+        <v>4500</v>
       </c>
       <c r="G114" s="5">
-        <v>3000</v>
+        <v>4500</v>
       </c>
       <c r="H114" s="5">
         <v>0</v>
       </c>
       <c r="I114" s="6">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="J114" s="6">
-        <v>146</v>
+        <v>134</v>
       </c>
       <c r="K114" s="6">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="L114" s="7">
-        <v>1351.35</v>
+        <v>1704.55</v>
       </c>
       <c r="M114" s="8" t="s">
         <v>18</v>
@@ -6620,25 +6620,25 @@
         <v>200</v>
       </c>
       <c r="F115" s="11">
-        <v>10800</v>
+        <v>7400</v>
       </c>
       <c r="G115" s="11">
-        <v>10800</v>
+        <v>7400</v>
       </c>
       <c r="H115" s="11">
         <v>0</v>
       </c>
       <c r="I115" s="12">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="J115" s="12">
         <v>158</v>
       </c>
       <c r="K115" s="12">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="L115" s="13">
-        <v>2907.92</v>
+        <v>2514.44</v>
       </c>
       <c r="M115" s="14" t="s">
         <v>18</v>
@@ -6664,10 +6664,10 @@
         <v>300</v>
       </c>
       <c r="F116" s="5">
-        <v>12300</v>
+        <v>6900</v>
       </c>
       <c r="G116" s="5">
-        <v>12300</v>
+        <v>6900</v>
       </c>
       <c r="H116" s="5">
         <v>0</v>
@@ -6676,13 +6676,13 @@
         <v>10</v>
       </c>
       <c r="J116" s="6">
-        <v>146</v>
+        <v>200</v>
       </c>
       <c r="K116" s="6">
         <v>42</v>
       </c>
       <c r="L116" s="7">
-        <v>3817.5</v>
+        <v>2798.05</v>
       </c>
       <c r="M116" s="8" t="s">
         <v>18</v>
@@ -6708,10 +6708,10 @@
         <v>400</v>
       </c>
       <c r="F117" s="11">
-        <v>21200</v>
+        <v>12400</v>
       </c>
       <c r="G117" s="11">
-        <v>21200</v>
+        <v>12400</v>
       </c>
       <c r="H117" s="11">
         <v>0</v>
@@ -6720,13 +6720,13 @@
         <v>9</v>
       </c>
       <c r="J117" s="12">
-        <v>222</v>
+        <v>187</v>
       </c>
       <c r="K117" s="12">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="L117" s="13">
-        <v>5242.33</v>
+        <v>4065.57</v>
       </c>
       <c r="M117" s="14" t="s">
         <v>18</v>
@@ -6752,25 +6752,25 @@
         <v>500</v>
       </c>
       <c r="F118" s="5">
-        <v>11000</v>
+        <v>27000</v>
       </c>
       <c r="G118" s="5">
-        <v>11000</v>
+        <v>27000</v>
       </c>
       <c r="H118" s="5">
         <v>0</v>
       </c>
       <c r="I118" s="6">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="J118" s="6">
-        <v>179</v>
+        <v>209</v>
       </c>
       <c r="K118" s="6">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="L118" s="7">
-        <v>4092.26</v>
+        <v>6189.82</v>
       </c>
       <c r="M118" s="8" t="s">
         <v>18</v>
@@ -6796,25 +6796,25 @@
         <v>10</v>
       </c>
       <c r="F119" s="11">
-        <v>410</v>
+        <v>690</v>
       </c>
       <c r="G119" s="11">
-        <v>410</v>
+        <v>690</v>
       </c>
       <c r="H119" s="11">
         <v>0</v>
       </c>
       <c r="I119" s="12">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="J119" s="12">
-        <v>97</v>
+        <v>121</v>
       </c>
       <c r="K119" s="12">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="L119" s="13">
-        <v>147.96</v>
+        <v>197.09</v>
       </c>
       <c r="M119" s="14" t="s">
         <v>18</v>
@@ -6840,25 +6840,25 @@
         <v>25</v>
       </c>
       <c r="F120" s="5">
-        <v>1375</v>
+        <v>1625</v>
       </c>
       <c r="G120" s="5">
-        <v>1375</v>
+        <v>1625</v>
       </c>
       <c r="H120" s="5">
         <v>0</v>
       </c>
       <c r="I120" s="6">
-        <v>37</v>
+        <v>40</v>
       </c>
       <c r="J120" s="6">
-        <v>771</v>
+        <v>642</v>
       </c>
       <c r="K120" s="6">
-        <v>109</v>
+        <v>112</v>
       </c>
       <c r="L120" s="7">
-        <v>183.46</v>
+        <v>185.08</v>
       </c>
       <c r="M120" s="8" t="s">
         <v>18</v>
@@ -6884,10 +6884,10 @@
         <v>50</v>
       </c>
       <c r="F121" s="11">
-        <v>1900</v>
+        <v>1650</v>
       </c>
       <c r="G121" s="11">
-        <v>1900</v>
+        <v>1650</v>
       </c>
       <c r="H121" s="11">
         <v>0</v>
@@ -6896,13 +6896,13 @@
         <v>10</v>
       </c>
       <c r="J121" s="12">
-        <v>128</v>
+        <v>138</v>
       </c>
       <c r="K121" s="12">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="L121" s="13">
-        <v>719.7</v>
+        <v>653.98</v>
       </c>
       <c r="M121" s="14" t="s">
         <v>18</v>
@@ -6928,25 +6928,25 @@
         <v>100</v>
       </c>
       <c r="F122" s="5">
-        <v>4100</v>
+        <v>3800</v>
       </c>
       <c r="G122" s="5">
-        <v>4100</v>
+        <v>3800</v>
       </c>
       <c r="H122" s="5">
         <v>0</v>
       </c>
       <c r="I122" s="6">
-        <v>110</v>
+        <v>126</v>
       </c>
       <c r="J122" s="6">
-        <v>1867</v>
+        <v>1818</v>
       </c>
       <c r="K122" s="6">
-        <v>357</v>
+        <v>354</v>
       </c>
       <c r="L122" s="7">
-        <v>254.07</v>
+        <v>254.15</v>
       </c>
       <c r="M122" s="8" t="s">
         <v>18</v>
@@ -6972,10 +6972,10 @@
         <v>150</v>
       </c>
       <c r="F123" s="11">
-        <v>5100</v>
+        <v>4800</v>
       </c>
       <c r="G123" s="11">
-        <v>5100</v>
+        <v>4800</v>
       </c>
       <c r="H123" s="11">
         <v>0</v>
@@ -6984,13 +6984,13 @@
         <v>10</v>
       </c>
       <c r="J123" s="12">
-        <v>167</v>
+        <v>133</v>
       </c>
       <c r="K123" s="12">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="L123" s="13">
-        <v>1895.91</v>
+        <v>1809.95</v>
       </c>
       <c r="M123" s="14" t="s">
         <v>18</v>
@@ -7016,25 +7016,25 @@
         <v>200</v>
       </c>
       <c r="F124" s="5">
-        <v>6000</v>
+        <v>6200</v>
       </c>
       <c r="G124" s="5">
-        <v>6000</v>
+        <v>6200</v>
       </c>
       <c r="H124" s="5">
         <v>0</v>
       </c>
       <c r="I124" s="6">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="J124" s="6">
-        <v>765</v>
+        <v>762</v>
       </c>
       <c r="K124" s="6">
-        <v>148</v>
+        <v>150</v>
       </c>
       <c r="L124" s="7">
-        <v>1010.1</v>
+        <v>1008.13</v>
       </c>
       <c r="M124" s="8" t="s">
         <v>18</v>
@@ -7060,10 +7060,10 @@
         <v>300</v>
       </c>
       <c r="F125" s="11">
-        <v>10200</v>
+        <v>16500</v>
       </c>
       <c r="G125" s="11">
-        <v>10200</v>
+        <v>16500</v>
       </c>
       <c r="H125" s="11">
         <v>0</v>
@@ -7072,13 +7072,13 @@
         <v>10</v>
       </c>
       <c r="J125" s="12">
-        <v>187</v>
+        <v>185</v>
       </c>
       <c r="K125" s="12">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="L125" s="13">
-        <v>3404.54</v>
+        <v>4330.71</v>
       </c>
       <c r="M125" s="14" t="s">
         <v>18</v>
@@ -7104,10 +7104,10 @@
         <v>400</v>
       </c>
       <c r="F126" s="5">
-        <v>10800</v>
+        <v>15600</v>
       </c>
       <c r="G126" s="5">
-        <v>10800</v>
+        <v>15600</v>
       </c>
       <c r="H126" s="5">
         <v>0</v>
@@ -7116,13 +7116,13 @@
         <v>10</v>
       </c>
       <c r="J126" s="6">
-        <v>226</v>
+        <v>194</v>
       </c>
       <c r="K126" s="6">
         <v>49</v>
       </c>
       <c r="L126" s="7">
-        <v>3825.72</v>
+        <v>4573.44</v>
       </c>
       <c r="M126" s="8" t="s">
         <v>18</v>
@@ -7148,25 +7148,25 @@
         <v>500</v>
       </c>
       <c r="F127" s="11">
-        <v>23000</v>
+        <v>25500</v>
       </c>
       <c r="G127" s="11">
-        <v>23000</v>
+        <v>25500</v>
       </c>
       <c r="H127" s="11">
         <v>0</v>
       </c>
       <c r="I127" s="12">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="J127" s="12">
-        <v>246</v>
+        <v>183</v>
       </c>
       <c r="K127" s="12">
         <v>51</v>
       </c>
       <c r="L127" s="13">
-        <v>5980.24</v>
+        <v>6218</v>
       </c>
       <c r="M127" s="14" t="s">
         <v>18</v>
@@ -7192,10 +7192,10 @@
         <v>10</v>
       </c>
       <c r="F128" s="5">
-        <v>580</v>
+        <v>510</v>
       </c>
       <c r="G128" s="5">
-        <v>580</v>
+        <v>510</v>
       </c>
       <c r="H128" s="5">
         <v>0</v>
@@ -7204,13 +7204,13 @@
         <v>10</v>
       </c>
       <c r="J128" s="6">
-        <v>133</v>
+        <v>103</v>
       </c>
       <c r="K128" s="6">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="L128" s="7">
-        <v>182.28</v>
+        <v>165.53</v>
       </c>
       <c r="M128" s="8" t="s">
         <v>18</v>
@@ -7236,10 +7236,10 @@
         <v>25</v>
       </c>
       <c r="F129" s="11">
-        <v>1225</v>
+        <v>1475</v>
       </c>
       <c r="G129" s="11">
-        <v>1225</v>
+        <v>1475</v>
       </c>
       <c r="H129" s="11">
         <v>0</v>
@@ -7248,13 +7248,13 @@
         <v>10</v>
       </c>
       <c r="J129" s="12">
-        <v>139</v>
+        <v>100</v>
       </c>
       <c r="K129" s="12">
         <v>32</v>
       </c>
       <c r="L129" s="13">
-        <v>399.28</v>
+        <v>435.36</v>
       </c>
       <c r="M129" s="14" t="s">
         <v>18</v>
@@ -7280,25 +7280,25 @@
         <v>50</v>
       </c>
       <c r="F130" s="5">
-        <v>2750</v>
+        <v>1250</v>
       </c>
       <c r="G130" s="5">
-        <v>2750</v>
+        <v>1250</v>
       </c>
       <c r="H130" s="5">
         <v>0</v>
       </c>
       <c r="I130" s="6">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="J130" s="6">
-        <v>140</v>
+        <v>123</v>
       </c>
       <c r="K130" s="6">
         <v>33</v>
       </c>
       <c r="L130" s="7">
-        <v>829.56</v>
+        <v>537.63</v>
       </c>
       <c r="M130" s="8" t="s">
         <v>18</v>
@@ -7324,25 +7324,25 @@
         <v>100</v>
       </c>
       <c r="F131" s="11">
-        <v>3100</v>
+        <v>4800</v>
       </c>
       <c r="G131" s="11">
-        <v>3100</v>
+        <v>4800</v>
       </c>
       <c r="H131" s="11">
         <v>0</v>
       </c>
       <c r="I131" s="12">
-        <v>40</v>
+        <v>43</v>
       </c>
       <c r="J131" s="12">
-        <v>849</v>
+        <v>721</v>
       </c>
       <c r="K131" s="12">
-        <v>133</v>
+        <v>123</v>
       </c>
       <c r="L131" s="13">
-        <v>551.31</v>
+        <v>648.3</v>
       </c>
       <c r="M131" s="14" t="s">
         <v>18</v>
@@ -7368,25 +7368,25 @@
         <v>150</v>
       </c>
       <c r="F132" s="5">
-        <v>10200</v>
+        <v>3300</v>
       </c>
       <c r="G132" s="5">
-        <v>10200</v>
+        <v>3300</v>
       </c>
       <c r="H132" s="5">
         <v>0</v>
       </c>
       <c r="I132" s="6">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="J132" s="6">
-        <v>170</v>
+        <v>143</v>
       </c>
       <c r="K132" s="6">
         <v>37</v>
       </c>
       <c r="L132" s="7">
-        <v>2539.84</v>
+        <v>1426.1</v>
       </c>
       <c r="M132" s="8" t="s">
         <v>18</v>
@@ -7412,25 +7412,25 @@
         <v>200</v>
       </c>
       <c r="F133" s="11">
-        <v>8600</v>
+        <v>7200</v>
       </c>
       <c r="G133" s="11">
-        <v>8600</v>
+        <v>7200</v>
       </c>
       <c r="H133" s="11">
         <v>0</v>
       </c>
       <c r="I133" s="12">
-        <v>110</v>
+        <v>112</v>
       </c>
       <c r="J133" s="12">
-        <v>2612</v>
+        <v>2639</v>
       </c>
       <c r="K133" s="12">
-        <v>412</v>
+        <v>433</v>
       </c>
       <c r="L133" s="13">
-        <v>447.54</v>
+        <v>421.35</v>
       </c>
       <c r="M133" s="14" t="s">
         <v>18</v>
@@ -7456,25 +7456,25 @@
         <v>300</v>
       </c>
       <c r="F134" s="5">
-        <v>12900</v>
+        <v>20700</v>
       </c>
       <c r="G134" s="5">
-        <v>12900</v>
+        <v>20700</v>
       </c>
       <c r="H134" s="5">
         <v>0</v>
       </c>
       <c r="I134" s="6">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="J134" s="6">
-        <v>180</v>
+        <v>208</v>
       </c>
       <c r="K134" s="6">
-        <v>45</v>
+        <v>42</v>
       </c>
       <c r="L134" s="7">
-        <v>3755.46</v>
+        <v>4706.68</v>
       </c>
       <c r="M134" s="8" t="s">
         <v>18</v>
@@ -7500,25 +7500,25 @@
         <v>400</v>
       </c>
       <c r="F135" s="11">
-        <v>21200</v>
+        <v>24800</v>
       </c>
       <c r="G135" s="11">
-        <v>21200</v>
+        <v>24800</v>
       </c>
       <c r="H135" s="11">
         <v>0</v>
       </c>
       <c r="I135" s="12">
-        <v>42</v>
+        <v>39</v>
       </c>
       <c r="J135" s="12">
-        <v>1148</v>
+        <v>1124</v>
       </c>
       <c r="K135" s="12">
-        <v>188</v>
+        <v>186</v>
       </c>
       <c r="L135" s="13">
-        <v>1849.27</v>
+        <v>1903.01</v>
       </c>
       <c r="M135" s="14" t="s">
         <v>18</v>
@@ -7544,25 +7544,25 @@
         <v>500</v>
       </c>
       <c r="F136" s="5">
-        <v>17000</v>
+        <v>23000</v>
       </c>
       <c r="G136" s="5">
-        <v>17000</v>
+        <v>23000</v>
       </c>
       <c r="H136" s="5">
         <v>0</v>
       </c>
       <c r="I136" s="6">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="J136" s="6">
         <v>182</v>
       </c>
       <c r="K136" s="6">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="L136" s="7">
-        <v>5044.51</v>
+        <v>5642.79</v>
       </c>
       <c r="M136" s="8" t="s">
         <v>18</v>
@@ -7588,10 +7588,10 @@
         <v>10</v>
       </c>
       <c r="F137" s="11">
-        <v>600</v>
+        <v>300</v>
       </c>
       <c r="G137" s="11">
-        <v>600</v>
+        <v>300</v>
       </c>
       <c r="H137" s="11">
         <v>0</v>
@@ -7600,13 +7600,13 @@
         <v>9</v>
       </c>
       <c r="J137" s="12">
-        <v>142</v>
+        <v>137</v>
       </c>
       <c r="K137" s="12">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="L137" s="13">
-        <v>185.19</v>
+        <v>123.46</v>
       </c>
       <c r="M137" s="14" t="s">
         <v>18</v>
@@ -7632,25 +7632,25 @@
         <v>25</v>
       </c>
       <c r="F138" s="5">
-        <v>800</v>
+        <v>500</v>
       </c>
       <c r="G138" s="5">
-        <v>800</v>
+        <v>500</v>
       </c>
       <c r="H138" s="5">
         <v>0</v>
       </c>
       <c r="I138" s="6">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="J138" s="6">
-        <v>139</v>
+        <v>112</v>
       </c>
       <c r="K138" s="6">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="L138" s="7">
-        <v>325.2</v>
+        <v>235.85</v>
       </c>
       <c r="M138" s="8" t="s">
         <v>18</v>
@@ -7676,10 +7676,10 @@
         <v>50</v>
       </c>
       <c r="F139" s="11">
-        <v>1850</v>
+        <v>1200</v>
       </c>
       <c r="G139" s="11">
-        <v>1850</v>
+        <v>1200</v>
       </c>
       <c r="H139" s="11">
         <v>0</v>
@@ -7688,13 +7688,13 @@
         <v>10</v>
       </c>
       <c r="J139" s="12">
-        <v>146</v>
+        <v>111</v>
       </c>
       <c r="K139" s="12">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="L139" s="13">
-        <v>689.27</v>
+        <v>534.76</v>
       </c>
       <c r="M139" s="14" t="s">
         <v>18</v>
@@ -7720,25 +7720,25 @@
         <v>100</v>
       </c>
       <c r="F140" s="5">
-        <v>5900</v>
+        <v>5100</v>
       </c>
       <c r="G140" s="5">
-        <v>5900</v>
+        <v>5100</v>
       </c>
       <c r="H140" s="5">
         <v>0</v>
       </c>
       <c r="I140" s="6">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="J140" s="6">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="K140" s="6">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="L140" s="7">
-        <v>1682.83</v>
+        <v>1552.51</v>
       </c>
       <c r="M140" s="8" t="s">
         <v>18</v>
@@ -7764,10 +7764,10 @@
         <v>150</v>
       </c>
       <c r="F141" s="11">
-        <v>4950</v>
+        <v>4200</v>
       </c>
       <c r="G141" s="11">
-        <v>4950</v>
+        <v>4200</v>
       </c>
       <c r="H141" s="11">
         <v>0</v>
@@ -7776,13 +7776,13 @@
         <v>10</v>
       </c>
       <c r="J141" s="12">
-        <v>135</v>
+        <v>171</v>
       </c>
       <c r="K141" s="12">
-        <v>35</v>
+        <v>38</v>
       </c>
       <c r="L141" s="13">
-        <v>1864.41</v>
+        <v>1638.07</v>
       </c>
       <c r="M141" s="14" t="s">
         <v>18</v>
@@ -7808,25 +7808,25 @@
         <v>200</v>
       </c>
       <c r="F142" s="5">
-        <v>4400</v>
+        <v>11000</v>
       </c>
       <c r="G142" s="5">
-        <v>4400</v>
+        <v>11000</v>
       </c>
       <c r="H142" s="5">
         <v>0</v>
       </c>
       <c r="I142" s="6">
-        <v>42</v>
+        <v>39</v>
       </c>
       <c r="J142" s="6">
-        <v>754</v>
+        <v>800</v>
       </c>
       <c r="K142" s="6">
-        <v>139</v>
+        <v>145</v>
       </c>
       <c r="L142" s="7">
-        <v>965.34</v>
+        <v>1160.95</v>
       </c>
       <c r="M142" s="8" t="s">
         <v>18</v>
@@ -7852,10 +7852,10 @@
         <v>300</v>
       </c>
       <c r="F143" s="11">
-        <v>17400</v>
+        <v>20400</v>
       </c>
       <c r="G143" s="11">
-        <v>17400</v>
+        <v>20400</v>
       </c>
       <c r="H143" s="11">
         <v>0</v>
@@ -7864,13 +7864,13 @@
         <v>9</v>
       </c>
       <c r="J143" s="12">
-        <v>206</v>
+        <v>198</v>
       </c>
       <c r="K143" s="12">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="L143" s="13">
-        <v>4233.58</v>
+        <v>4611.21</v>
       </c>
       <c r="M143" s="14" t="s">
         <v>18</v>
@@ -7896,25 +7896,25 @@
         <v>400</v>
       </c>
       <c r="F144" s="5">
-        <v>12000</v>
+        <v>22400</v>
       </c>
       <c r="G144" s="5">
-        <v>12000</v>
+        <v>22400</v>
       </c>
       <c r="H144" s="5">
         <v>0</v>
       </c>
       <c r="I144" s="6">
-        <v>126</v>
+        <v>110</v>
       </c>
       <c r="J144" s="6">
-        <v>2404</v>
+        <v>3326</v>
       </c>
       <c r="K144" s="6">
         <v>539</v>
       </c>
       <c r="L144" s="7">
-        <v>679.12</v>
+        <v>706.98</v>
       </c>
       <c r="M144" s="8" t="s">
         <v>18</v>
@@ -7940,25 +7940,25 @@
         <v>500</v>
       </c>
       <c r="F145" s="11">
-        <v>13000</v>
+        <v>32000</v>
       </c>
       <c r="G145" s="11">
-        <v>13000</v>
+        <v>32000</v>
       </c>
       <c r="H145" s="11">
         <v>0</v>
       </c>
       <c r="I145" s="12">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="J145" s="12">
-        <v>246</v>
+        <v>240</v>
       </c>
       <c r="K145" s="12">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="L145" s="13">
-        <v>4517.03</v>
+        <v>6374.5</v>
       </c>
       <c r="M145" s="14" t="s">
         <v>18</v>
@@ -7984,25 +7984,25 @@
         <v>10</v>
       </c>
       <c r="F146" s="5">
-        <v>260</v>
+        <v>200</v>
       </c>
       <c r="G146" s="5">
-        <v>260</v>
+        <v>200</v>
       </c>
       <c r="H146" s="5">
         <v>0</v>
       </c>
       <c r="I146" s="6">
-        <v>36</v>
+        <v>43</v>
       </c>
       <c r="J146" s="6">
-        <v>710</v>
+        <v>606</v>
       </c>
       <c r="K146" s="6">
-        <v>112</v>
+        <v>116</v>
       </c>
       <c r="L146" s="7">
-        <v>58.93</v>
+        <v>52.36</v>
       </c>
       <c r="M146" s="8" t="s">
         <v>18</v>
@@ -8028,10 +8028,10 @@
         <v>25</v>
       </c>
       <c r="F147" s="11">
-        <v>775</v>
+        <v>1150</v>
       </c>
       <c r="G147" s="11">
-        <v>775</v>
+        <v>1150</v>
       </c>
       <c r="H147" s="11">
         <v>0</v>
@@ -8040,13 +8040,13 @@
         <v>9</v>
       </c>
       <c r="J147" s="12">
-        <v>130</v>
+        <v>148</v>
       </c>
       <c r="K147" s="12">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="L147" s="13">
-        <v>318.93</v>
+        <v>393.03</v>
       </c>
       <c r="M147" s="14" t="s">
         <v>18</v>
@@ -8072,10 +8072,10 @@
         <v>50</v>
       </c>
       <c r="F148" s="5">
-        <v>1350</v>
+        <v>2350</v>
       </c>
       <c r="G148" s="5">
-        <v>1350</v>
+        <v>2350</v>
       </c>
       <c r="H148" s="5">
         <v>0</v>
@@ -8084,13 +8084,13 @@
         <v>10</v>
       </c>
       <c r="J148" s="6">
-        <v>139</v>
+        <v>154</v>
       </c>
       <c r="K148" s="6">
         <v>31</v>
       </c>
       <c r="L148" s="7">
-        <v>577.66</v>
+        <v>794.72</v>
       </c>
       <c r="M148" s="8" t="s">
         <v>18</v>
@@ -8116,25 +8116,25 @@
         <v>100</v>
       </c>
       <c r="F149" s="11">
-        <v>6700</v>
+        <v>4300</v>
       </c>
       <c r="G149" s="11">
-        <v>6700</v>
+        <v>4300</v>
       </c>
       <c r="H149" s="11">
         <v>0</v>
       </c>
       <c r="I149" s="12">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="J149" s="12">
-        <v>160</v>
+        <v>150</v>
       </c>
       <c r="K149" s="12">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="L149" s="13">
-        <v>1805.44</v>
+        <v>1430.95</v>
       </c>
       <c r="M149" s="14" t="s">
         <v>18</v>
@@ -8160,10 +8160,10 @@
         <v>150</v>
       </c>
       <c r="F150" s="5">
-        <v>6900</v>
+        <v>7350</v>
       </c>
       <c r="G150" s="5">
-        <v>6900</v>
+        <v>7350</v>
       </c>
       <c r="H150" s="5">
         <v>0</v>
@@ -8172,13 +8172,13 @@
         <v>9</v>
       </c>
       <c r="J150" s="6">
-        <v>123</v>
+        <v>153</v>
       </c>
       <c r="K150" s="6">
         <v>36</v>
       </c>
       <c r="L150" s="7">
-        <v>2186.31</v>
+        <v>2251.84</v>
       </c>
       <c r="M150" s="8" t="s">
         <v>18</v>
@@ -8204,10 +8204,10 @@
         <v>200</v>
       </c>
       <c r="F151" s="11">
-        <v>8800</v>
+        <v>11600</v>
       </c>
       <c r="G151" s="11">
-        <v>8800</v>
+        <v>11600</v>
       </c>
       <c r="H151" s="11">
         <v>0</v>
@@ -8216,13 +8216,13 @@
         <v>10</v>
       </c>
       <c r="J151" s="12">
-        <v>184</v>
+        <v>129</v>
       </c>
       <c r="K151" s="12">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="L151" s="13">
-        <v>2774.27</v>
+        <v>3036.65</v>
       </c>
       <c r="M151" s="14" t="s">
         <v>18</v>
@@ -8248,10 +8248,10 @@
         <v>300</v>
       </c>
       <c r="F152" s="5">
-        <v>18000</v>
+        <v>18600</v>
       </c>
       <c r="G152" s="5">
-        <v>18000</v>
+        <v>18600</v>
       </c>
       <c r="H152" s="5">
         <v>0</v>
@@ -8260,13 +8260,13 @@
         <v>9</v>
       </c>
       <c r="J152" s="6">
-        <v>200</v>
+        <v>155</v>
       </c>
       <c r="K152" s="6">
         <v>42</v>
       </c>
       <c r="L152" s="7">
-        <v>4477.61</v>
+        <v>4532.16</v>
       </c>
       <c r="M152" s="8" t="s">
         <v>18</v>
@@ -8292,25 +8292,25 @@
         <v>400</v>
       </c>
       <c r="F153" s="11">
-        <v>22800</v>
+        <v>18400</v>
       </c>
       <c r="G153" s="11">
-        <v>22800</v>
+        <v>18400</v>
       </c>
       <c r="H153" s="11">
         <v>0</v>
       </c>
       <c r="I153" s="12">
-        <v>36</v>
+        <v>40</v>
       </c>
       <c r="J153" s="12">
-        <v>889</v>
+        <v>894</v>
       </c>
       <c r="K153" s="12">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="L153" s="13">
-        <v>1986.93</v>
+        <v>1917.47</v>
       </c>
       <c r="M153" s="14" t="s">
         <v>18</v>
@@ -8336,10 +8336,10 @@
         <v>500</v>
       </c>
       <c r="F154" s="5">
-        <v>14500</v>
+        <v>25000</v>
       </c>
       <c r="G154" s="5">
-        <v>14500</v>
+        <v>25000</v>
       </c>
       <c r="H154" s="5">
         <v>0</v>
@@ -8348,13 +8348,13 @@
         <v>9</v>
       </c>
       <c r="J154" s="6">
-        <v>219</v>
+        <v>241</v>
       </c>
       <c r="K154" s="6">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="L154" s="7">
-        <v>4820.48</v>
+        <v>5952.38</v>
       </c>
       <c r="M154" s="8" t="s">
         <v>18</v>
@@ -8380,25 +8380,25 @@
         <v>10</v>
       </c>
       <c r="F155" s="11">
-        <v>420</v>
+        <v>280</v>
       </c>
       <c r="G155" s="11">
-        <v>420</v>
+        <v>280</v>
       </c>
       <c r="H155" s="11">
         <v>0</v>
       </c>
       <c r="I155" s="12">
-        <v>123</v>
+        <v>121</v>
       </c>
       <c r="J155" s="12">
-        <v>1891</v>
+        <v>2101</v>
       </c>
       <c r="K155" s="12">
-        <v>316</v>
+        <v>339</v>
       </c>
       <c r="L155" s="13">
-        <v>28.43</v>
+        <v>25.47</v>
       </c>
       <c r="M155" s="14" t="s">
         <v>18</v>
@@ -8424,25 +8424,25 @@
         <v>25</v>
       </c>
       <c r="F156" s="5">
-        <v>625</v>
+        <v>1350</v>
       </c>
       <c r="G156" s="5">
-        <v>625</v>
+        <v>1350</v>
       </c>
       <c r="H156" s="5">
         <v>0</v>
       </c>
       <c r="I156" s="6">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="J156" s="6">
-        <v>122</v>
+        <v>105</v>
       </c>
       <c r="K156" s="6">
         <v>30</v>
       </c>
       <c r="L156" s="7">
-        <v>277.78</v>
+        <v>432.69</v>
       </c>
       <c r="M156" s="8" t="s">
         <v>18</v>
@@ -8468,25 +8468,25 @@
         <v>50</v>
       </c>
       <c r="F157" s="11">
-        <v>3000</v>
+        <v>2100</v>
       </c>
       <c r="G157" s="11">
-        <v>3000</v>
+        <v>2100</v>
       </c>
       <c r="H157" s="11">
         <v>0</v>
       </c>
       <c r="I157" s="12">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="J157" s="12">
-        <v>773</v>
+        <v>662</v>
       </c>
       <c r="K157" s="12">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="L157" s="13">
-        <v>354.61</v>
+        <v>331.75</v>
       </c>
       <c r="M157" s="14" t="s">
         <v>18</v>
@@ -8512,10 +8512,10 @@
         <v>100</v>
       </c>
       <c r="F158" s="5">
-        <v>5100</v>
+        <v>4500</v>
       </c>
       <c r="G158" s="5">
-        <v>5100</v>
+        <v>4500</v>
       </c>
       <c r="H158" s="5">
         <v>0</v>
@@ -8524,13 +8524,13 @@
         <v>9</v>
       </c>
       <c r="J158" s="6">
-        <v>152</v>
+        <v>140</v>
       </c>
       <c r="K158" s="6">
-        <v>33</v>
+        <v>36</v>
       </c>
       <c r="L158" s="7">
-        <v>1602.26</v>
+        <v>1442.31</v>
       </c>
       <c r="M158" s="8" t="s">
         <v>18</v>
@@ -8556,10 +8556,10 @@
         <v>150</v>
       </c>
       <c r="F159" s="11">
-        <v>8700</v>
+        <v>3300</v>
       </c>
       <c r="G159" s="11">
-        <v>8700</v>
+        <v>3300</v>
       </c>
       <c r="H159" s="11">
         <v>0</v>
@@ -8568,13 +8568,13 @@
         <v>9</v>
       </c>
       <c r="J159" s="12">
-        <v>122</v>
+        <v>169</v>
       </c>
       <c r="K159" s="12">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="L159" s="13">
-        <v>2386.18</v>
+        <v>1412.67</v>
       </c>
       <c r="M159" s="14" t="s">
         <v>18</v>
@@ -8600,25 +8600,25 @@
         <v>200</v>
       </c>
       <c r="F160" s="5">
-        <v>8000</v>
+        <v>10600</v>
       </c>
       <c r="G160" s="5">
-        <v>8000</v>
+        <v>10600</v>
       </c>
       <c r="H160" s="5">
         <v>0</v>
       </c>
       <c r="I160" s="6">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="J160" s="6">
-        <v>170</v>
+        <v>172</v>
       </c>
       <c r="K160" s="6">
         <v>40</v>
       </c>
       <c r="L160" s="7">
-        <v>2580.65</v>
+        <v>2928.18</v>
       </c>
       <c r="M160" s="8" t="s">
         <v>18</v>
@@ -8644,25 +8644,25 @@
         <v>300</v>
       </c>
       <c r="F161" s="11">
-        <v>6300</v>
+        <v>12300</v>
       </c>
       <c r="G161" s="11">
-        <v>6300</v>
+        <v>12300</v>
       </c>
       <c r="H161" s="11">
         <v>0</v>
       </c>
       <c r="I161" s="12">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="J161" s="12">
-        <v>177</v>
+        <v>169</v>
       </c>
       <c r="K161" s="12">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="L161" s="13">
-        <v>2599.01</v>
+        <v>3677.13</v>
       </c>
       <c r="M161" s="14" t="s">
         <v>18</v>
@@ -8688,10 +8688,10 @@
         <v>400</v>
       </c>
       <c r="F162" s="5">
-        <v>11200</v>
+        <v>20400</v>
       </c>
       <c r="G162" s="5">
-        <v>11200</v>
+        <v>20400</v>
       </c>
       <c r="H162" s="5">
         <v>0</v>
@@ -8700,13 +8700,13 @@
         <v>9</v>
       </c>
       <c r="J162" s="6">
-        <v>215</v>
+        <v>181</v>
       </c>
       <c r="K162" s="6">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="L162" s="7">
-        <v>3977.27</v>
+        <v>5101.28</v>
       </c>
       <c r="M162" s="8" t="s">
         <v>18</v>
@@ -8732,10 +8732,10 @@
         <v>500</v>
       </c>
       <c r="F163" s="11">
-        <v>27000</v>
+        <v>28500</v>
       </c>
       <c r="G163" s="11">
-        <v>27000</v>
+        <v>28500</v>
       </c>
       <c r="H163" s="11">
         <v>0</v>
@@ -8744,13 +8744,13 @@
         <v>10</v>
       </c>
       <c r="J163" s="12">
-        <v>213</v>
+        <v>194</v>
       </c>
       <c r="K163" s="12">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="L163" s="13">
-        <v>6189.82</v>
+        <v>6466.98</v>
       </c>
       <c r="M163" s="14" t="s">
         <v>18</v>
@@ -8776,25 +8776,25 @@
         <v>10</v>
       </c>
       <c r="F164" s="5">
-        <v>270</v>
+        <v>620</v>
       </c>
       <c r="G164" s="5">
-        <v>270</v>
+        <v>620</v>
       </c>
       <c r="H164" s="5">
         <v>0</v>
       </c>
       <c r="I164" s="6">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="J164" s="6">
-        <v>606</v>
+        <v>768</v>
       </c>
       <c r="K164" s="6">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="L164" s="7">
-        <v>60.4</v>
+        <v>75.65</v>
       </c>
       <c r="M164" s="8" t="s">
         <v>18</v>
@@ -8820,10 +8820,10 @@
         <v>25</v>
       </c>
       <c r="F165" s="11">
-        <v>725</v>
+        <v>500</v>
       </c>
       <c r="G165" s="11">
-        <v>725</v>
+        <v>500</v>
       </c>
       <c r="H165" s="11">
         <v>0</v>
@@ -8832,13 +8832,13 @@
         <v>9</v>
       </c>
       <c r="J165" s="12">
-        <v>138</v>
+        <v>100</v>
       </c>
       <c r="K165" s="12">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="L165" s="13">
-        <v>305.91</v>
+        <v>240.38</v>
       </c>
       <c r="M165" s="14" t="s">
         <v>18</v>
@@ -8864,25 +8864,25 @@
         <v>50</v>
       </c>
       <c r="F166" s="5">
-        <v>2650</v>
+        <v>2150</v>
       </c>
       <c r="G166" s="5">
-        <v>2650</v>
+        <v>2150</v>
       </c>
       <c r="H166" s="5">
         <v>0</v>
       </c>
       <c r="I166" s="6">
-        <v>122</v>
+        <v>119</v>
       </c>
       <c r="J166" s="6">
-        <v>2004</v>
+        <v>2047</v>
       </c>
       <c r="K166" s="6">
-        <v>357</v>
+        <v>355</v>
       </c>
       <c r="L166" s="7">
-        <v>129.77</v>
+        <v>128.24</v>
       </c>
       <c r="M166" s="8" t="s">
         <v>18</v>
@@ -8908,25 +8908,25 @@
         <v>100</v>
       </c>
       <c r="F167" s="11">
-        <v>5700</v>
+        <v>4900</v>
       </c>
       <c r="G167" s="11">
-        <v>5700</v>
+        <v>4900</v>
       </c>
       <c r="H167" s="11">
         <v>0</v>
       </c>
       <c r="I167" s="12">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="J167" s="12">
-        <v>155</v>
+        <v>159</v>
       </c>
       <c r="K167" s="12">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="L167" s="13">
-        <v>1604.73</v>
+        <v>1524.11</v>
       </c>
       <c r="M167" s="14" t="s">
         <v>18</v>
@@ -8952,10 +8952,10 @@
         <v>150</v>
       </c>
       <c r="F168" s="5">
-        <v>4800</v>
+        <v>9600</v>
       </c>
       <c r="G168" s="5">
-        <v>4800</v>
+        <v>9600</v>
       </c>
       <c r="H168" s="5">
         <v>0</v>
@@ -8964,13 +8964,13 @@
         <v>40</v>
       </c>
       <c r="J168" s="6">
-        <v>958</v>
+        <v>655</v>
       </c>
       <c r="K168" s="6">
-        <v>129</v>
+        <v>131</v>
       </c>
       <c r="L168" s="7">
-        <v>852.88</v>
+        <v>971.27</v>
       </c>
       <c r="M168" s="8" t="s">
         <v>18</v>
@@ -8996,10 +8996,10 @@
         <v>200</v>
       </c>
       <c r="F169" s="11">
-        <v>7600</v>
+        <v>5000</v>
       </c>
       <c r="G169" s="11">
-        <v>7600</v>
+        <v>5000</v>
       </c>
       <c r="H169" s="11">
         <v>0</v>
@@ -9008,13 +9008,13 @@
         <v>10</v>
       </c>
       <c r="J169" s="12">
-        <v>175</v>
+        <v>167</v>
       </c>
       <c r="K169" s="12">
-        <v>40</v>
+        <v>37</v>
       </c>
       <c r="L169" s="13">
-        <v>2516.56</v>
+        <v>2061.86</v>
       </c>
       <c r="M169" s="14" t="s">
         <v>18</v>
@@ -9040,25 +9040,25 @@
         <v>300</v>
       </c>
       <c r="F170" s="5">
-        <v>6600</v>
+        <v>6900</v>
       </c>
       <c r="G170" s="5">
-        <v>6600</v>
+        <v>6900</v>
       </c>
       <c r="H170" s="5">
         <v>0</v>
       </c>
       <c r="I170" s="6">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="J170" s="6">
-        <v>200</v>
+        <v>202</v>
       </c>
       <c r="K170" s="6">
         <v>44</v>
       </c>
       <c r="L170" s="7">
-        <v>2674.23</v>
+        <v>2746.82</v>
       </c>
       <c r="M170" s="8" t="s">
         <v>18</v>
@@ -9084,25 +9084,25 @@
         <v>400</v>
       </c>
       <c r="F171" s="11">
-        <v>20800</v>
+        <v>22800</v>
       </c>
       <c r="G171" s="11">
-        <v>20800</v>
+        <v>22800</v>
       </c>
       <c r="H171" s="11">
         <v>0</v>
       </c>
       <c r="I171" s="12">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="J171" s="12">
-        <v>232</v>
+        <v>203</v>
       </c>
       <c r="K171" s="12">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="L171" s="13">
-        <v>5009.63</v>
+        <v>5310.97</v>
       </c>
       <c r="M171" s="14" t="s">
         <v>18</v>
@@ -9128,25 +9128,25 @@
         <v>500</v>
       </c>
       <c r="F172" s="5">
-        <v>10500</v>
+        <v>32000</v>
       </c>
       <c r="G172" s="5">
-        <v>10500</v>
+        <v>32000</v>
       </c>
       <c r="H172" s="5">
         <v>0</v>
       </c>
       <c r="I172" s="6">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="J172" s="6">
-        <v>239</v>
+        <v>255</v>
       </c>
       <c r="K172" s="6">
         <v>53</v>
       </c>
       <c r="L172" s="7">
-        <v>4018.37</v>
+        <v>6541.29</v>
       </c>
       <c r="M172" s="8" t="s">
         <v>18</v>
@@ -9172,10 +9172,10 @@
         <v>10</v>
       </c>
       <c r="F173" s="11">
-        <v>670</v>
+        <v>260</v>
       </c>
       <c r="G173" s="11">
-        <v>670</v>
+        <v>260</v>
       </c>
       <c r="H173" s="11">
         <v>0</v>
@@ -9184,13 +9184,13 @@
         <v>9</v>
       </c>
       <c r="J173" s="12">
-        <v>111</v>
+        <v>141</v>
       </c>
       <c r="K173" s="12">
         <v>30</v>
       </c>
       <c r="L173" s="13">
-        <v>190.88</v>
+        <v>114.04</v>
       </c>
       <c r="M173" s="14" t="s">
         <v>18</v>
@@ -9216,10 +9216,10 @@
         <v>25</v>
       </c>
       <c r="F174" s="5">
-        <v>525</v>
+        <v>1075</v>
       </c>
       <c r="G174" s="5">
-        <v>525</v>
+        <v>1075</v>
       </c>
       <c r="H174" s="5">
         <v>0</v>
@@ -9228,13 +9228,13 @@
         <v>9</v>
       </c>
       <c r="J174" s="6">
-        <v>130</v>
+        <v>102</v>
       </c>
       <c r="K174" s="6">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="L174" s="7">
-        <v>241.71</v>
+        <v>385.3</v>
       </c>
       <c r="M174" s="8" t="s">
         <v>18</v>
@@ -9260,25 +9260,25 @@
         <v>50</v>
       </c>
       <c r="F175" s="11">
-        <v>2250</v>
+        <v>3400</v>
       </c>
       <c r="G175" s="11">
-        <v>2250</v>
+        <v>3400</v>
       </c>
       <c r="H175" s="11">
         <v>0</v>
       </c>
       <c r="I175" s="12">
-        <v>37</v>
+        <v>42</v>
       </c>
       <c r="J175" s="12">
-        <v>642</v>
+        <v>698</v>
       </c>
       <c r="K175" s="12">
-        <v>114</v>
+        <v>122</v>
       </c>
       <c r="L175" s="13">
-        <v>339.37</v>
+        <v>347.08</v>
       </c>
       <c r="M175" s="14" t="s">
         <v>18</v>
@@ -9304,25 +9304,25 @@
         <v>100</v>
       </c>
       <c r="F176" s="5">
-        <v>2400</v>
+        <v>6000</v>
       </c>
       <c r="G176" s="5">
-        <v>2400</v>
+        <v>6000</v>
       </c>
       <c r="H176" s="5">
         <v>0</v>
       </c>
       <c r="I176" s="6">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="J176" s="6">
-        <v>157</v>
+        <v>141</v>
       </c>
       <c r="K176" s="6">
         <v>36</v>
       </c>
       <c r="L176" s="7">
-        <v>1015.23</v>
+        <v>1639.34</v>
       </c>
       <c r="M176" s="8" t="s">
         <v>18</v>
@@ -9348,25 +9348,25 @@
         <v>150</v>
       </c>
       <c r="F177" s="11">
-        <v>8250</v>
+        <v>6300</v>
       </c>
       <c r="G177" s="11">
-        <v>8250</v>
+        <v>6300</v>
       </c>
       <c r="H177" s="11">
         <v>0</v>
       </c>
       <c r="I177" s="12">
-        <v>130</v>
+        <v>117</v>
       </c>
       <c r="J177" s="12">
-        <v>2029</v>
+        <v>2091</v>
       </c>
       <c r="K177" s="12">
-        <v>415</v>
+        <v>393</v>
       </c>
       <c r="L177" s="13">
-        <v>339.16</v>
+        <v>349.88</v>
       </c>
       <c r="M177" s="14" t="s">
         <v>18</v>
@@ -9392,25 +9392,25 @@
         <v>200</v>
       </c>
       <c r="F178" s="5">
-        <v>7400</v>
+        <v>12600</v>
       </c>
       <c r="G178" s="5">
-        <v>7400</v>
+        <v>12600</v>
       </c>
       <c r="H178" s="5">
         <v>0</v>
       </c>
       <c r="I178" s="6">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="J178" s="6">
-        <v>137</v>
+        <v>135</v>
       </c>
       <c r="K178" s="6">
         <v>41</v>
       </c>
       <c r="L178" s="7">
-        <v>2452.77</v>
+        <v>3085.97</v>
       </c>
       <c r="M178" s="8" t="s">
         <v>18</v>
@@ -9436,25 +9436,25 @@
         <v>300</v>
       </c>
       <c r="F179" s="11">
-        <v>8400</v>
+        <v>10800</v>
       </c>
       <c r="G179" s="11">
-        <v>8400</v>
+        <v>10800</v>
       </c>
       <c r="H179" s="11">
         <v>0</v>
       </c>
       <c r="I179" s="12">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="J179" s="12">
-        <v>1076</v>
+        <v>971</v>
       </c>
       <c r="K179" s="12">
-        <v>158</v>
+        <v>164</v>
       </c>
       <c r="L179" s="13">
-        <v>1417.96</v>
+        <v>1458.67</v>
       </c>
       <c r="M179" s="14" t="s">
         <v>18</v>
@@ -9480,10 +9480,10 @@
         <v>400</v>
       </c>
       <c r="F180" s="5">
-        <v>12000</v>
+        <v>26000</v>
       </c>
       <c r="G180" s="5">
-        <v>12000</v>
+        <v>26000</v>
       </c>
       <c r="H180" s="5">
         <v>0</v>
@@ -9492,13 +9492,13 @@
         <v>10</v>
       </c>
       <c r="J180" s="6">
-        <v>222</v>
+        <v>188</v>
       </c>
       <c r="K180" s="6">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="L180" s="7">
-        <v>4081.63</v>
+        <v>5473.68</v>
       </c>
       <c r="M180" s="8" t="s">
         <v>18</v>
@@ -9524,10 +9524,10 @@
         <v>500</v>
       </c>
       <c r="F181" s="11">
-        <v>13500</v>
+        <v>24000</v>
       </c>
       <c r="G181" s="11">
-        <v>13500</v>
+        <v>24000</v>
       </c>
       <c r="H181" s="11">
         <v>0</v>
@@ -9536,13 +9536,13 @@
         <v>9</v>
       </c>
       <c r="J181" s="12">
-        <v>175</v>
+        <v>227</v>
       </c>
       <c r="K181" s="12">
-        <v>52</v>
+        <v>56</v>
       </c>
       <c r="L181" s="13">
-        <v>4648.76</v>
+        <v>5730.66</v>
       </c>
       <c r="M181" s="14" t="s">
         <v>18</v>
@@ -9568,10 +9568,10 @@
         <v>10</v>
       </c>
       <c r="F182" s="5">
-        <v>320</v>
+        <v>580</v>
       </c>
       <c r="G182" s="5">
-        <v>320</v>
+        <v>580</v>
       </c>
       <c r="H182" s="5">
         <v>0</v>
@@ -9580,13 +9580,13 @@
         <v>10</v>
       </c>
       <c r="J182" s="6">
-        <v>98</v>
+        <v>141</v>
       </c>
       <c r="K182" s="6">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="L182" s="7">
-        <v>133.56</v>
+        <v>182.28</v>
       </c>
       <c r="M182" s="8" t="s">
         <v>18</v>
@@ -9624,7 +9624,7 @@
         <v>10</v>
       </c>
       <c r="J183" s="12">
-        <v>121</v>
+        <v>112</v>
       </c>
       <c r="K183" s="12">
         <v>30</v>
@@ -9668,7 +9668,7 @@
         <v>10</v>
       </c>
       <c r="J184" s="6">
-        <v>109</v>
+        <v>149</v>
       </c>
       <c r="K184" s="6">
         <v>33</v>
@@ -9700,25 +9700,25 @@
         <v>100</v>
       </c>
       <c r="F185" s="11">
-        <v>2600</v>
+        <v>2000</v>
       </c>
       <c r="G185" s="11">
-        <v>2600</v>
+        <v>2000</v>
       </c>
       <c r="H185" s="11">
         <v>0</v>
       </c>
       <c r="I185" s="12">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="J185" s="12">
-        <v>114</v>
+        <v>161</v>
       </c>
       <c r="K185" s="12">
         <v>35</v>
       </c>
       <c r="L185" s="13">
-        <v>1078.84</v>
+        <v>909.09</v>
       </c>
       <c r="M185" s="14" t="s">
         <v>18</v>
@@ -9744,25 +9744,25 @@
         <v>150</v>
       </c>
       <c r="F186" s="5">
-        <v>3750</v>
+        <v>3300</v>
       </c>
       <c r="G186" s="5">
-        <v>3750</v>
+        <v>3300</v>
       </c>
       <c r="H186" s="5">
         <v>0</v>
       </c>
       <c r="I186" s="6">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="J186" s="6">
-        <v>860</v>
+        <v>661</v>
       </c>
       <c r="K186" s="6">
-        <v>138</v>
+        <v>142</v>
       </c>
       <c r="L186" s="7">
-        <v>757.58</v>
+        <v>713.67</v>
       </c>
       <c r="M186" s="8" t="s">
         <v>18</v>
@@ -9788,10 +9788,10 @@
         <v>200</v>
       </c>
       <c r="F187" s="11">
-        <v>13800</v>
+        <v>6200</v>
       </c>
       <c r="G187" s="11">
-        <v>13800</v>
+        <v>6200</v>
       </c>
       <c r="H187" s="11">
         <v>0</v>
@@ -9800,13 +9800,13 @@
         <v>10</v>
       </c>
       <c r="J187" s="12">
-        <v>178</v>
+        <v>132</v>
       </c>
       <c r="K187" s="12">
         <v>37</v>
       </c>
       <c r="L187" s="13">
-        <v>3404.89</v>
+        <v>2342.27</v>
       </c>
       <c r="M187" s="14" t="s">
         <v>18</v>
@@ -9832,25 +9832,25 @@
         <v>300</v>
       </c>
       <c r="F188" s="5">
-        <v>15000</v>
+        <v>9600</v>
       </c>
       <c r="G188" s="5">
-        <v>15000</v>
+        <v>9600</v>
       </c>
       <c r="H188" s="5">
         <v>0</v>
       </c>
       <c r="I188" s="6">
-        <v>130</v>
+        <v>112</v>
       </c>
       <c r="J188" s="6">
-        <v>3011</v>
+        <v>3024</v>
       </c>
       <c r="K188" s="6">
-        <v>492</v>
+        <v>468</v>
       </c>
       <c r="L188" s="7">
-        <v>574.71</v>
+        <v>582.67</v>
       </c>
       <c r="M188" s="8" t="s">
         <v>18</v>
@@ -9876,10 +9876,10 @@
         <v>400</v>
       </c>
       <c r="F189" s="11">
-        <v>12400</v>
+        <v>24000</v>
       </c>
       <c r="G189" s="11">
-        <v>12400</v>
+        <v>24000</v>
       </c>
       <c r="H189" s="11">
         <v>0</v>
@@ -9888,13 +9888,13 @@
         <v>9</v>
       </c>
       <c r="J189" s="12">
-        <v>182</v>
+        <v>174</v>
       </c>
       <c r="K189" s="12">
-        <v>50</v>
+        <v>47</v>
       </c>
       <c r="L189" s="13">
-        <v>4065.57</v>
+        <v>5555.56</v>
       </c>
       <c r="M189" s="14" t="s">
         <v>18</v>
@@ -9920,10 +9920,10 @@
         <v>500</v>
       </c>
       <c r="F190" s="5">
-        <v>19000</v>
+        <v>27500</v>
       </c>
       <c r="G190" s="5">
-        <v>19000</v>
+        <v>27500</v>
       </c>
       <c r="H190" s="5">
         <v>0</v>
@@ -9932,13 +9932,13 @@
         <v>42</v>
       </c>
       <c r="J190" s="6">
-        <v>1162</v>
+        <v>985</v>
       </c>
       <c r="K190" s="6">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="L190" s="7">
-        <v>2178.9</v>
+        <v>2290.71</v>
       </c>
       <c r="M190" s="8" t="s">
         <v>18</v>
@@ -9964,25 +9964,25 @@
         <v>10</v>
       </c>
       <c r="F191" s="11">
-        <v>650</v>
+        <v>520</v>
       </c>
       <c r="G191" s="11">
-        <v>650</v>
+        <v>520</v>
       </c>
       <c r="H191" s="11">
         <v>0</v>
       </c>
       <c r="I191" s="12">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="J191" s="12">
-        <v>126</v>
+        <v>121</v>
       </c>
       <c r="K191" s="12">
         <v>29</v>
       </c>
       <c r="L191" s="13">
-        <v>192.02</v>
+        <v>172.87</v>
       </c>
       <c r="M191" s="14" t="s">
         <v>18</v>
@@ -10008,10 +10008,10 @@
         <v>25</v>
       </c>
       <c r="F192" s="5">
-        <v>1150</v>
+        <v>750</v>
       </c>
       <c r="G192" s="5">
-        <v>1150</v>
+        <v>750</v>
       </c>
       <c r="H192" s="5">
         <v>0</v>
@@ -10020,13 +10020,13 @@
         <v>9</v>
       </c>
       <c r="J192" s="6">
-        <v>139</v>
+        <v>124</v>
       </c>
       <c r="K192" s="6">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="L192" s="7">
-        <v>386.94</v>
+        <v>312.5</v>
       </c>
       <c r="M192" s="8" t="s">
         <v>18</v>
@@ -10052,10 +10052,10 @@
         <v>50</v>
       </c>
       <c r="F193" s="11">
-        <v>3000</v>
+        <v>2900</v>
       </c>
       <c r="G193" s="11">
-        <v>3000</v>
+        <v>2900</v>
       </c>
       <c r="H193" s="11">
         <v>0</v>
@@ -10064,13 +10064,13 @@
         <v>10</v>
       </c>
       <c r="J193" s="12">
-        <v>108</v>
+        <v>138</v>
       </c>
       <c r="K193" s="12">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="L193" s="13">
-        <v>877.19</v>
+        <v>849.44</v>
       </c>
       <c r="M193" s="14" t="s">
         <v>18</v>
@@ -10096,25 +10096,25 @@
         <v>100</v>
       </c>
       <c r="F194" s="5">
-        <v>4100</v>
+        <v>4600</v>
       </c>
       <c r="G194" s="5">
-        <v>4100</v>
+        <v>4600</v>
       </c>
       <c r="H194" s="5">
         <v>0</v>
       </c>
       <c r="I194" s="6">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="J194" s="6">
-        <v>144</v>
+        <v>116</v>
       </c>
       <c r="K194" s="6">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="L194" s="7">
-        <v>1437.08</v>
+        <v>1501.31</v>
       </c>
       <c r="M194" s="8" t="s">
         <v>18</v>
@@ -10140,10 +10140,10 @@
         <v>150</v>
       </c>
       <c r="F195" s="11">
-        <v>3300</v>
+        <v>8700</v>
       </c>
       <c r="G195" s="11">
-        <v>3300</v>
+        <v>8700</v>
       </c>
       <c r="H195" s="11">
         <v>0</v>
@@ -10152,13 +10152,13 @@
         <v>9</v>
       </c>
       <c r="J195" s="12">
-        <v>131</v>
+        <v>166</v>
       </c>
       <c r="K195" s="12">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="L195" s="13">
-        <v>1453.74</v>
+        <v>2424.75</v>
       </c>
       <c r="M195" s="14" t="s">
         <v>18</v>
@@ -10184,25 +10184,25 @@
         <v>200</v>
       </c>
       <c r="F196" s="5">
-        <v>13200</v>
+        <v>5400</v>
       </c>
       <c r="G196" s="5">
-        <v>13200</v>
+        <v>5400</v>
       </c>
       <c r="H196" s="5">
         <v>0</v>
       </c>
       <c r="I196" s="6">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="J196" s="6">
-        <v>174</v>
+        <v>157</v>
       </c>
       <c r="K196" s="6">
         <v>40</v>
       </c>
       <c r="L196" s="7">
-        <v>3188.41</v>
+        <v>2093.02</v>
       </c>
       <c r="M196" s="8" t="s">
         <v>18</v>
@@ -10228,25 +10228,25 @@
         <v>300</v>
       </c>
       <c r="F197" s="11">
-        <v>11700</v>
+        <v>13500</v>
       </c>
       <c r="G197" s="11">
-        <v>11700</v>
+        <v>13500</v>
       </c>
       <c r="H197" s="11">
         <v>0</v>
       </c>
       <c r="I197" s="12">
-        <v>38</v>
+        <v>41</v>
       </c>
       <c r="J197" s="12">
-        <v>1146</v>
+        <v>821</v>
       </c>
       <c r="K197" s="12">
-        <v>155</v>
+        <v>162</v>
       </c>
       <c r="L197" s="13">
-        <v>1550.7</v>
+        <v>1535.84</v>
       </c>
       <c r="M197" s="14" t="s">
         <v>18</v>
@@ -10272,25 +10272,25 @@
         <v>400</v>
       </c>
       <c r="F198" s="5">
-        <v>24000</v>
+        <v>23600</v>
       </c>
       <c r="G198" s="5">
-        <v>24000</v>
+        <v>23600</v>
       </c>
       <c r="H198" s="5">
         <v>0</v>
       </c>
       <c r="I198" s="6">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="J198" s="6">
-        <v>208</v>
+        <v>203</v>
       </c>
       <c r="K198" s="6">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="L198" s="7">
-        <v>5633.8</v>
+        <v>5523.05</v>
       </c>
       <c r="M198" s="8" t="s">
         <v>18</v>
@@ -10316,25 +10316,25 @@
         <v>500</v>
       </c>
       <c r="F199" s="11">
-        <v>34500</v>
+        <v>30000</v>
       </c>
       <c r="G199" s="11">
-        <v>34500</v>
+        <v>30000</v>
       </c>
       <c r="H199" s="11">
         <v>0</v>
       </c>
       <c r="I199" s="12">
-        <v>116</v>
+        <v>110</v>
       </c>
       <c r="J199" s="12">
-        <v>3303</v>
+        <v>2666</v>
       </c>
       <c r="K199" s="12">
-        <v>587</v>
+        <v>553</v>
       </c>
       <c r="L199" s="13">
-        <v>821.37</v>
+        <v>865.05</v>
       </c>
       <c r="M199" s="14" t="s">
         <v>18</v>
@@ -10360,10 +10360,10 @@
         <v>10</v>
       </c>
       <c r="F200" s="5">
-        <v>630</v>
+        <v>420</v>
       </c>
       <c r="G200" s="5">
-        <v>630</v>
+        <v>420</v>
       </c>
       <c r="H200" s="5">
         <v>0</v>
@@ -10372,13 +10372,13 @@
         <v>9</v>
       </c>
       <c r="J200" s="6">
-        <v>101</v>
+        <v>138</v>
       </c>
       <c r="K200" s="6">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="L200" s="7">
-        <v>185.84</v>
+        <v>154.53</v>
       </c>
       <c r="M200" s="8" t="s">
         <v>18</v>
@@ -10404,25 +10404,25 @@
         <v>25</v>
       </c>
       <c r="F201" s="11">
-        <v>1600</v>
+        <v>1525</v>
       </c>
       <c r="G201" s="11">
-        <v>1600</v>
+        <v>1525</v>
       </c>
       <c r="H201" s="11">
         <v>0</v>
       </c>
       <c r="I201" s="12">
-        <v>41</v>
+        <v>37</v>
       </c>
       <c r="J201" s="12">
-        <v>788</v>
+        <v>758</v>
       </c>
       <c r="K201" s="12">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="L201" s="13">
-        <v>185.96</v>
+        <v>185.75</v>
       </c>
       <c r="M201" s="14" t="s">
         <v>18</v>
@@ -10448,10 +10448,10 @@
         <v>50</v>
       </c>
       <c r="F202" s="5">
-        <v>1950</v>
+        <v>3100</v>
       </c>
       <c r="G202" s="5">
-        <v>1950</v>
+        <v>3100</v>
       </c>
       <c r="H202" s="5">
         <v>0</v>
@@ -10460,13 +10460,13 @@
         <v>10</v>
       </c>
       <c r="J202" s="6">
-        <v>115</v>
+        <v>133</v>
       </c>
       <c r="K202" s="6">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="L202" s="7">
-        <v>719.82</v>
+        <v>874.22</v>
       </c>
       <c r="M202" s="8" t="s">
         <v>18</v>
@@ -10492,25 +10492,25 @@
         <v>100</v>
       </c>
       <c r="F203" s="11">
-        <v>6500</v>
+        <v>6900</v>
       </c>
       <c r="G203" s="11">
-        <v>6500</v>
+        <v>6900</v>
       </c>
       <c r="H203" s="11">
         <v>0</v>
       </c>
       <c r="I203" s="12">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="J203" s="12">
-        <v>166</v>
+        <v>119</v>
       </c>
       <c r="K203" s="12">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="L203" s="13">
-        <v>1721.85</v>
+        <v>1826.85</v>
       </c>
       <c r="M203" s="14" t="s">
         <v>18</v>
@@ -10536,10 +10536,10 @@
         <v>150</v>
       </c>
       <c r="F204" s="5">
-        <v>5400</v>
+        <v>7050</v>
       </c>
       <c r="G204" s="5">
-        <v>5400</v>
+        <v>7050</v>
       </c>
       <c r="H204" s="5">
         <v>0</v>
@@ -10548,13 +10548,13 @@
         <v>9</v>
       </c>
       <c r="J204" s="6">
-        <v>137</v>
+        <v>155</v>
       </c>
       <c r="K204" s="6">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="L204" s="7">
-        <v>1956.52</v>
+        <v>2176.6</v>
       </c>
       <c r="M204" s="8" t="s">
         <v>18</v>
@@ -10580,10 +10580,10 @@
         <v>200</v>
       </c>
       <c r="F205" s="11">
-        <v>12000</v>
+        <v>10200</v>
       </c>
       <c r="G205" s="11">
-        <v>12000</v>
+        <v>10200</v>
       </c>
       <c r="H205" s="11">
         <v>0</v>
@@ -10592,13 +10592,13 @@
         <v>9</v>
       </c>
       <c r="J205" s="12">
-        <v>171</v>
+        <v>182</v>
       </c>
       <c r="K205" s="12">
-        <v>41</v>
+        <v>38</v>
       </c>
       <c r="L205" s="13">
-        <v>3030.3</v>
+        <v>2966.84</v>
       </c>
       <c r="M205" s="14" t="s">
         <v>18</v>
@@ -10624,25 +10624,25 @@
         <v>300</v>
       </c>
       <c r="F206" s="5">
-        <v>15600</v>
+        <v>16200</v>
       </c>
       <c r="G206" s="5">
-        <v>15600</v>
+        <v>16200</v>
       </c>
       <c r="H206" s="5">
         <v>0</v>
       </c>
       <c r="I206" s="6">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="J206" s="6">
-        <v>161</v>
+        <v>209</v>
       </c>
       <c r="K206" s="6">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="L206" s="7">
-        <v>4175.59</v>
+        <v>4179.57</v>
       </c>
       <c r="M206" s="8" t="s">
         <v>18</v>
@@ -10668,25 +10668,25 @@
         <v>400</v>
       </c>
       <c r="F207" s="11">
-        <v>19200</v>
+        <v>20400</v>
       </c>
       <c r="G207" s="11">
-        <v>19200</v>
+        <v>20400</v>
       </c>
       <c r="H207" s="11">
         <v>0</v>
       </c>
       <c r="I207" s="12">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="J207" s="12">
-        <v>161</v>
+        <v>163</v>
       </c>
       <c r="K207" s="12">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="L207" s="13">
-        <v>4923.08</v>
+        <v>5101.28</v>
       </c>
       <c r="M207" s="14" t="s">
         <v>18</v>
@@ -10712,25 +10712,25 @@
         <v>500</v>
       </c>
       <c r="F208" s="5">
-        <v>27000</v>
+        <v>20000</v>
       </c>
       <c r="G208" s="5">
-        <v>27000</v>
+        <v>20000</v>
       </c>
       <c r="H208" s="5">
         <v>0</v>
       </c>
       <c r="I208" s="6">
-        <v>40</v>
+        <v>37</v>
       </c>
       <c r="J208" s="6">
-        <v>1247</v>
+        <v>1233</v>
       </c>
       <c r="K208" s="6">
-        <v>193</v>
+        <v>200</v>
       </c>
       <c r="L208" s="7">
-        <v>2264.72</v>
+        <v>2105.26</v>
       </c>
       <c r="M208" s="8" t="s">
         <v>18</v>
@@ -10756,10 +10756,10 @@
         <v>10</v>
       </c>
       <c r="F209" s="11">
-        <v>380</v>
+        <v>390</v>
       </c>
       <c r="G209" s="11">
-        <v>380</v>
+        <v>390</v>
       </c>
       <c r="H209" s="11">
         <v>0</v>
@@ -10768,13 +10768,13 @@
         <v>10</v>
       </c>
       <c r="J209" s="12">
-        <v>126</v>
+        <v>135</v>
       </c>
       <c r="K209" s="12">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="L209" s="13">
-        <v>146.04</v>
+        <v>146.07</v>
       </c>
       <c r="M209" s="14" t="s">
         <v>18</v>
@@ -10800,25 +10800,25 @@
         <v>25</v>
       </c>
       <c r="F210" s="5">
-        <v>675</v>
+        <v>1450</v>
       </c>
       <c r="G210" s="5">
-        <v>675</v>
+        <v>1450</v>
       </c>
       <c r="H210" s="5">
         <v>0</v>
       </c>
       <c r="I210" s="6">
-        <v>126</v>
+        <v>112</v>
       </c>
       <c r="J210" s="6">
-        <v>1724</v>
+        <v>1716</v>
       </c>
       <c r="K210" s="6">
-        <v>338</v>
+        <v>334</v>
       </c>
       <c r="L210" s="7">
-        <v>63.52</v>
+        <v>69.47</v>
       </c>
       <c r="M210" s="8" t="s">
         <v>18</v>
@@ -10844,10 +10844,10 @@
         <v>50</v>
       </c>
       <c r="F211" s="11">
-        <v>1250</v>
+        <v>2300</v>
       </c>
       <c r="G211" s="11">
-        <v>1250</v>
+        <v>2300</v>
       </c>
       <c r="H211" s="11">
         <v>0</v>
@@ -10856,13 +10856,13 @@
         <v>9</v>
       </c>
       <c r="J211" s="12">
-        <v>135</v>
+        <v>118</v>
       </c>
       <c r="K211" s="12">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="L211" s="13">
-        <v>543.48</v>
+        <v>762.09</v>
       </c>
       <c r="M211" s="14" t="s">
         <v>18</v>
@@ -10888,25 +10888,25 @@
         <v>100</v>
       </c>
       <c r="F212" s="5">
-        <v>6700</v>
+        <v>6200</v>
       </c>
       <c r="G212" s="5">
-        <v>6700</v>
+        <v>6200</v>
       </c>
       <c r="H212" s="5">
         <v>0</v>
       </c>
       <c r="I212" s="6">
-        <v>41</v>
+        <v>38</v>
       </c>
       <c r="J212" s="6">
-        <v>655</v>
+        <v>898</v>
       </c>
       <c r="K212" s="6">
-        <v>129</v>
+        <v>132</v>
       </c>
       <c r="L212" s="7">
-        <v>660.55</v>
+        <v>640.23</v>
       </c>
       <c r="M212" s="8" t="s">
         <v>18</v>
@@ -10932,10 +10932,10 @@
         <v>150</v>
       </c>
       <c r="F213" s="11">
-        <v>6600</v>
+        <v>7650</v>
       </c>
       <c r="G213" s="11">
-        <v>6600</v>
+        <v>7650</v>
       </c>
       <c r="H213" s="11">
         <v>0</v>
@@ -10944,13 +10944,13 @@
         <v>9</v>
       </c>
       <c r="J213" s="12">
-        <v>127</v>
+        <v>153</v>
       </c>
       <c r="K213" s="12">
         <v>37</v>
       </c>
       <c r="L213" s="13">
-        <v>2109.97</v>
+        <v>2258.64</v>
       </c>
       <c r="M213" s="14" t="s">
         <v>18</v>
@@ -10976,25 +10976,25 @@
         <v>200</v>
       </c>
       <c r="F214" s="5">
-        <v>11000</v>
+        <v>13600</v>
       </c>
       <c r="G214" s="5">
-        <v>11000</v>
+        <v>13600</v>
       </c>
       <c r="H214" s="5">
         <v>0</v>
       </c>
       <c r="I214" s="6">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="J214" s="6">
-        <v>173</v>
+        <v>167</v>
       </c>
       <c r="K214" s="6">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="L214" s="7">
-        <v>2929.43</v>
+        <v>3275.53</v>
       </c>
       <c r="M214" s="8" t="s">
         <v>18</v>
@@ -11020,10 +11020,10 @@
         <v>300</v>
       </c>
       <c r="F215" s="11">
-        <v>15300</v>
+        <v>12600</v>
       </c>
       <c r="G215" s="11">
-        <v>15300</v>
+        <v>12600</v>
       </c>
       <c r="H215" s="11">
         <v>0</v>
@@ -11032,13 +11032,13 @@
         <v>9</v>
       </c>
       <c r="J215" s="12">
-        <v>187</v>
+        <v>197</v>
       </c>
       <c r="K215" s="12">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="L215" s="13">
-        <v>4086.54</v>
+        <v>3811.25</v>
       </c>
       <c r="M215" s="14" t="s">
         <v>18</v>
@@ -11064,10 +11064,10 @@
         <v>400</v>
       </c>
       <c r="F216" s="5">
-        <v>16800</v>
+        <v>8000</v>
       </c>
       <c r="G216" s="5">
-        <v>16800</v>
+        <v>8000</v>
       </c>
       <c r="H216" s="5">
         <v>0</v>
@@ -11076,13 +11076,13 @@
         <v>9</v>
       </c>
       <c r="J216" s="6">
-        <v>210</v>
+        <v>219</v>
       </c>
       <c r="K216" s="6">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="L216" s="7">
-        <v>4895.1</v>
+        <v>3252.03</v>
       </c>
       <c r="M216" s="8" t="s">
         <v>18</v>
@@ -11108,10 +11108,10 @@
         <v>500</v>
       </c>
       <c r="F217" s="11">
-        <v>26000</v>
+        <v>16000</v>
       </c>
       <c r="G217" s="11">
-        <v>26000</v>
+        <v>16000</v>
       </c>
       <c r="H217" s="11">
         <v>0</v>
@@ -11120,13 +11120,13 @@
         <v>10</v>
       </c>
       <c r="J217" s="12">
-        <v>185</v>
+        <v>196</v>
       </c>
       <c r="K217" s="12">
-        <v>55</v>
+        <v>52</v>
       </c>
       <c r="L217" s="13">
-        <v>5963.3</v>
+        <v>5056.89</v>
       </c>
       <c r="M217" s="14" t="s">
         <v>18</v>
@@ -11152,10 +11152,10 @@
         <v>10</v>
       </c>
       <c r="F218" s="5">
-        <v>510</v>
+        <v>440</v>
       </c>
       <c r="G218" s="5">
-        <v>510</v>
+        <v>440</v>
       </c>
       <c r="H218" s="5">
         <v>0</v>
@@ -11164,13 +11164,13 @@
         <v>10</v>
       </c>
       <c r="J218" s="6">
-        <v>121</v>
+        <v>98</v>
       </c>
       <c r="K218" s="6">
         <v>29</v>
       </c>
       <c r="L218" s="7">
-        <v>171.2</v>
+        <v>158.5</v>
       </c>
       <c r="M218" s="8" t="s">
         <v>18</v>
@@ -11196,10 +11196,10 @@
         <v>25</v>
       </c>
       <c r="F219" s="11">
-        <v>1225</v>
+        <v>1200</v>
       </c>
       <c r="G219" s="11">
-        <v>1225</v>
+        <v>1200</v>
       </c>
       <c r="H219" s="11">
         <v>0</v>
@@ -11208,13 +11208,13 @@
         <v>37</v>
       </c>
       <c r="J219" s="12">
-        <v>618</v>
+        <v>800</v>
       </c>
       <c r="K219" s="12">
         <v>117</v>
       </c>
       <c r="L219" s="13">
-        <v>169.36</v>
+        <v>168.63</v>
       </c>
       <c r="M219" s="14" t="s">
         <v>18</v>
@@ -11240,25 +11240,25 @@
         <v>50</v>
       </c>
       <c r="F220" s="5">
-        <v>2400</v>
+        <v>2750</v>
       </c>
       <c r="G220" s="5">
-        <v>2400</v>
+        <v>2750</v>
       </c>
       <c r="H220" s="5">
         <v>0</v>
       </c>
       <c r="I220" s="6">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="J220" s="6">
-        <v>153</v>
+        <v>147</v>
       </c>
       <c r="K220" s="6">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="L220" s="7">
-        <v>803.21</v>
+        <v>843.56</v>
       </c>
       <c r="M220" s="8" t="s">
         <v>18</v>
@@ -11284,25 +11284,25 @@
         <v>100</v>
       </c>
       <c r="F221" s="11">
-        <v>4400</v>
+        <v>6900</v>
       </c>
       <c r="G221" s="11">
-        <v>4400</v>
+        <v>6900</v>
       </c>
       <c r="H221" s="11">
         <v>0</v>
       </c>
       <c r="I221" s="12">
-        <v>109</v>
+        <v>122</v>
       </c>
       <c r="J221" s="12">
-        <v>2278</v>
+        <v>2223</v>
       </c>
       <c r="K221" s="12">
-        <v>356</v>
+        <v>355</v>
       </c>
       <c r="L221" s="13">
-        <v>256.35</v>
+        <v>265.44</v>
       </c>
       <c r="M221" s="14" t="s">
         <v>18</v>
@@ -11328,10 +11328,10 @@
         <v>150</v>
       </c>
       <c r="F222" s="5">
-        <v>8700</v>
+        <v>10350</v>
       </c>
       <c r="G222" s="5">
-        <v>8700</v>
+        <v>10350</v>
       </c>
       <c r="H222" s="5">
         <v>0</v>
@@ -11340,13 +11340,13 @@
         <v>10</v>
       </c>
       <c r="J222" s="6">
-        <v>142</v>
+        <v>161</v>
       </c>
       <c r="K222" s="6">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="L222" s="7">
-        <v>2348.81</v>
+        <v>2553.66</v>
       </c>
       <c r="M222" s="8" t="s">
         <v>18</v>
@@ -11372,10 +11372,10 @@
         <v>200</v>
       </c>
       <c r="F223" s="11">
-        <v>7400</v>
+        <v>9000</v>
       </c>
       <c r="G223" s="11">
-        <v>7400</v>
+        <v>9000</v>
       </c>
       <c r="H223" s="11">
         <v>0</v>
@@ -11384,13 +11384,13 @@
         <v>40</v>
       </c>
       <c r="J223" s="12">
-        <v>809</v>
+        <v>761</v>
       </c>
       <c r="K223" s="12">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="L223" s="13">
-        <v>1089.68</v>
+        <v>1140.68</v>
       </c>
       <c r="M223" s="14" t="s">
         <v>18</v>
@@ -11416,10 +11416,10 @@
         <v>300</v>
       </c>
       <c r="F224" s="5">
-        <v>13800</v>
+        <v>6600</v>
       </c>
       <c r="G224" s="5">
-        <v>13800</v>
+        <v>6600</v>
       </c>
       <c r="H224" s="5">
         <v>0</v>
@@ -11428,13 +11428,13 @@
         <v>10</v>
       </c>
       <c r="J224" s="6">
-        <v>144</v>
+        <v>195</v>
       </c>
       <c r="K224" s="6">
-        <v>42</v>
+        <v>45</v>
       </c>
       <c r="L224" s="7">
-        <v>4020.98</v>
+        <v>2650.6</v>
       </c>
       <c r="M224" s="8" t="s">
         <v>18</v>
@@ -11460,25 +11460,25 @@
         <v>400</v>
       </c>
       <c r="F225" s="11">
-        <v>13600</v>
+        <v>20000</v>
       </c>
       <c r="G225" s="11">
-        <v>13600</v>
+        <v>20000</v>
       </c>
       <c r="H225" s="11">
         <v>0</v>
       </c>
       <c r="I225" s="12">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="J225" s="12">
-        <v>211</v>
+        <v>199</v>
       </c>
       <c r="K225" s="12">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="L225" s="13">
-        <v>4295.64</v>
+        <v>5000</v>
       </c>
       <c r="M225" s="14" t="s">
         <v>18</v>
@@ -11504,25 +11504,25 @@
         <v>500</v>
       </c>
       <c r="F226" s="5">
-        <v>18000</v>
+        <v>11500</v>
       </c>
       <c r="G226" s="5">
-        <v>18000</v>
+        <v>11500</v>
       </c>
       <c r="H226" s="5">
         <v>0</v>
       </c>
       <c r="I226" s="6">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="J226" s="6">
-        <v>240</v>
+        <v>243</v>
       </c>
       <c r="K226" s="6">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="L226" s="7">
-        <v>5226.48</v>
+        <v>4159.13</v>
       </c>
       <c r="M226" s="8" t="s">
         <v>18</v>
@@ -11548,25 +11548,25 @@
         <v>10</v>
       </c>
       <c r="F227" s="11">
-        <v>600</v>
+        <v>690</v>
       </c>
       <c r="G227" s="11">
-        <v>600</v>
+        <v>690</v>
       </c>
       <c r="H227" s="11">
         <v>0</v>
       </c>
       <c r="I227" s="12">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="J227" s="12">
-        <v>102</v>
+        <v>117</v>
       </c>
       <c r="K227" s="12">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="L227" s="13">
-        <v>185.19</v>
+        <v>189.61</v>
       </c>
       <c r="M227" s="14" t="s">
         <v>18</v>
@@ -11592,10 +11592,10 @@
         <v>25</v>
       </c>
       <c r="F228" s="5">
-        <v>1425</v>
+        <v>825</v>
       </c>
       <c r="G228" s="5">
-        <v>1425</v>
+        <v>825</v>
       </c>
       <c r="H228" s="5">
         <v>0</v>
@@ -11604,13 +11604,13 @@
         <v>9</v>
       </c>
       <c r="J228" s="6">
-        <v>143</v>
+        <v>148</v>
       </c>
       <c r="K228" s="6">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="L228" s="7">
-        <v>428.7</v>
+        <v>326.99</v>
       </c>
       <c r="M228" s="8" t="s">
         <v>18</v>
@@ -11636,25 +11636,25 @@
         <v>50</v>
       </c>
       <c r="F229" s="11">
-        <v>1350</v>
+        <v>3200</v>
       </c>
       <c r="G229" s="11">
-        <v>1350</v>
+        <v>3200</v>
       </c>
       <c r="H229" s="11">
         <v>0</v>
       </c>
       <c r="I229" s="12">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="J229" s="12">
-        <v>135</v>
+        <v>109</v>
       </c>
       <c r="K229" s="12">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="L229" s="13">
-        <v>577.66</v>
+        <v>885.94</v>
       </c>
       <c r="M229" s="14" t="s">
         <v>18</v>
@@ -11689,10 +11689,10 @@
         <v>0</v>
       </c>
       <c r="I230" s="6">
-        <v>42</v>
+        <v>36</v>
       </c>
       <c r="J230" s="6">
-        <v>853</v>
+        <v>673</v>
       </c>
       <c r="K230" s="6">
         <v>129</v>
@@ -11724,10 +11724,10 @@
         <v>150</v>
       </c>
       <c r="F231" s="11">
-        <v>3150</v>
+        <v>6450</v>
       </c>
       <c r="G231" s="11">
-        <v>3150</v>
+        <v>6450</v>
       </c>
       <c r="H231" s="11">
         <v>0</v>
@@ -11736,13 +11736,13 @@
         <v>10</v>
       </c>
       <c r="J231" s="12">
-        <v>145</v>
+        <v>178</v>
       </c>
       <c r="K231" s="12">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="L231" s="13">
-        <v>1370.76</v>
+        <v>2086.7</v>
       </c>
       <c r="M231" s="14" t="s">
         <v>18</v>
@@ -11768,25 +11768,25 @@
         <v>200</v>
       </c>
       <c r="F232" s="5">
-        <v>12600</v>
+        <v>5000</v>
       </c>
       <c r="G232" s="5">
-        <v>12600</v>
+        <v>5000</v>
       </c>
       <c r="H232" s="5">
         <v>0</v>
       </c>
       <c r="I232" s="6">
-        <v>114</v>
+        <v>124</v>
       </c>
       <c r="J232" s="6">
-        <v>2021</v>
+        <v>1948</v>
       </c>
       <c r="K232" s="6">
-        <v>439</v>
+        <v>430</v>
       </c>
       <c r="L232" s="7">
-        <v>432.14</v>
+        <v>408.16</v>
       </c>
       <c r="M232" s="8" t="s">
         <v>18</v>
@@ -11812,10 +11812,10 @@
         <v>300</v>
       </c>
       <c r="F233" s="11">
-        <v>17100</v>
+        <v>17700</v>
       </c>
       <c r="G233" s="11">
-        <v>17100</v>
+        <v>17700</v>
       </c>
       <c r="H233" s="11">
         <v>0</v>
@@ -11824,13 +11824,13 @@
         <v>9</v>
       </c>
       <c r="J233" s="12">
-        <v>161</v>
+        <v>195</v>
       </c>
       <c r="K233" s="12">
         <v>44</v>
       </c>
       <c r="L233" s="13">
-        <v>4266.47</v>
+        <v>4321.29</v>
       </c>
       <c r="M233" s="14" t="s">
         <v>18</v>
@@ -11856,25 +11856,25 @@
         <v>400</v>
       </c>
       <c r="F234" s="5">
-        <v>27200</v>
+        <v>16800</v>
       </c>
       <c r="G234" s="5">
-        <v>27200</v>
+        <v>16800</v>
       </c>
       <c r="H234" s="5">
         <v>0</v>
       </c>
       <c r="I234" s="6">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="J234" s="6">
-        <v>897</v>
+        <v>1054</v>
       </c>
       <c r="K234" s="6">
-        <v>176</v>
+        <v>174</v>
       </c>
       <c r="L234" s="7">
-        <v>2019.6</v>
+        <v>1907.36</v>
       </c>
       <c r="M234" s="8" t="s">
         <v>18</v>
@@ -11900,10 +11900,10 @@
         <v>500</v>
       </c>
       <c r="F235" s="11">
-        <v>10000</v>
+        <v>25500</v>
       </c>
       <c r="G235" s="11">
-        <v>10000</v>
+        <v>25500</v>
       </c>
       <c r="H235" s="11">
         <v>0</v>
@@ -11912,13 +11912,13 @@
         <v>9</v>
       </c>
       <c r="J235" s="12">
-        <v>210</v>
+        <v>204</v>
       </c>
       <c r="K235" s="12">
-        <v>56</v>
+        <v>51</v>
       </c>
       <c r="L235" s="13">
-        <v>3816.79</v>
+        <v>6218</v>
       </c>
       <c r="M235" s="14" t="s">
         <v>18</v>
@@ -11944,10 +11944,10 @@
         <v>10</v>
       </c>
       <c r="F236" s="5">
-        <v>310</v>
+        <v>360</v>
       </c>
       <c r="G236" s="5">
-        <v>310</v>
+        <v>360</v>
       </c>
       <c r="H236" s="5">
         <v>0</v>
@@ -11956,13 +11956,13 @@
         <v>9</v>
       </c>
       <c r="J236" s="6">
-        <v>121</v>
+        <v>133</v>
       </c>
       <c r="K236" s="6">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="L236" s="7">
-        <v>127.57</v>
+        <v>141.51</v>
       </c>
       <c r="M236" s="8" t="s">
         <v>18</v>
@@ -11988,10 +11988,10 @@
         <v>25</v>
       </c>
       <c r="F237" s="11">
-        <v>1525</v>
+        <v>1600</v>
       </c>
       <c r="G237" s="11">
-        <v>1525</v>
+        <v>1600</v>
       </c>
       <c r="H237" s="11">
         <v>0</v>
@@ -12000,13 +12000,13 @@
         <v>9</v>
       </c>
       <c r="J237" s="12">
-        <v>109</v>
+        <v>140</v>
       </c>
       <c r="K237" s="12">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="L237" s="13">
-        <v>449.72</v>
+        <v>450.96</v>
       </c>
       <c r="M237" s="14" t="s">
         <v>18</v>
@@ -12032,25 +12032,25 @@
         <v>50</v>
       </c>
       <c r="F238" s="5">
-        <v>2650</v>
+        <v>2400</v>
       </c>
       <c r="G238" s="5">
-        <v>2650</v>
+        <v>2400</v>
       </c>
       <c r="H238" s="5">
         <v>0</v>
       </c>
       <c r="I238" s="6">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="J238" s="6">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="K238" s="6">
         <v>33</v>
       </c>
       <c r="L238" s="7">
-        <v>815.64</v>
+        <v>778.21</v>
       </c>
       <c r="M238" s="8" t="s">
         <v>18</v>
@@ -12076,25 +12076,25 @@
         <v>100</v>
       </c>
       <c r="F239" s="11">
-        <v>5400</v>
+        <v>4900</v>
       </c>
       <c r="G239" s="11">
-        <v>5400</v>
+        <v>4900</v>
       </c>
       <c r="H239" s="11">
         <v>0</v>
       </c>
       <c r="I239" s="12">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="J239" s="12">
-        <v>160</v>
+        <v>157</v>
       </c>
       <c r="K239" s="12">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="L239" s="13">
-        <v>1618.71</v>
+        <v>1572.02</v>
       </c>
       <c r="M239" s="14" t="s">
         <v>18</v>
@@ -12120,10 +12120,10 @@
         <v>150</v>
       </c>
       <c r="F240" s="5">
-        <v>4500</v>
+        <v>9750</v>
       </c>
       <c r="G240" s="5">
-        <v>4500</v>
+        <v>9750</v>
       </c>
       <c r="H240" s="5">
         <v>0</v>
@@ -12132,13 +12132,13 @@
         <v>10</v>
       </c>
       <c r="J240" s="6">
-        <v>136</v>
+        <v>133</v>
       </c>
       <c r="K240" s="6">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="L240" s="7">
-        <v>1704.55</v>
+        <v>2496.8</v>
       </c>
       <c r="M240" s="8" t="s">
         <v>18</v>
@@ -12164,25 +12164,25 @@
         <v>200</v>
       </c>
       <c r="F241" s="11">
-        <v>9600</v>
+        <v>10200</v>
       </c>
       <c r="G241" s="11">
-        <v>9600</v>
+        <v>10200</v>
       </c>
       <c r="H241" s="11">
         <v>0</v>
       </c>
       <c r="I241" s="12">
-        <v>43</v>
+        <v>39</v>
       </c>
       <c r="J241" s="12">
-        <v>893</v>
+        <v>904</v>
       </c>
       <c r="K241" s="12">
-        <v>144</v>
+        <v>137</v>
       </c>
       <c r="L241" s="13">
-        <v>1141.23</v>
+        <v>1201.84</v>
       </c>
       <c r="M241" s="14" t="s">
         <v>18</v>
@@ -12208,25 +12208,25 @@
         <v>300</v>
       </c>
       <c r="F242" s="5">
-        <v>17700</v>
+        <v>11700</v>
       </c>
       <c r="G242" s="5">
-        <v>17700</v>
+        <v>11700</v>
       </c>
       <c r="H242" s="5">
         <v>0</v>
       </c>
       <c r="I242" s="6">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="J242" s="6">
-        <v>181</v>
+        <v>191</v>
       </c>
       <c r="K242" s="6">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="L242" s="7">
-        <v>4259.93</v>
+        <v>3682.72</v>
       </c>
       <c r="M242" s="8" t="s">
         <v>18</v>
@@ -12252,25 +12252,25 @@
         <v>400</v>
       </c>
       <c r="F243" s="11">
-        <v>12800</v>
+        <v>10000</v>
       </c>
       <c r="G243" s="11">
-        <v>12800</v>
+        <v>10000</v>
       </c>
       <c r="H243" s="11">
         <v>0</v>
       </c>
       <c r="I243" s="12">
-        <v>116</v>
+        <v>113</v>
       </c>
       <c r="J243" s="12">
-        <v>2518</v>
+        <v>2612</v>
       </c>
       <c r="K243" s="12">
-        <v>532</v>
+        <v>521</v>
       </c>
       <c r="L243" s="13">
-        <v>691</v>
+        <v>688.47</v>
       </c>
       <c r="M243" s="14" t="s">
         <v>18</v>
@@ -12296,10 +12296,10 @@
         <v>500</v>
       </c>
       <c r="F244" s="5">
-        <v>12500</v>
+        <v>22500</v>
       </c>
       <c r="G244" s="5">
-        <v>12500</v>
+        <v>22500</v>
       </c>
       <c r="H244" s="5">
         <v>0</v>
@@ -12308,13 +12308,13 @@
         <v>9</v>
       </c>
       <c r="J244" s="6">
-        <v>223</v>
+        <v>247</v>
       </c>
       <c r="K244" s="6">
-        <v>55</v>
+        <v>52</v>
       </c>
       <c r="L244" s="7">
-        <v>4347.83</v>
+        <v>5859.38</v>
       </c>
       <c r="M244" s="8" t="s">
         <v>18</v>
@@ -12340,10 +12340,10 @@
         <v>10</v>
       </c>
       <c r="F245" s="11">
-        <v>270</v>
+        <v>440</v>
       </c>
       <c r="G245" s="11">
-        <v>270</v>
+        <v>440</v>
       </c>
       <c r="H245" s="11">
         <v>0</v>
@@ -12352,13 +12352,13 @@
         <v>42</v>
       </c>
       <c r="J245" s="12">
-        <v>683</v>
+        <v>737</v>
       </c>
       <c r="K245" s="12">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="L245" s="13">
-        <v>61.14</v>
+        <v>70.88</v>
       </c>
       <c r="M245" s="14" t="s">
         <v>18</v>
@@ -12384,25 +12384,25 @@
         <v>25</v>
       </c>
       <c r="F246" s="5">
-        <v>1075</v>
+        <v>1725</v>
       </c>
       <c r="G246" s="5">
-        <v>1075</v>
+        <v>1725</v>
       </c>
       <c r="H246" s="5">
         <v>0</v>
       </c>
       <c r="I246" s="6">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="J246" s="6">
-        <v>115</v>
+        <v>142</v>
       </c>
       <c r="K246" s="6">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="L246" s="7">
-        <v>391.34</v>
+        <v>483.19</v>
       </c>
       <c r="M246" s="8" t="s">
         <v>18</v>
@@ -12428,25 +12428,25 @@
         <v>50</v>
       </c>
       <c r="F247" s="11">
-        <v>2750</v>
+        <v>1300</v>
       </c>
       <c r="G247" s="11">
-        <v>2750</v>
+        <v>1300</v>
       </c>
       <c r="H247" s="11">
         <v>0</v>
       </c>
       <c r="I247" s="12">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="J247" s="12">
-        <v>148</v>
+        <v>105</v>
       </c>
       <c r="K247" s="12">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="L247" s="13">
-        <v>829.56</v>
+        <v>557.46</v>
       </c>
       <c r="M247" s="14" t="s">
         <v>18</v>
@@ -12472,25 +12472,25 @@
         <v>100</v>
       </c>
       <c r="F248" s="5">
-        <v>6000</v>
+        <v>2600</v>
       </c>
       <c r="G248" s="5">
-        <v>6000</v>
+        <v>2600</v>
       </c>
       <c r="H248" s="5">
         <v>0</v>
       </c>
       <c r="I248" s="6">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="J248" s="6">
         <v>111</v>
       </c>
       <c r="K248" s="6">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="L248" s="7">
-        <v>1666.67</v>
+        <v>1067.32</v>
       </c>
       <c r="M248" s="8" t="s">
         <v>18</v>
@@ -12516,10 +12516,10 @@
         <v>150</v>
       </c>
       <c r="F249" s="11">
-        <v>5100</v>
+        <v>8850</v>
       </c>
       <c r="G249" s="11">
-        <v>5100</v>
+        <v>8850</v>
       </c>
       <c r="H249" s="11">
         <v>0</v>
@@ -12528,13 +12528,13 @@
         <v>10</v>
       </c>
       <c r="J249" s="12">
-        <v>177</v>
+        <v>142</v>
       </c>
       <c r="K249" s="12">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="L249" s="13">
-        <v>1872.25</v>
+        <v>2402.93</v>
       </c>
       <c r="M249" s="14" t="s">
         <v>18</v>
@@ -12560,10 +12560,10 @@
         <v>200</v>
       </c>
       <c r="F250" s="5">
-        <v>7600</v>
+        <v>10600</v>
       </c>
       <c r="G250" s="5">
-        <v>7600</v>
+        <v>10600</v>
       </c>
       <c r="H250" s="5">
         <v>0</v>
@@ -12572,13 +12572,13 @@
         <v>9</v>
       </c>
       <c r="J250" s="6">
-        <v>128</v>
+        <v>185</v>
       </c>
       <c r="K250" s="6">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="L250" s="7">
-        <v>2581.52</v>
+        <v>2928.18</v>
       </c>
       <c r="M250" s="8" t="s">
         <v>18</v>
@@ -12604,25 +12604,25 @@
         <v>300</v>
       </c>
       <c r="F251" s="11">
-        <v>10500</v>
+        <v>18000</v>
       </c>
       <c r="G251" s="11">
-        <v>10500</v>
+        <v>18000</v>
       </c>
       <c r="H251" s="11">
         <v>0</v>
       </c>
       <c r="I251" s="12">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="J251" s="12">
-        <v>154</v>
+        <v>160</v>
       </c>
       <c r="K251" s="12">
         <v>42</v>
       </c>
       <c r="L251" s="13">
-        <v>3535.35</v>
+        <v>4477.61</v>
       </c>
       <c r="M251" s="14" t="s">
         <v>18</v>
@@ -12648,25 +12648,25 @@
         <v>400</v>
       </c>
       <c r="F252" s="5">
-        <v>13600</v>
+        <v>12000</v>
       </c>
       <c r="G252" s="5">
-        <v>13600</v>
+        <v>12000</v>
       </c>
       <c r="H252" s="5">
         <v>0</v>
       </c>
       <c r="I252" s="6">
-        <v>37</v>
+        <v>41</v>
       </c>
       <c r="J252" s="6">
-        <v>854</v>
+        <v>867</v>
       </c>
       <c r="K252" s="6">
-        <v>181</v>
+        <v>187</v>
       </c>
       <c r="L252" s="7">
-        <v>1776.85</v>
+        <v>1687.76</v>
       </c>
       <c r="M252" s="8" t="s">
         <v>18</v>
@@ -12692,10 +12692,10 @@
         <v>500</v>
       </c>
       <c r="F253" s="11">
-        <v>19500</v>
+        <v>19000</v>
       </c>
       <c r="G253" s="11">
-        <v>19500</v>
+        <v>19000</v>
       </c>
       <c r="H253" s="11">
         <v>0</v>
@@ -12704,13 +12704,13 @@
         <v>9</v>
       </c>
       <c r="J253" s="12">
-        <v>256</v>
+        <v>203</v>
       </c>
       <c r="K253" s="12">
-        <v>52</v>
+        <v>55</v>
       </c>
       <c r="L253" s="13">
-        <v>5527.21</v>
+        <v>5292.48</v>
       </c>
       <c r="M253" s="14" t="s">
         <v>18</v>
@@ -12736,25 +12736,25 @@
         <v>10</v>
       </c>
       <c r="F254" s="5">
-        <v>510</v>
+        <v>540</v>
       </c>
       <c r="G254" s="5">
-        <v>510</v>
+        <v>540</v>
       </c>
       <c r="H254" s="5">
         <v>0</v>
       </c>
       <c r="I254" s="6">
-        <v>115</v>
+        <v>124</v>
       </c>
       <c r="J254" s="6">
-        <v>2114</v>
+        <v>1689</v>
       </c>
       <c r="K254" s="6">
-        <v>310</v>
+        <v>312</v>
       </c>
       <c r="L254" s="7">
-        <v>29.46</v>
+        <v>29.43</v>
       </c>
       <c r="M254" s="8" t="s">
         <v>18</v>
@@ -12780,10 +12780,10 @@
         <v>25</v>
       </c>
       <c r="F255" s="11">
-        <v>1000</v>
+        <v>1075</v>
       </c>
       <c r="G255" s="11">
-        <v>1000</v>
+        <v>1075</v>
       </c>
       <c r="H255" s="11">
         <v>0</v>
@@ -12792,13 +12792,13 @@
         <v>10</v>
       </c>
       <c r="J255" s="12">
-        <v>119</v>
+        <v>104</v>
       </c>
       <c r="K255" s="12">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="L255" s="13">
-        <v>364.96</v>
+        <v>391.34</v>
       </c>
       <c r="M255" s="14" t="s">
         <v>18</v>
@@ -12824,25 +12824,25 @@
         <v>50</v>
       </c>
       <c r="F256" s="5">
-        <v>3050</v>
+        <v>2250</v>
       </c>
       <c r="G256" s="5">
-        <v>3050</v>
+        <v>2250</v>
       </c>
       <c r="H256" s="5">
         <v>0</v>
       </c>
       <c r="I256" s="6">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="J256" s="6">
-        <v>767</v>
+        <v>781</v>
       </c>
       <c r="K256" s="6">
-        <v>116</v>
+        <v>123</v>
       </c>
       <c r="L256" s="7">
-        <v>355.64</v>
+        <v>319.83</v>
       </c>
       <c r="M256" s="8" t="s">
         <v>18</v>
@@ -12868,10 +12868,10 @@
         <v>100</v>
       </c>
       <c r="F257" s="11">
-        <v>5400</v>
+        <v>5100</v>
       </c>
       <c r="G257" s="11">
-        <v>5400</v>
+        <v>5100</v>
       </c>
       <c r="H257" s="11">
         <v>0</v>
@@ -12880,13 +12880,13 @@
         <v>10</v>
       </c>
       <c r="J257" s="12">
-        <v>121</v>
+        <v>129</v>
       </c>
       <c r="K257" s="12">
-        <v>33</v>
+        <v>36</v>
       </c>
       <c r="L257" s="13">
-        <v>1645.34</v>
+        <v>1528.78</v>
       </c>
       <c r="M257" s="14" t="s">
         <v>18</v>
@@ -12912,10 +12912,10 @@
         <v>150</v>
       </c>
       <c r="F258" s="5">
-        <v>4500</v>
+        <v>9600</v>
       </c>
       <c r="G258" s="5">
-        <v>4500</v>
+        <v>9600</v>
       </c>
       <c r="H258" s="5">
         <v>0</v>
@@ -12924,13 +12924,13 @@
         <v>9</v>
       </c>
       <c r="J258" s="6">
-        <v>151</v>
+        <v>133</v>
       </c>
       <c r="K258" s="6">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="L258" s="7">
-        <v>1704.55</v>
+        <v>2523.66</v>
       </c>
       <c r="M258" s="8" t="s">
         <v>18</v>
@@ -12956,25 +12956,25 @@
         <v>200</v>
       </c>
       <c r="F259" s="11">
-        <v>12000</v>
+        <v>11800</v>
       </c>
       <c r="G259" s="11">
-        <v>12000</v>
+        <v>11800</v>
       </c>
       <c r="H259" s="11">
         <v>0</v>
       </c>
       <c r="I259" s="12">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="J259" s="12">
-        <v>134</v>
+        <v>147</v>
       </c>
       <c r="K259" s="12">
         <v>40</v>
       </c>
       <c r="L259" s="13">
-        <v>3076.92</v>
+        <v>3056.99</v>
       </c>
       <c r="M259" s="14" t="s">
         <v>18</v>
@@ -13000,10 +13000,10 @@
         <v>300</v>
       </c>
       <c r="F260" s="5">
-        <v>10800</v>
+        <v>20400</v>
       </c>
       <c r="G260" s="5">
-        <v>10800</v>
+        <v>20400</v>
       </c>
       <c r="H260" s="5">
         <v>0</v>
@@ -13012,13 +13012,13 @@
         <v>10</v>
       </c>
       <c r="J260" s="6">
-        <v>195</v>
+        <v>203</v>
       </c>
       <c r="K260" s="6">
         <v>43</v>
       </c>
       <c r="L260" s="7">
-        <v>3543.31</v>
+        <v>4611.21</v>
       </c>
       <c r="M260" s="8" t="s">
         <v>18</v>
@@ -13044,10 +13044,10 @@
         <v>400</v>
       </c>
       <c r="F261" s="11">
-        <v>27600</v>
+        <v>25200</v>
       </c>
       <c r="G261" s="11">
-        <v>27600</v>
+        <v>25200</v>
       </c>
       <c r="H261" s="11">
         <v>0</v>
@@ -13056,13 +13056,13 @@
         <v>10</v>
       </c>
       <c r="J261" s="12">
-        <v>168</v>
+        <v>205</v>
       </c>
       <c r="K261" s="12">
         <v>47</v>
       </c>
       <c r="L261" s="13">
-        <v>5819.1</v>
+        <v>5648.96</v>
       </c>
       <c r="M261" s="14" t="s">
         <v>18</v>
@@ -13088,10 +13088,10 @@
         <v>500</v>
       </c>
       <c r="F262" s="5">
-        <v>13000</v>
+        <v>11500</v>
       </c>
       <c r="G262" s="5">
-        <v>13000</v>
+        <v>11500</v>
       </c>
       <c r="H262" s="5">
         <v>0</v>
@@ -13100,13 +13100,13 @@
         <v>10</v>
       </c>
       <c r="J262" s="6">
-        <v>212</v>
+        <v>199</v>
       </c>
       <c r="K262" s="6">
         <v>52</v>
       </c>
       <c r="L262" s="7">
-        <v>4558.2</v>
+        <v>4265.58</v>
       </c>
       <c r="M262" s="8" t="s">
         <v>18</v>
@@ -13132,25 +13132,25 @@
         <v>10</v>
       </c>
       <c r="F263" s="11">
-        <v>440</v>
+        <v>380</v>
       </c>
       <c r="G263" s="11">
-        <v>440</v>
+        <v>380</v>
       </c>
       <c r="H263" s="11">
         <v>0</v>
       </c>
       <c r="I263" s="12">
-        <v>39</v>
+        <v>36</v>
       </c>
       <c r="J263" s="12">
-        <v>595</v>
+        <v>714</v>
       </c>
       <c r="K263" s="12">
-        <v>115</v>
+        <v>111</v>
       </c>
       <c r="L263" s="13">
-        <v>67.07</v>
+        <v>66.46</v>
       </c>
       <c r="M263" s="14" t="s">
         <v>18</v>
@@ -13176,25 +13176,25 @@
         <v>25</v>
       </c>
       <c r="F264" s="5">
-        <v>1150</v>
+        <v>1725</v>
       </c>
       <c r="G264" s="5">
-        <v>1150</v>
+        <v>1725</v>
       </c>
       <c r="H264" s="5">
         <v>0</v>
       </c>
       <c r="I264" s="6">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="J264" s="6">
-        <v>144</v>
+        <v>141</v>
       </c>
       <c r="K264" s="6">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="L264" s="7">
-        <v>399.31</v>
+        <v>465.21</v>
       </c>
       <c r="M264" s="8" t="s">
         <v>18</v>
@@ -13220,10 +13220,10 @@
         <v>50</v>
       </c>
       <c r="F265" s="11">
-        <v>3450</v>
+        <v>1300</v>
       </c>
       <c r="G265" s="11">
-        <v>3450</v>
+        <v>1300</v>
       </c>
       <c r="H265" s="11">
         <v>0</v>
@@ -13232,13 +13232,13 @@
         <v>122</v>
       </c>
       <c r="J265" s="12">
-        <v>2091</v>
+        <v>1931</v>
       </c>
       <c r="K265" s="12">
-        <v>342</v>
+        <v>336</v>
       </c>
       <c r="L265" s="13">
-        <v>137.46</v>
+        <v>127</v>
       </c>
       <c r="M265" s="14" t="s">
         <v>18</v>
@@ -13264,10 +13264,10 @@
         <v>100</v>
       </c>
       <c r="F266" s="5">
-        <v>3300</v>
+        <v>5100</v>
       </c>
       <c r="G266" s="5">
-        <v>3300</v>
+        <v>5100</v>
       </c>
       <c r="H266" s="5">
         <v>0</v>
@@ -13276,13 +13276,13 @@
         <v>10</v>
       </c>
       <c r="J266" s="6">
-        <v>114</v>
+        <v>119</v>
       </c>
       <c r="K266" s="6">
         <v>34</v>
       </c>
       <c r="L266" s="7">
-        <v>1258.58</v>
+        <v>1576.99</v>
       </c>
       <c r="M266" s="8" t="s">
         <v>18</v>
@@ -13308,25 +13308,25 @@
         <v>150</v>
       </c>
       <c r="F267" s="11">
-        <v>3750</v>
+        <v>8100</v>
       </c>
       <c r="G267" s="11">
-        <v>3750</v>
+        <v>8100</v>
       </c>
       <c r="H267" s="11">
         <v>0</v>
       </c>
       <c r="I267" s="12">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="J267" s="12">
-        <v>893</v>
+        <v>778</v>
       </c>
       <c r="K267" s="12">
-        <v>133</v>
+        <v>143</v>
       </c>
       <c r="L267" s="13">
-        <v>777.2</v>
+        <v>878.33</v>
       </c>
       <c r="M267" s="14" t="s">
         <v>18</v>
@@ -13352,25 +13352,25 @@
         <v>200</v>
       </c>
       <c r="F268" s="5">
-        <v>8000</v>
+        <v>4800</v>
       </c>
       <c r="G268" s="5">
-        <v>8000</v>
+        <v>4800</v>
       </c>
       <c r="H268" s="5">
         <v>0</v>
       </c>
       <c r="I268" s="6">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="J268" s="6">
-        <v>174</v>
+        <v>161</v>
       </c>
       <c r="K268" s="6">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="L268" s="7">
-        <v>2614.38</v>
+        <v>2010.05</v>
       </c>
       <c r="M268" s="8" t="s">
         <v>18</v>
@@ -13396,10 +13396,10 @@
         <v>300</v>
       </c>
       <c r="F269" s="11">
-        <v>11400</v>
+        <v>6600</v>
       </c>
       <c r="G269" s="11">
-        <v>11400</v>
+        <v>6600</v>
       </c>
       <c r="H269" s="11">
         <v>0</v>
@@ -13408,13 +13408,13 @@
         <v>10</v>
       </c>
       <c r="J269" s="12">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="K269" s="12">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="L269" s="13">
-        <v>3637.52</v>
+        <v>2674.23</v>
       </c>
       <c r="M269" s="14" t="s">
         <v>18</v>
@@ -13440,10 +13440,10 @@
         <v>400</v>
       </c>
       <c r="F270" s="5">
-        <v>12000</v>
+        <v>16000</v>
       </c>
       <c r="G270" s="5">
-        <v>12000</v>
+        <v>16000</v>
       </c>
       <c r="H270" s="5">
         <v>0</v>
@@ -13452,13 +13452,13 @@
         <v>10</v>
       </c>
       <c r="J270" s="6">
-        <v>188</v>
+        <v>171</v>
       </c>
       <c r="K270" s="6">
-        <v>51</v>
+        <v>47</v>
       </c>
       <c r="L270" s="7">
-        <v>3960.4</v>
+        <v>4733.73</v>
       </c>
       <c r="M270" s="8" t="s">
         <v>18</v>
@@ -13484,10 +13484,10 @@
         <v>500</v>
       </c>
       <c r="F271" s="11">
-        <v>32000</v>
+        <v>16000</v>
       </c>
       <c r="G271" s="11">
-        <v>32000</v>
+        <v>16000</v>
       </c>
       <c r="H271" s="11">
         <v>0</v>
@@ -13496,13 +13496,13 @@
         <v>9</v>
       </c>
       <c r="J271" s="12">
-        <v>241</v>
+        <v>217</v>
       </c>
       <c r="K271" s="12">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="L271" s="13">
-        <v>6717.04</v>
+        <v>5056.89</v>
       </c>
       <c r="M271" s="14" t="s">
         <v>18</v>
@@ -13528,10 +13528,10 @@
         <v>10</v>
       </c>
       <c r="F272" s="5">
-        <v>220</v>
+        <v>320</v>
       </c>
       <c r="G272" s="5">
-        <v>220</v>
+        <v>320</v>
       </c>
       <c r="H272" s="5">
         <v>0</v>
@@ -13540,13 +13540,13 @@
         <v>10</v>
       </c>
       <c r="J272" s="6">
-        <v>126</v>
+        <v>144</v>
       </c>
       <c r="K272" s="6">
         <v>29</v>
       </c>
       <c r="L272" s="7">
-        <v>102.9</v>
+        <v>131.8</v>
       </c>
       <c r="M272" s="8" t="s">
         <v>18</v>
@@ -13572,10 +13572,10 @@
         <v>25</v>
       </c>
       <c r="F273" s="11">
-        <v>1600</v>
+        <v>700</v>
       </c>
       <c r="G273" s="11">
-        <v>1600</v>
+        <v>700</v>
       </c>
       <c r="H273" s="11">
         <v>0</v>
@@ -13584,13 +13584,13 @@
         <v>9</v>
       </c>
       <c r="J273" s="12">
-        <v>116</v>
+        <v>148</v>
       </c>
       <c r="K273" s="12">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="L273" s="13">
-        <v>467.84</v>
+        <v>292.15</v>
       </c>
       <c r="M273" s="14" t="s">
         <v>18</v>
@@ -13616,10 +13616,10 @@
         <v>50</v>
       </c>
       <c r="F274" s="5">
-        <v>2150</v>
+        <v>2950</v>
       </c>
       <c r="G274" s="5">
-        <v>2150</v>
+        <v>2950</v>
       </c>
       <c r="H274" s="5">
         <v>0</v>
@@ -13628,13 +13628,13 @@
         <v>43</v>
       </c>
       <c r="J274" s="6">
-        <v>683</v>
+        <v>758</v>
       </c>
       <c r="K274" s="6">
-        <v>117</v>
+        <v>113</v>
       </c>
       <c r="L274" s="7">
-        <v>329.2</v>
+        <v>361.21</v>
       </c>
       <c r="M274" s="8" t="s">
         <v>18</v>
@@ -13660,25 +13660,25 @@
         <v>100</v>
       </c>
       <c r="F275" s="11">
-        <v>3000</v>
+        <v>4600</v>
       </c>
       <c r="G275" s="11">
-        <v>3000</v>
+        <v>4600</v>
       </c>
       <c r="H275" s="11">
         <v>0</v>
       </c>
       <c r="I275" s="12">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="J275" s="12">
-        <v>147</v>
+        <v>113</v>
       </c>
       <c r="K275" s="12">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="L275" s="13">
-        <v>1190.48</v>
+        <v>1479.1</v>
       </c>
       <c r="M275" s="14" t="s">
         <v>18</v>
@@ -13704,10 +13704,10 @@
         <v>150</v>
       </c>
       <c r="F276" s="5">
-        <v>9150</v>
+        <v>7500</v>
       </c>
       <c r="G276" s="5">
-        <v>9150</v>
+        <v>7500</v>
       </c>
       <c r="H276" s="5">
         <v>0</v>
@@ -13716,13 +13716,13 @@
         <v>111</v>
       </c>
       <c r="J276" s="6">
-        <v>2572</v>
+        <v>2540</v>
       </c>
       <c r="K276" s="6">
-        <v>413</v>
+        <v>383</v>
       </c>
       <c r="L276" s="7">
-        <v>342.79</v>
+        <v>363.2</v>
       </c>
       <c r="M276" s="8" t="s">
         <v>18</v>
@@ -13748,10 +13748,10 @@
         <v>200</v>
       </c>
       <c r="F277" s="11">
-        <v>13800</v>
+        <v>7800</v>
       </c>
       <c r="G277" s="11">
-        <v>13800</v>
+        <v>7800</v>
       </c>
       <c r="H277" s="11">
         <v>0</v>
@@ -13760,13 +13760,13 @@
         <v>9</v>
       </c>
       <c r="J277" s="12">
-        <v>152</v>
+        <v>147</v>
       </c>
       <c r="K277" s="12">
         <v>40</v>
       </c>
       <c r="L277" s="13">
-        <v>3239.44</v>
+        <v>2549.02</v>
       </c>
       <c r="M277" s="14" t="s">
         <v>18</v>
@@ -13801,16 +13801,16 @@
         <v>0</v>
       </c>
       <c r="I278" s="6">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="J278" s="6">
-        <v>1110</v>
+        <v>989</v>
       </c>
       <c r="K278" s="6">
-        <v>163</v>
+        <v>158</v>
       </c>
       <c r="L278" s="7">
-        <v>1602.62</v>
+        <v>1646.6</v>
       </c>
       <c r="M278" s="8" t="s">
         <v>18</v>
@@ -13836,10 +13836,10 @@
         <v>400</v>
       </c>
       <c r="F279" s="11">
-        <v>25600</v>
+        <v>16400</v>
       </c>
       <c r="G279" s="11">
-        <v>25600</v>
+        <v>16400</v>
       </c>
       <c r="H279" s="11">
         <v>0</v>
@@ -13848,13 +13848,13 @@
         <v>9</v>
       </c>
       <c r="J279" s="12">
-        <v>221</v>
+        <v>194</v>
       </c>
       <c r="K279" s="12">
         <v>46</v>
       </c>
       <c r="L279" s="13">
-        <v>5760.58</v>
+        <v>4843.47</v>
       </c>
       <c r="M279" s="14" t="s">
         <v>18</v>
@@ -13880,25 +13880,25 @@
         <v>500</v>
       </c>
       <c r="F280" s="5">
-        <v>18500</v>
+        <v>32000</v>
       </c>
       <c r="G280" s="5">
-        <v>18500</v>
+        <v>32000</v>
       </c>
       <c r="H280" s="5">
         <v>0</v>
       </c>
       <c r="I280" s="6">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="J280" s="6">
-        <v>250</v>
+        <v>181</v>
       </c>
       <c r="K280" s="6">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="L280" s="7">
-        <v>5233.38</v>
+        <v>6294.26</v>
       </c>
       <c r="M280" s="8" t="s">
         <v>18</v>
@@ -13924,25 +13924,25 @@
         <v>10</v>
       </c>
       <c r="F281" s="11">
-        <v>280</v>
+        <v>350</v>
       </c>
       <c r="G281" s="11">
-        <v>280</v>
+        <v>350</v>
       </c>
       <c r="H281" s="11">
         <v>0</v>
       </c>
       <c r="I281" s="12">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="J281" s="12">
-        <v>106</v>
+        <v>128</v>
       </c>
       <c r="K281" s="12">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="L281" s="13">
-        <v>119.66</v>
+        <v>139.17</v>
       </c>
       <c r="M281" s="14" t="s">
         <v>18</v>
@@ -13968,25 +13968,25 @@
         <v>25</v>
       </c>
       <c r="F282" s="5">
-        <v>1675</v>
+        <v>1150</v>
       </c>
       <c r="G282" s="5">
-        <v>1675</v>
+        <v>1150</v>
       </c>
       <c r="H282" s="5">
         <v>0</v>
       </c>
       <c r="I282" s="6">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="J282" s="6">
-        <v>123</v>
+        <v>129</v>
       </c>
       <c r="K282" s="6">
         <v>30</v>
       </c>
       <c r="L282" s="7">
-        <v>477.21</v>
+        <v>399.31</v>
       </c>
       <c r="M282" s="8" t="s">
         <v>18</v>
@@ -14012,25 +14012,25 @@
         <v>50</v>
       </c>
       <c r="F283" s="11">
-        <v>3350</v>
+        <v>1550</v>
       </c>
       <c r="G283" s="11">
-        <v>3350</v>
+        <v>1550</v>
       </c>
       <c r="H283" s="11">
         <v>0</v>
       </c>
       <c r="I283" s="12">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="J283" s="12">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="K283" s="12">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="L283" s="13">
-        <v>954.42</v>
+        <v>629.83</v>
       </c>
       <c r="M283" s="14" t="s">
         <v>18</v>
@@ -14056,25 +14056,25 @@
         <v>100</v>
       </c>
       <c r="F284" s="5">
-        <v>5500</v>
+        <v>4100</v>
       </c>
       <c r="G284" s="5">
-        <v>5500</v>
+        <v>4100</v>
       </c>
       <c r="H284" s="5">
         <v>0</v>
       </c>
       <c r="I284" s="6">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="J284" s="6">
-        <v>162</v>
+        <v>113</v>
       </c>
       <c r="K284" s="6">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="L284" s="7">
-        <v>1605.84</v>
+        <v>1416.72</v>
       </c>
       <c r="M284" s="8" t="s">
         <v>18</v>
@@ -14100,25 +14100,25 @@
         <v>150</v>
       </c>
       <c r="F285" s="11">
-        <v>3600</v>
+        <v>4050</v>
       </c>
       <c r="G285" s="11">
-        <v>3600</v>
+        <v>4050</v>
       </c>
       <c r="H285" s="11">
         <v>0</v>
       </c>
       <c r="I285" s="12">
-        <v>42</v>
+        <v>36</v>
       </c>
       <c r="J285" s="12">
-        <v>706</v>
+        <v>869</v>
       </c>
       <c r="K285" s="12">
-        <v>130</v>
+        <v>135</v>
       </c>
       <c r="L285" s="13">
-        <v>779.22</v>
+        <v>787.17</v>
       </c>
       <c r="M285" s="14" t="s">
         <v>18</v>
@@ -14144,10 +14144,10 @@
         <v>200</v>
       </c>
       <c r="F286" s="5">
-        <v>13600</v>
+        <v>6400</v>
       </c>
       <c r="G286" s="5">
-        <v>13600</v>
+        <v>6400</v>
       </c>
       <c r="H286" s="5">
         <v>0</v>
@@ -14156,13 +14156,13 @@
         <v>10</v>
       </c>
       <c r="J286" s="6">
-        <v>140</v>
+        <v>166</v>
       </c>
       <c r="K286" s="6">
         <v>39</v>
       </c>
       <c r="L286" s="7">
-        <v>3275.53</v>
+        <v>2328.97</v>
       </c>
       <c r="M286" s="8" t="s">
         <v>18</v>
@@ -14188,25 +14188,25 @@
         <v>300</v>
       </c>
       <c r="F287" s="11">
-        <v>16500</v>
+        <v>11400</v>
       </c>
       <c r="G287" s="11">
-        <v>16500</v>
+        <v>11400</v>
       </c>
       <c r="H287" s="11">
         <v>0</v>
       </c>
       <c r="I287" s="12">
-        <v>127</v>
+        <v>113</v>
       </c>
       <c r="J287" s="12">
-        <v>2256</v>
+        <v>2932</v>
       </c>
       <c r="K287" s="12">
-        <v>454</v>
+        <v>464</v>
       </c>
       <c r="L287" s="13">
-        <v>623.35</v>
+        <v>595.86</v>
       </c>
       <c r="M287" s="14" t="s">
         <v>18</v>
@@ -14232,25 +14232,25 @@
         <v>400</v>
       </c>
       <c r="F288" s="5">
-        <v>9200</v>
+        <v>10400</v>
       </c>
       <c r="G288" s="5">
-        <v>9200</v>
+        <v>10400</v>
       </c>
       <c r="H288" s="5">
         <v>0</v>
       </c>
       <c r="I288" s="6">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="J288" s="6">
-        <v>167</v>
+        <v>227</v>
       </c>
       <c r="K288" s="6">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="L288" s="7">
-        <v>3471.7</v>
+        <v>3784.57</v>
       </c>
       <c r="M288" s="8" t="s">
         <v>18</v>
@@ -14276,25 +14276,25 @@
         <v>500</v>
       </c>
       <c r="F289" s="11">
-        <v>17000</v>
+        <v>32500</v>
       </c>
       <c r="G289" s="11">
-        <v>17000</v>
+        <v>32500</v>
       </c>
       <c r="H289" s="11">
         <v>0</v>
       </c>
       <c r="I289" s="12">
-        <v>43</v>
+        <v>40</v>
       </c>
       <c r="J289" s="12">
-        <v>1051</v>
+        <v>1302</v>
       </c>
       <c r="K289" s="12">
-        <v>207</v>
+        <v>192</v>
       </c>
       <c r="L289" s="13">
-        <v>1991.1</v>
+        <v>2324.75</v>
       </c>
       <c r="M289" s="14" t="s">
         <v>18</v>
@@ -14320,25 +14320,25 @@
         <v>10</v>
       </c>
       <c r="F290" s="5">
-        <v>450</v>
+        <v>540</v>
       </c>
       <c r="G290" s="5">
-        <v>450</v>
+        <v>540</v>
       </c>
       <c r="H290" s="5">
         <v>0</v>
       </c>
       <c r="I290" s="6">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="J290" s="6">
-        <v>98</v>
+        <v>113</v>
       </c>
       <c r="K290" s="6">
         <v>29</v>
       </c>
       <c r="L290" s="7">
-        <v>160.43</v>
+        <v>176.13</v>
       </c>
       <c r="M290" s="8" t="s">
         <v>18</v>
@@ -14364,25 +14364,25 @@
         <v>25</v>
       </c>
       <c r="F291" s="11">
-        <v>1450</v>
+        <v>750</v>
       </c>
       <c r="G291" s="11">
-        <v>1450</v>
+        <v>750</v>
       </c>
       <c r="H291" s="11">
         <v>0</v>
       </c>
       <c r="I291" s="12">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="J291" s="12">
-        <v>100</v>
+        <v>139</v>
       </c>
       <c r="K291" s="12">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="L291" s="13">
-        <v>439.66</v>
+        <v>304.88</v>
       </c>
       <c r="M291" s="14" t="s">
         <v>18</v>
@@ -14408,10 +14408,10 @@
         <v>50</v>
       </c>
       <c r="F292" s="5">
-        <v>3050</v>
+        <v>1500</v>
       </c>
       <c r="G292" s="5">
-        <v>3050</v>
+        <v>1500</v>
       </c>
       <c r="H292" s="5">
         <v>0</v>
@@ -14420,13 +14420,13 @@
         <v>9</v>
       </c>
       <c r="J292" s="6">
-        <v>127</v>
+        <v>149</v>
       </c>
       <c r="K292" s="6">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="L292" s="7">
-        <v>868.2</v>
+        <v>609.76</v>
       </c>
       <c r="M292" s="8" t="s">
         <v>18</v>
@@ -14452,10 +14452,10 @@
         <v>100</v>
       </c>
       <c r="F293" s="11">
-        <v>6200</v>
+        <v>2700</v>
       </c>
       <c r="G293" s="11">
-        <v>6200</v>
+        <v>2700</v>
       </c>
       <c r="H293" s="11">
         <v>0</v>
@@ -14464,13 +14464,13 @@
         <v>10</v>
       </c>
       <c r="J293" s="12">
-        <v>160</v>
+        <v>128</v>
       </c>
       <c r="K293" s="12">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="L293" s="13">
-        <v>1689.37</v>
+        <v>1129.23</v>
       </c>
       <c r="M293" s="14" t="s">
         <v>18</v>
@@ -14496,25 +14496,25 @@
         <v>150</v>
       </c>
       <c r="F294" s="5">
-        <v>3450</v>
+        <v>9000</v>
       </c>
       <c r="G294" s="5">
-        <v>3450</v>
+        <v>9000</v>
       </c>
       <c r="H294" s="5">
         <v>0</v>
       </c>
       <c r="I294" s="6">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="J294" s="6">
-        <v>152</v>
+        <v>135</v>
       </c>
       <c r="K294" s="6">
-        <v>38</v>
+        <v>35</v>
       </c>
       <c r="L294" s="7">
-        <v>1453.24</v>
+        <v>2500</v>
       </c>
       <c r="M294" s="8" t="s">
         <v>18</v>
@@ -14540,10 +14540,10 @@
         <v>200</v>
       </c>
       <c r="F295" s="11">
-        <v>5600</v>
+        <v>7800</v>
       </c>
       <c r="G295" s="11">
-        <v>5600</v>
+        <v>7800</v>
       </c>
       <c r="H295" s="11">
         <v>0</v>
@@ -14552,13 +14552,13 @@
         <v>9</v>
       </c>
       <c r="J295" s="12">
-        <v>132</v>
+        <v>159</v>
       </c>
       <c r="K295" s="12">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="L295" s="13">
-        <v>2184.09</v>
+        <v>2549.02</v>
       </c>
       <c r="M295" s="14" t="s">
         <v>18</v>
@@ -14584,25 +14584,25 @@
         <v>300</v>
       </c>
       <c r="F296" s="5">
-        <v>7800</v>
+        <v>10800</v>
       </c>
       <c r="G296" s="5">
-        <v>7800</v>
+        <v>10800</v>
       </c>
       <c r="H296" s="5">
         <v>0</v>
       </c>
       <c r="I296" s="6">
-        <v>38</v>
+        <v>41</v>
       </c>
       <c r="J296" s="6">
-        <v>825</v>
+        <v>899</v>
       </c>
       <c r="K296" s="6">
-        <v>157</v>
+        <v>164</v>
       </c>
       <c r="L296" s="7">
-        <v>1397.35</v>
+        <v>1458.67</v>
       </c>
       <c r="M296" s="8" t="s">
         <v>18</v>
@@ -14628,25 +14628,25 @@
         <v>400</v>
       </c>
       <c r="F297" s="11">
-        <v>14400</v>
+        <v>18400</v>
       </c>
       <c r="G297" s="11">
-        <v>14400</v>
+        <v>18400</v>
       </c>
       <c r="H297" s="11">
         <v>0</v>
       </c>
       <c r="I297" s="12">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="J297" s="12">
-        <v>180</v>
+        <v>226</v>
       </c>
       <c r="K297" s="12">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="L297" s="13">
-        <v>4316.55</v>
+        <v>4901.44</v>
       </c>
       <c r="M297" s="14" t="s">
         <v>18</v>
@@ -14672,25 +14672,25 @@
         <v>500</v>
       </c>
       <c r="F298" s="5">
-        <v>22500</v>
+        <v>19500</v>
       </c>
       <c r="G298" s="5">
-        <v>22500</v>
+        <v>19500</v>
       </c>
       <c r="H298" s="5">
         <v>0</v>
       </c>
       <c r="I298" s="6">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="J298" s="6">
-        <v>3312</v>
+        <v>3746</v>
       </c>
       <c r="K298" s="6">
-        <v>595</v>
+        <v>552</v>
       </c>
       <c r="L298" s="7">
-        <v>795.76</v>
+        <v>846.8</v>
       </c>
       <c r="M298" s="8" t="s">
         <v>18</v>
@@ -14716,10 +14716,10 @@
         <v>10</v>
       </c>
       <c r="F299" s="11">
-        <v>440</v>
+        <v>310</v>
       </c>
       <c r="G299" s="11">
-        <v>440</v>
+        <v>310</v>
       </c>
       <c r="H299" s="11">
         <v>0</v>
@@ -14728,13 +14728,13 @@
         <v>9</v>
       </c>
       <c r="J299" s="12">
-        <v>144</v>
+        <v>139</v>
       </c>
       <c r="K299" s="12">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="L299" s="13">
-        <v>158.5</v>
+        <v>127.57</v>
       </c>
       <c r="M299" s="14" t="s">
         <v>18</v>
@@ -14760,10 +14760,10 @@
         <v>25</v>
       </c>
       <c r="F300" s="5">
-        <v>600</v>
+        <v>850</v>
       </c>
       <c r="G300" s="5">
-        <v>600</v>
+        <v>850</v>
       </c>
       <c r="H300" s="5">
         <v>0</v>
@@ -14772,13 +14772,13 @@
         <v>36</v>
       </c>
       <c r="J300" s="6">
-        <v>622</v>
+        <v>562</v>
       </c>
       <c r="K300" s="6">
-        <v>119</v>
+        <v>113</v>
       </c>
       <c r="L300" s="7">
-        <v>137.74</v>
+        <v>159.12</v>
       </c>
       <c r="M300" s="8" t="s">
         <v>18</v>
@@ -14804,10 +14804,10 @@
         <v>50</v>
       </c>
       <c r="F301" s="11">
-        <v>1750</v>
+        <v>3000</v>
       </c>
       <c r="G301" s="11">
-        <v>1750</v>
+        <v>3000</v>
       </c>
       <c r="H301" s="11">
         <v>0</v>
@@ -14816,13 +14816,13 @@
         <v>9</v>
       </c>
       <c r="J301" s="12">
-        <v>122</v>
+        <v>119</v>
       </c>
       <c r="K301" s="12">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="L301" s="13">
-        <v>676.98</v>
+        <v>877.19</v>
       </c>
       <c r="M301" s="14" t="s">
         <v>18</v>
@@ -14848,25 +14848,25 @@
         <v>100</v>
       </c>
       <c r="F302" s="5">
-        <v>6400</v>
+        <v>5300</v>
       </c>
       <c r="G302" s="5">
-        <v>6400</v>
+        <v>5300</v>
       </c>
       <c r="H302" s="5">
         <v>0</v>
       </c>
       <c r="I302" s="6">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="J302" s="6">
-        <v>165</v>
+        <v>120</v>
       </c>
       <c r="K302" s="6">
-        <v>33</v>
+        <v>36</v>
       </c>
       <c r="L302" s="7">
-        <v>1771.87</v>
+        <v>1555.16</v>
       </c>
       <c r="M302" s="8" t="s">
         <v>18</v>
@@ -14892,25 +14892,25 @@
         <v>150</v>
       </c>
       <c r="F303" s="11">
-        <v>7950</v>
+        <v>5550</v>
       </c>
       <c r="G303" s="11">
-        <v>7950</v>
+        <v>5550</v>
       </c>
       <c r="H303" s="11">
         <v>0</v>
       </c>
       <c r="I303" s="12">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="J303" s="12">
-        <v>144</v>
+        <v>121</v>
       </c>
       <c r="K303" s="12">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="L303" s="13">
-        <v>2228.76</v>
+        <v>1909.84</v>
       </c>
       <c r="M303" s="14" t="s">
         <v>18</v>
@@ -14936,10 +14936,10 @@
         <v>200</v>
       </c>
       <c r="F304" s="5">
-        <v>13600</v>
+        <v>4800</v>
       </c>
       <c r="G304" s="5">
-        <v>13600</v>
+        <v>4800</v>
       </c>
       <c r="H304" s="5">
         <v>0</v>
@@ -14948,13 +14948,13 @@
         <v>10</v>
       </c>
       <c r="J304" s="6">
-        <v>174</v>
+        <v>159</v>
       </c>
       <c r="K304" s="6">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="L304" s="7">
-        <v>3386.45</v>
+        <v>1990.05</v>
       </c>
       <c r="M304" s="8" t="s">
         <v>18</v>
@@ -14980,10 +14980,10 @@
         <v>300</v>
       </c>
       <c r="F305" s="11">
-        <v>14400</v>
+        <v>12600</v>
       </c>
       <c r="G305" s="11">
-        <v>14400</v>
+        <v>12600</v>
       </c>
       <c r="H305" s="11">
         <v>0</v>
@@ -14992,13 +14992,13 @@
         <v>10</v>
       </c>
       <c r="J305" s="12">
-        <v>186</v>
+        <v>155</v>
       </c>
       <c r="K305" s="12">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="L305" s="13">
-        <v>3986.71</v>
+        <v>3716.81</v>
       </c>
       <c r="M305" s="14" t="s">
         <v>18</v>
@@ -15024,25 +15024,25 @@
         <v>400</v>
       </c>
       <c r="F306" s="5">
-        <v>21200</v>
+        <v>20800</v>
       </c>
       <c r="G306" s="5">
-        <v>21200</v>
+        <v>20800</v>
       </c>
       <c r="H306" s="5">
         <v>0</v>
       </c>
       <c r="I306" s="6">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="J306" s="6">
-        <v>182</v>
+        <v>172</v>
       </c>
       <c r="K306" s="6">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="L306" s="7">
-        <v>5242.33</v>
+        <v>5073.17</v>
       </c>
       <c r="M306" s="8" t="s">
         <v>18</v>
@@ -15068,25 +15068,25 @@
         <v>500</v>
       </c>
       <c r="F307" s="11">
-        <v>21500</v>
+        <v>18000</v>
       </c>
       <c r="G307" s="11">
-        <v>21500</v>
+        <v>18000</v>
       </c>
       <c r="H307" s="11">
         <v>0</v>
       </c>
       <c r="I307" s="12">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="J307" s="12">
-        <v>1316</v>
+        <v>1065</v>
       </c>
       <c r="K307" s="12">
-        <v>196</v>
+        <v>206</v>
       </c>
       <c r="L307" s="13">
-        <v>2165.59</v>
+        <v>2018.84</v>
       </c>
       <c r="M307" s="14" t="s">
         <v>18</v>
@@ -15112,10 +15112,10 @@
         <v>10</v>
       </c>
       <c r="F308" s="5">
-        <v>380</v>
+        <v>440</v>
       </c>
       <c r="G308" s="5">
-        <v>380</v>
+        <v>440</v>
       </c>
       <c r="H308" s="5">
         <v>0</v>
@@ -15124,13 +15124,13 @@
         <v>9</v>
       </c>
       <c r="J308" s="6">
-        <v>112</v>
+        <v>104</v>
       </c>
       <c r="K308" s="6">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="L308" s="7">
-        <v>143.94</v>
+        <v>153.63</v>
       </c>
       <c r="M308" s="8" t="s">
         <v>18</v>
@@ -15156,25 +15156,25 @@
         <v>25</v>
       </c>
       <c r="F309" s="11">
-        <v>1075</v>
+        <v>1125</v>
       </c>
       <c r="G309" s="11">
-        <v>1075</v>
+        <v>1125</v>
       </c>
       <c r="H309" s="11">
         <v>0</v>
       </c>
       <c r="I309" s="12">
-        <v>118</v>
+        <v>111</v>
       </c>
       <c r="J309" s="12">
-        <v>2103</v>
+        <v>1988</v>
       </c>
       <c r="K309" s="12">
-        <v>324</v>
+        <v>328</v>
       </c>
       <c r="L309" s="13">
-        <v>69.66</v>
+        <v>69.19</v>
       </c>
       <c r="M309" s="14" t="s">
         <v>18</v>
@@ -15200,25 +15200,25 @@
         <v>50</v>
       </c>
       <c r="F310" s="5">
-        <v>1000</v>
+        <v>2950</v>
       </c>
       <c r="G310" s="5">
-        <v>1000</v>
+        <v>2950</v>
       </c>
       <c r="H310" s="5">
         <v>0</v>
       </c>
       <c r="I310" s="6">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="J310" s="6">
-        <v>131</v>
+        <v>115</v>
       </c>
       <c r="K310" s="6">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="L310" s="7">
-        <v>462.96</v>
+        <v>870.72</v>
       </c>
       <c r="M310" s="8" t="s">
         <v>18</v>
@@ -15244,25 +15244,25 @@
         <v>100</v>
       </c>
       <c r="F311" s="11">
-        <v>4100</v>
+        <v>3700</v>
       </c>
       <c r="G311" s="11">
-        <v>4100</v>
+        <v>3700</v>
       </c>
       <c r="H311" s="11">
         <v>0</v>
       </c>
       <c r="I311" s="12">
-        <v>40</v>
+        <v>36</v>
       </c>
       <c r="J311" s="12">
-        <v>867</v>
+        <v>659</v>
       </c>
       <c r="K311" s="12">
-        <v>133</v>
+        <v>124</v>
       </c>
       <c r="L311" s="13">
-        <v>589.67</v>
+        <v>607.75</v>
       </c>
       <c r="M311" s="14" t="s">
         <v>18</v>
@@ -15288,25 +15288,25 @@
         <v>150</v>
       </c>
       <c r="F312" s="5">
-        <v>4800</v>
+        <v>6600</v>
       </c>
       <c r="G312" s="5">
-        <v>4800</v>
+        <v>6600</v>
       </c>
       <c r="H312" s="5">
         <v>0</v>
       </c>
       <c r="I312" s="6">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="J312" s="6">
-        <v>144</v>
+        <v>164</v>
       </c>
       <c r="K312" s="6">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="L312" s="7">
-        <v>1788.38</v>
+        <v>2140.08</v>
       </c>
       <c r="M312" s="8" t="s">
         <v>18</v>
@@ -15332,10 +15332,10 @@
         <v>200</v>
       </c>
       <c r="F313" s="11">
-        <v>13600</v>
+        <v>5600</v>
       </c>
       <c r="G313" s="11">
-        <v>13600</v>
+        <v>5600</v>
       </c>
       <c r="H313" s="11">
         <v>0</v>
@@ -15344,13 +15344,13 @@
         <v>10</v>
       </c>
       <c r="J313" s="12">
-        <v>177</v>
+        <v>153</v>
       </c>
       <c r="K313" s="12">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="L313" s="13">
-        <v>3330.07</v>
+        <v>2208.2</v>
       </c>
       <c r="M313" s="14" t="s">
         <v>18</v>
@@ -15376,25 +15376,25 @@
         <v>300</v>
       </c>
       <c r="F314" s="5">
-        <v>7500</v>
+        <v>9300</v>
       </c>
       <c r="G314" s="5">
-        <v>7500</v>
+        <v>9300</v>
       </c>
       <c r="H314" s="5">
         <v>0</v>
       </c>
       <c r="I314" s="6">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="J314" s="6">
-        <v>172</v>
+        <v>161</v>
       </c>
       <c r="K314" s="6">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="L314" s="7">
-        <v>2912.62</v>
+        <v>3247.21</v>
       </c>
       <c r="M314" s="8" t="s">
         <v>18</v>
@@ -15420,10 +15420,10 @@
         <v>400</v>
       </c>
       <c r="F315" s="11">
-        <v>21600</v>
+        <v>27600</v>
       </c>
       <c r="G315" s="11">
-        <v>21600</v>
+        <v>27600</v>
       </c>
       <c r="H315" s="11">
         <v>0</v>
@@ -15432,13 +15432,13 @@
         <v>9</v>
       </c>
       <c r="J315" s="12">
-        <v>206</v>
+        <v>201</v>
       </c>
       <c r="K315" s="12">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="L315" s="13">
-        <v>5077.57</v>
+        <v>5654.58</v>
       </c>
       <c r="M315" s="14" t="s">
         <v>18</v>
@@ -15464,10 +15464,10 @@
         <v>500</v>
       </c>
       <c r="F316" s="5">
-        <v>25000</v>
+        <v>14500</v>
       </c>
       <c r="G316" s="5">
-        <v>25000</v>
+        <v>14500</v>
       </c>
       <c r="H316" s="5">
         <v>0</v>
@@ -15476,13 +15476,13 @@
         <v>10</v>
       </c>
       <c r="J316" s="6">
-        <v>237</v>
+        <v>215</v>
       </c>
       <c r="K316" s="6">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="L316" s="7">
-        <v>6024.1</v>
+        <v>4729.29</v>
       </c>
       <c r="M316" s="8" t="s">
         <v>18</v>
@@ -15508,10 +15508,10 @@
         <v>10</v>
       </c>
       <c r="F317" s="11">
-        <v>680</v>
+        <v>290</v>
       </c>
       <c r="G317" s="11">
-        <v>680</v>
+        <v>290</v>
       </c>
       <c r="H317" s="11">
         <v>0</v>
@@ -15520,13 +15520,13 @@
         <v>9</v>
       </c>
       <c r="J317" s="12">
-        <v>138</v>
+        <v>105</v>
       </c>
       <c r="K317" s="12">
-        <v>28</v>
+        <v>31</v>
       </c>
       <c r="L317" s="13">
-        <v>199.76</v>
+        <v>120.88</v>
       </c>
       <c r="M317" s="14" t="s">
         <v>18</v>
@@ -15552,25 +15552,25 @@
         <v>25</v>
       </c>
       <c r="F318" s="5">
-        <v>775</v>
+        <v>1700</v>
       </c>
       <c r="G318" s="5">
-        <v>775</v>
+        <v>1700</v>
       </c>
       <c r="H318" s="5">
         <v>0</v>
       </c>
       <c r="I318" s="6">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="J318" s="6">
-        <v>615</v>
+        <v>732</v>
       </c>
       <c r="K318" s="6">
-        <v>114</v>
+        <v>118</v>
       </c>
       <c r="L318" s="7">
-        <v>153.95</v>
+        <v>178.5</v>
       </c>
       <c r="M318" s="8" t="s">
         <v>18</v>
@@ -15596,25 +15596,25 @@
         <v>50</v>
       </c>
       <c r="F319" s="11">
-        <v>1250</v>
+        <v>1650</v>
       </c>
       <c r="G319" s="11">
-        <v>1250</v>
+        <v>1650</v>
       </c>
       <c r="H319" s="11">
         <v>0</v>
       </c>
       <c r="I319" s="12">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="J319" s="12">
-        <v>132</v>
+        <v>140</v>
       </c>
       <c r="K319" s="12">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="L319" s="13">
-        <v>537.63</v>
+        <v>653.98</v>
       </c>
       <c r="M319" s="14" t="s">
         <v>18</v>
@@ -15640,25 +15640,25 @@
         <v>100</v>
       </c>
       <c r="F320" s="5">
-        <v>5900</v>
+        <v>4700</v>
       </c>
       <c r="G320" s="5">
-        <v>5900</v>
+        <v>4700</v>
       </c>
       <c r="H320" s="5">
         <v>0</v>
       </c>
       <c r="I320" s="6">
-        <v>124</v>
+        <v>127</v>
       </c>
       <c r="J320" s="6">
-        <v>2346</v>
+        <v>2503</v>
       </c>
       <c r="K320" s="6">
-        <v>363</v>
+        <v>373</v>
       </c>
       <c r="L320" s="7">
-        <v>257.45</v>
+        <v>246.97</v>
       </c>
       <c r="M320" s="8" t="s">
         <v>18</v>
@@ -15684,25 +15684,25 @@
         <v>150</v>
       </c>
       <c r="F321" s="11">
-        <v>9000</v>
+        <v>7950</v>
       </c>
       <c r="G321" s="11">
-        <v>9000</v>
+        <v>7950</v>
       </c>
       <c r="H321" s="11">
         <v>0</v>
       </c>
       <c r="I321" s="12">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="J321" s="12">
-        <v>173</v>
+        <v>164</v>
       </c>
       <c r="K321" s="12">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="L321" s="13">
-        <v>2459.02</v>
+        <v>2262.38</v>
       </c>
       <c r="M321" s="14" t="s">
         <v>18</v>
